--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AF1D34-9A15-4DE1-B0A6-9FF0F488FA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741FF2B8-4825-4285-B469-8167E1F1BA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="11" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="名字规范！！！" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8577" uniqueCount="2193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8578" uniqueCount="2193">
   <si>
     <t>SONG</t>
   </si>
@@ -7157,7 +7157,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
+    <numFmt numFmtId="176" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -7292,7 +7292,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7323,6 +7323,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -7337,7 +7343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7350,7 +7356,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -7429,6 +7435,8 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -24403,7 +24411,7 @@
       <c r="N8" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="O8" s="32" t="s">
+      <c r="O8" s="49" t="s">
         <v>204</v>
       </c>
       <c r="P8" s="32" t="s">
@@ -24451,7 +24459,7 @@
       <c r="N9" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="O9" s="32" t="s">
+      <c r="O9" s="49" t="s">
         <v>204</v>
       </c>
       <c r="P9" s="32"/>
@@ -24497,7 +24505,7 @@
       <c r="N10" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="O10" s="32" t="s">
+      <c r="O10" s="49" t="s">
         <v>204</v>
       </c>
       <c r="P10" s="32"/>
@@ -24543,7 +24551,7 @@
       <c r="N11" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="O11" s="17"/>
+      <c r="O11" s="49"/>
       <c r="P11" s="17" t="s">
         <v>222</v>
       </c>
@@ -24589,7 +24597,7 @@
       <c r="N12" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="O12" s="17"/>
+      <c r="O12" s="49"/>
       <c r="P12" s="17" t="s">
         <v>226</v>
       </c>
@@ -24637,7 +24645,7 @@
       <c r="N13" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="O13" t="s">
+      <c r="O13" s="49" t="s">
         <v>233</v>
       </c>
       <c r="P13" t="s">
@@ -24687,7 +24695,7 @@
       <c r="N14" t="s">
         <v>238</v>
       </c>
-      <c r="O14" t="s">
+      <c r="O14" s="49" t="s">
         <v>24</v>
       </c>
       <c r="P14" t="s">
@@ -24737,7 +24745,7 @@
       <c r="N15" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="O15" t="s">
+      <c r="O15" s="49" t="s">
         <v>245</v>
       </c>
       <c r="P15" t="s">
@@ -24787,7 +24795,7 @@
       <c r="N16" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="O16" t="s">
+      <c r="O16" s="49" t="s">
         <v>245</v>
       </c>
       <c r="P16" t="s">
@@ -24837,7 +24845,7 @@
       <c r="N17" t="s">
         <v>260</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O17" s="49" t="s">
         <v>261</v>
       </c>
       <c r="P17" t="s">
@@ -24887,7 +24895,7 @@
       <c r="N18" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="O18" t="s">
+      <c r="O18" s="49" t="s">
         <v>261</v>
       </c>
       <c r="P18" t="s">
@@ -24937,7 +24945,7 @@
       <c r="N19" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="O19" t="s">
+      <c r="O19" s="49" t="s">
         <v>245</v>
       </c>
       <c r="P19" t="s">
@@ -24987,7 +24995,7 @@
       <c r="N20" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="O20" t="s">
+      <c r="O20" s="49" t="s">
         <v>280</v>
       </c>
       <c r="P20" t="s">
@@ -25037,7 +25045,7 @@
       <c r="N21" t="s">
         <v>287</v>
       </c>
-      <c r="O21" t="s">
+      <c r="O21" s="49" t="s">
         <v>280</v>
       </c>
       <c r="P21" t="s">
@@ -25087,7 +25095,7 @@
       <c r="N22" s="46" t="s">
         <v>2079</v>
       </c>
-      <c r="O22" t="s">
+      <c r="O22" s="49" t="s">
         <v>294</v>
       </c>
       <c r="P22" t="s">
@@ -25137,7 +25145,7 @@
       <c r="N23" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="O23" t="s">
+      <c r="O23" s="49" t="s">
         <v>301</v>
       </c>
       <c r="P23" t="s">
@@ -25187,7 +25195,7 @@
       <c r="N24" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="O24" t="s">
+      <c r="O24" s="49" t="s">
         <v>309</v>
       </c>
       <c r="P24" t="s">
@@ -25237,7 +25245,7 @@
       <c r="N25" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="O25" t="s">
+      <c r="O25" s="49" t="s">
         <v>301</v>
       </c>
       <c r="P25" t="s">
@@ -25287,7 +25295,7 @@
       <c r="N26" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="O26" t="s">
+      <c r="O26" s="49" t="s">
         <v>301</v>
       </c>
       <c r="P26" t="s">
@@ -25337,7 +25345,7 @@
       <c r="N27" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O27" s="49" t="s">
         <v>301</v>
       </c>
       <c r="P27" t="s">
@@ -25387,7 +25395,7 @@
       <c r="N28" s="46" t="s">
         <v>2081</v>
       </c>
-      <c r="O28" s="43" t="s">
+      <c r="O28" s="50" t="s">
         <v>338</v>
       </c>
       <c r="P28" t="s">
@@ -25437,7 +25445,7 @@
       <c r="N29" t="s">
         <v>347</v>
       </c>
-      <c r="O29" t="s">
+      <c r="O29" s="49" t="s">
         <v>294</v>
       </c>
       <c r="P29" t="s">
@@ -25487,7 +25495,7 @@
       <c r="N30" t="s">
         <v>354</v>
       </c>
-      <c r="O30" s="43" t="s">
+      <c r="O30" s="50" t="s">
         <v>338</v>
       </c>
       <c r="P30" t="s">
@@ -25537,7 +25545,7 @@
       <c r="N31" s="46" t="s">
         <v>2083</v>
       </c>
-      <c r="O31" t="s">
+      <c r="O31" s="49" t="s">
         <v>294</v>
       </c>
       <c r="P31" t="s">
@@ -25584,6 +25592,7 @@
       <c r="N32" s="21" t="s">
         <v>368</v>
       </c>
+      <c r="O32" s="49"/>
       <c r="P32" s="17" t="s">
         <v>369</v>
       </c>
@@ -25625,6 +25634,7 @@
       <c r="N33" s="21" t="s">
         <v>375</v>
       </c>
+      <c r="O33" s="49"/>
       <c r="P33" t="s">
         <v>376</v>
       </c>
@@ -25668,6 +25678,9 @@
       </c>
       <c r="N34" s="46" t="s">
         <v>2131</v>
+      </c>
+      <c r="O34" s="49" t="s">
+        <v>1839</v>
       </c>
       <c r="P34" s="45" t="s">
         <v>2076</v>

--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yumin\web\MujicaTimeLineWeb\_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8295B2-A658-4BB5-A9BA-31163195F74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="6" activeTab="13"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="名字规范！！！" sheetId="1" r:id="rId1"/>
@@ -31,12 +32,12 @@
     <sheet name="discography_bonus_contents" sheetId="17" r:id="rId17"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">lives!$A$1:$H$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">lyrics_atlas_rules!$A$1:$D$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">songs!$A$1:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">setlist!$A$1:$G$554</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">song_comments!$A$1:$D$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">song_live_history!$A$1:$F$468</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">lives!$A$1:$H$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">setlist!$A$1:$G$554</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">songs!$A$1:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">timeline!$A$1:$J$268</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,8 +49,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -57,17 +56,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wijipedia</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>手动填写链接优先；留空时，生成器按演出名和曲名自动查找 song_live_history 的 video_url。</t>
@@ -8056,15 +8056,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8076,7 +8072,7 @@
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -8098,13 +8094,13 @@
       <sz val="13"/>
       <color rgb="FF0F1419"/>
       <name val="MS Gothic"/>
-      <charset val="128"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Emoji"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -8137,7 +8133,7 @@
       <sz val="9.75"/>
       <color rgb="FF9599A6"/>
       <name val="Courier New"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="9.35"/>
@@ -8149,18 +8145,19 @@
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="initial"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF131313"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF131313"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -8168,6 +8165,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -8176,152 +8174,25 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8358,194 +8229,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -8553,258 +8238,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -8813,15 +8259,15 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8830,7 +8276,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8855,7 +8301,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8867,7 +8313,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -8896,61 +8342,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -9235,19 +8638,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:B48"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="33.2727272727273" customWidth="1"/>
+    <col min="2" max="2" width="33.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -9394,7 +8798,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:2">
+    <row r="19" spans="1:2" ht="15" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -9587,24 +8991,24 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="45.9090909090909" customWidth="1"/>
-    <col min="2" max="2" width="46.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="17.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="55.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="47.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="14.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="17.9090909090909" customWidth="1"/>
+    <col min="1" max="1" width="45.90625" customWidth="1"/>
+    <col min="2" max="2" width="46.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="55.08984375" customWidth="1"/>
+    <col min="5" max="5" width="47.6328125" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -10133,7 +9537,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" spans="1:7">
+    <row r="24" spans="1:7" ht="16.5" customHeight="1">
       <c r="A24" t="s">
         <v>78</v>
       </c>
@@ -10202,7 +9606,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:7">
+    <row r="27" spans="1:7" ht="16.5" customHeight="1">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -10225,7 +9629,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1" spans="1:7">
+    <row r="28" spans="1:7" ht="28" customHeight="1">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -10248,7 +9652,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="29" s="15" customFormat="1" ht="42" customHeight="1" spans="1:7">
+    <row r="29" spans="1:7" s="15" customFormat="1" ht="42" customHeight="1">
       <c r="A29" s="15" t="s">
         <v>78</v>
       </c>
@@ -10294,7 +9698,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="31" ht="47" customHeight="1" spans="1:7">
+    <row r="31" spans="1:7" ht="47" customHeight="1">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -10452,7 +9856,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="38" ht="33" customHeight="1" spans="1:7">
+    <row r="38" spans="1:7" ht="33" customHeight="1">
       <c r="A38" t="s">
         <v>78</v>
       </c>
@@ -10475,7 +9879,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="39" ht="30.5" customHeight="1" spans="1:7">
+    <row r="39" spans="1:7" ht="30.5" customHeight="1">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -10498,7 +9902,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="40" ht="47" customHeight="1" spans="1:7">
+    <row r="40" spans="1:7" ht="47" customHeight="1">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -10621,7 +10025,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="46" s="15" customFormat="1" spans="1:7">
+    <row r="46" spans="1:7" s="15" customFormat="1">
       <c r="A46" s="15" t="s">
         <v>79</v>
       </c>
@@ -10960,7 +10364,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="61" ht="28" customHeight="1" spans="1:7">
+    <row r="61" spans="1:7" ht="28" customHeight="1">
       <c r="A61" t="s">
         <v>79</v>
       </c>
@@ -11006,7 +10410,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="63" ht="44.5" customHeight="1" spans="1:7">
+    <row r="63" spans="1:7" ht="44.5" customHeight="1">
       <c r="A63" t="s">
         <v>79</v>
       </c>
@@ -11026,7 +10430,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="64" ht="22.5" customHeight="1" spans="1:7">
+    <row r="64" spans="1:7" ht="22.5" customHeight="1">
       <c r="A64" t="s">
         <v>79</v>
       </c>
@@ -11112,7 +10516,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="68" ht="49.5" customHeight="1" spans="1:7">
+    <row r="68" spans="1:7" ht="49.5" customHeight="1">
       <c r="A68" t="s">
         <v>79</v>
       </c>
@@ -11135,7 +10539,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="69" ht="49.5" customHeight="1" spans="1:7">
+    <row r="69" spans="1:7" ht="49.5" customHeight="1">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -11158,7 +10562,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="70" ht="30.5" customHeight="1" spans="1:7">
+    <row r="70" spans="1:7" ht="30.5" customHeight="1">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -11521,42 +10925,42 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E11" r:id="rId1" display="https://x.com/bang_dream_info/status/2088182616268910792?s=20"/>
-    <hyperlink ref="E23" r:id="rId2" display="https://x.com/Watase_Yuzuki/status/2088065379088347150?s=20"/>
-    <hyperlink ref="E24" r:id="rId3" display="https://x.com/Watase_Yuzuki/status/2088179201157537898?s=20"/>
-    <hyperlink ref="E25" r:id="rId4" display="https://x.com/Watase_Yuzuki/status/2088786673832538180?s=20"/>
-    <hyperlink ref="E26" r:id="rId5" display="https://x.com/sasakirico/status/2087837294204240082?s=20"/>
-    <hyperlink ref="E27" r:id="rId6" display="https://x.com/sasakirico/status/2088071499219644718?s=20"/>
-    <hyperlink ref="E28" r:id="rId7" display="https://x.com/sasakirico/status/2088175045470458281?s=20"/>
-    <hyperlink ref="E29" r:id="rId8" display="https://x.com/sasakirico/status/2088789235675627903?s=20"/>
-    <hyperlink ref="E39" r:id="rId9" display="https://x.com/Kanon_Takao/status/2088627188316930108?s=20"/>
-    <hyperlink ref="E40" r:id="rId10" display="https://x.com/Kanon_Takao/status/2088823105057853755?s=20"/>
-    <hyperlink ref="E41" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E42" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E43" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E44" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E45" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E47" r:id="rId12" display="https://x.com/BABYMETAL_JAPAN/status/2089290445172125822?s=20"/>
-    <hyperlink ref="E61" r:id="rId13" display="https://x.com/Watase_Yuzuki/status/2088894872896061845?s=20"/>
-    <hyperlink ref="E62" r:id="rId14" display="https://x.com/Watase_Yuzuki/status/2089309227349320029?s=20"/>
-    <hyperlink ref="E63" r:id="rId15" display="https://x.com/sasakirico/status/2088912851788599553?s=20"/>
-    <hyperlink ref="E71" r:id="rId16" display="https://spice.eplus.jp/articles/331632"/>
-    <hyperlink ref="E72" r:id="rId17" display="https://natalie.mu/comic/gallery/news/588794/2400212"/>
+    <hyperlink ref="E11" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="E23" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
+    <hyperlink ref="E24" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
+    <hyperlink ref="E25" r:id="rId4" xr:uid="{00000000-0004-0000-0900-000003000000}"/>
+    <hyperlink ref="E26" r:id="rId5" xr:uid="{00000000-0004-0000-0900-000004000000}"/>
+    <hyperlink ref="E27" r:id="rId6" xr:uid="{00000000-0004-0000-0900-000005000000}"/>
+    <hyperlink ref="E28" r:id="rId7" xr:uid="{00000000-0004-0000-0900-000006000000}"/>
+    <hyperlink ref="E29" r:id="rId8" xr:uid="{00000000-0004-0000-0900-000007000000}"/>
+    <hyperlink ref="E39" r:id="rId9" xr:uid="{00000000-0004-0000-0900-000008000000}"/>
+    <hyperlink ref="E40" r:id="rId10" xr:uid="{00000000-0004-0000-0900-000009000000}"/>
+    <hyperlink ref="E41" r:id="rId11" xr:uid="{00000000-0004-0000-0900-00000A000000}"/>
+    <hyperlink ref="E42" r:id="rId12" xr:uid="{00000000-0004-0000-0900-00000B000000}"/>
+    <hyperlink ref="E43" r:id="rId13" xr:uid="{00000000-0004-0000-0900-00000C000000}"/>
+    <hyperlink ref="E44" r:id="rId14" xr:uid="{00000000-0004-0000-0900-00000D000000}"/>
+    <hyperlink ref="E45" r:id="rId15" xr:uid="{00000000-0004-0000-0900-00000E000000}"/>
+    <hyperlink ref="E47" r:id="rId16" xr:uid="{00000000-0004-0000-0900-00000F000000}"/>
+    <hyperlink ref="E61" r:id="rId17" xr:uid="{00000000-0004-0000-0900-000010000000}"/>
+    <hyperlink ref="E62" r:id="rId18" xr:uid="{00000000-0004-0000-0900-000011000000}"/>
+    <hyperlink ref="E63" r:id="rId19" xr:uid="{00000000-0004-0000-0900-000012000000}"/>
+    <hyperlink ref="E71" r:id="rId20" xr:uid="{00000000-0004-0000-0900-000013000000}"/>
+    <hyperlink ref="E72" r:id="rId21" xr:uid="{00000000-0004-0000-0900-000014000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:E566"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="31.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="16.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -14414,25 +13818,24 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:J268"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.8181818181818" customWidth="1"/>
-    <col min="2" max="2" width="30.4545454545455" customWidth="1"/>
-    <col min="4" max="4" width="61.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="7.18181818181818" customWidth="1"/>
-    <col min="7" max="7" width="22.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="12.7272727272727" customWidth="1"/>
-    <col min="9" max="9" width="111.818181818182" customWidth="1"/>
-    <col min="10" max="10" width="21.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" customWidth="1"/>
+    <col min="4" max="4" width="61.26953125" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" customWidth="1"/>
+    <col min="7" max="7" width="22.81640625" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="9" width="111.81640625" customWidth="1"/>
+    <col min="10" max="10" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -15033,7 +14436,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="24" ht="124" customHeight="1" spans="1:10">
+    <row r="24" spans="1:10" ht="124" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>1765</v>
       </c>
@@ -15056,7 +14459,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="25" ht="124" customHeight="1" spans="1:10">
+    <row r="25" spans="1:10" ht="124" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>1765</v>
       </c>
@@ -15079,7 +14482,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="26" ht="124" customHeight="1" spans="1:10">
+    <row r="26" spans="1:10" ht="124" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>1765</v>
       </c>
@@ -15102,7 +14505,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="27" ht="124" customHeight="1" spans="1:10">
+    <row r="27" spans="1:10" ht="124" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>1765</v>
       </c>
@@ -15125,7 +14528,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="28" ht="124" customHeight="1" spans="1:10">
+    <row r="28" spans="1:10" ht="124" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>1765</v>
       </c>
@@ -15148,7 +14551,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="29" ht="124" customHeight="1" spans="1:10">
+    <row r="29" spans="1:10" ht="124" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>1765</v>
       </c>
@@ -15171,7 +14574,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="30" ht="124" customHeight="1" spans="1:10">
+    <row r="30" spans="1:10" ht="124" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>1765</v>
       </c>
@@ -15194,7 +14597,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="31" ht="124" customHeight="1" spans="1:10">
+    <row r="31" spans="1:10" ht="124" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>1765</v>
       </c>
@@ -15220,7 +14623,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="32" ht="124" customHeight="1" spans="1:10">
+    <row r="32" spans="1:10" ht="124" customHeight="1">
       <c r="A32" s="8" t="s">
         <v>1765</v>
       </c>
@@ -15246,7 +14649,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="33" ht="197.5" customHeight="1" spans="1:10">
+    <row r="33" spans="1:10" ht="197.5" customHeight="1">
       <c r="A33" s="8" t="s">
         <v>1777</v>
       </c>
@@ -15269,7 +14672,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="34" ht="197.5" customHeight="1" spans="1:10">
+    <row r="34" spans="1:10" ht="197.5" customHeight="1">
       <c r="A34" s="8" t="s">
         <v>1777</v>
       </c>
@@ -15292,7 +14695,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="35" ht="197.5" customHeight="1" spans="1:10">
+    <row r="35" spans="1:10" ht="197.5" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>1777</v>
       </c>
@@ -15315,7 +14718,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="36" ht="197.5" customHeight="1" spans="1:10">
+    <row r="36" spans="1:10" ht="197.5" customHeight="1">
       <c r="A36" s="8" t="s">
         <v>1777</v>
       </c>
@@ -15338,7 +14741,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="37" ht="197.5" customHeight="1" spans="1:10">
+    <row r="37" spans="1:10" ht="197.5" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>1777</v>
       </c>
@@ -15361,7 +14764,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="38" ht="197.5" customHeight="1" spans="1:10">
+    <row r="38" spans="1:10" ht="197.5" customHeight="1">
       <c r="A38" s="8" t="s">
         <v>1777</v>
       </c>
@@ -15384,7 +14787,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="39" ht="197.5" customHeight="1" spans="1:10">
+    <row r="39" spans="1:10" ht="197.5" customHeight="1">
       <c r="A39" s="8" t="s">
         <v>1777</v>
       </c>
@@ -15407,7 +14810,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="40" ht="197.5" customHeight="1" spans="1:10">
+    <row r="40" spans="1:10" ht="197.5" customHeight="1">
       <c r="A40" s="8" t="s">
         <v>1777</v>
       </c>
@@ -15430,7 +14833,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="41" ht="197.5" customHeight="1" spans="1:10">
+    <row r="41" spans="1:10" ht="197.5" customHeight="1">
       <c r="A41" s="8" t="s">
         <v>1777</v>
       </c>
@@ -15456,7 +14859,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="42" ht="58.5" customHeight="1" spans="1:10">
+    <row r="42" spans="1:10" ht="58.5" customHeight="1">
       <c r="A42" s="8" t="s">
         <v>1789</v>
       </c>
@@ -15479,7 +14882,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="43" ht="58.5" customHeight="1" spans="1:10">
+    <row r="43" spans="1:10" ht="58.5" customHeight="1">
       <c r="A43" s="8" t="s">
         <v>1789</v>
       </c>
@@ -15505,7 +14908,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="44" ht="84" customHeight="1" spans="1:10">
+    <row r="44" spans="1:10" ht="84" customHeight="1">
       <c r="A44" s="8" t="s">
         <v>1794</v>
       </c>
@@ -15528,7 +14931,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="45" ht="84" customHeight="1" spans="1:10">
+    <row r="45" spans="1:10" ht="84" customHeight="1">
       <c r="A45" s="8" t="s">
         <v>1794</v>
       </c>
@@ -15551,7 +14954,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="46" ht="84" customHeight="1" spans="1:10">
+    <row r="46" spans="1:10" ht="84" customHeight="1">
       <c r="A46" s="8" t="s">
         <v>1794</v>
       </c>
@@ -15574,7 +14977,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="47" ht="84" customHeight="1" spans="1:10">
+    <row r="47" spans="1:10" ht="84" customHeight="1">
       <c r="A47" s="8" t="s">
         <v>1794</v>
       </c>
@@ -15597,7 +15000,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="48" ht="84" customHeight="1" spans="1:10">
+    <row r="48" spans="1:10" ht="84" customHeight="1">
       <c r="A48" s="8" t="s">
         <v>1794</v>
       </c>
@@ -15623,7 +15026,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="49" ht="84" customHeight="1" spans="1:10">
+    <row r="49" spans="1:10" ht="84" customHeight="1">
       <c r="A49" s="8" t="s">
         <v>1794</v>
       </c>
@@ -15649,7 +15052,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="50" ht="105.5" customHeight="1" spans="1:10">
+    <row r="50" spans="1:10" ht="105.5" customHeight="1">
       <c r="A50" s="8" t="s">
         <v>1803</v>
       </c>
@@ -15672,7 +15075,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="51" ht="105.5" customHeight="1" spans="1:10">
+    <row r="51" spans="1:10" ht="105.5" customHeight="1">
       <c r="A51" s="8" t="s">
         <v>1803</v>
       </c>
@@ -15695,7 +15098,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="52" ht="105.5" customHeight="1" spans="1:10">
+    <row r="52" spans="1:10" ht="105.5" customHeight="1">
       <c r="A52" s="8" t="s">
         <v>1803</v>
       </c>
@@ -15721,7 +15124,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="53" ht="126" customHeight="1" spans="1:10">
+    <row r="53" spans="1:10" ht="126" customHeight="1">
       <c r="A53" s="8" t="s">
         <v>1809</v>
       </c>
@@ -15744,7 +15147,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="54" ht="126" customHeight="1" spans="1:10">
+    <row r="54" spans="1:10" ht="126" customHeight="1">
       <c r="A54" s="8" t="s">
         <v>1809</v>
       </c>
@@ -15767,7 +15170,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="55" ht="126" customHeight="1" spans="1:10">
+    <row r="55" spans="1:10" ht="126" customHeight="1">
       <c r="A55" s="8" t="s">
         <v>1809</v>
       </c>
@@ -15790,7 +15193,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="56" ht="126" customHeight="1" spans="1:10">
+    <row r="56" spans="1:10" ht="126" customHeight="1">
       <c r="A56" s="8" t="s">
         <v>1809</v>
       </c>
@@ -15813,7 +15216,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="57" ht="126" customHeight="1" spans="1:10">
+    <row r="57" spans="1:10" ht="126" customHeight="1">
       <c r="A57" s="8" t="s">
         <v>1809</v>
       </c>
@@ -15839,7 +15242,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="58" ht="47" customHeight="1" spans="1:10">
+    <row r="58" spans="1:10" ht="47" customHeight="1">
       <c r="A58" s="8" t="s">
         <v>1817</v>
       </c>
@@ -15862,7 +15265,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="59" ht="47" customHeight="1" spans="1:10">
+    <row r="59" spans="1:10" ht="47" customHeight="1">
       <c r="A59" s="8" t="s">
         <v>1817</v>
       </c>
@@ -15885,7 +15288,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="60" ht="47" customHeight="1" spans="1:10">
+    <row r="60" spans="1:10" ht="47" customHeight="1">
       <c r="A60" s="8" t="s">
         <v>1817</v>
       </c>
@@ -16032,7 +15435,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="66" ht="84" customHeight="1" spans="1:10">
+    <row r="66" spans="1:10" ht="84" customHeight="1">
       <c r="A66" s="8" t="s">
         <v>1831</v>
       </c>
@@ -16055,7 +15458,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="67" ht="84" customHeight="1" spans="1:10">
+    <row r="67" spans="1:10" ht="84" customHeight="1">
       <c r="A67" s="8" t="s">
         <v>1831</v>
       </c>
@@ -16078,7 +15481,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="68" ht="84" customHeight="1" spans="1:10">
+    <row r="68" spans="1:10" ht="84" customHeight="1">
       <c r="A68" s="8" t="s">
         <v>1831</v>
       </c>
@@ -16101,7 +15504,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="69" ht="84" customHeight="1" spans="1:10">
+    <row r="69" spans="1:10" ht="84" customHeight="1">
       <c r="A69" s="8" t="s">
         <v>1831</v>
       </c>
@@ -16124,7 +15527,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="70" ht="84" customHeight="1" spans="1:10">
+    <row r="70" spans="1:10" ht="84" customHeight="1">
       <c r="A70" s="8" t="s">
         <v>1831</v>
       </c>
@@ -16150,7 +15553,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="71" ht="154" customHeight="1" spans="1:10">
+    <row r="71" spans="1:10" ht="154" customHeight="1">
       <c r="A71" s="8" t="s">
         <v>1839</v>
       </c>
@@ -16173,7 +15576,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="72" ht="154" customHeight="1" spans="1:10">
+    <row r="72" spans="1:10" ht="154" customHeight="1">
       <c r="A72" s="8" t="s">
         <v>1839</v>
       </c>
@@ -16196,7 +15599,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="73" ht="154" customHeight="1" spans="1:10">
+    <row r="73" spans="1:10" ht="154" customHeight="1">
       <c r="A73" s="8" t="s">
         <v>1839</v>
       </c>
@@ -16219,7 +15622,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="74" ht="154" customHeight="1" spans="1:10">
+    <row r="74" spans="1:10" ht="154" customHeight="1">
       <c r="A74" s="8" t="s">
         <v>1839</v>
       </c>
@@ -16242,7 +15645,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="75" ht="154" customHeight="1" spans="1:10">
+    <row r="75" spans="1:10" ht="154" customHeight="1">
       <c r="A75" s="8" t="s">
         <v>1839</v>
       </c>
@@ -16265,7 +15668,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="76" ht="154" customHeight="1" spans="1:10">
+    <row r="76" spans="1:10" ht="154" customHeight="1">
       <c r="A76" s="8" t="s">
         <v>1839</v>
       </c>
@@ -16288,7 +15691,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="77" ht="154" customHeight="1" spans="1:10">
+    <row r="77" spans="1:10" ht="154" customHeight="1">
       <c r="A77" s="8" t="s">
         <v>1839</v>
       </c>
@@ -16314,7 +15717,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="78" ht="154" customHeight="1" spans="1:10">
+    <row r="78" spans="1:10" ht="154" customHeight="1">
       <c r="A78" s="8" t="s">
         <v>1839</v>
       </c>
@@ -16340,7 +15743,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="79" ht="140" customHeight="1" spans="1:10">
+    <row r="79" spans="1:10" ht="140" customHeight="1">
       <c r="A79" t="s">
         <v>1839</v>
       </c>
@@ -16364,7 +15767,7 @@
       </c>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" ht="140" customHeight="1" spans="1:10">
+    <row r="80" spans="1:10" ht="140" customHeight="1">
       <c r="A80" t="s">
         <v>1839</v>
       </c>
@@ -16495,7 +15898,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="85" ht="98" customHeight="1" spans="1:10">
+    <row r="85" spans="1:10" ht="98" customHeight="1">
       <c r="A85" s="5">
         <v>45301</v>
       </c>
@@ -16518,7 +15921,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="86" ht="98" customHeight="1" spans="1:10">
+    <row r="86" spans="1:10" ht="98" customHeight="1">
       <c r="A86" s="5">
         <v>45301</v>
       </c>
@@ -16541,7 +15944,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="87" ht="98" customHeight="1" spans="1:10">
+    <row r="87" spans="1:10" ht="98" customHeight="1">
       <c r="A87" s="5">
         <v>45301</v>
       </c>
@@ -16567,7 +15970,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="88" ht="98" customHeight="1" spans="1:10">
+    <row r="88" spans="1:10" ht="98" customHeight="1">
       <c r="A88" s="5">
         <v>45301</v>
       </c>
@@ -17769,7 +17172,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="137" ht="196" customHeight="1" spans="1:10">
+    <row r="137" spans="1:10" ht="196" customHeight="1">
       <c r="A137" s="5">
         <v>45323</v>
       </c>
@@ -17792,7 +17195,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="138" ht="196" customHeight="1" spans="1:10">
+    <row r="138" spans="1:10" ht="196" customHeight="1">
       <c r="A138" s="5">
         <v>45323</v>
       </c>
@@ -17815,7 +17218,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="139" ht="196" customHeight="1" spans="1:10">
+    <row r="139" spans="1:10" ht="196" customHeight="1">
       <c r="A139" s="5">
         <v>45323</v>
       </c>
@@ -17838,7 +17241,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="140" ht="196" customHeight="1" spans="1:10">
+    <row r="140" spans="1:10" ht="196" customHeight="1">
       <c r="A140" s="5">
         <v>45323</v>
       </c>
@@ -17861,7 +17264,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="141" ht="196" customHeight="1" spans="1:10">
+    <row r="141" spans="1:10" ht="196" customHeight="1">
       <c r="A141" s="5">
         <v>45323</v>
       </c>
@@ -17884,7 +17287,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="142" ht="196" customHeight="1" spans="1:10">
+    <row r="142" spans="1:10" ht="196" customHeight="1">
       <c r="A142" s="5">
         <v>45323</v>
       </c>
@@ -17907,7 +17310,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="143" ht="196" customHeight="1" spans="1:10">
+    <row r="143" spans="1:10" ht="196" customHeight="1">
       <c r="A143" s="5">
         <v>45323</v>
       </c>
@@ -17930,7 +17333,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="144" ht="196" customHeight="1" spans="1:10">
+    <row r="144" spans="1:10" ht="196" customHeight="1">
       <c r="A144" s="5">
         <v>45323</v>
       </c>
@@ -17954,7 +17357,7 @@
       </c>
       <c r="I144" s="10"/>
     </row>
-    <row r="145" ht="196" customHeight="1" spans="1:10">
+    <row r="145" spans="1:10" ht="196" customHeight="1">
       <c r="A145" s="5">
         <v>45323</v>
       </c>
@@ -17981,7 +17384,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="146" ht="196" customHeight="1" spans="1:10">
+    <row r="146" spans="1:10" ht="196" customHeight="1">
       <c r="A146" s="5">
         <v>45323</v>
       </c>
@@ -18007,7 +17410,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="147" ht="84" customHeight="1" spans="1:10">
+    <row r="147" spans="1:10" ht="84" customHeight="1">
       <c r="A147" s="5">
         <v>45336</v>
       </c>
@@ -18033,7 +17436,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="148" ht="84" customHeight="1" spans="1:10">
+    <row r="148" spans="1:10" ht="84" customHeight="1">
       <c r="A148" s="5">
         <v>45336</v>
       </c>
@@ -18060,7 +17463,7 @@
       </c>
       <c r="I148" s="9"/>
     </row>
-    <row r="149" ht="84" customHeight="1" spans="1:10">
+    <row r="149" spans="1:10" ht="84" customHeight="1">
       <c r="A149" s="5">
         <v>45336</v>
       </c>
@@ -18086,7 +17489,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="150" ht="84" customHeight="1" spans="1:10">
+    <row r="150" spans="1:10" ht="84" customHeight="1">
       <c r="A150" s="5">
         <v>45336</v>
       </c>
@@ -18109,7 +17512,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="151" ht="84" customHeight="1" spans="1:10">
+    <row r="151" spans="1:10" ht="84" customHeight="1">
       <c r="A151" s="5">
         <v>45336</v>
       </c>
@@ -18135,7 +17538,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="152" ht="84" customHeight="1" spans="1:10">
+    <row r="152" spans="1:10" ht="84" customHeight="1">
       <c r="A152" s="5">
         <v>45336</v>
       </c>
@@ -18662,7 +18065,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="174" ht="84" customHeight="1" spans="1:10">
+    <row r="174" spans="1:10" ht="84" customHeight="1">
       <c r="A174" s="5">
         <v>45343</v>
       </c>
@@ -18685,7 +18088,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="175" ht="84" customHeight="1" spans="1:10">
+    <row r="175" spans="1:10" ht="84" customHeight="1">
       <c r="A175" s="5">
         <v>45343</v>
       </c>
@@ -18711,7 +18114,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="176" ht="84" customHeight="1" spans="1:10">
+    <row r="176" spans="1:10" ht="84" customHeight="1">
       <c r="A176" s="5">
         <v>45343</v>
       </c>
@@ -19140,7 +18543,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="194" ht="70" customHeight="1" spans="1:10">
+    <row r="194" spans="1:10" ht="70" customHeight="1">
       <c r="A194" s="5">
         <v>45360</v>
       </c>
@@ -19164,7 +18567,7 @@
       </c>
       <c r="I194" s="10"/>
     </row>
-    <row r="195" ht="70" customHeight="1" spans="1:10">
+    <row r="195" spans="1:10" ht="70" customHeight="1">
       <c r="A195" s="5">
         <v>45360</v>
       </c>
@@ -19294,7 +18697,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="200" ht="15.5" customHeight="1" spans="1:10">
+    <row r="200" spans="1:10" ht="15.5" customHeight="1">
       <c r="A200" s="5">
         <v>45374</v>
       </c>
@@ -19692,7 +19095,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="217" ht="126" customHeight="1" spans="1:10">
+    <row r="217" spans="1:10" ht="126" customHeight="1">
       <c r="A217" s="5">
         <v>45457</v>
       </c>
@@ -19716,7 +19119,7 @@
       </c>
       <c r="I217" s="9"/>
     </row>
-    <row r="218" ht="126" customHeight="1" spans="1:10">
+    <row r="218" spans="1:10" ht="126" customHeight="1">
       <c r="A218" s="5">
         <v>45457</v>
       </c>
@@ -19742,7 +19145,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="219" ht="126" customHeight="1" spans="1:10">
+    <row r="219" spans="1:10" ht="126" customHeight="1">
       <c r="A219" s="5">
         <v>45457</v>
       </c>
@@ -19768,7 +19171,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="220" ht="70" customHeight="1" spans="1:10">
+    <row r="220" spans="1:10" ht="70" customHeight="1">
       <c r="A220" s="5">
         <v>45469</v>
       </c>
@@ -19792,7 +19195,7 @@
       </c>
       <c r="I220" s="9"/>
     </row>
-    <row r="221" ht="70" customHeight="1" spans="1:10">
+    <row r="221" spans="1:10" ht="70" customHeight="1">
       <c r="A221" s="5">
         <v>45469</v>
       </c>
@@ -19816,7 +19219,7 @@
       </c>
       <c r="I221" s="9"/>
     </row>
-    <row r="222" ht="70" customHeight="1" spans="1:10">
+    <row r="222" spans="1:10" ht="70" customHeight="1">
       <c r="A222" s="5">
         <v>45469</v>
       </c>
@@ -19842,7 +19245,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="223" ht="42" customHeight="1" spans="1:10">
+    <row r="223" spans="1:10" ht="42" customHeight="1">
       <c r="A223" s="5">
         <v>45481</v>
       </c>
@@ -19865,7 +19268,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="224" ht="42" customHeight="1" spans="1:10">
+    <row r="224" spans="1:10" ht="42" customHeight="1">
       <c r="A224" s="5">
         <v>45481</v>
       </c>
@@ -19888,7 +19291,7 @@
         <v>2086</v>
       </c>
     </row>
-    <row r="225" ht="42" customHeight="1" spans="1:10">
+    <row r="225" spans="1:10" ht="42" customHeight="1">
       <c r="A225" s="5">
         <v>45481</v>
       </c>
@@ -19914,7 +19317,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="226" ht="42" customHeight="1" spans="1:10">
+    <row r="226" spans="1:10" ht="42" customHeight="1">
       <c r="A226" s="5">
         <v>45481</v>
       </c>
@@ -19940,7 +19343,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="227" ht="28" customHeight="1" spans="1:10">
+    <row r="227" spans="1:10" ht="28" customHeight="1">
       <c r="A227" s="5">
         <v>45517</v>
       </c>
@@ -19966,7 +19369,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="228" ht="28" customHeight="1" spans="1:10">
+    <row r="228" spans="1:10" ht="28" customHeight="1">
       <c r="A228" s="5">
         <v>45517</v>
       </c>
@@ -19989,7 +19392,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="229" ht="98" customHeight="1" spans="1:10">
+    <row r="229" spans="1:10" ht="98" customHeight="1">
       <c r="A229" s="5">
         <v>45545</v>
       </c>
@@ -20012,7 +19415,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="230" ht="98" customHeight="1" spans="1:10">
+    <row r="230" spans="1:10" ht="98" customHeight="1">
       <c r="A230" s="5">
         <v>45545</v>
       </c>
@@ -20035,7 +19438,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="231" ht="98" customHeight="1" spans="1:10">
+    <row r="231" spans="1:10" ht="98" customHeight="1">
       <c r="A231" s="5">
         <v>45545</v>
       </c>
@@ -20258,7 +19661,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="240" ht="28" customHeight="1" spans="1:10">
+    <row r="240" spans="1:10" ht="28" customHeight="1">
       <c r="A240" s="5">
         <v>45569</v>
       </c>
@@ -20282,7 +19685,7 @@
       </c>
       <c r="I240" s="9"/>
     </row>
-    <row r="241" ht="28" customHeight="1" spans="1:10">
+    <row r="241" spans="1:10" ht="28" customHeight="1">
       <c r="A241" s="5">
         <v>45569</v>
       </c>
@@ -20308,7 +19711,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="242" ht="30.5" customHeight="1" spans="1:10">
+    <row r="242" spans="1:10" ht="30.5" customHeight="1">
       <c r="A242" s="5">
         <v>45593</v>
       </c>
@@ -20334,7 +19737,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="243" ht="30.5" customHeight="1" spans="1:10">
+    <row r="243" spans="1:10" ht="30.5" customHeight="1">
       <c r="A243" s="5">
         <v>45593</v>
       </c>
@@ -20357,7 +19760,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="244" ht="30.5" customHeight="1" spans="1:10">
+    <row r="244" spans="1:10" ht="30.5" customHeight="1">
       <c r="A244" s="5">
         <v>45593</v>
       </c>
@@ -20380,7 +19783,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="245" ht="109.5" customHeight="1" spans="1:10">
+    <row r="245" spans="1:10" ht="109.5" customHeight="1">
       <c r="A245" s="5">
         <v>45598</v>
       </c>
@@ -20403,7 +19806,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="246" ht="109.5" customHeight="1" spans="1:10">
+    <row r="246" spans="1:10" ht="109.5" customHeight="1">
       <c r="A246" s="5">
         <v>45598</v>
       </c>
@@ -20426,7 +19829,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="247" ht="109.5" customHeight="1" spans="1:10">
+    <row r="247" spans="1:10" ht="109.5" customHeight="1">
       <c r="A247" s="5">
         <v>45598</v>
       </c>
@@ -20449,7 +19852,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="248" ht="109.5" customHeight="1" spans="1:10">
+    <row r="248" spans="1:10" ht="109.5" customHeight="1">
       <c r="A248" s="5">
         <v>45598</v>
       </c>
@@ -20475,7 +19878,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="249" ht="109.5" customHeight="1" spans="1:10">
+    <row r="249" spans="1:10" ht="109.5" customHeight="1">
       <c r="A249" s="5">
         <v>45598</v>
       </c>
@@ -20501,7 +19904,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="250" ht="136" customHeight="1" spans="1:10">
+    <row r="250" spans="1:10" ht="136" customHeight="1">
       <c r="A250" s="5">
         <v>45606</v>
       </c>
@@ -20524,7 +19927,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="251" ht="136" customHeight="1" spans="1:10">
+    <row r="251" spans="1:10" ht="136" customHeight="1">
       <c r="A251" s="5">
         <v>45606</v>
       </c>
@@ -20547,7 +19950,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="252" ht="136" customHeight="1" spans="1:10">
+    <row r="252" spans="1:10" ht="136" customHeight="1">
       <c r="A252" s="5">
         <v>45606</v>
       </c>
@@ -20573,7 +19976,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="253" ht="16.5" customHeight="1" spans="1:10">
+    <row r="253" spans="1:10" ht="16.5" customHeight="1">
       <c r="A253" s="5">
         <v>45650</v>
       </c>
@@ -20596,7 +19999,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="254" ht="16.5" customHeight="1" spans="1:10">
+    <row r="254" spans="1:10" ht="16.5" customHeight="1">
       <c r="A254" s="5">
         <v>45650</v>
       </c>
@@ -20763,7 +20166,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="261" ht="77.5" customHeight="1" spans="1:10">
+    <row r="261" spans="1:10" ht="77.5" customHeight="1">
       <c r="A261" s="5">
         <v>45655</v>
       </c>
@@ -20787,7 +20190,7 @@
       </c>
       <c r="I261" s="9"/>
     </row>
-    <row r="262" ht="77.5" customHeight="1" spans="1:10">
+    <row r="262" spans="1:10" ht="77.5" customHeight="1">
       <c r="A262" s="5">
         <v>45655</v>
       </c>
@@ -20810,7 +20213,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="263" ht="77.5" customHeight="1" spans="1:10">
+    <row r="263" spans="1:10" ht="77.5" customHeight="1">
       <c r="A263" s="5">
         <v>45655</v>
       </c>
@@ -20833,7 +20236,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="264" ht="77.5" customHeight="1" spans="1:10">
+    <row r="264" spans="1:10" ht="77.5" customHeight="1">
       <c r="A264" s="5">
         <v>45655</v>
       </c>
@@ -20856,7 +20259,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="265" ht="77.5" customHeight="1" spans="1:10">
+    <row r="265" spans="1:10" ht="77.5" customHeight="1">
       <c r="A265" s="5">
         <v>45655</v>
       </c>
@@ -20905,7 +20308,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="267" ht="77.5" customHeight="1" spans="1:10">
+    <row r="267" spans="1:10" ht="77.5" customHeight="1">
       <c r="A267" s="5">
         <v>45655</v>
       </c>
@@ -20931,7 +20334,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="268" ht="197.5" customHeight="1" spans="1:10">
+    <row r="268" spans="1:10" ht="197.5" customHeight="1">
       <c r="A268" s="8" t="s">
         <v>1777</v>
       </c>
@@ -20958,30 +20361,28 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J268" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:J268" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I22" r:id="rId1" display="https://x.com/Kanon_Takao/status/1695354653582746087&#10;"/>
-    <hyperlink ref="I32" r:id="rId2" display="https://x.com/Kanon_Takao/status/1706878641228190181"/>
-    <hyperlink ref="I41" r:id="rId3" display="https://x.com/Kanon_Takao/status/1719212653686788414"/>
+    <hyperlink ref="I22" r:id="rId1" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
+    <hyperlink ref="I32" r:id="rId2" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
+    <hyperlink ref="I41" r:id="rId3" xr:uid="{00000000-0004-0000-0B00-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="43.2727272727273" customWidth="1"/>
-    <col min="2" max="2" width="24.9090909090909" customWidth="1"/>
-    <col min="3" max="3" width="23.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="43.26953125" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" customWidth="1"/>
     <col min="4" max="4" width="74" customWidth="1"/>
-    <col min="5" max="5" width="27.6363636363636" customWidth="1"/>
+    <col min="5" max="5" width="27.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -21305,27 +20706,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:O16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="28.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="29.4545454545455" customWidth="1"/>
-    <col min="3" max="3" width="50.2727272727273" customWidth="1"/>
-    <col min="4" max="4" width="13.5454545454545" customWidth="1"/>
-    <col min="5" max="5" width="14.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="11.3636363636364" customWidth="1"/>
-    <col min="7" max="7" width="16.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="37.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="28.6363636363636" customWidth="1"/>
-    <col min="10" max="10" width="23.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" customWidth="1"/>
+    <col min="8" max="8" width="37.26953125" customWidth="1"/>
+    <col min="9" max="9" width="28.6328125" customWidth="1"/>
+    <col min="10" max="10" width="23.26953125" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22079,27 +21479,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:O40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="22.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="13.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="11.3636363636364" customWidth="1"/>
-    <col min="6" max="6" width="28.6363636363636" customWidth="1"/>
-    <col min="7" max="7" width="22.1818181818182" customWidth="1"/>
-    <col min="8" max="8" width="34.0909090909091" customWidth="1"/>
-    <col min="9" max="9" width="13.5454545454545" customWidth="1"/>
-    <col min="10" max="10" width="51.1818181818182" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
+    <col min="6" max="6" width="28.6328125" customWidth="1"/>
+    <col min="7" max="7" width="22.1796875" customWidth="1"/>
+    <col min="8" max="8" width="34.08984375" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" customWidth="1"/>
+    <col min="10" max="10" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -23594,20 +22993,19 @@
       <c r="E40" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:I204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="22.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="55.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="6" max="6" width="55.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -24022,7 +23420,7 @@
         <v>4</v>
       </c>
       <c r="H20" s="2">
-        <v>0.205555555555555</v>
+        <v>0.20555555555555499</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -24045,7 +23443,7 @@
         <v>6</v>
       </c>
       <c r="H21" s="2">
-        <v>0.193055555555556</v>
+        <v>0.19305555555555601</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -24091,7 +23489,7 @@
         <v>10</v>
       </c>
       <c r="H23" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -24114,7 +23512,7 @@
         <v>12</v>
       </c>
       <c r="H24" s="2">
-        <v>0.177083333333333</v>
+        <v>0.17708333333333301</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -24220,7 +23618,7 @@
         <v>4</v>
       </c>
       <c r="H29" s="2">
-        <v>0.205555555555555</v>
+        <v>0.20555555555555499</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -24243,7 +23641,7 @@
         <v>6</v>
       </c>
       <c r="H30" s="2">
-        <v>0.193055555555556</v>
+        <v>0.19305555555555601</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -24289,7 +23687,7 @@
         <v>10</v>
       </c>
       <c r="H32" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -24312,7 +23710,7 @@
         <v>12</v>
       </c>
       <c r="H33" s="2">
-        <v>0.177083333333333</v>
+        <v>0.17708333333333301</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24335,7 +23733,7 @@
         <v>24</v>
       </c>
       <c r="H34" s="2">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -24358,7 +23756,7 @@
         <v>26</v>
       </c>
       <c r="H35" s="2">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -24381,7 +23779,7 @@
         <v>2404</v>
       </c>
       <c r="H36" s="2">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -24404,7 +23802,7 @@
         <v>2405</v>
       </c>
       <c r="H37" s="2">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -24447,7 +23845,7 @@
         <v>24</v>
       </c>
       <c r="H39" s="2">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -24470,7 +23868,7 @@
         <v>26</v>
       </c>
       <c r="H40" s="2">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -24493,7 +23891,7 @@
         <v>2404</v>
       </c>
       <c r="H41" s="2">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -24516,7 +23914,7 @@
         <v>2405</v>
       </c>
       <c r="H42" s="2">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -24562,7 +23960,7 @@
         <v>2407</v>
       </c>
       <c r="H44" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -24585,7 +23983,7 @@
         <v>2408</v>
       </c>
       <c r="H45" s="2">
-        <v>0.176388888888889</v>
+        <v>0.17638888888888901</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -24608,7 +24006,7 @@
         <v>14</v>
       </c>
       <c r="H46" s="2">
-        <v>0.184027777777778</v>
+        <v>0.18402777777777801</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -24631,7 +24029,7 @@
         <v>16</v>
       </c>
       <c r="H47" s="2">
-        <v>0.127083333333333</v>
+        <v>0.12708333333333299</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -24654,7 +24052,7 @@
         <v>18</v>
       </c>
       <c r="H48" s="2">
-        <v>0.220138888888889</v>
+        <v>0.22013888888888899</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -24746,7 +24144,7 @@
         <v>2407</v>
       </c>
       <c r="H52" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -24769,7 +24167,7 @@
         <v>2408</v>
       </c>
       <c r="H53" s="2">
-        <v>0.176388888888889</v>
+        <v>0.17638888888888901</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -24792,7 +24190,7 @@
         <v>14</v>
       </c>
       <c r="H54" s="2">
-        <v>0.184027777777778</v>
+        <v>0.18402777777777801</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -24815,7 +24213,7 @@
         <v>16</v>
       </c>
       <c r="H55" s="2">
-        <v>0.127083333333333</v>
+        <v>0.12708333333333299</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -24838,7 +24236,7 @@
         <v>18</v>
       </c>
       <c r="H56" s="2">
-        <v>0.220138888888889</v>
+        <v>0.22013888888888899</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -24861,7 +24259,7 @@
         <v>28</v>
       </c>
       <c r="H57" s="2">
-        <v>0.217361111111111</v>
+        <v>0.21736111111111101</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -24930,10 +24328,10 @@
         <v>34</v>
       </c>
       <c r="H60" s="2">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" spans="1:9">
+        <v>0.16666666666666699</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15" customHeight="1">
       <c r="A61" t="s">
         <v>2227</v>
       </c>
@@ -24953,7 +24351,7 @@
         <v>36</v>
       </c>
       <c r="H61" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -24996,7 +24394,7 @@
         <v>28</v>
       </c>
       <c r="H63" s="2">
-        <v>0.217361111111111</v>
+        <v>0.21736111111111101</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -25065,10 +24463,10 @@
         <v>34</v>
       </c>
       <c r="H66" s="2">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="1:8">
+        <v>0.16666666666666699</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15" customHeight="1">
       <c r="A67" t="s">
         <v>2227</v>
       </c>
@@ -25088,7 +24486,7 @@
         <v>36</v>
       </c>
       <c r="H67" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -25131,7 +24529,7 @@
         <v>28</v>
       </c>
       <c r="H69" s="2">
-        <v>0.217361111111111</v>
+        <v>0.21736111111111101</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -25200,10 +24598,10 @@
         <v>34</v>
       </c>
       <c r="H72" s="2">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" spans="1:8">
+        <v>0.16666666666666699</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15" customHeight="1">
       <c r="A73" t="s">
         <v>2227</v>
       </c>
@@ -25223,7 +24621,7 @@
         <v>36</v>
       </c>
       <c r="H73" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -25246,7 +24644,7 @@
         <v>38</v>
       </c>
       <c r="H74" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -25292,7 +24690,7 @@
         <v>2412</v>
       </c>
       <c r="H76" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -25315,7 +24713,7 @@
         <v>2413</v>
       </c>
       <c r="H77" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -25358,7 +24756,7 @@
         <v>38</v>
       </c>
       <c r="H79" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -25404,7 +24802,7 @@
         <v>2412</v>
       </c>
       <c r="H81" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -25427,7 +24825,7 @@
         <v>2413</v>
       </c>
       <c r="H82" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -25450,7 +24848,7 @@
         <v>38</v>
       </c>
       <c r="H83" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -25473,7 +24871,7 @@
         <v>40</v>
       </c>
       <c r="H84" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -25496,7 +24894,7 @@
         <v>44</v>
       </c>
       <c r="H85" s="2">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -25519,7 +24917,7 @@
         <v>46</v>
       </c>
       <c r="H86" s="2">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -25542,7 +24940,7 @@
         <v>48</v>
       </c>
       <c r="H87" s="2">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -25565,7 +24963,7 @@
         <v>50</v>
       </c>
       <c r="H88" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -25588,7 +24986,7 @@
         <v>52</v>
       </c>
       <c r="H89" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -25631,7 +25029,7 @@
         <v>38</v>
       </c>
       <c r="H91" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -25654,7 +25052,7 @@
         <v>40</v>
       </c>
       <c r="H92" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -25677,7 +25075,7 @@
         <v>44</v>
       </c>
       <c r="H93" s="2">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -25700,7 +25098,7 @@
         <v>46</v>
       </c>
       <c r="H94" s="2">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -25723,7 +25121,7 @@
         <v>48</v>
       </c>
       <c r="H95" s="2">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -25746,7 +25144,7 @@
         <v>50</v>
       </c>
       <c r="H96" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -25769,7 +25167,7 @@
         <v>52</v>
       </c>
       <c r="H97" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -25812,7 +25210,7 @@
         <v>38</v>
       </c>
       <c r="H99" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -25835,7 +25233,7 @@
         <v>40</v>
       </c>
       <c r="H100" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -25858,7 +25256,7 @@
         <v>44</v>
       </c>
       <c r="H101" s="2">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -25881,7 +25279,7 @@
         <v>46</v>
       </c>
       <c r="H102" s="2">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -25904,7 +25302,7 @@
         <v>48</v>
       </c>
       <c r="H103" s="2">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -25927,7 +25325,7 @@
         <v>50</v>
       </c>
       <c r="H104" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -25950,7 +25348,7 @@
         <v>52</v>
       </c>
       <c r="H105" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -26293,7 +25691,7 @@
         <v>2429</v>
       </c>
       <c r="H122" s="2">
-        <v>0.229861111111111</v>
+        <v>0.22986111111111099</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -26316,7 +25714,7 @@
         <v>2430</v>
       </c>
       <c r="H123" s="2">
-        <v>0.205555555555555</v>
+        <v>0.20555555555555499</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -26339,7 +25737,7 @@
         <v>2431</v>
       </c>
       <c r="H124" s="2">
-        <v>0.272222222222222</v>
+        <v>0.27222222222222198</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -26362,7 +25760,7 @@
         <v>2432</v>
       </c>
       <c r="H125" s="2">
-        <v>0.2125</v>
+        <v>0.21249999999999999</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -26425,7 +25823,7 @@
         <v>54</v>
       </c>
       <c r="H128" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -26448,7 +25846,7 @@
         <v>58</v>
       </c>
       <c r="H129" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -26471,7 +25869,7 @@
         <v>2433</v>
       </c>
       <c r="H130" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -26494,7 +25892,7 @@
         <v>2434</v>
       </c>
       <c r="H131" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -26597,7 +25995,7 @@
         <v>54</v>
       </c>
       <c r="H136" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -26620,7 +26018,7 @@
         <v>58</v>
       </c>
       <c r="H137" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -26643,7 +26041,7 @@
         <v>2433</v>
       </c>
       <c r="H138" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -26666,7 +26064,7 @@
         <v>2434</v>
       </c>
       <c r="H139" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -26729,7 +26127,7 @@
         <v>54</v>
       </c>
       <c r="H142" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -26752,7 +26150,7 @@
         <v>58</v>
       </c>
       <c r="H143" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -26775,7 +26173,7 @@
         <v>2433</v>
       </c>
       <c r="H144" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -26798,7 +26196,7 @@
         <v>2434</v>
       </c>
       <c r="H145" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -26821,7 +26219,7 @@
         <v>38</v>
       </c>
       <c r="H146" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -26844,7 +26242,7 @@
         <v>40</v>
       </c>
       <c r="H147" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -26867,7 +26265,7 @@
         <v>44</v>
       </c>
       <c r="H148" s="2">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -26890,7 +26288,7 @@
         <v>46</v>
       </c>
       <c r="H149" s="2">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -26913,7 +26311,7 @@
         <v>48</v>
       </c>
       <c r="H150" s="2">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -26936,7 +26334,7 @@
         <v>50</v>
       </c>
       <c r="H151" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -26959,7 +26357,7 @@
         <v>52</v>
       </c>
       <c r="H152" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -27068,7 +26466,7 @@
         <v>38</v>
       </c>
       <c r="H157" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -27137,7 +26535,7 @@
         <v>50</v>
       </c>
       <c r="H160" s="2">
-        <v>0.16875</v>
+        <v>0.16875000000000001</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -27160,7 +26558,7 @@
         <v>40</v>
       </c>
       <c r="H161" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -27229,7 +26627,7 @@
         <v>56</v>
       </c>
       <c r="H164" s="2">
-        <v>0.154861111111111</v>
+        <v>0.15486111111111101</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -27275,7 +26673,7 @@
         <v>48</v>
       </c>
       <c r="H166" s="2">
-        <v>0.159722222222222</v>
+        <v>0.15972222222222199</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -27321,7 +26719,7 @@
         <v>6</v>
       </c>
       <c r="H168" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -27367,10 +26765,10 @@
         <v>44</v>
       </c>
       <c r="H170" s="2">
-        <v>0.13125</v>
-      </c>
-    </row>
-    <row r="171" ht="15" customHeight="1" spans="1:8">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="15" customHeight="1">
       <c r="A171" t="s">
         <v>205</v>
       </c>
@@ -27390,7 +26788,7 @@
         <v>36</v>
       </c>
       <c r="H171" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -27453,7 +26851,7 @@
         <v>38</v>
       </c>
       <c r="H174" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -27522,7 +26920,7 @@
         <v>50</v>
       </c>
       <c r="H177" s="2">
-        <v>0.16875</v>
+        <v>0.16875000000000001</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -27545,7 +26943,7 @@
         <v>40</v>
       </c>
       <c r="H178" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -27614,7 +27012,7 @@
         <v>56</v>
       </c>
       <c r="H181" s="2">
-        <v>0.154861111111111</v>
+        <v>0.15486111111111101</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -27660,7 +27058,7 @@
         <v>48</v>
       </c>
       <c r="H183" s="2">
-        <v>0.159722222222222</v>
+        <v>0.15972222222222199</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -27706,7 +27104,7 @@
         <v>6</v>
       </c>
       <c r="H185" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -27752,10 +27150,10 @@
         <v>44</v>
       </c>
       <c r="H187" s="2">
-        <v>0.13125</v>
-      </c>
-    </row>
-    <row r="188" ht="15" customHeight="1" spans="1:8">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="15" customHeight="1">
       <c r="A188" t="s">
         <v>205</v>
       </c>
@@ -27775,7 +27173,7 @@
         <v>36</v>
       </c>
       <c r="H188" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -27818,7 +27216,7 @@
         <v>38</v>
       </c>
       <c r="H190" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -27887,7 +27285,7 @@
         <v>50</v>
       </c>
       <c r="H193" s="2">
-        <v>0.16875</v>
+        <v>0.16875000000000001</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -27910,7 +27308,7 @@
         <v>40</v>
       </c>
       <c r="H194" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -27979,7 +27377,7 @@
         <v>56</v>
       </c>
       <c r="H197" s="2">
-        <v>0.154861111111111</v>
+        <v>0.15486111111111101</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -28025,7 +27423,7 @@
         <v>48</v>
       </c>
       <c r="H199" s="2">
-        <v>0.159722222222222</v>
+        <v>0.15972222222222199</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -28071,7 +27469,7 @@
         <v>6</v>
       </c>
       <c r="H201" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -28117,10 +27515,10 @@
         <v>44</v>
       </c>
       <c r="H203" s="2">
-        <v>0.13125</v>
-      </c>
-    </row>
-    <row r="204" ht="15" customHeight="1" spans="1:8">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="15" customHeight="1">
       <c r="A204" t="s">
         <v>205</v>
       </c>
@@ -28140,26 +27538,25 @@
         <v>36</v>
       </c>
       <c r="H204" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="33.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="24.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="10.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="25.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" customWidth="1"/>
+    <col min="5" max="5" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -28304,7 +27701,7 @@
         <v>2465</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" t="s">
         <v>2235</v>
       </c>
@@ -28815,22 +28212,22 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="65.1818181818182" customWidth="1"/>
+    <col min="3" max="3" width="65.1796875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28904,7 +28301,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" ht="21" hidden="1" customHeight="1" spans="1:4">
+    <row r="6" spans="1:4" ht="21" hidden="1" customHeight="1">
       <c r="A6" s="47" t="s">
         <v>94</v>
       </c>
@@ -28916,7 +28313,7 @@
       </c>
       <c r="D6" s="47"/>
     </row>
-    <row r="7" hidden="1" spans="1:4">
+    <row r="7" spans="1:4" hidden="1">
       <c r="A7" s="47" t="s">
         <v>94</v>
       </c>
@@ -28956,7 +28353,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:4">
+    <row r="10" spans="1:4" hidden="1">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -29290,30 +28687,29 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D33" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:D33" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="equal" val="similar"/>
-        <customFilter operator="equal" val="combine"/>
-      </customFilters>
+      <filters>
+        <filter val="similar"/>
+        <filter val="combine"/>
+      </filters>
     </filterColumn>
-    <extLst/>
   </autoFilter>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="117.181818181818" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="117.1796875" customWidth="1"/>
     <col min="3" max="3" width="9" style="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -29560,23 +28956,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.6363636363636" customWidth="1"/>
-    <col min="2" max="2" width="52.6363636363636" customWidth="1"/>
-    <col min="3" max="3" width="16.6363636363636" customWidth="1"/>
-    <col min="4" max="4" width="12.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" customWidth="1"/>
+    <col min="2" max="2" width="52.6328125" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -29730,7 +29126,7 @@
         <v>46280</v>
       </c>
       <c r="D11" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -29744,7 +29140,7 @@
         <v>46280</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -29758,7 +29154,7 @@
         <v>46280</v>
       </c>
       <c r="D13" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -29790,39 +29186,39 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15 A18:A1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15 A18:A1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"song,live,interview,discography"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D15 D18:D1000">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D18:D1000 D2:D15" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="29.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="57.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="11.3636363636364" customWidth="1"/>
+    <col min="1" max="2" width="29.7265625" customWidth="1"/>
+    <col min="3" max="3" width="57.90625" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
     <col min="5" max="5" width="20" style="25" customWidth="1"/>
-    <col min="6" max="6" width="23.2727272727273" customWidth="1"/>
-    <col min="7" max="7" width="9.27272727272727" customWidth="1"/>
-    <col min="8" max="8" width="10.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="38.3636363636364" customWidth="1"/>
-    <col min="10" max="10" width="35.1818181818182" customWidth="1"/>
-    <col min="11" max="11" width="55.6363636363636" customWidth="1"/>
-    <col min="12" max="12" width="51.3636363636364" customWidth="1"/>
-    <col min="13" max="14" width="50.6363636363636" customWidth="1"/>
-    <col min="15" max="15" width="51.3636363636364" customWidth="1"/>
-    <col min="16" max="16" width="21.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="23.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" customWidth="1"/>
+    <col min="9" max="9" width="38.36328125" customWidth="1"/>
+    <col min="10" max="10" width="35.1796875" customWidth="1"/>
+    <col min="11" max="11" width="55.6328125" customWidth="1"/>
+    <col min="12" max="12" width="51.36328125" customWidth="1"/>
+    <col min="13" max="14" width="50.6328125" customWidth="1"/>
+    <col min="15" max="15" width="51.36328125" customWidth="1"/>
+    <col min="16" max="16" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -30125,7 +29521,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:16">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -30175,7 +29571,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="8" ht="15.5" customHeight="1" spans="1:16">
+    <row r="8" spans="1:16" ht="15.5" customHeight="1">
       <c r="A8" s="34" t="s">
         <v>273</v>
       </c>
@@ -30269,7 +29665,7 @@
       </c>
       <c r="P9" s="34"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:16">
+    <row r="10" spans="1:16" ht="15" customHeight="1">
       <c r="A10" s="34" t="s">
         <v>18</v>
       </c>
@@ -30315,7 +29711,7 @@
       </c>
       <c r="P10" s="34"/>
     </row>
-    <row r="11" ht="14.5" customHeight="1" spans="1:16">
+    <row r="11" spans="1:16" ht="14.5" customHeight="1">
       <c r="A11" s="15" t="s">
         <v>20</v>
       </c>
@@ -30361,7 +29757,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="12" ht="14.5" customHeight="1" spans="1:16">
+    <row r="12" spans="1:16" ht="14.5" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>22</v>
       </c>
@@ -30557,7 +29953,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="16" ht="14.5" customHeight="1" spans="1:16">
+    <row r="16" spans="1:16" ht="14.5" customHeight="1">
       <c r="A16" t="s">
         <v>324</v>
       </c>
@@ -30657,7 +30053,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:16">
+    <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" t="s">
         <v>340</v>
       </c>
@@ -30707,7 +30103,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:16">
+    <row r="19" spans="1:16" ht="15" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -30857,7 +30253,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="22" ht="14.5" customHeight="1" spans="1:16">
+    <row r="22" spans="1:16" ht="14.5" customHeight="1">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -30907,7 +30303,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="23" ht="14.5" customHeight="1" spans="1:16">
+    <row r="23" spans="1:16" ht="14.5" customHeight="1">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -31057,7 +30453,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:16">
+    <row r="26" spans="1:16" ht="14.5" customHeight="1">
       <c r="A26" t="s">
         <v>399</v>
       </c>
@@ -31107,7 +30503,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="27" s="34" customFormat="1" ht="15.5" customHeight="1" spans="1:16">
+    <row r="27" spans="1:16" s="34" customFormat="1" ht="15.5" customHeight="1">
       <c r="A27" t="s">
         <v>407</v>
       </c>
@@ -31157,7 +30553,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="28" s="34" customFormat="1" spans="1:16">
+    <row r="28" spans="1:16" s="34" customFormat="1">
       <c r="A28" s="48" t="s">
         <v>54</v>
       </c>
@@ -31207,7 +30603,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="29" s="34" customFormat="1" spans="1:16">
+    <row r="29" spans="1:16" s="34" customFormat="1">
       <c r="A29" t="s">
         <v>421</v>
       </c>
@@ -31257,7 +30653,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="30" s="15" customFormat="1" spans="1:16">
+    <row r="30" spans="1:16" s="15" customFormat="1">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -31307,7 +30703,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="31" s="15" customFormat="1" spans="1:16">
+    <row r="31" spans="1:16" s="15" customFormat="1">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -31357,7 +30753,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="32" s="15" customFormat="1" ht="14.5" customHeight="1" spans="1:16">
+    <row r="32" spans="1:16" s="15" customFormat="1" ht="14.5" customHeight="1">
       <c r="A32" s="15" t="s">
         <v>445</v>
       </c>
@@ -31492,35 +30888,33 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P34" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:P34" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="L7" r:id="rId1" display="https://www.bilibili.com/video/BV1MP411h759"/>
-    <hyperlink ref="L13" r:id="rId2" display="https://www.bilibili.com/video/BV1Xg4y1k7GH"/>
-    <hyperlink ref="L14" r:id="rId3" display="https://www.bilibili.com/video/BV1Ai4y167MU"/>
-    <hyperlink ref="L18" r:id="rId4" display="https://www.bilibili.com/video/BV1Cz421e79N"/>
-    <hyperlink ref="L22" r:id="rId5" display="https://www.bilibili.com/video/BV1EvcdenE9h"/>
-    <hyperlink ref="L27" r:id="rId6" display="https://www.bilibili.com/video/BV1RtZmYGE3a"/>
-    <hyperlink ref="L32" r:id="rId7" display="https://www.bilibili.com/video/BV1X58m6AENA"/>
+    <hyperlink ref="L7" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="L13" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="L14" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="L18" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="L22" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="L27" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="L32" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:E193"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="32.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="67.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="27.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="13.5454545454545" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" customWidth="1"/>
+    <col min="3" max="3" width="67.54296875" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31557,7 +30951,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="14.5" customHeight="1">
       <c r="A3" t="s">
         <v>331</v>
       </c>
@@ -31644,7 +31038,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" spans="1:5">
+    <row r="9" spans="1:5" ht="13.5" customHeight="1">
       <c r="A9" t="s">
         <v>237</v>
       </c>
@@ -31854,7 +31248,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" spans="1:5">
+    <row r="24" spans="1:5" ht="18" customHeight="1">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -31868,7 +31262,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:5">
+    <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="A25" t="s">
         <v>304</v>
       </c>
@@ -31966,7 +31360,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:5">
+    <row r="32" spans="1:5" ht="14.5" customHeight="1">
       <c r="A32" t="s">
         <v>317</v>
       </c>
@@ -31983,7 +31377,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:5">
+    <row r="33" spans="1:5" ht="14.5" customHeight="1">
       <c r="A33" t="s">
         <v>324</v>
       </c>
@@ -32000,7 +31394,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:5">
+    <row r="34" spans="1:5" ht="14.5" customHeight="1">
       <c r="A34" t="s">
         <v>340</v>
       </c>
@@ -32017,7 +31411,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="35" ht="15.5" customHeight="1" spans="1:5">
+    <row r="35" spans="1:5" ht="15.5" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -32046,7 +31440,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:5">
+    <row r="37" spans="1:5" ht="15" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -32063,7 +31457,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:5">
+    <row r="38" spans="1:5" ht="15" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -32080,7 +31474,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:5">
+    <row r="39" spans="1:5" ht="14.5" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
@@ -32097,7 +31491,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:5">
+    <row r="40" spans="1:5" ht="15" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>390</v>
       </c>
@@ -32114,7 +31508,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:5">
+    <row r="41" spans="1:5" ht="15" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>399</v>
       </c>
@@ -32131,7 +31525,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:5">
+    <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>407</v>
       </c>
@@ -32683,36 +32077,34 @@
       <c r="C193" s="33"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D51" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:D51" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C14" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="C16" r:id="rId2" display="https://www.animatetimes.com/news/details.php?id=1711341102&amp;p=2"/>
-    <hyperlink ref="C18" r:id="rId3" display="https://www.lisani.jp/0000271996/4/?show_more=1"/>
-    <hyperlink ref="C22" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="B25" r:id="rId4" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n&#10;佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n&#10;高尾：就像剑一样呢。 \n&#10;佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n&#10;高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n&#10;佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n&#10;——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n&#10;佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n&#10;——也是一首很容易入耳的歌呢。\n&#10;高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n&#10;佐佐木： 谢谢——！"/>
-    <hyperlink ref="C25" r:id="rId4" display="https://www.animatetimes.com/news/details.php?id=1711342991&amp;p=2"/>
-    <hyperlink ref="C27" r:id="rId5" display="https://www.lisani.jp/0000256138/?show_more=1"/>
-    <hyperlink ref="C28" r:id="rId6" display="https://www.animatetimes.com/news/details.php?id=1711342991"/>
-    <hyperlink ref="C31" r:id="rId7" display="https://natalie.mu/music/pp/avemujica01/page/2"/>
+    <hyperlink ref="C14" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="C16" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="C18" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="C22" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="B25" r:id="rId5" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n_x000a_佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n_x000a_高尾：就像剑一样呢。 \n_x000a_佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n_x000a_高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n_x000a_佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n_x000a_——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n_x000a_佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n_x000a_——也是一首很容易入耳的歌呢。\n_x000a_高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n_x000a_佐佐木： 谢谢——！" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
+    <hyperlink ref="C25" r:id="rId6" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
+    <hyperlink ref="C27" r:id="rId7" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
+    <hyperlink ref="C28" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
+    <hyperlink ref="C31" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F468"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="12.8181818181818" style="5" customWidth="1"/>
-    <col min="3" max="3" width="49.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="69.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="39.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="29.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" customWidth="1"/>
+    <col min="4" max="4" width="69.26953125" customWidth="1"/>
+    <col min="6" max="6" width="39.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -32980,7 +32372,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" ht="16" customHeight="1">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -33151,7 +32543,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" spans="1:6">
+    <row r="24" spans="1:6" ht="16" customHeight="1">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -33632,7 +33024,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="50" ht="13.5" customHeight="1" spans="1:6">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1">
       <c r="A50" t="s">
         <v>225</v>
       </c>
@@ -34566,7 +33958,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1" spans="1:6">
+    <row r="100" spans="1:6" ht="16" customHeight="1">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -34680,7 +34072,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1" spans="1:6">
+    <row r="106" spans="1:6" ht="16" customHeight="1">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -34888,7 +34280,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1" spans="1:6">
+    <row r="117" spans="1:6" ht="16" customHeight="1">
       <c r="A117" t="s">
         <v>10</v>
       </c>
@@ -35218,7 +34610,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1" spans="1:6">
+    <row r="135" spans="1:6" ht="16" customHeight="1">
       <c r="A135" t="s">
         <v>251</v>
       </c>
@@ -35426,7 +34818,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="146" ht="16" customHeight="1" spans="1:6">
+    <row r="146" spans="1:6" ht="16" customHeight="1">
       <c r="A146" t="s">
         <v>251</v>
       </c>
@@ -35591,7 +34983,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="155" ht="16" customHeight="1" spans="1:6">
+    <row r="155" spans="1:6" ht="16" customHeight="1">
       <c r="A155" t="s">
         <v>58</v>
       </c>
@@ -35881,7 +35273,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="171" ht="16" customHeight="1" spans="1:6">
+    <row r="171" spans="1:6" ht="16" customHeight="1">
       <c r="A171" t="s">
         <v>317</v>
       </c>
@@ -37809,7 +37201,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="274" ht="15" customHeight="1" spans="1:6">
+    <row r="274" spans="1:6" ht="15" customHeight="1">
       <c r="A274" s="1" t="s">
         <v>36</v>
       </c>
@@ -37829,7 +37221,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="275" ht="15" customHeight="1" spans="1:6">
+    <row r="275" spans="1:6" ht="15" customHeight="1">
       <c r="A275" s="1" t="s">
         <v>36</v>
       </c>
@@ -37849,7 +37241,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="276" ht="15" customHeight="1" spans="1:6">
+    <row r="276" spans="1:6" ht="15" customHeight="1">
       <c r="A276" s="1" t="s">
         <v>36</v>
       </c>
@@ -37869,7 +37261,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="277" ht="15" customHeight="1" spans="1:6">
+    <row r="277" spans="1:6" ht="15" customHeight="1">
       <c r="A277" s="1" t="s">
         <v>36</v>
       </c>
@@ -37889,7 +37281,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="278" ht="15" customHeight="1" spans="1:6">
+    <row r="278" spans="1:6" ht="15" customHeight="1">
       <c r="A278" s="1" t="s">
         <v>36</v>
       </c>
@@ -37909,7 +37301,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="279" ht="15" customHeight="1" spans="1:6">
+    <row r="279" spans="1:6" ht="15" customHeight="1">
       <c r="A279" s="1" t="s">
         <v>36</v>
       </c>
@@ -37929,7 +37321,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="280" ht="15" customHeight="1" spans="1:6">
+    <row r="280" spans="1:6" ht="15" customHeight="1">
       <c r="A280" s="1" t="s">
         <v>36</v>
       </c>
@@ -41249,7 +40641,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="458" ht="16" customHeight="1" spans="1:6">
+    <row r="458" spans="1:6" ht="16" customHeight="1">
       <c r="A458" t="s">
         <v>273</v>
       </c>
@@ -41464,259 +40856,258 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F468" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:F468" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.acfun.cn/v/ac47931167" tooltip="https://www.acfun.cn/v/ac47931167"/>
-    <hyperlink ref="F3" r:id="rId2" display="https://www.acfun.cn/v/ac47931167_2"/>
-    <hyperlink ref="F7" r:id="rId3" display="https://www.acfun.cn/v/ac47931167_3"/>
-    <hyperlink ref="F8" r:id="rId4" display="https://www.acfun.cn/v/ac47931167_4"/>
-    <hyperlink ref="F9" r:id="rId5" display="https://www.acfun.cn/v/ac47931167_5"/>
-    <hyperlink ref="F10" r:id="rId6" display="https://www.acfun.cn/v/ac47931167_6"/>
-    <hyperlink ref="F12" r:id="rId7" display="https://www.acfun.cn/v/ac47931167_7"/>
-    <hyperlink ref="F14" r:id="rId8" display="https://www.acfun.cn/v/ac47934758"/>
-    <hyperlink ref="F15" r:id="rId9" display="https://www.acfun.cn/v/ac47934758_2"/>
-    <hyperlink ref="F16" r:id="rId10" display="https://www.acfun.cn/v/ac47934758_3"/>
-    <hyperlink ref="F18" r:id="rId11" display="https://www.acfun.cn/v/ac47934758_4"/>
-    <hyperlink ref="F20" r:id="rId12" display="https://www.acfun.cn/v/ac47934758_5"/>
-    <hyperlink ref="F22" r:id="rId13" display="https://www.acfun.cn/v/ac47934758_6"/>
-    <hyperlink ref="F23" r:id="rId14" display="https://www.acfun.cn/v/ac47934758_7"/>
-    <hyperlink ref="F24" r:id="rId15" display="https://www.acfun.cn/v/ac47934758_8"/>
-    <hyperlink ref="F25" r:id="rId16" display="https://www.acfun.cn/v/ac47934758_9"/>
-    <hyperlink ref="F27" r:id="rId17" display="https://www.acfun.cn/v/ac47934758_10"/>
-    <hyperlink ref="F28" r:id="rId18" display="https://www.acfun.cn/v/ac47934815"/>
-    <hyperlink ref="F29" r:id="rId19" display="https://www.acfun.cn/v/ac47934815_2"/>
-    <hyperlink ref="F31" r:id="rId20" display="https://www.acfun.cn/v/ac47934815_3"/>
-    <hyperlink ref="F32" r:id="rId21" display="https://www.acfun.cn/v/ac47934815_4"/>
-    <hyperlink ref="F33" r:id="rId22" display="https://www.acfun.cn/v/ac47934815_5"/>
-    <hyperlink ref="F34" r:id="rId23" display="https://www.acfun.cn/v/ac47934815_6"/>
-    <hyperlink ref="F39" r:id="rId24" display="https://www.acfun.cn/v/ac47934815_7"/>
-    <hyperlink ref="F69" r:id="rId25" display="https://www.acfun.cn/v/ac47935101_2"/>
-    <hyperlink ref="F71" r:id="rId26" display="https://www.acfun.cn/v/ac47935101_3"/>
-    <hyperlink ref="F73" r:id="rId27" display="https://www.acfun.cn/v/ac47935101_4"/>
-    <hyperlink ref="F74" r:id="rId28" display="https://www.acfun.cn/v/ac47935101_5"/>
-    <hyperlink ref="F75" r:id="rId29" display="https://www.acfun.cn/v/ac47935101_6"/>
-    <hyperlink ref="F76" r:id="rId30" display="https://www.acfun.cn/v/ac47935101_7"/>
-    <hyperlink ref="F77" r:id="rId31" display="https://www.acfun.cn/v/ac47935101_8"/>
-    <hyperlink ref="F78" r:id="rId32" display="https://www.acfun.cn/v/ac47935101_9"/>
-    <hyperlink ref="F80" r:id="rId33" display="https://www.acfun.cn/v/ac47935101_10"/>
-    <hyperlink ref="F87" r:id="rId34" display="https://www.acfun.cn/v/ac48752881_2"/>
-    <hyperlink ref="F101" r:id="rId35" display="https://www.acfun.cn/v/ac47924476_8"/>
-    <hyperlink ref="F105" r:id="rId36" display="https://www.acfun.cn/v/ac47935303"/>
-    <hyperlink ref="F106" r:id="rId37" display="https://www.acfun.cn/v/ac47935303_2"/>
-    <hyperlink ref="F107" r:id="rId38" display="https://www.acfun.cn/v/ac47935303_3"/>
-    <hyperlink ref="F109" r:id="rId39" display="https://www.acfun.cn/v/ac47935303_4"/>
-    <hyperlink ref="F113" r:id="rId40" display="https://www.acfun.cn/v/ac47935303_5"/>
-    <hyperlink ref="F114" r:id="rId41" display="https://www.acfun.cn/v/ac47935303_6"/>
-    <hyperlink ref="F115" r:id="rId42" display="https://www.acfun.cn/v/ac47935303_7"/>
-    <hyperlink ref="F116" r:id="rId43" display="https://www.acfun.cn/v/ac47935303_8"/>
-    <hyperlink ref="F118" r:id="rId44" display="https://www.acfun.cn/v/ac47935303_9"/>
-    <hyperlink ref="F119" r:id="rId45" display="https://www.acfun.cn/v/ac47935303_10"/>
-    <hyperlink ref="F120" r:id="rId46" display="https://www.acfun.cn/v/ac48116488"/>
-    <hyperlink ref="F122" r:id="rId47" display="https://www.acfun.cn/v/ac48116488_2"/>
-    <hyperlink ref="F128" r:id="rId48" display="https://www.acfun.cn/v/ac48116488_3"/>
-    <hyperlink ref="F129" r:id="rId49" display="https://www.acfun.cn/v/ac48116488_4"/>
-    <hyperlink ref="F133" r:id="rId50" display="https://www.acfun.cn/v/ac48116488_5"/>
-    <hyperlink ref="F134" r:id="rId51" display="https://www.acfun.cn/v/ac47934950"/>
-    <hyperlink ref="F135" r:id="rId52" display="https://www.acfun.cn/v/ac47934950_2"/>
-    <hyperlink ref="F136" r:id="rId53" display="https://www.acfun.cn/v/ac47934950_3"/>
-    <hyperlink ref="F138" r:id="rId54" display="https://www.acfun.cn/v/ac47934950_4"/>
-    <hyperlink ref="F140" r:id="rId55" display="https://www.acfun.cn/v/ac47934950_5"/>
-    <hyperlink ref="F141" r:id="rId56" display="https://www.acfun.cn/v/ac47934950_6"/>
-    <hyperlink ref="F142" r:id="rId57" display="https://www.acfun.cn/v/ac47934950_7"/>
-    <hyperlink ref="F143" r:id="rId58" display="https://www.acfun.cn/v/ac47934950_8"/>
-    <hyperlink ref="F149" r:id="rId59" display="https://www.acfun.cn/v/ac47934950_9"/>
-    <hyperlink ref="F167" r:id="rId60" display="https://www.acfun.cn/v/ac48115972_7"/>
-    <hyperlink ref="F168" r:id="rId61" display="https://www.acfun.cn/v/ac47931569" tooltip="https://www.acfun.cn/v/ac47931569"/>
-    <hyperlink ref="F170" r:id="rId62" display="https://www.acfun.cn/v/ac47931569_2"/>
-    <hyperlink ref="F171" r:id="rId63" display="https://www.acfun.cn/v/ac47931569_3"/>
-    <hyperlink ref="F172" r:id="rId64" display="https://www.acfun.cn/v/ac47931569_4"/>
-    <hyperlink ref="F173" r:id="rId65" display="https://www.acfun.cn/v/ac47931569_5"/>
-    <hyperlink ref="F174" r:id="rId66" display="https://www.acfun.cn/v/ac47931569_6"/>
-    <hyperlink ref="F175" r:id="rId67" display="https://www.acfun.cn/v/ac47931569_7"/>
-    <hyperlink ref="F176" r:id="rId68" display="https://www.acfun.cn/v/ac47931569_8"/>
-    <hyperlink ref="F177" r:id="rId69" display="https://www.acfun.cn/v/ac47931569_9"/>
-    <hyperlink ref="F178" r:id="rId70" display="https://www.acfun.cn/v/ac47931569_10"/>
-    <hyperlink ref="F179" r:id="rId71" display="https://www.acfun.cn/v/ac47931603" tooltip="https://www.acfun.cn/v/ac47931603"/>
-    <hyperlink ref="F181" r:id="rId72" display="https://www.acfun.cn/v/ac47931603_2"/>
-    <hyperlink ref="F183" r:id="rId73" display="https://www.acfun.cn/v/ac47931603_3"/>
-    <hyperlink ref="F184" r:id="rId74" display="https://www.acfun.cn/v/ac47931603_4"/>
-    <hyperlink ref="F186" r:id="rId75" display="https://www.acfun.cn/v/ac47931603_5"/>
-    <hyperlink ref="F192" r:id="rId76" display="https://www.acfun.cn/v/ac47931603_6"/>
-    <hyperlink ref="F193" r:id="rId77" display="https://www.acfun.cn/v/ac47931603_7"/>
-    <hyperlink ref="F198" r:id="rId78" display="https://www.acfun.cn/v/ac47931603_8"/>
-    <hyperlink ref="F199" r:id="rId79" display="https://www.acfun.cn/v/ac47933063"/>
-    <hyperlink ref="F201" r:id="rId80" display="https://www.acfun.cn/v/ac47933063_2"/>
-    <hyperlink ref="F202" r:id="rId81" display="https://www.acfun.cn/v/ac47933063_3"/>
-    <hyperlink ref="F203" r:id="rId82" display="https://www.acfun.cn/v/ac47933063_4"/>
-    <hyperlink ref="F204" r:id="rId83" display="https://www.acfun.cn/v/ac47933063_5"/>
-    <hyperlink ref="F206" r:id="rId84" display="https://www.acfun.cn/v/ac47933063_6"/>
-    <hyperlink ref="F207" r:id="rId85" display="https://www.acfun.cn/v/ac47933063_7"/>
-    <hyperlink ref="F208" r:id="rId86" display="https://www.acfun.cn/v/ac47933063_8"/>
-    <hyperlink ref="F209" r:id="rId87" display="https://www.acfun.cn/v/ac47933063_9"/>
-    <hyperlink ref="F211" r:id="rId88" display="https://www.acfun.cn/v/ac47933063_10"/>
-    <hyperlink ref="F213" r:id="rId89" display="https://www.acfun.cn/v/ac48409409_1" tooltip="https://www.acfun.cn/v/ac48409409_1"/>
-    <hyperlink ref="F219" r:id="rId90" display="https://www.acfun.cn/v/ac48409409_2"/>
-    <hyperlink ref="F220" r:id="rId91" display="https://www.acfun.cn/v/ac48409409_3"/>
-    <hyperlink ref="F225" r:id="rId92" display="https://www.acfun.cn/v/ac48409409_4"/>
-    <hyperlink ref="F235" r:id="rId93" display="https://www.acfun.cn/v/ac47931075"/>
-    <hyperlink ref="F236" r:id="rId94" display="https://www.acfun.cn/v/ac47931075_2"/>
-    <hyperlink ref="F238" r:id="rId95" display="https://www.acfun.cn/v/ac47931075_3"/>
-    <hyperlink ref="F240" r:id="rId96" display="https://www.acfun.cn/v/ac47931075_4"/>
-    <hyperlink ref="F241" r:id="rId97" display="https://www.acfun.cn/v/ac47931075_5"/>
-    <hyperlink ref="F242" r:id="rId98" display="https://www.acfun.cn/v/ac47931075_6"/>
-    <hyperlink ref="F244" r:id="rId99" display="https://www.acfun.cn/v/ac47933675"/>
-    <hyperlink ref="F246" r:id="rId100" display="https://www.acfun.cn/v/ac47933675_2"/>
-    <hyperlink ref="F248" r:id="rId101" display="https://www.acfun.cn/v/ac47933675_3"/>
-    <hyperlink ref="F249" r:id="rId102" display="https://www.acfun.cn/v/ac47933675_4"/>
-    <hyperlink ref="F250" r:id="rId103" display="https://www.acfun.cn/v/ac47933675_5"/>
-    <hyperlink ref="F251" r:id="rId104" display="https://www.acfun.cn/v/ac47933675_6"/>
-    <hyperlink ref="F252" r:id="rId105" display="https://www.acfun.cn/v/ac47933675_7"/>
-    <hyperlink ref="F257" r:id="rId106" display="https://www.acfun.cn/v/ac47933675_8"/>
-    <hyperlink ref="F259" r:id="rId107" display="https://www.acfun.cn/v/ac47934854"/>
-    <hyperlink ref="F260" r:id="rId108" display="https://www.acfun.cn/v/ac47934854_2"/>
-    <hyperlink ref="F261" r:id="rId109" display="https://www.acfun.cn/v/ac47934854_3"/>
-    <hyperlink ref="F262" r:id="rId110" display="https://www.acfun.cn/v/ac47934854_4"/>
-    <hyperlink ref="F263" r:id="rId111" display="https://www.acfun.cn/v/ac47934854_5"/>
-    <hyperlink ref="F264" r:id="rId112" display="https://www.acfun.cn/v/ac47934854_6"/>
-    <hyperlink ref="F266" r:id="rId113" display="https://www.acfun.cn/v/ac47934854_7"/>
-    <hyperlink ref="F272" r:id="rId114" display="https://www.acfun.cn/v/ac47934854_8"/>
-    <hyperlink ref="F274" r:id="rId115" display="https://www.acfun.cn/v/ac47933636"/>
-    <hyperlink ref="F275" r:id="rId116" display="https://www.acfun.cn/v/ac47933636_2"/>
-    <hyperlink ref="F276" r:id="rId117" display="https://www.acfun.cn/v/ac47933636_3"/>
-    <hyperlink ref="F277" r:id="rId118" display="https://www.acfun.cn/v/ac47933636_4"/>
-    <hyperlink ref="F278" r:id="rId119" display="https://www.acfun.cn/v/ac47933636_5"/>
-    <hyperlink ref="F279" r:id="rId120" display="https://www.acfun.cn/v/ac47933636_6"/>
-    <hyperlink ref="F281" r:id="rId121" display="https://www.acfun.cn/v/ac47930865"/>
-    <hyperlink ref="F282" r:id="rId122" display="https://www.acfun.cn/v/ac47930865_2"/>
-    <hyperlink ref="F284" r:id="rId123" display="https://www.acfun.cn/v/ac47930865_3"/>
-    <hyperlink ref="F286" r:id="rId124" display="https://www.acfun.cn/v/ac47930865_4"/>
-    <hyperlink ref="F291" r:id="rId125" display="https://www.acfun.cn/v/ac47930865_5"/>
-    <hyperlink ref="F292" r:id="rId126" display="https://www.acfun.cn/v/ac47930865_6"/>
-    <hyperlink ref="F296" r:id="rId127" display="https://www.acfun.cn/v/ac47932379"/>
-    <hyperlink ref="F297" r:id="rId128" display="https://www.acfun.cn/v/ac47932379_2"/>
-    <hyperlink ref="F298" r:id="rId129" display="https://www.acfun.cn/v/ac47932379_3"/>
-    <hyperlink ref="F299" r:id="rId130" display="https://www.acfun.cn/v/ac47932379_4"/>
-    <hyperlink ref="F300" r:id="rId131" display="https://www.acfun.cn/v/ac47932379_5"/>
-    <hyperlink ref="F301" r:id="rId132" display="https://www.acfun.cn/v/ac47932379_6"/>
-    <hyperlink ref="F304" r:id="rId133" display="https://www.acfun.cn/v/ac47932379_7"/>
-    <hyperlink ref="F306" r:id="rId134" display="https://www.acfun.cn/v/ac47932379_8"/>
-    <hyperlink ref="F307" r:id="rId135" display="https://www.acfun.cn/v/ac47932379_9"/>
-    <hyperlink ref="F308" r:id="rId136" display="https://www.acfun.cn/v/ac47932379_10"/>
-    <hyperlink ref="F309" r:id="rId137" display="https://www.acfun.cn/v/ac48055738"/>
-    <hyperlink ref="F310" r:id="rId138" display="https://www.acfun.cn/v/ac48055738_2"/>
-    <hyperlink ref="F311" r:id="rId139" display="https://www.acfun.cn/v/ac48055738_3"/>
-    <hyperlink ref="F312" r:id="rId140" display="https://www.acfun.cn/v/ac48055738_4"/>
-    <hyperlink ref="F313" r:id="rId141" display="https://www.acfun.cn/v/ac48055738_5"/>
-    <hyperlink ref="F314" r:id="rId142" display="https://www.acfun.cn/v/ac48055738_6"/>
-    <hyperlink ref="F316" r:id="rId143" display="https://www.acfun.cn/v/ac48055738_7"/>
-    <hyperlink ref="F317" r:id="rId144" display="https://www.acfun.cn/v/ac48055738_8"/>
-    <hyperlink ref="F319" r:id="rId145" display="https://www.acfun.cn/v/ac48055738_9"/>
-    <hyperlink ref="F325" r:id="rId146" display="https://www.acfun.cn/v/ac48751334"/>
-    <hyperlink ref="F326" r:id="rId147" display="https://www.acfun.cn/v/ac48751334_2"/>
-    <hyperlink ref="F331" r:id="rId148" display="https://www.acfun.cn/v/ac48751334_3" tooltip="https://www.acfun.cn/v/ac48751334_3"/>
-    <hyperlink ref="F332" r:id="rId149" display="https://www.acfun.cn/v/ac47931260"/>
-    <hyperlink ref="F333" r:id="rId150" display="https://www.acfun.cn/v/ac47931260_2"/>
-    <hyperlink ref="F335" r:id="rId151" display="https://www.acfun.cn/v/ac47931260_3"/>
-    <hyperlink ref="F336" r:id="rId152" display="https://www.acfun.cn/v/ac47931260_4"/>
-    <hyperlink ref="F337" r:id="rId153" display="https://www.acfun.cn/v/ac47931260_5"/>
-    <hyperlink ref="F338" r:id="rId154" display="https://www.acfun.cn/v/ac47931260_6"/>
-    <hyperlink ref="F339" r:id="rId155" display="https://www.acfun.cn/v/ac47931260_7"/>
-    <hyperlink ref="F345" r:id="rId156" display="https://www.acfun.cn/v/ac47931260_8"/>
-    <hyperlink ref="F346" r:id="rId157" display="https://www.acfun.cn/v/ac47932208"/>
-    <hyperlink ref="F347" r:id="rId158" display="https://www.acfun.cn/v/ac47932208_2"/>
-    <hyperlink ref="F348" r:id="rId159" display="https://www.acfun.cn/v/ac47932208_3"/>
-    <hyperlink ref="F349" r:id="rId160" display="https://www.acfun.cn/v/ac47932208_4"/>
-    <hyperlink ref="F350" r:id="rId161" display="https://www.acfun.cn/v/ac47932208_5"/>
-    <hyperlink ref="F351" r:id="rId162" display="https://www.acfun.cn/v/ac47932208_6"/>
-    <hyperlink ref="F352" r:id="rId163" display="https://www.acfun.cn/v/ac47932208_7"/>
-    <hyperlink ref="F358" r:id="rId164" display="https://www.acfun.cn/v/ac47932208_8"/>
-    <hyperlink ref="F359" r:id="rId165" display="https://www.acfun.cn/v/ac47932208_9"/>
-    <hyperlink ref="F363" r:id="rId166" display="https://www.acfun.cn/v/ac47932208_10"/>
-    <hyperlink ref="F364" r:id="rId167" display="https://www.acfun.cn/v/ac47931830"/>
-    <hyperlink ref="F365" r:id="rId168" display="https://www.acfun.cn/v/ac47931830_2"/>
-    <hyperlink ref="F368" r:id="rId169" display="https://www.acfun.cn/v/ac47931830_3"/>
-    <hyperlink ref="F369" r:id="rId170" display="https://www.acfun.cn/v/ac47931830_4"/>
-    <hyperlink ref="F370" r:id="rId171" display="https://www.acfun.cn/v/ac47931830_5"/>
-    <hyperlink ref="F372" r:id="rId172" display="https://www.acfun.cn/v/ac47931830_6"/>
-    <hyperlink ref="F373" r:id="rId173" display="https://www.acfun.cn/v/ac47931830_7"/>
-    <hyperlink ref="F374" r:id="rId174" display="https://www.acfun.cn/v/ac47931830_8"/>
-    <hyperlink ref="F376" r:id="rId175" display="https://www.acfun.cn/v/ac47931830_9"/>
-    <hyperlink ref="F378" r:id="rId176" display="https://www.acfun.cn/v/ac47931830_10"/>
-    <hyperlink ref="F384" r:id="rId177" display="https://www.acfun.cn/v/ac48751840"/>
-    <hyperlink ref="F385" r:id="rId178" display="https://www.acfun.cn/v/ac48751840_2"/>
-    <hyperlink ref="F389" r:id="rId179" display="https://www.acfun.cn/v/ac48751840_3"/>
-    <hyperlink ref="F390" r:id="rId180" display="https://www.acfun.cn/v/ac47931318"/>
-    <hyperlink ref="F391" r:id="rId181" display="https://www.acfun.cn/v/ac47931318_2"/>
-    <hyperlink ref="F395" r:id="rId182" display="https://www.acfun.cn/v/ac47931318_3"/>
-    <hyperlink ref="F396" r:id="rId183" display="https://www.acfun.cn/v/ac47931318_4"/>
-    <hyperlink ref="F397" r:id="rId184" display="https://www.acfun.cn/v/ac47931318_5"/>
-    <hyperlink ref="F398" r:id="rId185" display="https://www.acfun.cn/v/ac47931318_6"/>
-    <hyperlink ref="F399" r:id="rId186" display="https://www.acfun.cn/v/ac47931318_7"/>
-    <hyperlink ref="F400" r:id="rId187" display="https://www.acfun.cn/v/ac47931318_8"/>
-    <hyperlink ref="F401" r:id="rId188" display="https://www.acfun.cn/v/ac47931318_9"/>
-    <hyperlink ref="F402" r:id="rId189" display="https://www.acfun.cn/v/ac47931318_10"/>
-    <hyperlink ref="F403" r:id="rId190" display="https://www.acfun.cn/v/ac48311717"/>
-    <hyperlink ref="F405" r:id="rId191" display="https://www.acfun.cn/v/ac48311717_2"/>
-    <hyperlink ref="F406" r:id="rId192" display="https://www.acfun.cn/v/ac48311717_3"/>
-    <hyperlink ref="F408" r:id="rId193" display="https://www.acfun.cn/v/ac48311717_4"/>
-    <hyperlink ref="F414" r:id="rId194" display="https://www.acfun.cn/v/ac48311717_5"/>
-    <hyperlink ref="F415" r:id="rId195" display="https://www.acfun.cn/v/ac48311717_6"/>
-    <hyperlink ref="F420" r:id="rId196" display="https://www.acfun.cn/v/ac48311717_7"/>
-    <hyperlink ref="F421" r:id="rId197" display="https://www.acfun.cn/v/ac47932123"/>
-    <hyperlink ref="F422" r:id="rId198" display="https://www.acfun.cn/v/ac47932123_2"/>
-    <hyperlink ref="F424" r:id="rId199" display="https://www.acfun.cn/v/ac47932123_3"/>
-    <hyperlink ref="F425" r:id="rId200" display="https://www.acfun.cn/v/ac47932123_4" tooltip="https://www.acfun.cn/v/ac47932123_4"/>
-    <hyperlink ref="F426" r:id="rId201" display="https://www.acfun.cn/v/ac47932123_5"/>
-    <hyperlink ref="F427" r:id="rId202" display="https://www.acfun.cn/v/ac47932123_6"/>
-    <hyperlink ref="F428" r:id="rId203" display="https://www.acfun.cn/v/ac47932123_7"/>
-    <hyperlink ref="F430" r:id="rId204" display="https://www.acfun.cn/v/ac47932123_8"/>
-    <hyperlink ref="F434" r:id="rId205" display="https://www.acfun.cn/v/ac47930836"/>
-    <hyperlink ref="F435" r:id="rId206" display="https://www.acfun.cn/v/ac47930836_2"/>
-    <hyperlink ref="F436" r:id="rId207" display="https://www.acfun.cn/v/ac47930836_3"/>
-    <hyperlink ref="F438" r:id="rId208" display="https://www.acfun.cn/v/ac47930836_4"/>
-    <hyperlink ref="F440" r:id="rId209" display="https://www.acfun.cn/v/ac47930836_5"/>
-    <hyperlink ref="F441" r:id="rId210" display="https://www.acfun.cn/v/ac47930836_6"/>
-    <hyperlink ref="F447" r:id="rId211" display="https://www.acfun.cn/v/ac47930836_7"/>
-    <hyperlink ref="F448" r:id="rId212" display="https://www.acfun.cn/v/ac47930836_8"/>
-    <hyperlink ref="F451" r:id="rId213" display="https://www.acfun.cn/v/ac47935835"/>
-    <hyperlink ref="F452" r:id="rId214" display="https://www.acfun.cn/v/ac47935862" tooltip="https://www.acfun.cn/v/ac47935862"/>
-    <hyperlink ref="F453" r:id="rId215" display="https://www.acfun.cn/v/ac47932937" tooltip="https://www.acfun.cn/v/ac47932937"/>
-    <hyperlink ref="F454" r:id="rId216" display="https://www.acfun.cn/v/ac47932937_2"/>
-    <hyperlink ref="F455" r:id="rId217" display="https://www.acfun.cn/v/ac47932937_3"/>
-    <hyperlink ref="F457" r:id="rId218" display="https://www.acfun.cn/v/ac47932937_4"/>
-    <hyperlink ref="F458" r:id="rId219" display="https://www.acfun.cn/v/ac47932937_5"/>
-    <hyperlink ref="F459" r:id="rId220" display="https://www.acfun.cn/v/ac47932763" tooltip="https://www.acfun.cn/v/ac47932763"/>
-    <hyperlink ref="F460" r:id="rId221" display="https://www.acfun.cn/v/ac47932763_2"/>
-    <hyperlink ref="F461" r:id="rId222" display="https://www.acfun.cn/v/ac47932763_3"/>
-    <hyperlink ref="F463" r:id="rId223" display="https://www.acfun.cn/v/ac47932763_4"/>
-    <hyperlink ref="F464" r:id="rId224" display="https://www.acfun.cn/v/ac47931710" tooltip="https://www.acfun.cn/v/ac47931710"/>
-    <hyperlink ref="F465" r:id="rId225" display="https://www.acfun.cn/v/ac47931710_2"/>
-    <hyperlink ref="F466" r:id="rId226" display="https://www.acfun.cn/v/ac47931710_3"/>
-    <hyperlink ref="F468" r:id="rId227" display="https://www.acfun.cn/v/ac47931710_4"/>
+    <hyperlink ref="F2" r:id="rId1" tooltip="https://www.acfun.cn/v/ac47931167" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
+    <hyperlink ref="F14" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
+    <hyperlink ref="F16" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
+    <hyperlink ref="F18" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
+    <hyperlink ref="F20" r:id="rId12" xr:uid="{00000000-0004-0000-0600-00000B000000}"/>
+    <hyperlink ref="F22" r:id="rId13" xr:uid="{00000000-0004-0000-0600-00000C000000}"/>
+    <hyperlink ref="F23" r:id="rId14" xr:uid="{00000000-0004-0000-0600-00000D000000}"/>
+    <hyperlink ref="F24" r:id="rId15" xr:uid="{00000000-0004-0000-0600-00000E000000}"/>
+    <hyperlink ref="F25" r:id="rId16" xr:uid="{00000000-0004-0000-0600-00000F000000}"/>
+    <hyperlink ref="F27" r:id="rId17" xr:uid="{00000000-0004-0000-0600-000010000000}"/>
+    <hyperlink ref="F28" r:id="rId18" xr:uid="{00000000-0004-0000-0600-000011000000}"/>
+    <hyperlink ref="F29" r:id="rId19" xr:uid="{00000000-0004-0000-0600-000012000000}"/>
+    <hyperlink ref="F31" r:id="rId20" xr:uid="{00000000-0004-0000-0600-000013000000}"/>
+    <hyperlink ref="F32" r:id="rId21" xr:uid="{00000000-0004-0000-0600-000014000000}"/>
+    <hyperlink ref="F33" r:id="rId22" xr:uid="{00000000-0004-0000-0600-000015000000}"/>
+    <hyperlink ref="F34" r:id="rId23" xr:uid="{00000000-0004-0000-0600-000016000000}"/>
+    <hyperlink ref="F39" r:id="rId24" xr:uid="{00000000-0004-0000-0600-000017000000}"/>
+    <hyperlink ref="F69" r:id="rId25" xr:uid="{00000000-0004-0000-0600-000018000000}"/>
+    <hyperlink ref="F71" r:id="rId26" xr:uid="{00000000-0004-0000-0600-000019000000}"/>
+    <hyperlink ref="F73" r:id="rId27" xr:uid="{00000000-0004-0000-0600-00001A000000}"/>
+    <hyperlink ref="F74" r:id="rId28" xr:uid="{00000000-0004-0000-0600-00001B000000}"/>
+    <hyperlink ref="F75" r:id="rId29" xr:uid="{00000000-0004-0000-0600-00001C000000}"/>
+    <hyperlink ref="F76" r:id="rId30" xr:uid="{00000000-0004-0000-0600-00001D000000}"/>
+    <hyperlink ref="F77" r:id="rId31" xr:uid="{00000000-0004-0000-0600-00001E000000}"/>
+    <hyperlink ref="F78" r:id="rId32" xr:uid="{00000000-0004-0000-0600-00001F000000}"/>
+    <hyperlink ref="F80" r:id="rId33" xr:uid="{00000000-0004-0000-0600-000020000000}"/>
+    <hyperlink ref="F87" r:id="rId34" xr:uid="{00000000-0004-0000-0600-000021000000}"/>
+    <hyperlink ref="F101" r:id="rId35" xr:uid="{00000000-0004-0000-0600-000022000000}"/>
+    <hyperlink ref="F105" r:id="rId36" xr:uid="{00000000-0004-0000-0600-000023000000}"/>
+    <hyperlink ref="F106" r:id="rId37" xr:uid="{00000000-0004-0000-0600-000024000000}"/>
+    <hyperlink ref="F107" r:id="rId38" xr:uid="{00000000-0004-0000-0600-000025000000}"/>
+    <hyperlink ref="F109" r:id="rId39" xr:uid="{00000000-0004-0000-0600-000026000000}"/>
+    <hyperlink ref="F113" r:id="rId40" xr:uid="{00000000-0004-0000-0600-000027000000}"/>
+    <hyperlink ref="F114" r:id="rId41" xr:uid="{00000000-0004-0000-0600-000028000000}"/>
+    <hyperlink ref="F115" r:id="rId42" xr:uid="{00000000-0004-0000-0600-000029000000}"/>
+    <hyperlink ref="F116" r:id="rId43" xr:uid="{00000000-0004-0000-0600-00002A000000}"/>
+    <hyperlink ref="F118" r:id="rId44" xr:uid="{00000000-0004-0000-0600-00002B000000}"/>
+    <hyperlink ref="F119" r:id="rId45" xr:uid="{00000000-0004-0000-0600-00002C000000}"/>
+    <hyperlink ref="F120" r:id="rId46" xr:uid="{00000000-0004-0000-0600-00002D000000}"/>
+    <hyperlink ref="F122" r:id="rId47" xr:uid="{00000000-0004-0000-0600-00002E000000}"/>
+    <hyperlink ref="F128" r:id="rId48" xr:uid="{00000000-0004-0000-0600-00002F000000}"/>
+    <hyperlink ref="F129" r:id="rId49" xr:uid="{00000000-0004-0000-0600-000030000000}"/>
+    <hyperlink ref="F133" r:id="rId50" xr:uid="{00000000-0004-0000-0600-000031000000}"/>
+    <hyperlink ref="F134" r:id="rId51" xr:uid="{00000000-0004-0000-0600-000032000000}"/>
+    <hyperlink ref="F135" r:id="rId52" xr:uid="{00000000-0004-0000-0600-000033000000}"/>
+    <hyperlink ref="F136" r:id="rId53" xr:uid="{00000000-0004-0000-0600-000034000000}"/>
+    <hyperlink ref="F138" r:id="rId54" xr:uid="{00000000-0004-0000-0600-000035000000}"/>
+    <hyperlink ref="F140" r:id="rId55" xr:uid="{00000000-0004-0000-0600-000036000000}"/>
+    <hyperlink ref="F141" r:id="rId56" xr:uid="{00000000-0004-0000-0600-000037000000}"/>
+    <hyperlink ref="F142" r:id="rId57" xr:uid="{00000000-0004-0000-0600-000038000000}"/>
+    <hyperlink ref="F143" r:id="rId58" xr:uid="{00000000-0004-0000-0600-000039000000}"/>
+    <hyperlink ref="F149" r:id="rId59" xr:uid="{00000000-0004-0000-0600-00003A000000}"/>
+    <hyperlink ref="F167" r:id="rId60" xr:uid="{00000000-0004-0000-0600-00003B000000}"/>
+    <hyperlink ref="F168" r:id="rId61" tooltip="https://www.acfun.cn/v/ac47931569" xr:uid="{00000000-0004-0000-0600-00003C000000}"/>
+    <hyperlink ref="F170" r:id="rId62" xr:uid="{00000000-0004-0000-0600-00003D000000}"/>
+    <hyperlink ref="F171" r:id="rId63" xr:uid="{00000000-0004-0000-0600-00003E000000}"/>
+    <hyperlink ref="F172" r:id="rId64" xr:uid="{00000000-0004-0000-0600-00003F000000}"/>
+    <hyperlink ref="F173" r:id="rId65" xr:uid="{00000000-0004-0000-0600-000040000000}"/>
+    <hyperlink ref="F174" r:id="rId66" xr:uid="{00000000-0004-0000-0600-000041000000}"/>
+    <hyperlink ref="F175" r:id="rId67" xr:uid="{00000000-0004-0000-0600-000042000000}"/>
+    <hyperlink ref="F176" r:id="rId68" xr:uid="{00000000-0004-0000-0600-000043000000}"/>
+    <hyperlink ref="F177" r:id="rId69" xr:uid="{00000000-0004-0000-0600-000044000000}"/>
+    <hyperlink ref="F178" r:id="rId70" xr:uid="{00000000-0004-0000-0600-000045000000}"/>
+    <hyperlink ref="F179" r:id="rId71" tooltip="https://www.acfun.cn/v/ac47931603" xr:uid="{00000000-0004-0000-0600-000046000000}"/>
+    <hyperlink ref="F181" r:id="rId72" xr:uid="{00000000-0004-0000-0600-000047000000}"/>
+    <hyperlink ref="F183" r:id="rId73" xr:uid="{00000000-0004-0000-0600-000048000000}"/>
+    <hyperlink ref="F184" r:id="rId74" xr:uid="{00000000-0004-0000-0600-000049000000}"/>
+    <hyperlink ref="F186" r:id="rId75" xr:uid="{00000000-0004-0000-0600-00004A000000}"/>
+    <hyperlink ref="F192" r:id="rId76" xr:uid="{00000000-0004-0000-0600-00004B000000}"/>
+    <hyperlink ref="F193" r:id="rId77" xr:uid="{00000000-0004-0000-0600-00004C000000}"/>
+    <hyperlink ref="F198" r:id="rId78" xr:uid="{00000000-0004-0000-0600-00004D000000}"/>
+    <hyperlink ref="F199" r:id="rId79" xr:uid="{00000000-0004-0000-0600-00004E000000}"/>
+    <hyperlink ref="F201" r:id="rId80" xr:uid="{00000000-0004-0000-0600-00004F000000}"/>
+    <hyperlink ref="F202" r:id="rId81" xr:uid="{00000000-0004-0000-0600-000050000000}"/>
+    <hyperlink ref="F203" r:id="rId82" xr:uid="{00000000-0004-0000-0600-000051000000}"/>
+    <hyperlink ref="F204" r:id="rId83" xr:uid="{00000000-0004-0000-0600-000052000000}"/>
+    <hyperlink ref="F206" r:id="rId84" xr:uid="{00000000-0004-0000-0600-000053000000}"/>
+    <hyperlink ref="F207" r:id="rId85" xr:uid="{00000000-0004-0000-0600-000054000000}"/>
+    <hyperlink ref="F208" r:id="rId86" xr:uid="{00000000-0004-0000-0600-000055000000}"/>
+    <hyperlink ref="F209" r:id="rId87" xr:uid="{00000000-0004-0000-0600-000056000000}"/>
+    <hyperlink ref="F211" r:id="rId88" xr:uid="{00000000-0004-0000-0600-000057000000}"/>
+    <hyperlink ref="F213" r:id="rId89" tooltip="https://www.acfun.cn/v/ac48409409_1" xr:uid="{00000000-0004-0000-0600-000058000000}"/>
+    <hyperlink ref="F219" r:id="rId90" xr:uid="{00000000-0004-0000-0600-000059000000}"/>
+    <hyperlink ref="F220" r:id="rId91" xr:uid="{00000000-0004-0000-0600-00005A000000}"/>
+    <hyperlink ref="F225" r:id="rId92" xr:uid="{00000000-0004-0000-0600-00005B000000}"/>
+    <hyperlink ref="F235" r:id="rId93" xr:uid="{00000000-0004-0000-0600-00005C000000}"/>
+    <hyperlink ref="F236" r:id="rId94" xr:uid="{00000000-0004-0000-0600-00005D000000}"/>
+    <hyperlink ref="F238" r:id="rId95" xr:uid="{00000000-0004-0000-0600-00005E000000}"/>
+    <hyperlink ref="F240" r:id="rId96" xr:uid="{00000000-0004-0000-0600-00005F000000}"/>
+    <hyperlink ref="F241" r:id="rId97" xr:uid="{00000000-0004-0000-0600-000060000000}"/>
+    <hyperlink ref="F242" r:id="rId98" xr:uid="{00000000-0004-0000-0600-000061000000}"/>
+    <hyperlink ref="F244" r:id="rId99" xr:uid="{00000000-0004-0000-0600-000062000000}"/>
+    <hyperlink ref="F246" r:id="rId100" xr:uid="{00000000-0004-0000-0600-000063000000}"/>
+    <hyperlink ref="F248" r:id="rId101" xr:uid="{00000000-0004-0000-0600-000064000000}"/>
+    <hyperlink ref="F249" r:id="rId102" xr:uid="{00000000-0004-0000-0600-000065000000}"/>
+    <hyperlink ref="F250" r:id="rId103" xr:uid="{00000000-0004-0000-0600-000066000000}"/>
+    <hyperlink ref="F251" r:id="rId104" xr:uid="{00000000-0004-0000-0600-000067000000}"/>
+    <hyperlink ref="F252" r:id="rId105" xr:uid="{00000000-0004-0000-0600-000068000000}"/>
+    <hyperlink ref="F257" r:id="rId106" xr:uid="{00000000-0004-0000-0600-000069000000}"/>
+    <hyperlink ref="F259" r:id="rId107" xr:uid="{00000000-0004-0000-0600-00006A000000}"/>
+    <hyperlink ref="F260" r:id="rId108" xr:uid="{00000000-0004-0000-0600-00006B000000}"/>
+    <hyperlink ref="F261" r:id="rId109" xr:uid="{00000000-0004-0000-0600-00006C000000}"/>
+    <hyperlink ref="F262" r:id="rId110" xr:uid="{00000000-0004-0000-0600-00006D000000}"/>
+    <hyperlink ref="F263" r:id="rId111" xr:uid="{00000000-0004-0000-0600-00006E000000}"/>
+    <hyperlink ref="F264" r:id="rId112" xr:uid="{00000000-0004-0000-0600-00006F000000}"/>
+    <hyperlink ref="F266" r:id="rId113" xr:uid="{00000000-0004-0000-0600-000070000000}"/>
+    <hyperlink ref="F272" r:id="rId114" xr:uid="{00000000-0004-0000-0600-000071000000}"/>
+    <hyperlink ref="F274" r:id="rId115" xr:uid="{00000000-0004-0000-0600-000072000000}"/>
+    <hyperlink ref="F275" r:id="rId116" xr:uid="{00000000-0004-0000-0600-000073000000}"/>
+    <hyperlink ref="F276" r:id="rId117" xr:uid="{00000000-0004-0000-0600-000074000000}"/>
+    <hyperlink ref="F277" r:id="rId118" xr:uid="{00000000-0004-0000-0600-000075000000}"/>
+    <hyperlink ref="F278" r:id="rId119" xr:uid="{00000000-0004-0000-0600-000076000000}"/>
+    <hyperlink ref="F279" r:id="rId120" xr:uid="{00000000-0004-0000-0600-000077000000}"/>
+    <hyperlink ref="F281" r:id="rId121" xr:uid="{00000000-0004-0000-0600-000078000000}"/>
+    <hyperlink ref="F282" r:id="rId122" xr:uid="{00000000-0004-0000-0600-000079000000}"/>
+    <hyperlink ref="F284" r:id="rId123" xr:uid="{00000000-0004-0000-0600-00007A000000}"/>
+    <hyperlink ref="F286" r:id="rId124" xr:uid="{00000000-0004-0000-0600-00007B000000}"/>
+    <hyperlink ref="F291" r:id="rId125" xr:uid="{00000000-0004-0000-0600-00007C000000}"/>
+    <hyperlink ref="F292" r:id="rId126" xr:uid="{00000000-0004-0000-0600-00007D000000}"/>
+    <hyperlink ref="F296" r:id="rId127" xr:uid="{00000000-0004-0000-0600-00007E000000}"/>
+    <hyperlink ref="F297" r:id="rId128" xr:uid="{00000000-0004-0000-0600-00007F000000}"/>
+    <hyperlink ref="F298" r:id="rId129" xr:uid="{00000000-0004-0000-0600-000080000000}"/>
+    <hyperlink ref="F299" r:id="rId130" xr:uid="{00000000-0004-0000-0600-000081000000}"/>
+    <hyperlink ref="F300" r:id="rId131" xr:uid="{00000000-0004-0000-0600-000082000000}"/>
+    <hyperlink ref="F301" r:id="rId132" xr:uid="{00000000-0004-0000-0600-000083000000}"/>
+    <hyperlink ref="F304" r:id="rId133" xr:uid="{00000000-0004-0000-0600-000084000000}"/>
+    <hyperlink ref="F306" r:id="rId134" xr:uid="{00000000-0004-0000-0600-000085000000}"/>
+    <hyperlink ref="F307" r:id="rId135" xr:uid="{00000000-0004-0000-0600-000086000000}"/>
+    <hyperlink ref="F308" r:id="rId136" xr:uid="{00000000-0004-0000-0600-000087000000}"/>
+    <hyperlink ref="F309" r:id="rId137" xr:uid="{00000000-0004-0000-0600-000088000000}"/>
+    <hyperlink ref="F310" r:id="rId138" xr:uid="{00000000-0004-0000-0600-000089000000}"/>
+    <hyperlink ref="F311" r:id="rId139" xr:uid="{00000000-0004-0000-0600-00008A000000}"/>
+    <hyperlink ref="F312" r:id="rId140" xr:uid="{00000000-0004-0000-0600-00008B000000}"/>
+    <hyperlink ref="F313" r:id="rId141" xr:uid="{00000000-0004-0000-0600-00008C000000}"/>
+    <hyperlink ref="F314" r:id="rId142" xr:uid="{00000000-0004-0000-0600-00008D000000}"/>
+    <hyperlink ref="F316" r:id="rId143" xr:uid="{00000000-0004-0000-0600-00008E000000}"/>
+    <hyperlink ref="F317" r:id="rId144" xr:uid="{00000000-0004-0000-0600-00008F000000}"/>
+    <hyperlink ref="F319" r:id="rId145" xr:uid="{00000000-0004-0000-0600-000090000000}"/>
+    <hyperlink ref="F325" r:id="rId146" xr:uid="{00000000-0004-0000-0600-000091000000}"/>
+    <hyperlink ref="F326" r:id="rId147" xr:uid="{00000000-0004-0000-0600-000092000000}"/>
+    <hyperlink ref="F331" r:id="rId148" tooltip="https://www.acfun.cn/v/ac48751334_3" xr:uid="{00000000-0004-0000-0600-000093000000}"/>
+    <hyperlink ref="F332" r:id="rId149" xr:uid="{00000000-0004-0000-0600-000094000000}"/>
+    <hyperlink ref="F333" r:id="rId150" xr:uid="{00000000-0004-0000-0600-000095000000}"/>
+    <hyperlink ref="F335" r:id="rId151" xr:uid="{00000000-0004-0000-0600-000096000000}"/>
+    <hyperlink ref="F336" r:id="rId152" xr:uid="{00000000-0004-0000-0600-000097000000}"/>
+    <hyperlink ref="F337" r:id="rId153" xr:uid="{00000000-0004-0000-0600-000098000000}"/>
+    <hyperlink ref="F338" r:id="rId154" xr:uid="{00000000-0004-0000-0600-000099000000}"/>
+    <hyperlink ref="F339" r:id="rId155" xr:uid="{00000000-0004-0000-0600-00009A000000}"/>
+    <hyperlink ref="F345" r:id="rId156" xr:uid="{00000000-0004-0000-0600-00009B000000}"/>
+    <hyperlink ref="F346" r:id="rId157" xr:uid="{00000000-0004-0000-0600-00009C000000}"/>
+    <hyperlink ref="F347" r:id="rId158" xr:uid="{00000000-0004-0000-0600-00009D000000}"/>
+    <hyperlink ref="F348" r:id="rId159" xr:uid="{00000000-0004-0000-0600-00009E000000}"/>
+    <hyperlink ref="F349" r:id="rId160" xr:uid="{00000000-0004-0000-0600-00009F000000}"/>
+    <hyperlink ref="F350" r:id="rId161" xr:uid="{00000000-0004-0000-0600-0000A0000000}"/>
+    <hyperlink ref="F351" r:id="rId162" xr:uid="{00000000-0004-0000-0600-0000A1000000}"/>
+    <hyperlink ref="F352" r:id="rId163" xr:uid="{00000000-0004-0000-0600-0000A2000000}"/>
+    <hyperlink ref="F358" r:id="rId164" xr:uid="{00000000-0004-0000-0600-0000A3000000}"/>
+    <hyperlink ref="F359" r:id="rId165" xr:uid="{00000000-0004-0000-0600-0000A4000000}"/>
+    <hyperlink ref="F363" r:id="rId166" xr:uid="{00000000-0004-0000-0600-0000A5000000}"/>
+    <hyperlink ref="F364" r:id="rId167" xr:uid="{00000000-0004-0000-0600-0000A6000000}"/>
+    <hyperlink ref="F365" r:id="rId168" xr:uid="{00000000-0004-0000-0600-0000A7000000}"/>
+    <hyperlink ref="F368" r:id="rId169" xr:uid="{00000000-0004-0000-0600-0000A8000000}"/>
+    <hyperlink ref="F369" r:id="rId170" xr:uid="{00000000-0004-0000-0600-0000A9000000}"/>
+    <hyperlink ref="F370" r:id="rId171" xr:uid="{00000000-0004-0000-0600-0000AA000000}"/>
+    <hyperlink ref="F372" r:id="rId172" xr:uid="{00000000-0004-0000-0600-0000AB000000}"/>
+    <hyperlink ref="F373" r:id="rId173" xr:uid="{00000000-0004-0000-0600-0000AC000000}"/>
+    <hyperlink ref="F374" r:id="rId174" xr:uid="{00000000-0004-0000-0600-0000AD000000}"/>
+    <hyperlink ref="F376" r:id="rId175" xr:uid="{00000000-0004-0000-0600-0000AE000000}"/>
+    <hyperlink ref="F378" r:id="rId176" xr:uid="{00000000-0004-0000-0600-0000AF000000}"/>
+    <hyperlink ref="F384" r:id="rId177" xr:uid="{00000000-0004-0000-0600-0000B0000000}"/>
+    <hyperlink ref="F385" r:id="rId178" xr:uid="{00000000-0004-0000-0600-0000B1000000}"/>
+    <hyperlink ref="F389" r:id="rId179" xr:uid="{00000000-0004-0000-0600-0000B2000000}"/>
+    <hyperlink ref="F390" r:id="rId180" xr:uid="{00000000-0004-0000-0600-0000B3000000}"/>
+    <hyperlink ref="F391" r:id="rId181" xr:uid="{00000000-0004-0000-0600-0000B4000000}"/>
+    <hyperlink ref="F395" r:id="rId182" xr:uid="{00000000-0004-0000-0600-0000B5000000}"/>
+    <hyperlink ref="F396" r:id="rId183" xr:uid="{00000000-0004-0000-0600-0000B6000000}"/>
+    <hyperlink ref="F397" r:id="rId184" xr:uid="{00000000-0004-0000-0600-0000B7000000}"/>
+    <hyperlink ref="F398" r:id="rId185" xr:uid="{00000000-0004-0000-0600-0000B8000000}"/>
+    <hyperlink ref="F399" r:id="rId186" xr:uid="{00000000-0004-0000-0600-0000B9000000}"/>
+    <hyperlink ref="F400" r:id="rId187" xr:uid="{00000000-0004-0000-0600-0000BA000000}"/>
+    <hyperlink ref="F401" r:id="rId188" xr:uid="{00000000-0004-0000-0600-0000BB000000}"/>
+    <hyperlink ref="F402" r:id="rId189" xr:uid="{00000000-0004-0000-0600-0000BC000000}"/>
+    <hyperlink ref="F403" r:id="rId190" xr:uid="{00000000-0004-0000-0600-0000BD000000}"/>
+    <hyperlink ref="F405" r:id="rId191" xr:uid="{00000000-0004-0000-0600-0000BE000000}"/>
+    <hyperlink ref="F406" r:id="rId192" xr:uid="{00000000-0004-0000-0600-0000BF000000}"/>
+    <hyperlink ref="F408" r:id="rId193" xr:uid="{00000000-0004-0000-0600-0000C0000000}"/>
+    <hyperlink ref="F414" r:id="rId194" xr:uid="{00000000-0004-0000-0600-0000C1000000}"/>
+    <hyperlink ref="F415" r:id="rId195" xr:uid="{00000000-0004-0000-0600-0000C2000000}"/>
+    <hyperlink ref="F420" r:id="rId196" xr:uid="{00000000-0004-0000-0600-0000C3000000}"/>
+    <hyperlink ref="F421" r:id="rId197" xr:uid="{00000000-0004-0000-0600-0000C4000000}"/>
+    <hyperlink ref="F422" r:id="rId198" xr:uid="{00000000-0004-0000-0600-0000C5000000}"/>
+    <hyperlink ref="F424" r:id="rId199" xr:uid="{00000000-0004-0000-0600-0000C6000000}"/>
+    <hyperlink ref="F425" r:id="rId200" tooltip="https://www.acfun.cn/v/ac47932123_4" xr:uid="{00000000-0004-0000-0600-0000C7000000}"/>
+    <hyperlink ref="F426" r:id="rId201" xr:uid="{00000000-0004-0000-0600-0000C8000000}"/>
+    <hyperlink ref="F427" r:id="rId202" xr:uid="{00000000-0004-0000-0600-0000C9000000}"/>
+    <hyperlink ref="F428" r:id="rId203" xr:uid="{00000000-0004-0000-0600-0000CA000000}"/>
+    <hyperlink ref="F430" r:id="rId204" xr:uid="{00000000-0004-0000-0600-0000CB000000}"/>
+    <hyperlink ref="F434" r:id="rId205" xr:uid="{00000000-0004-0000-0600-0000CC000000}"/>
+    <hyperlink ref="F435" r:id="rId206" xr:uid="{00000000-0004-0000-0600-0000CD000000}"/>
+    <hyperlink ref="F436" r:id="rId207" xr:uid="{00000000-0004-0000-0600-0000CE000000}"/>
+    <hyperlink ref="F438" r:id="rId208" xr:uid="{00000000-0004-0000-0600-0000CF000000}"/>
+    <hyperlink ref="F440" r:id="rId209" xr:uid="{00000000-0004-0000-0600-0000D0000000}"/>
+    <hyperlink ref="F441" r:id="rId210" xr:uid="{00000000-0004-0000-0600-0000D1000000}"/>
+    <hyperlink ref="F447" r:id="rId211" xr:uid="{00000000-0004-0000-0600-0000D2000000}"/>
+    <hyperlink ref="F448" r:id="rId212" xr:uid="{00000000-0004-0000-0600-0000D3000000}"/>
+    <hyperlink ref="F451" r:id="rId213" xr:uid="{00000000-0004-0000-0600-0000D4000000}"/>
+    <hyperlink ref="F452" r:id="rId214" tooltip="https://www.acfun.cn/v/ac47935862" xr:uid="{00000000-0004-0000-0600-0000D5000000}"/>
+    <hyperlink ref="F453" r:id="rId215" tooltip="https://www.acfun.cn/v/ac47932937" xr:uid="{00000000-0004-0000-0600-0000D6000000}"/>
+    <hyperlink ref="F454" r:id="rId216" xr:uid="{00000000-0004-0000-0600-0000D7000000}"/>
+    <hyperlink ref="F455" r:id="rId217" xr:uid="{00000000-0004-0000-0600-0000D8000000}"/>
+    <hyperlink ref="F457" r:id="rId218" xr:uid="{00000000-0004-0000-0600-0000D9000000}"/>
+    <hyperlink ref="F458" r:id="rId219" xr:uid="{00000000-0004-0000-0600-0000DA000000}"/>
+    <hyperlink ref="F459" r:id="rId220" tooltip="https://www.acfun.cn/v/ac47932763" xr:uid="{00000000-0004-0000-0600-0000DB000000}"/>
+    <hyperlink ref="F460" r:id="rId221" xr:uid="{00000000-0004-0000-0600-0000DC000000}"/>
+    <hyperlink ref="F461" r:id="rId222" xr:uid="{00000000-0004-0000-0600-0000DD000000}"/>
+    <hyperlink ref="F463" r:id="rId223" xr:uid="{00000000-0004-0000-0600-0000DE000000}"/>
+    <hyperlink ref="F464" r:id="rId224" tooltip="https://www.acfun.cn/v/ac47931710" xr:uid="{00000000-0004-0000-0600-0000DF000000}"/>
+    <hyperlink ref="F465" r:id="rId225" xr:uid="{00000000-0004-0000-0600-0000E0000000}"/>
+    <hyperlink ref="F466" r:id="rId226" xr:uid="{00000000-0004-0000-0600-0000E1000000}"/>
+    <hyperlink ref="F468" r:id="rId227" xr:uid="{00000000-0004-0000-0600-0000E2000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="52.4545454545455" style="3" customWidth="1"/>
+    <col min="1" max="1" width="52.453125" style="3" customWidth="1"/>
     <col min="2" max="2" width="20" style="19" customWidth="1"/>
-    <col min="3" max="3" width="38.4545454545455" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.8181818181818" style="3" customWidth="1"/>
-    <col min="5" max="5" width="28.6363636363636" style="3" customWidth="1"/>
-    <col min="6" max="6" width="48.0909090909091" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.5454545454545" style="3" customWidth="1"/>
+    <col min="3" max="3" width="38.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="28.6328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="48.08984375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" style="3" customWidth="1"/>
     <col min="8" max="8" width="14" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.4545454545455" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -41777,7 +41168,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:9">
+    <row r="3" spans="1:9" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -41887,7 +41278,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" spans="1:9">
+    <row r="7" spans="1:9" ht="16" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -43019,43 +42410,41 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H48" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:H48" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.acfun.cn/v/ac48837138"/>
-    <hyperlink ref="F10" r:id="rId2" display="https://www.acfun.cn/v/ac48796276"/>
-    <hyperlink ref="F15" r:id="rId3" display="https://www.bilibili.com/video/BV1aAZYYAEEQ"/>
-    <hyperlink ref="F17" r:id="rId4" display="https://www.bilibili.com/video/BV1RV2eBeEAd"/>
-    <hyperlink ref="F19" r:id="rId5" display="https://www.bilibili.com/video/BV1pB3izpExm"/>
-    <hyperlink ref="F24" r:id="rId6" display="https://www.acfun.cn/v/ac48737511"/>
-    <hyperlink ref="F28" r:id="rId7" display="https://www.acfun.cn/v/ac48832641" tooltip="https://www.acfun.cn/v/ac48832641"/>
-    <hyperlink ref="F29" r:id="rId8" display="https://www.acfun.cn/v/ac48832628" tooltip="https://www.acfun.cn/v/ac48832628"/>
-    <hyperlink ref="F30" r:id="rId9" display="https://www.acfun.cn/v/ac48691288" tooltip="https://www.acfun.cn/v/ac48691288"/>
-    <hyperlink ref="F33" r:id="rId10" display="https://www.acfun.cn/v/ac48832656"/>
-    <hyperlink ref="F34" r:id="rId11" display="https://www.bilibili.com/video/BV1TFJW6FEeP"/>
-    <hyperlink ref="F36" r:id="rId12" display="https://www.bilibili.com/video/BV18RdHBnELz"/>
-    <hyperlink ref="F42" r:id="rId13" display="https://www.acfun.cn/v/ac48645465" tooltip="https://www.acfun.cn/v/ac48645465"/>
-    <hyperlink ref="F43" r:id="rId14" display="https://www.acfun.cn/v/ac48644820" tooltip="https://www.acfun.cn/v/ac48644820"/>
-    <hyperlink ref="F48" r:id="rId15" display="https://www.bilibili.com/video/BV17iYj6bE6G" tooltip="https://www.bilibili.com/video/BV17iYj6bE6G"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="F10" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
+    <hyperlink ref="F15" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
+    <hyperlink ref="F17" r:id="rId4" xr:uid="{00000000-0004-0000-0700-000003000000}"/>
+    <hyperlink ref="F19" r:id="rId5" xr:uid="{00000000-0004-0000-0700-000004000000}"/>
+    <hyperlink ref="F24" r:id="rId6" xr:uid="{00000000-0004-0000-0700-000005000000}"/>
+    <hyperlink ref="F28" r:id="rId7" tooltip="https://www.acfun.cn/v/ac48832641" xr:uid="{00000000-0004-0000-0700-000006000000}"/>
+    <hyperlink ref="F29" r:id="rId8" tooltip="https://www.acfun.cn/v/ac48832628" xr:uid="{00000000-0004-0000-0700-000007000000}"/>
+    <hyperlink ref="F30" r:id="rId9" tooltip="https://www.acfun.cn/v/ac48691288" xr:uid="{00000000-0004-0000-0700-000008000000}"/>
+    <hyperlink ref="F33" r:id="rId10" xr:uid="{00000000-0004-0000-0700-000009000000}"/>
+    <hyperlink ref="F34" r:id="rId11" xr:uid="{00000000-0004-0000-0700-00000A000000}"/>
+    <hyperlink ref="F36" r:id="rId12" xr:uid="{00000000-0004-0000-0700-00000B000000}"/>
+    <hyperlink ref="F42" r:id="rId13" tooltip="https://www.acfun.cn/v/ac48645465" xr:uid="{00000000-0004-0000-0700-00000C000000}"/>
+    <hyperlink ref="F43" r:id="rId14" tooltip="https://www.acfun.cn/v/ac48644820" xr:uid="{00000000-0004-0000-0700-00000D000000}"/>
+    <hyperlink ref="F48" r:id="rId15" tooltip="https://www.bilibili.com/video/BV17iYj6bE6G" xr:uid="{00000000-0004-0000-0700-00000E000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:G554"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="83.2727272727273" customWidth="1"/>
-    <col min="2" max="2" width="10.2727272727273" customWidth="1"/>
-    <col min="3" max="3" width="39.7272727272727" customWidth="1"/>
-    <col min="4" max="4" width="16.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="45.9090909090909" customWidth="1"/>
-    <col min="6" max="6" width="15.7272727272727" customWidth="1"/>
+    <col min="1" max="1" width="83.26953125" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
+    <col min="5" max="5" width="45.90625" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -43673,7 +43062,7 @@
       </c>
       <c r="G43" s="19"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:7">
+    <row r="44" spans="1:7" ht="15" customHeight="1">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -44933,7 +44322,7 @@
       </c>
       <c r="G136" s="19"/>
     </row>
-    <row r="137" ht="15" customHeight="1" spans="1:7">
+    <row r="137" spans="1:7" ht="15" customHeight="1">
       <c r="A137" s="3" t="s">
         <v>21</v>
       </c>
@@ -45236,7 +44625,7 @@
       </c>
       <c r="G159" s="19"/>
     </row>
-    <row r="160" ht="15" customHeight="1" spans="1:7">
+    <row r="160" spans="1:7" ht="15" customHeight="1">
       <c r="A160" s="3" t="s">
         <v>27</v>
       </c>
@@ -46077,7 +45466,7 @@
       </c>
       <c r="G222" s="19"/>
     </row>
-    <row r="223" ht="18" customHeight="1" spans="1:7">
+    <row r="223" spans="1:7" ht="18" customHeight="1">
       <c r="A223" t="s">
         <v>45</v>
       </c>
@@ -46149,7 +45538,7 @@
       </c>
       <c r="G226" s="19"/>
     </row>
-    <row r="227" ht="15" customHeight="1" spans="1:7">
+    <row r="227" spans="1:7" ht="15" customHeight="1">
       <c r="A227" t="s">
         <v>45</v>
       </c>
@@ -46386,7 +45775,7 @@
       </c>
       <c r="G242" s="19"/>
     </row>
-    <row r="243" ht="18" customHeight="1" spans="1:7">
+    <row r="243" spans="1:7" ht="18" customHeight="1">
       <c r="A243" t="s">
         <v>47</v>
       </c>
@@ -46458,7 +45847,7 @@
       </c>
       <c r="G246" s="19"/>
     </row>
-    <row r="247" ht="15" customHeight="1" spans="1:7">
+    <row r="247" spans="1:7" ht="15" customHeight="1">
       <c r="A247" t="s">
         <v>47</v>
       </c>
@@ -46695,7 +46084,7 @@
       </c>
       <c r="G262" s="19"/>
     </row>
-    <row r="263" ht="13.5" customHeight="1" spans="1:7">
+    <row r="263" spans="1:7" ht="13.5" customHeight="1">
       <c r="A263" t="s">
         <v>49</v>
       </c>
@@ -50510,15 +49899,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G554" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:G554" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G163" r:id="rId3" display="https://www.acfun.cn/v/ac47932379_3"/>
-    <hyperlink ref="G177" r:id="rId4" display="https://www.acfun.cn/v/ac47932379_4"/>
+    <hyperlink ref="G163" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="G177" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yumin\web\MujicaTimeLineWeb\_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A142DBB-0A29-458F-9E49-B01A99AD8D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="7"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="名字规范！！！" sheetId="1" r:id="rId1"/>
@@ -31,12 +32,12 @@
     <sheet name="discography_bonus_contents" sheetId="17" r:id="rId17"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">lives!$A$1:$H$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">lyrics_atlas_rules!$A$1:$D$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">songs!$A$1:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">setlist!$A$1:$G$554</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">song_comments!$A$1:$D$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">song_live_history!$A$1:$F$468</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">lives!$A$1:$H$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">setlist!$A$1:$G$554</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">songs!$A$1:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">timeline!$A$1:$J$268</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,8 +49,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -57,17 +56,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wijipedia</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>手动填写链接优先；留空时，生成器按演出名和曲名自动查找 song_live_history 的 video_url。</t>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10523" uniqueCount="2521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10549" uniqueCount="2535">
   <si>
     <t>SONG</t>
   </si>
@@ -8079,19 +8079,70 @@
   <si>
     <t>黒のバースデイ(Ulterius Procedere ver.)</t>
   </si>
+  <si>
+    <t>SGC HALL ARIAKE</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zepp Osaka Bayside</t>
+  </si>
+  <si>
+    <t>EVANESCENCE D1</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>EVANESCENCE D2</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>EVANESCENCE D3</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>EVANESCENCE 2026 JAPAN D1</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>EVANESCENCE 2026 JAPAN D2</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>EVANESCENCE 2026 JAPAN D3</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>../images/logo/evanescenced1logo.webp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>../images/logo/evanescenced2logo.webp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>../images/logo/evanescenced3logo.webp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>../images/evanescence kv.webp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.09.17</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.live样式优化 2.live新增即将到来的演出展示</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8103,7 +8154,7 @@
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -8125,13 +8176,13 @@
       <sz val="13"/>
       <color rgb="FF0F1419"/>
       <name val="MS Gothic"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Emoji"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -8164,7 +8215,7 @@
       <sz val="9.75"/>
       <color rgb="FF9599A6"/>
       <name val="Courier New"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="9.35"/>
@@ -8176,18 +8227,19 @@
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="initial"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF131313"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF131313"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -8195,6 +8247,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -8203,152 +8256,33 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8385,194 +8319,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -8580,258 +8328,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -8840,15 +8349,15 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8857,7 +8366,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8882,7 +8391,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8894,7 +8403,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -8922,62 +8431,23 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -9262,19 +8732,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="33.2727272727273" customWidth="1"/>
+    <col min="2" max="2" width="33.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -9421,7 +8892,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:2">
+    <row r="19" spans="1:2" ht="15" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -9623,25 +9094,40 @@
         <v>81</v>
       </c>
     </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="49" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="49" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="49" t="s">
+        <v>2528</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="45.9090909090909" customWidth="1"/>
-    <col min="2" max="2" width="46.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="17.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="55.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="47.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="14.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="17.9090909090909" customWidth="1"/>
+    <col min="1" max="1" width="45.90625" customWidth="1"/>
+    <col min="2" max="2" width="46.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="55.08984375" customWidth="1"/>
+    <col min="5" max="5" width="47.6328125" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -10170,7 +9656,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" spans="1:7">
+    <row r="24" spans="1:7" ht="16.5" customHeight="1">
       <c r="A24" t="s">
         <v>78</v>
       </c>
@@ -10239,7 +9725,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:7">
+    <row r="27" spans="1:7" ht="16.5" customHeight="1">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -10262,7 +9748,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1" spans="1:7">
+    <row r="28" spans="1:7" ht="28" customHeight="1">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -10285,7 +9771,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="29" s="15" customFormat="1" ht="42" customHeight="1" spans="1:7">
+    <row r="29" spans="1:7" s="15" customFormat="1" ht="42" customHeight="1">
       <c r="A29" s="15" t="s">
         <v>78</v>
       </c>
@@ -10331,7 +9817,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="31" ht="47" customHeight="1" spans="1:7">
+    <row r="31" spans="1:7" ht="47" customHeight="1">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -10489,7 +9975,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="38" ht="33" customHeight="1" spans="1:7">
+    <row r="38" spans="1:7" ht="33" customHeight="1">
       <c r="A38" t="s">
         <v>78</v>
       </c>
@@ -10512,7 +9998,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="39" ht="30.5" customHeight="1" spans="1:7">
+    <row r="39" spans="1:7" ht="30.5" customHeight="1">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -10535,7 +10021,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="40" ht="47" customHeight="1" spans="1:7">
+    <row r="40" spans="1:7" ht="47" customHeight="1">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -10658,7 +10144,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="46" s="15" customFormat="1" spans="1:7">
+    <row r="46" spans="1:7" s="15" customFormat="1">
       <c r="A46" s="15" t="s">
         <v>79</v>
       </c>
@@ -10997,7 +10483,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="61" ht="28" customHeight="1" spans="1:7">
+    <row r="61" spans="1:7" ht="28" customHeight="1">
       <c r="A61" t="s">
         <v>79</v>
       </c>
@@ -11043,7 +10529,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="63" ht="44.5" customHeight="1" spans="1:7">
+    <row r="63" spans="1:7" ht="44.5" customHeight="1">
       <c r="A63" t="s">
         <v>79</v>
       </c>
@@ -11063,7 +10549,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="64" ht="22.5" customHeight="1" spans="1:7">
+    <row r="64" spans="1:7" ht="22.5" customHeight="1">
       <c r="A64" t="s">
         <v>79</v>
       </c>
@@ -11149,7 +10635,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="68" ht="49.5" customHeight="1" spans="1:7">
+    <row r="68" spans="1:7" ht="49.5" customHeight="1">
       <c r="A68" t="s">
         <v>79</v>
       </c>
@@ -11172,7 +10658,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="69" ht="49.5" customHeight="1" spans="1:7">
+    <row r="69" spans="1:7" ht="49.5" customHeight="1">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -11195,7 +10681,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="70" ht="30.5" customHeight="1" spans="1:7">
+    <row r="70" spans="1:7" ht="30.5" customHeight="1">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -11558,42 +11044,42 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E11" r:id="rId1" display="https://x.com/bang_dream_info/status/2088182616268910792?s=20"/>
-    <hyperlink ref="E23" r:id="rId2" display="https://x.com/Watase_Yuzuki/status/2088065379088347150?s=20"/>
-    <hyperlink ref="E24" r:id="rId3" display="https://x.com/Watase_Yuzuki/status/2088179201157537898?s=20"/>
-    <hyperlink ref="E25" r:id="rId4" display="https://x.com/Watase_Yuzuki/status/2088786673832538180?s=20"/>
-    <hyperlink ref="E26" r:id="rId5" display="https://x.com/sasakirico/status/2087837294204240082?s=20"/>
-    <hyperlink ref="E27" r:id="rId6" display="https://x.com/sasakirico/status/2088071499219644718?s=20"/>
-    <hyperlink ref="E28" r:id="rId7" display="https://x.com/sasakirico/status/2088175045470458281?s=20"/>
-    <hyperlink ref="E29" r:id="rId8" display="https://x.com/sasakirico/status/2088789235675627903?s=20"/>
-    <hyperlink ref="E39" r:id="rId9" display="https://x.com/Kanon_Takao/status/2088627188316930108?s=20"/>
-    <hyperlink ref="E40" r:id="rId10" display="https://x.com/Kanon_Takao/status/2088823105057853755?s=20"/>
-    <hyperlink ref="E41" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E42" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E43" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E44" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E45" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E47" r:id="rId12" display="https://x.com/BABYMETAL_JAPAN/status/2089290445172125822?s=20"/>
-    <hyperlink ref="E61" r:id="rId13" display="https://x.com/Watase_Yuzuki/status/2088894872896061845?s=20"/>
-    <hyperlink ref="E62" r:id="rId14" display="https://x.com/Watase_Yuzuki/status/2089309227349320029?s=20"/>
-    <hyperlink ref="E63" r:id="rId15" display="https://x.com/sasakirico/status/2088912851788599553?s=20"/>
-    <hyperlink ref="E71" r:id="rId16" display="https://spice.eplus.jp/articles/331632"/>
-    <hyperlink ref="E72" r:id="rId17" display="https://natalie.mu/comic/gallery/news/588794/2400212"/>
+    <hyperlink ref="E11" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="E23" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
+    <hyperlink ref="E24" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
+    <hyperlink ref="E25" r:id="rId4" xr:uid="{00000000-0004-0000-0900-000003000000}"/>
+    <hyperlink ref="E26" r:id="rId5" xr:uid="{00000000-0004-0000-0900-000004000000}"/>
+    <hyperlink ref="E27" r:id="rId6" xr:uid="{00000000-0004-0000-0900-000005000000}"/>
+    <hyperlink ref="E28" r:id="rId7" xr:uid="{00000000-0004-0000-0900-000006000000}"/>
+    <hyperlink ref="E29" r:id="rId8" xr:uid="{00000000-0004-0000-0900-000007000000}"/>
+    <hyperlink ref="E39" r:id="rId9" xr:uid="{00000000-0004-0000-0900-000008000000}"/>
+    <hyperlink ref="E40" r:id="rId10" xr:uid="{00000000-0004-0000-0900-000009000000}"/>
+    <hyperlink ref="E41" r:id="rId11" xr:uid="{00000000-0004-0000-0900-00000A000000}"/>
+    <hyperlink ref="E42" r:id="rId12" xr:uid="{00000000-0004-0000-0900-00000B000000}"/>
+    <hyperlink ref="E43" r:id="rId13" xr:uid="{00000000-0004-0000-0900-00000C000000}"/>
+    <hyperlink ref="E44" r:id="rId14" xr:uid="{00000000-0004-0000-0900-00000D000000}"/>
+    <hyperlink ref="E45" r:id="rId15" xr:uid="{00000000-0004-0000-0900-00000E000000}"/>
+    <hyperlink ref="E47" r:id="rId16" xr:uid="{00000000-0004-0000-0900-00000F000000}"/>
+    <hyperlink ref="E61" r:id="rId17" xr:uid="{00000000-0004-0000-0900-000010000000}"/>
+    <hyperlink ref="E62" r:id="rId18" xr:uid="{00000000-0004-0000-0900-000011000000}"/>
+    <hyperlink ref="E63" r:id="rId19" xr:uid="{00000000-0004-0000-0900-000012000000}"/>
+    <hyperlink ref="E71" r:id="rId20" xr:uid="{00000000-0004-0000-0900-000013000000}"/>
+    <hyperlink ref="E72" r:id="rId21" xr:uid="{00000000-0004-0000-0900-000014000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:E566"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="31.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="16.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -14451,25 +13937,24 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:J268"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.8181818181818" customWidth="1"/>
-    <col min="2" max="2" width="30.4545454545455" customWidth="1"/>
-    <col min="4" max="4" width="61.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="7.18181818181818" customWidth="1"/>
-    <col min="7" max="7" width="22.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="12.7272727272727" customWidth="1"/>
-    <col min="9" max="9" width="111.818181818182" customWidth="1"/>
-    <col min="10" max="10" width="21.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" customWidth="1"/>
+    <col min="4" max="4" width="61.26953125" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" customWidth="1"/>
+    <col min="7" max="7" width="22.81640625" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="9" width="111.81640625" customWidth="1"/>
+    <col min="10" max="10" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -15070,7 +14555,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="24" ht="124" customHeight="1" spans="1:10">
+    <row r="24" spans="1:10" ht="124" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>1774</v>
       </c>
@@ -15093,7 +14578,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="25" ht="124" customHeight="1" spans="1:10">
+    <row r="25" spans="1:10" ht="124" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>1774</v>
       </c>
@@ -15116,7 +14601,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="26" ht="124" customHeight="1" spans="1:10">
+    <row r="26" spans="1:10" ht="124" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>1774</v>
       </c>
@@ -15139,7 +14624,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="27" ht="124" customHeight="1" spans="1:10">
+    <row r="27" spans="1:10" ht="124" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>1774</v>
       </c>
@@ -15162,7 +14647,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="28" ht="124" customHeight="1" spans="1:10">
+    <row r="28" spans="1:10" ht="124" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>1774</v>
       </c>
@@ -15185,7 +14670,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="29" ht="124" customHeight="1" spans="1:10">
+    <row r="29" spans="1:10" ht="124" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>1774</v>
       </c>
@@ -15208,7 +14693,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="30" ht="124" customHeight="1" spans="1:10">
+    <row r="30" spans="1:10" ht="124" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>1774</v>
       </c>
@@ -15231,7 +14716,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="31" ht="124" customHeight="1" spans="1:10">
+    <row r="31" spans="1:10" ht="124" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>1774</v>
       </c>
@@ -15257,7 +14742,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="32" ht="124" customHeight="1" spans="1:10">
+    <row r="32" spans="1:10" ht="124" customHeight="1">
       <c r="A32" s="8" t="s">
         <v>1774</v>
       </c>
@@ -15283,7 +14768,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="33" ht="197.5" customHeight="1" spans="1:10">
+    <row r="33" spans="1:10" ht="197.5" customHeight="1">
       <c r="A33" s="8" t="s">
         <v>1786</v>
       </c>
@@ -15306,7 +14791,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="34" ht="197.5" customHeight="1" spans="1:10">
+    <row r="34" spans="1:10" ht="197.5" customHeight="1">
       <c r="A34" s="8" t="s">
         <v>1786</v>
       </c>
@@ -15329,7 +14814,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="35" ht="197.5" customHeight="1" spans="1:10">
+    <row r="35" spans="1:10" ht="197.5" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>1786</v>
       </c>
@@ -15352,7 +14837,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="36" ht="197.5" customHeight="1" spans="1:10">
+    <row r="36" spans="1:10" ht="197.5" customHeight="1">
       <c r="A36" s="8" t="s">
         <v>1786</v>
       </c>
@@ -15375,7 +14860,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="37" ht="197.5" customHeight="1" spans="1:10">
+    <row r="37" spans="1:10" ht="197.5" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>1786</v>
       </c>
@@ -15398,7 +14883,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="38" ht="197.5" customHeight="1" spans="1:10">
+    <row r="38" spans="1:10" ht="197.5" customHeight="1">
       <c r="A38" s="8" t="s">
         <v>1786</v>
       </c>
@@ -15421,7 +14906,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="39" ht="197.5" customHeight="1" spans="1:10">
+    <row r="39" spans="1:10" ht="197.5" customHeight="1">
       <c r="A39" s="8" t="s">
         <v>1786</v>
       </c>
@@ -15444,7 +14929,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="40" ht="197.5" customHeight="1" spans="1:10">
+    <row r="40" spans="1:10" ht="197.5" customHeight="1">
       <c r="A40" s="8" t="s">
         <v>1786</v>
       </c>
@@ -15467,7 +14952,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="41" ht="197.5" customHeight="1" spans="1:10">
+    <row r="41" spans="1:10" ht="197.5" customHeight="1">
       <c r="A41" s="8" t="s">
         <v>1786</v>
       </c>
@@ -15493,7 +14978,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="42" ht="58.5" customHeight="1" spans="1:10">
+    <row r="42" spans="1:10" ht="58.5" customHeight="1">
       <c r="A42" s="8" t="s">
         <v>1798</v>
       </c>
@@ -15516,7 +15001,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="43" ht="58.5" customHeight="1" spans="1:10">
+    <row r="43" spans="1:10" ht="58.5" customHeight="1">
       <c r="A43" s="8" t="s">
         <v>1798</v>
       </c>
@@ -15542,7 +15027,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="44" ht="84" customHeight="1" spans="1:10">
+    <row r="44" spans="1:10" ht="84" customHeight="1">
       <c r="A44" s="8" t="s">
         <v>1803</v>
       </c>
@@ -15565,7 +15050,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="45" ht="84" customHeight="1" spans="1:10">
+    <row r="45" spans="1:10" ht="84" customHeight="1">
       <c r="A45" s="8" t="s">
         <v>1803</v>
       </c>
@@ -15588,7 +15073,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="46" ht="84" customHeight="1" spans="1:10">
+    <row r="46" spans="1:10" ht="84" customHeight="1">
       <c r="A46" s="8" t="s">
         <v>1803</v>
       </c>
@@ -15611,7 +15096,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="47" ht="84" customHeight="1" spans="1:10">
+    <row r="47" spans="1:10" ht="84" customHeight="1">
       <c r="A47" s="8" t="s">
         <v>1803</v>
       </c>
@@ -15634,7 +15119,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="48" ht="84" customHeight="1" spans="1:10">
+    <row r="48" spans="1:10" ht="84" customHeight="1">
       <c r="A48" s="8" t="s">
         <v>1803</v>
       </c>
@@ -15660,7 +15145,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="49" ht="84" customHeight="1" spans="1:10">
+    <row r="49" spans="1:10" ht="84" customHeight="1">
       <c r="A49" s="8" t="s">
         <v>1803</v>
       </c>
@@ -15686,7 +15171,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="50" ht="105.5" customHeight="1" spans="1:10">
+    <row r="50" spans="1:10" ht="105.5" customHeight="1">
       <c r="A50" s="8" t="s">
         <v>1812</v>
       </c>
@@ -15709,7 +15194,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="51" ht="105.5" customHeight="1" spans="1:10">
+    <row r="51" spans="1:10" ht="105.5" customHeight="1">
       <c r="A51" s="8" t="s">
         <v>1812</v>
       </c>
@@ -15732,7 +15217,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="52" ht="105.5" customHeight="1" spans="1:10">
+    <row r="52" spans="1:10" ht="105.5" customHeight="1">
       <c r="A52" s="8" t="s">
         <v>1812</v>
       </c>
@@ -15758,7 +15243,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="53" ht="126" customHeight="1" spans="1:10">
+    <row r="53" spans="1:10" ht="126" customHeight="1">
       <c r="A53" s="8" t="s">
         <v>1818</v>
       </c>
@@ -15781,7 +15266,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="54" ht="126" customHeight="1" spans="1:10">
+    <row r="54" spans="1:10" ht="126" customHeight="1">
       <c r="A54" s="8" t="s">
         <v>1818</v>
       </c>
@@ -15804,7 +15289,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="55" ht="126" customHeight="1" spans="1:10">
+    <row r="55" spans="1:10" ht="126" customHeight="1">
       <c r="A55" s="8" t="s">
         <v>1818</v>
       </c>
@@ -15827,7 +15312,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="56" ht="126" customHeight="1" spans="1:10">
+    <row r="56" spans="1:10" ht="126" customHeight="1">
       <c r="A56" s="8" t="s">
         <v>1818</v>
       </c>
@@ -15850,7 +15335,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="57" ht="126" customHeight="1" spans="1:10">
+    <row r="57" spans="1:10" ht="126" customHeight="1">
       <c r="A57" s="8" t="s">
         <v>1818</v>
       </c>
@@ -15876,7 +15361,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="58" ht="47" customHeight="1" spans="1:10">
+    <row r="58" spans="1:10" ht="47" customHeight="1">
       <c r="A58" s="8" t="s">
         <v>1826</v>
       </c>
@@ -15899,7 +15384,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="59" ht="47" customHeight="1" spans="1:10">
+    <row r="59" spans="1:10" ht="47" customHeight="1">
       <c r="A59" s="8" t="s">
         <v>1826</v>
       </c>
@@ -15922,7 +15407,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="60" ht="47" customHeight="1" spans="1:10">
+    <row r="60" spans="1:10" ht="47" customHeight="1">
       <c r="A60" s="8" t="s">
         <v>1826</v>
       </c>
@@ -16069,7 +15554,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="66" ht="84" customHeight="1" spans="1:10">
+    <row r="66" spans="1:10" ht="84" customHeight="1">
       <c r="A66" s="8" t="s">
         <v>1840</v>
       </c>
@@ -16092,7 +15577,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="67" ht="84" customHeight="1" spans="1:10">
+    <row r="67" spans="1:10" ht="84" customHeight="1">
       <c r="A67" s="8" t="s">
         <v>1840</v>
       </c>
@@ -16115,7 +15600,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="68" ht="84" customHeight="1" spans="1:10">
+    <row r="68" spans="1:10" ht="84" customHeight="1">
       <c r="A68" s="8" t="s">
         <v>1840</v>
       </c>
@@ -16138,7 +15623,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="69" ht="84" customHeight="1" spans="1:10">
+    <row r="69" spans="1:10" ht="84" customHeight="1">
       <c r="A69" s="8" t="s">
         <v>1840</v>
       </c>
@@ -16161,7 +15646,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="70" ht="84" customHeight="1" spans="1:10">
+    <row r="70" spans="1:10" ht="84" customHeight="1">
       <c r="A70" s="8" t="s">
         <v>1840</v>
       </c>
@@ -16187,7 +15672,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="71" ht="154" customHeight="1" spans="1:10">
+    <row r="71" spans="1:10" ht="154" customHeight="1">
       <c r="A71" s="8" t="s">
         <v>1848</v>
       </c>
@@ -16210,7 +15695,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="72" ht="154" customHeight="1" spans="1:10">
+    <row r="72" spans="1:10" ht="154" customHeight="1">
       <c r="A72" s="8" t="s">
         <v>1848</v>
       </c>
@@ -16233,7 +15718,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="73" ht="154" customHeight="1" spans="1:10">
+    <row r="73" spans="1:10" ht="154" customHeight="1">
       <c r="A73" s="8" t="s">
         <v>1848</v>
       </c>
@@ -16256,7 +15741,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="74" ht="154" customHeight="1" spans="1:10">
+    <row r="74" spans="1:10" ht="154" customHeight="1">
       <c r="A74" s="8" t="s">
         <v>1848</v>
       </c>
@@ -16279,7 +15764,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="75" ht="154" customHeight="1" spans="1:10">
+    <row r="75" spans="1:10" ht="154" customHeight="1">
       <c r="A75" s="8" t="s">
         <v>1848</v>
       </c>
@@ -16302,7 +15787,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="76" ht="154" customHeight="1" spans="1:10">
+    <row r="76" spans="1:10" ht="154" customHeight="1">
       <c r="A76" s="8" t="s">
         <v>1848</v>
       </c>
@@ -16325,7 +15810,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="77" ht="154" customHeight="1" spans="1:10">
+    <row r="77" spans="1:10" ht="154" customHeight="1">
       <c r="A77" s="8" t="s">
         <v>1848</v>
       </c>
@@ -16351,7 +15836,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="78" ht="154" customHeight="1" spans="1:10">
+    <row r="78" spans="1:10" ht="154" customHeight="1">
       <c r="A78" s="8" t="s">
         <v>1848</v>
       </c>
@@ -16377,7 +15862,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="79" ht="140" customHeight="1" spans="1:10">
+    <row r="79" spans="1:10" ht="140" customHeight="1">
       <c r="A79" t="s">
         <v>1848</v>
       </c>
@@ -16401,7 +15886,7 @@
       </c>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" ht="140" customHeight="1" spans="1:10">
+    <row r="80" spans="1:10" ht="140" customHeight="1">
       <c r="A80" t="s">
         <v>1848</v>
       </c>
@@ -16532,7 +16017,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="85" ht="98" customHeight="1" spans="1:10">
+    <row r="85" spans="1:10" ht="98" customHeight="1">
       <c r="A85" s="5">
         <v>45301</v>
       </c>
@@ -16555,7 +16040,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="86" ht="98" customHeight="1" spans="1:10">
+    <row r="86" spans="1:10" ht="98" customHeight="1">
       <c r="A86" s="5">
         <v>45301</v>
       </c>
@@ -16578,7 +16063,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="87" ht="98" customHeight="1" spans="1:10">
+    <row r="87" spans="1:10" ht="98" customHeight="1">
       <c r="A87" s="5">
         <v>45301</v>
       </c>
@@ -16604,7 +16089,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="88" ht="98" customHeight="1" spans="1:10">
+    <row r="88" spans="1:10" ht="98" customHeight="1">
       <c r="A88" s="5">
         <v>45301</v>
       </c>
@@ -17806,7 +17291,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="137" ht="196" customHeight="1" spans="1:10">
+    <row r="137" spans="1:10" ht="196" customHeight="1">
       <c r="A137" s="5">
         <v>45323</v>
       </c>
@@ -17829,7 +17314,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="138" ht="196" customHeight="1" spans="1:10">
+    <row r="138" spans="1:10" ht="196" customHeight="1">
       <c r="A138" s="5">
         <v>45323</v>
       </c>
@@ -17852,7 +17337,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="139" ht="196" customHeight="1" spans="1:10">
+    <row r="139" spans="1:10" ht="196" customHeight="1">
       <c r="A139" s="5">
         <v>45323</v>
       </c>
@@ -17875,7 +17360,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="140" ht="196" customHeight="1" spans="1:10">
+    <row r="140" spans="1:10" ht="196" customHeight="1">
       <c r="A140" s="5">
         <v>45323</v>
       </c>
@@ -17898,7 +17383,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="141" ht="196" customHeight="1" spans="1:10">
+    <row r="141" spans="1:10" ht="196" customHeight="1">
       <c r="A141" s="5">
         <v>45323</v>
       </c>
@@ -17921,7 +17406,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="142" ht="196" customHeight="1" spans="1:10">
+    <row r="142" spans="1:10" ht="196" customHeight="1">
       <c r="A142" s="5">
         <v>45323</v>
       </c>
@@ -17944,7 +17429,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="143" ht="196" customHeight="1" spans="1:10">
+    <row r="143" spans="1:10" ht="196" customHeight="1">
       <c r="A143" s="5">
         <v>45323</v>
       </c>
@@ -17967,7 +17452,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="144" ht="196" customHeight="1" spans="1:10">
+    <row r="144" spans="1:10" ht="196" customHeight="1">
       <c r="A144" s="5">
         <v>45323</v>
       </c>
@@ -17991,7 +17476,7 @@
       </c>
       <c r="I144" s="10"/>
     </row>
-    <row r="145" ht="196" customHeight="1" spans="1:10">
+    <row r="145" spans="1:10" ht="196" customHeight="1">
       <c r="A145" s="5">
         <v>45323</v>
       </c>
@@ -18018,7 +17503,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="146" ht="196" customHeight="1" spans="1:10">
+    <row r="146" spans="1:10" ht="196" customHeight="1">
       <c r="A146" s="5">
         <v>45323</v>
       </c>
@@ -18044,7 +17529,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="147" ht="84" customHeight="1" spans="1:10">
+    <row r="147" spans="1:10" ht="84" customHeight="1">
       <c r="A147" s="5">
         <v>45336</v>
       </c>
@@ -18070,7 +17555,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="148" ht="84" customHeight="1" spans="1:10">
+    <row r="148" spans="1:10" ht="84" customHeight="1">
       <c r="A148" s="5">
         <v>45336</v>
       </c>
@@ -18097,7 +17582,7 @@
       </c>
       <c r="I148" s="9"/>
     </row>
-    <row r="149" ht="84" customHeight="1" spans="1:10">
+    <row r="149" spans="1:10" ht="84" customHeight="1">
       <c r="A149" s="5">
         <v>45336</v>
       </c>
@@ -18123,7 +17608,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="150" ht="84" customHeight="1" spans="1:10">
+    <row r="150" spans="1:10" ht="84" customHeight="1">
       <c r="A150" s="5">
         <v>45336</v>
       </c>
@@ -18146,7 +17631,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="151" ht="84" customHeight="1" spans="1:10">
+    <row r="151" spans="1:10" ht="84" customHeight="1">
       <c r="A151" s="5">
         <v>45336</v>
       </c>
@@ -18172,7 +17657,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="152" ht="84" customHeight="1" spans="1:10">
+    <row r="152" spans="1:10" ht="84" customHeight="1">
       <c r="A152" s="5">
         <v>45336</v>
       </c>
@@ -18699,7 +18184,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="174" ht="84" customHeight="1" spans="1:10">
+    <row r="174" spans="1:10" ht="84" customHeight="1">
       <c r="A174" s="5">
         <v>45343</v>
       </c>
@@ -18722,7 +18207,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="175" ht="84" customHeight="1" spans="1:10">
+    <row r="175" spans="1:10" ht="84" customHeight="1">
       <c r="A175" s="5">
         <v>45343</v>
       </c>
@@ -18748,7 +18233,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="176" ht="84" customHeight="1" spans="1:10">
+    <row r="176" spans="1:10" ht="84" customHeight="1">
       <c r="A176" s="5">
         <v>45343</v>
       </c>
@@ -19177,7 +18662,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="194" ht="70" customHeight="1" spans="1:10">
+    <row r="194" spans="1:10" ht="70" customHeight="1">
       <c r="A194" s="5">
         <v>45360</v>
       </c>
@@ -19201,7 +18686,7 @@
       </c>
       <c r="I194" s="10"/>
     </row>
-    <row r="195" ht="70" customHeight="1" spans="1:10">
+    <row r="195" spans="1:10" ht="70" customHeight="1">
       <c r="A195" s="5">
         <v>45360</v>
       </c>
@@ -19331,7 +18816,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="200" ht="15.5" customHeight="1" spans="1:10">
+    <row r="200" spans="1:10" ht="15.5" customHeight="1">
       <c r="A200" s="5">
         <v>45374</v>
       </c>
@@ -19729,7 +19214,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="217" ht="126" customHeight="1" spans="1:10">
+    <row r="217" spans="1:10" ht="126" customHeight="1">
       <c r="A217" s="5">
         <v>45457</v>
       </c>
@@ -19753,7 +19238,7 @@
       </c>
       <c r="I217" s="9"/>
     </row>
-    <row r="218" ht="126" customHeight="1" spans="1:10">
+    <row r="218" spans="1:10" ht="126" customHeight="1">
       <c r="A218" s="5">
         <v>45457</v>
       </c>
@@ -19779,7 +19264,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="219" ht="126" customHeight="1" spans="1:10">
+    <row r="219" spans="1:10" ht="126" customHeight="1">
       <c r="A219" s="5">
         <v>45457</v>
       </c>
@@ -19805,7 +19290,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="220" ht="70" customHeight="1" spans="1:10">
+    <row r="220" spans="1:10" ht="70" customHeight="1">
       <c r="A220" s="5">
         <v>45469</v>
       </c>
@@ -19829,7 +19314,7 @@
       </c>
       <c r="I220" s="9"/>
     </row>
-    <row r="221" ht="70" customHeight="1" spans="1:10">
+    <row r="221" spans="1:10" ht="70" customHeight="1">
       <c r="A221" s="5">
         <v>45469</v>
       </c>
@@ -19853,7 +19338,7 @@
       </c>
       <c r="I221" s="9"/>
     </row>
-    <row r="222" ht="70" customHeight="1" spans="1:10">
+    <row r="222" spans="1:10" ht="70" customHeight="1">
       <c r="A222" s="5">
         <v>45469</v>
       </c>
@@ -19879,7 +19364,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="223" ht="42" customHeight="1" spans="1:10">
+    <row r="223" spans="1:10" ht="42" customHeight="1">
       <c r="A223" s="5">
         <v>45481</v>
       </c>
@@ -19902,7 +19387,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="224" ht="42" customHeight="1" spans="1:10">
+    <row r="224" spans="1:10" ht="42" customHeight="1">
       <c r="A224" s="5">
         <v>45481</v>
       </c>
@@ -19925,7 +19410,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="225" ht="42" customHeight="1" spans="1:10">
+    <row r="225" spans="1:10" ht="42" customHeight="1">
       <c r="A225" s="5">
         <v>45481</v>
       </c>
@@ -19951,7 +19436,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="226" ht="42" customHeight="1" spans="1:10">
+    <row r="226" spans="1:10" ht="42" customHeight="1">
       <c r="A226" s="5">
         <v>45481</v>
       </c>
@@ -19977,7 +19462,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="227" ht="28" customHeight="1" spans="1:10">
+    <row r="227" spans="1:10" ht="28" customHeight="1">
       <c r="A227" s="5">
         <v>45517</v>
       </c>
@@ -20003,7 +19488,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="228" ht="28" customHeight="1" spans="1:10">
+    <row r="228" spans="1:10" ht="28" customHeight="1">
       <c r="A228" s="5">
         <v>45517</v>
       </c>
@@ -20026,7 +19511,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="229" ht="98" customHeight="1" spans="1:10">
+    <row r="229" spans="1:10" ht="98" customHeight="1">
       <c r="A229" s="5">
         <v>45545</v>
       </c>
@@ -20049,7 +19534,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="230" ht="98" customHeight="1" spans="1:10">
+    <row r="230" spans="1:10" ht="98" customHeight="1">
       <c r="A230" s="5">
         <v>45545</v>
       </c>
@@ -20072,7 +19557,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="231" ht="98" customHeight="1" spans="1:10">
+    <row r="231" spans="1:10" ht="98" customHeight="1">
       <c r="A231" s="5">
         <v>45545</v>
       </c>
@@ -20295,7 +19780,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="240" ht="28" customHeight="1" spans="1:10">
+    <row r="240" spans="1:10" ht="28" customHeight="1">
       <c r="A240" s="5">
         <v>45569</v>
       </c>
@@ -20319,7 +19804,7 @@
       </c>
       <c r="I240" s="9"/>
     </row>
-    <row r="241" ht="28" customHeight="1" spans="1:10">
+    <row r="241" spans="1:10" ht="28" customHeight="1">
       <c r="A241" s="5">
         <v>45569</v>
       </c>
@@ -20345,7 +19830,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="242" ht="30.5" customHeight="1" spans="1:10">
+    <row r="242" spans="1:10" ht="30.5" customHeight="1">
       <c r="A242" s="5">
         <v>45593</v>
       </c>
@@ -20371,7 +19856,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="243" ht="30.5" customHeight="1" spans="1:10">
+    <row r="243" spans="1:10" ht="30.5" customHeight="1">
       <c r="A243" s="5">
         <v>45593</v>
       </c>
@@ -20394,7 +19879,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="244" ht="30.5" customHeight="1" spans="1:10">
+    <row r="244" spans="1:10" ht="30.5" customHeight="1">
       <c r="A244" s="5">
         <v>45593</v>
       </c>
@@ -20417,7 +19902,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="245" ht="109.5" customHeight="1" spans="1:10">
+    <row r="245" spans="1:10" ht="109.5" customHeight="1">
       <c r="A245" s="5">
         <v>45598</v>
       </c>
@@ -20440,7 +19925,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="246" ht="109.5" customHeight="1" spans="1:10">
+    <row r="246" spans="1:10" ht="109.5" customHeight="1">
       <c r="A246" s="5">
         <v>45598</v>
       </c>
@@ -20463,7 +19948,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="247" ht="109.5" customHeight="1" spans="1:10">
+    <row r="247" spans="1:10" ht="109.5" customHeight="1">
       <c r="A247" s="5">
         <v>45598</v>
       </c>
@@ -20486,7 +19971,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="248" ht="109.5" customHeight="1" spans="1:10">
+    <row r="248" spans="1:10" ht="109.5" customHeight="1">
       <c r="A248" s="5">
         <v>45598</v>
       </c>
@@ -20512,7 +19997,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="249" ht="109.5" customHeight="1" spans="1:10">
+    <row r="249" spans="1:10" ht="109.5" customHeight="1">
       <c r="A249" s="5">
         <v>45598</v>
       </c>
@@ -20538,7 +20023,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="250" ht="136" customHeight="1" spans="1:10">
+    <row r="250" spans="1:10" ht="136" customHeight="1">
       <c r="A250" s="5">
         <v>45606</v>
       </c>
@@ -20561,7 +20046,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="251" ht="136" customHeight="1" spans="1:10">
+    <row r="251" spans="1:10" ht="136" customHeight="1">
       <c r="A251" s="5">
         <v>45606</v>
       </c>
@@ -20584,7 +20069,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="252" ht="136" customHeight="1" spans="1:10">
+    <row r="252" spans="1:10" ht="136" customHeight="1">
       <c r="A252" s="5">
         <v>45606</v>
       </c>
@@ -20610,7 +20095,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="253" ht="16.5" customHeight="1" spans="1:10">
+    <row r="253" spans="1:10" ht="16.5" customHeight="1">
       <c r="A253" s="5">
         <v>45650</v>
       </c>
@@ -20633,7 +20118,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="254" ht="16.5" customHeight="1" spans="1:10">
+    <row r="254" spans="1:10" ht="16.5" customHeight="1">
       <c r="A254" s="5">
         <v>45650</v>
       </c>
@@ -20800,7 +20285,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="261" ht="77.5" customHeight="1" spans="1:10">
+    <row r="261" spans="1:10" ht="77.5" customHeight="1">
       <c r="A261" s="5">
         <v>45655</v>
       </c>
@@ -20824,7 +20309,7 @@
       </c>
       <c r="I261" s="9"/>
     </row>
-    <row r="262" ht="77.5" customHeight="1" spans="1:10">
+    <row r="262" spans="1:10" ht="77.5" customHeight="1">
       <c r="A262" s="5">
         <v>45655</v>
       </c>
@@ -20847,7 +20332,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="263" ht="77.5" customHeight="1" spans="1:10">
+    <row r="263" spans="1:10" ht="77.5" customHeight="1">
       <c r="A263" s="5">
         <v>45655</v>
       </c>
@@ -20870,7 +20355,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="264" ht="77.5" customHeight="1" spans="1:10">
+    <row r="264" spans="1:10" ht="77.5" customHeight="1">
       <c r="A264" s="5">
         <v>45655</v>
       </c>
@@ -20893,7 +20378,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="265" ht="77.5" customHeight="1" spans="1:10">
+    <row r="265" spans="1:10" ht="77.5" customHeight="1">
       <c r="A265" s="5">
         <v>45655</v>
       </c>
@@ -20942,7 +20427,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="267" ht="77.5" customHeight="1" spans="1:10">
+    <row r="267" spans="1:10" ht="77.5" customHeight="1">
       <c r="A267" s="5">
         <v>45655</v>
       </c>
@@ -20968,7 +20453,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="268" ht="197.5" customHeight="1" spans="1:10">
+    <row r="268" spans="1:10" ht="197.5" customHeight="1">
       <c r="A268" s="8" t="s">
         <v>1786</v>
       </c>
@@ -20995,30 +20480,28 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J268" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:J268" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I22" r:id="rId1" display="https://x.com/Kanon_Takao/status/1695354653582746087&#10;"/>
-    <hyperlink ref="I32" r:id="rId2" display="https://x.com/Kanon_Takao/status/1706878641228190181"/>
-    <hyperlink ref="I41" r:id="rId3" display="https://x.com/Kanon_Takao/status/1719212653686788414"/>
+    <hyperlink ref="I22" r:id="rId1" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
+    <hyperlink ref="I32" r:id="rId2" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
+    <hyperlink ref="I41" r:id="rId3" xr:uid="{00000000-0004-0000-0B00-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="43.2727272727273" customWidth="1"/>
-    <col min="2" max="2" width="24.9090909090909" customWidth="1"/>
-    <col min="3" max="3" width="23.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="43.26953125" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" customWidth="1"/>
     <col min="4" max="4" width="74" customWidth="1"/>
-    <col min="5" max="5" width="27.6363636363636" customWidth="1"/>
+    <col min="5" max="5" width="27.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -21318,7 +20801,7 @@
         <v>2192</v>
       </c>
       <c r="F15" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -21342,27 +20825,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:O16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="28.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="29.4545454545455" customWidth="1"/>
-    <col min="3" max="3" width="50.2727272727273" customWidth="1"/>
-    <col min="4" max="4" width="13.5454545454545" customWidth="1"/>
-    <col min="5" max="5" width="14.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="11.3636363636364" customWidth="1"/>
-    <col min="7" max="7" width="16.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="37.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="28.6363636363636" customWidth="1"/>
-    <col min="10" max="10" width="23.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" customWidth="1"/>
+    <col min="8" max="8" width="37.26953125" customWidth="1"/>
+    <col min="9" max="9" width="28.6328125" customWidth="1"/>
+    <col min="10" max="10" width="23.26953125" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22116,27 +21598,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:O40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="22.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="13.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="11.3636363636364" customWidth="1"/>
-    <col min="6" max="6" width="28.6363636363636" customWidth="1"/>
-    <col min="7" max="7" width="22.1818181818182" customWidth="1"/>
-    <col min="8" max="8" width="34.0909090909091" customWidth="1"/>
-    <col min="9" max="9" width="13.5454545454545" customWidth="1"/>
-    <col min="10" max="10" width="51.1818181818182" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
+    <col min="6" max="6" width="28.6328125" customWidth="1"/>
+    <col min="7" max="7" width="22.1796875" customWidth="1"/>
+    <col min="8" max="8" width="34.08984375" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" customWidth="1"/>
+    <col min="10" max="10" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -23631,20 +23112,19 @@
       <c r="E40" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:I204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="22.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="55.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="6" max="6" width="55.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -24059,7 +23539,7 @@
         <v>4</v>
       </c>
       <c r="H20" s="2">
-        <v>0.205555555555555</v>
+        <v>0.20555555555555499</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -24082,7 +23562,7 @@
         <v>6</v>
       </c>
       <c r="H21" s="2">
-        <v>0.193055555555556</v>
+        <v>0.19305555555555601</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -24128,7 +23608,7 @@
         <v>10</v>
       </c>
       <c r="H23" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -24151,7 +23631,7 @@
         <v>12</v>
       </c>
       <c r="H24" s="2">
-        <v>0.177083333333333</v>
+        <v>0.17708333333333301</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -24257,7 +23737,7 @@
         <v>4</v>
       </c>
       <c r="H29" s="2">
-        <v>0.205555555555555</v>
+        <v>0.20555555555555499</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -24280,7 +23760,7 @@
         <v>6</v>
       </c>
       <c r="H30" s="2">
-        <v>0.193055555555556</v>
+        <v>0.19305555555555601</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -24326,7 +23806,7 @@
         <v>10</v>
       </c>
       <c r="H32" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -24349,7 +23829,7 @@
         <v>12</v>
       </c>
       <c r="H33" s="2">
-        <v>0.177083333333333</v>
+        <v>0.17708333333333301</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24372,7 +23852,7 @@
         <v>24</v>
       </c>
       <c r="H34" s="2">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -24395,7 +23875,7 @@
         <v>26</v>
       </c>
       <c r="H35" s="2">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -24418,7 +23898,7 @@
         <v>2413</v>
       </c>
       <c r="H36" s="2">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -24441,7 +23921,7 @@
         <v>2414</v>
       </c>
       <c r="H37" s="2">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -24484,7 +23964,7 @@
         <v>24</v>
       </c>
       <c r="H39" s="2">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -24507,7 +23987,7 @@
         <v>26</v>
       </c>
       <c r="H40" s="2">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -24530,7 +24010,7 @@
         <v>2413</v>
       </c>
       <c r="H41" s="2">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -24553,7 +24033,7 @@
         <v>2414</v>
       </c>
       <c r="H42" s="2">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -24599,7 +24079,7 @@
         <v>2416</v>
       </c>
       <c r="H44" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -24622,7 +24102,7 @@
         <v>2417</v>
       </c>
       <c r="H45" s="2">
-        <v>0.176388888888889</v>
+        <v>0.17638888888888901</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -24645,7 +24125,7 @@
         <v>14</v>
       </c>
       <c r="H46" s="2">
-        <v>0.184027777777778</v>
+        <v>0.18402777777777801</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -24668,7 +24148,7 @@
         <v>16</v>
       </c>
       <c r="H47" s="2">
-        <v>0.127083333333333</v>
+        <v>0.12708333333333299</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -24691,7 +24171,7 @@
         <v>18</v>
       </c>
       <c r="H48" s="2">
-        <v>0.220138888888889</v>
+        <v>0.22013888888888899</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -24783,7 +24263,7 @@
         <v>2416</v>
       </c>
       <c r="H52" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -24806,7 +24286,7 @@
         <v>2417</v>
       </c>
       <c r="H53" s="2">
-        <v>0.176388888888889</v>
+        <v>0.17638888888888901</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -24829,7 +24309,7 @@
         <v>14</v>
       </c>
       <c r="H54" s="2">
-        <v>0.184027777777778</v>
+        <v>0.18402777777777801</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -24852,7 +24332,7 @@
         <v>16</v>
       </c>
       <c r="H55" s="2">
-        <v>0.127083333333333</v>
+        <v>0.12708333333333299</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -24875,7 +24355,7 @@
         <v>18</v>
       </c>
       <c r="H56" s="2">
-        <v>0.220138888888889</v>
+        <v>0.22013888888888899</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -24898,7 +24378,7 @@
         <v>28</v>
       </c>
       <c r="H57" s="2">
-        <v>0.217361111111111</v>
+        <v>0.21736111111111101</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -24967,10 +24447,10 @@
         <v>34</v>
       </c>
       <c r="H60" s="2">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" spans="1:9">
+        <v>0.16666666666666699</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15" customHeight="1">
       <c r="A61" t="s">
         <v>2236</v>
       </c>
@@ -24990,7 +24470,7 @@
         <v>36</v>
       </c>
       <c r="H61" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -25033,7 +24513,7 @@
         <v>28</v>
       </c>
       <c r="H63" s="2">
-        <v>0.217361111111111</v>
+        <v>0.21736111111111101</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -25102,10 +24582,10 @@
         <v>34</v>
       </c>
       <c r="H66" s="2">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="1:8">
+        <v>0.16666666666666699</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15" customHeight="1">
       <c r="A67" t="s">
         <v>2236</v>
       </c>
@@ -25125,7 +24605,7 @@
         <v>36</v>
       </c>
       <c r="H67" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -25168,7 +24648,7 @@
         <v>28</v>
       </c>
       <c r="H69" s="2">
-        <v>0.217361111111111</v>
+        <v>0.21736111111111101</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -25237,10 +24717,10 @@
         <v>34</v>
       </c>
       <c r="H72" s="2">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" spans="1:8">
+        <v>0.16666666666666699</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15" customHeight="1">
       <c r="A73" t="s">
         <v>2236</v>
       </c>
@@ -25260,7 +24740,7 @@
         <v>36</v>
       </c>
       <c r="H73" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -25283,7 +24763,7 @@
         <v>38</v>
       </c>
       <c r="H74" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -25329,7 +24809,7 @@
         <v>2421</v>
       </c>
       <c r="H76" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -25352,7 +24832,7 @@
         <v>2422</v>
       </c>
       <c r="H77" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -25395,7 +24875,7 @@
         <v>38</v>
       </c>
       <c r="H79" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -25441,7 +24921,7 @@
         <v>2421</v>
       </c>
       <c r="H81" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -25464,7 +24944,7 @@
         <v>2422</v>
       </c>
       <c r="H82" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -25487,7 +24967,7 @@
         <v>38</v>
       </c>
       <c r="H83" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -25510,7 +24990,7 @@
         <v>40</v>
       </c>
       <c r="H84" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -25533,7 +25013,7 @@
         <v>44</v>
       </c>
       <c r="H85" s="2">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -25556,7 +25036,7 @@
         <v>46</v>
       </c>
       <c r="H86" s="2">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -25579,7 +25059,7 @@
         <v>48</v>
       </c>
       <c r="H87" s="2">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -25602,7 +25082,7 @@
         <v>50</v>
       </c>
       <c r="H88" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -25625,7 +25105,7 @@
         <v>52</v>
       </c>
       <c r="H89" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -25668,7 +25148,7 @@
         <v>38</v>
       </c>
       <c r="H91" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -25691,7 +25171,7 @@
         <v>40</v>
       </c>
       <c r="H92" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -25714,7 +25194,7 @@
         <v>44</v>
       </c>
       <c r="H93" s="2">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -25737,7 +25217,7 @@
         <v>46</v>
       </c>
       <c r="H94" s="2">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -25760,7 +25240,7 @@
         <v>48</v>
       </c>
       <c r="H95" s="2">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -25783,7 +25263,7 @@
         <v>50</v>
       </c>
       <c r="H96" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -25806,7 +25286,7 @@
         <v>52</v>
       </c>
       <c r="H97" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -25849,7 +25329,7 @@
         <v>38</v>
       </c>
       <c r="H99" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -25872,7 +25352,7 @@
         <v>40</v>
       </c>
       <c r="H100" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -25895,7 +25375,7 @@
         <v>44</v>
       </c>
       <c r="H101" s="2">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -25918,7 +25398,7 @@
         <v>46</v>
       </c>
       <c r="H102" s="2">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -25941,7 +25421,7 @@
         <v>48</v>
       </c>
       <c r="H103" s="2">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -25964,7 +25444,7 @@
         <v>50</v>
       </c>
       <c r="H104" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -25987,7 +25467,7 @@
         <v>52</v>
       </c>
       <c r="H105" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -26330,7 +25810,7 @@
         <v>2438</v>
       </c>
       <c r="H122" s="2">
-        <v>0.229861111111111</v>
+        <v>0.22986111111111099</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -26353,7 +25833,7 @@
         <v>2439</v>
       </c>
       <c r="H123" s="2">
-        <v>0.205555555555555</v>
+        <v>0.20555555555555499</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -26376,7 +25856,7 @@
         <v>2440</v>
       </c>
       <c r="H124" s="2">
-        <v>0.272222222222222</v>
+        <v>0.27222222222222198</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -26399,7 +25879,7 @@
         <v>2441</v>
       </c>
       <c r="H125" s="2">
-        <v>0.2125</v>
+        <v>0.21249999999999999</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -26462,7 +25942,7 @@
         <v>54</v>
       </c>
       <c r="H128" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -26485,7 +25965,7 @@
         <v>58</v>
       </c>
       <c r="H129" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -26508,7 +25988,7 @@
         <v>2442</v>
       </c>
       <c r="H130" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -26531,7 +26011,7 @@
         <v>2443</v>
       </c>
       <c r="H131" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -26634,7 +26114,7 @@
         <v>54</v>
       </c>
       <c r="H136" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -26657,7 +26137,7 @@
         <v>58</v>
       </c>
       <c r="H137" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -26680,7 +26160,7 @@
         <v>2442</v>
       </c>
       <c r="H138" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -26703,7 +26183,7 @@
         <v>2443</v>
       </c>
       <c r="H139" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -26766,7 +26246,7 @@
         <v>54</v>
       </c>
       <c r="H142" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -26789,7 +26269,7 @@
         <v>58</v>
       </c>
       <c r="H143" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -26812,7 +26292,7 @@
         <v>2442</v>
       </c>
       <c r="H144" s="2">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -26835,7 +26315,7 @@
         <v>2443</v>
       </c>
       <c r="H145" s="2">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -26858,7 +26338,7 @@
         <v>38</v>
       </c>
       <c r="H146" s="2">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -26881,7 +26361,7 @@
         <v>40</v>
       </c>
       <c r="H147" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -26904,7 +26384,7 @@
         <v>44</v>
       </c>
       <c r="H148" s="2">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -26927,7 +26407,7 @@
         <v>46</v>
       </c>
       <c r="H149" s="2">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -26950,7 +26430,7 @@
         <v>48</v>
       </c>
       <c r="H150" s="2">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -26973,7 +26453,7 @@
         <v>50</v>
       </c>
       <c r="H151" s="2">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -26996,7 +26476,7 @@
         <v>52</v>
       </c>
       <c r="H152" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -27105,7 +26585,7 @@
         <v>38</v>
       </c>
       <c r="H157" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -27174,7 +26654,7 @@
         <v>50</v>
       </c>
       <c r="H160" s="2">
-        <v>0.16875</v>
+        <v>0.16875000000000001</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -27197,7 +26677,7 @@
         <v>40</v>
       </c>
       <c r="H161" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -27266,7 +26746,7 @@
         <v>56</v>
       </c>
       <c r="H164" s="2">
-        <v>0.154861111111111</v>
+        <v>0.15486111111111101</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -27312,7 +26792,7 @@
         <v>48</v>
       </c>
       <c r="H166" s="2">
-        <v>0.159722222222222</v>
+        <v>0.15972222222222199</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -27358,7 +26838,7 @@
         <v>6</v>
       </c>
       <c r="H168" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -27404,10 +26884,10 @@
         <v>44</v>
       </c>
       <c r="H170" s="2">
-        <v>0.13125</v>
-      </c>
-    </row>
-    <row r="171" ht="15" customHeight="1" spans="1:8">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="15" customHeight="1">
       <c r="A171" t="s">
         <v>206</v>
       </c>
@@ -27427,7 +26907,7 @@
         <v>36</v>
       </c>
       <c r="H171" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -27490,7 +26970,7 @@
         <v>38</v>
       </c>
       <c r="H174" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -27559,7 +27039,7 @@
         <v>50</v>
       </c>
       <c r="H177" s="2">
-        <v>0.16875</v>
+        <v>0.16875000000000001</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -27582,7 +27062,7 @@
         <v>40</v>
       </c>
       <c r="H178" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -27651,7 +27131,7 @@
         <v>56</v>
       </c>
       <c r="H181" s="2">
-        <v>0.154861111111111</v>
+        <v>0.15486111111111101</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -27697,7 +27177,7 @@
         <v>48</v>
       </c>
       <c r="H183" s="2">
-        <v>0.159722222222222</v>
+        <v>0.15972222222222199</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -27743,7 +27223,7 @@
         <v>6</v>
       </c>
       <c r="H185" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -27789,10 +27269,10 @@
         <v>44</v>
       </c>
       <c r="H187" s="2">
-        <v>0.13125</v>
-      </c>
-    </row>
-    <row r="188" ht="15" customHeight="1" spans="1:8">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="15" customHeight="1">
       <c r="A188" t="s">
         <v>206</v>
       </c>
@@ -27812,7 +27292,7 @@
         <v>36</v>
       </c>
       <c r="H188" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -27855,7 +27335,7 @@
         <v>38</v>
       </c>
       <c r="H190" s="2">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -27924,7 +27404,7 @@
         <v>50</v>
       </c>
       <c r="H193" s="2">
-        <v>0.16875</v>
+        <v>0.16875000000000001</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -27947,7 +27427,7 @@
         <v>40</v>
       </c>
       <c r="H194" s="2">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -28016,7 +27496,7 @@
         <v>56</v>
       </c>
       <c r="H197" s="2">
-        <v>0.154861111111111</v>
+        <v>0.15486111111111101</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -28062,7 +27542,7 @@
         <v>48</v>
       </c>
       <c r="H199" s="2">
-        <v>0.159722222222222</v>
+        <v>0.15972222222222199</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -28108,7 +27588,7 @@
         <v>6</v>
       </c>
       <c r="H201" s="2">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -28154,10 +27634,10 @@
         <v>44</v>
       </c>
       <c r="H203" s="2">
-        <v>0.13125</v>
-      </c>
-    </row>
-    <row r="204" ht="15" customHeight="1" spans="1:8">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="15" customHeight="1">
       <c r="A204" t="s">
         <v>206</v>
       </c>
@@ -28177,26 +27657,25 @@
         <v>36</v>
       </c>
       <c r="H204" s="2">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="33.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="24.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="10.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="25.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" customWidth="1"/>
+    <col min="5" max="5" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -28341,7 +27820,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" t="s">
         <v>2244</v>
       </c>
@@ -28852,22 +28331,22 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="65.1818181818182" customWidth="1"/>
+    <col min="3" max="3" width="65.1796875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28941,7 +28420,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" ht="21" hidden="1" customHeight="1" spans="1:4">
+    <row r="6" spans="1:4" ht="21" hidden="1" customHeight="1">
       <c r="A6" s="47" t="s">
         <v>96</v>
       </c>
@@ -28953,7 +28432,7 @@
       </c>
       <c r="D6" s="47"/>
     </row>
-    <row r="7" hidden="1" spans="1:4">
+    <row r="7" spans="1:4" hidden="1">
       <c r="A7" s="47" t="s">
         <v>96</v>
       </c>
@@ -28993,7 +28472,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:4">
+    <row r="10" spans="1:4" hidden="1">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -29327,30 +28806,29 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D33" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:D33" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="equal" val="similar"/>
-        <customFilter operator="equal" val="combine"/>
-      </customFilters>
+      <filters>
+        <filter val="similar"/>
+        <filter val="combine"/>
+      </filters>
     </filterColumn>
-    <extLst/>
   </autoFilter>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="117.181818181818" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="117.1796875" customWidth="1"/>
     <col min="3" max="3" width="9" style="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -29596,24 +29074,32 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="49" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>2534</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.6363636363636" customWidth="1"/>
-    <col min="2" max="2" width="52.6363636363636" customWidth="1"/>
-    <col min="3" max="3" width="16.6363636363636" customWidth="1"/>
-    <col min="4" max="4" width="12.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" customWidth="1"/>
+    <col min="2" max="2" width="52.6328125" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -29809,7 +29295,7 @@
         <v>46279</v>
       </c>
       <c r="D14" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -29826,40 +29312,54 @@
         <v>209</v>
       </c>
     </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" t="s">
+        <v>198</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46282</v>
+      </c>
+      <c r="D16" t="s">
+        <v>209</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15 A18:A1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16 A18:A1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"song,live,interview,discography"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D15 D18:D1000">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D18:D1000 D2:D16" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="29.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="57.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="11.3636363636364" customWidth="1"/>
+    <col min="1" max="2" width="29.7265625" customWidth="1"/>
+    <col min="3" max="3" width="57.90625" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
     <col min="5" max="5" width="20" style="25" customWidth="1"/>
-    <col min="6" max="6" width="23.2727272727273" customWidth="1"/>
-    <col min="7" max="7" width="9.27272727272727" customWidth="1"/>
-    <col min="8" max="8" width="10.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="38.3636363636364" customWidth="1"/>
-    <col min="10" max="10" width="35.1818181818182" customWidth="1"/>
-    <col min="11" max="11" width="55.6363636363636" customWidth="1"/>
-    <col min="12" max="12" width="51.3636363636364" customWidth="1"/>
-    <col min="13" max="14" width="50.6363636363636" customWidth="1"/>
-    <col min="15" max="15" width="51.3636363636364" customWidth="1"/>
-    <col min="16" max="16" width="21.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="23.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" customWidth="1"/>
+    <col min="9" max="9" width="38.36328125" customWidth="1"/>
+    <col min="10" max="10" width="35.1796875" customWidth="1"/>
+    <col min="11" max="11" width="55.6328125" customWidth="1"/>
+    <col min="12" max="12" width="51.36328125" customWidth="1"/>
+    <col min="13" max="14" width="50.6328125" customWidth="1"/>
+    <col min="15" max="15" width="51.36328125" customWidth="1"/>
+    <col min="16" max="16" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -30162,7 +29662,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:16">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -30212,7 +29712,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="8" ht="15.5" customHeight="1" spans="1:16">
+    <row r="8" spans="1:16" ht="15.5" customHeight="1">
       <c r="A8" s="34" t="s">
         <v>275</v>
       </c>
@@ -30306,7 +29806,7 @@
       </c>
       <c r="P9" s="34"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:16">
+    <row r="10" spans="1:16" ht="15" customHeight="1">
       <c r="A10" s="34" t="s">
         <v>18</v>
       </c>
@@ -30352,7 +29852,7 @@
       </c>
       <c r="P10" s="34"/>
     </row>
-    <row r="11" ht="14.5" customHeight="1" spans="1:16">
+    <row r="11" spans="1:16" ht="14.5" customHeight="1">
       <c r="A11" s="15" t="s">
         <v>20</v>
       </c>
@@ -30398,7 +29898,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="12" ht="14.5" customHeight="1" spans="1:16">
+    <row r="12" spans="1:16" ht="14.5" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>22</v>
       </c>
@@ -30594,7 +30094,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="16" ht="14.5" customHeight="1" spans="1:16">
+    <row r="16" spans="1:16" ht="14.5" customHeight="1">
       <c r="A16" t="s">
         <v>326</v>
       </c>
@@ -30694,7 +30194,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:16">
+    <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" t="s">
         <v>342</v>
       </c>
@@ -30744,7 +30244,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:16">
+    <row r="19" spans="1:16" ht="15" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -30894,7 +30394,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="22" ht="14.5" customHeight="1" spans="1:16">
+    <row r="22" spans="1:16" ht="14.5" customHeight="1">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -30944,7 +30444,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="23" ht="14.5" customHeight="1" spans="1:16">
+    <row r="23" spans="1:16" ht="14.5" customHeight="1">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -31094,7 +30594,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:16">
+    <row r="26" spans="1:16" ht="14.5" customHeight="1">
       <c r="A26" t="s">
         <v>401</v>
       </c>
@@ -31144,7 +30644,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="27" s="34" customFormat="1" ht="15.5" customHeight="1" spans="1:16">
+    <row r="27" spans="1:16" s="34" customFormat="1" ht="15.5" customHeight="1">
       <c r="A27" t="s">
         <v>409</v>
       </c>
@@ -31194,7 +30694,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="28" s="34" customFormat="1" spans="1:16">
+    <row r="28" spans="1:16" s="34" customFormat="1">
       <c r="A28" s="48" t="s">
         <v>54</v>
       </c>
@@ -31244,7 +30744,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="29" s="34" customFormat="1" spans="1:16">
+    <row r="29" spans="1:16" s="34" customFormat="1">
       <c r="A29" t="s">
         <v>423</v>
       </c>
@@ -31294,7 +30794,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="30" s="15" customFormat="1" spans="1:16">
+    <row r="30" spans="1:16" s="15" customFormat="1">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -31344,7 +30844,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="31" s="15" customFormat="1" spans="1:16">
+    <row r="31" spans="1:16" s="15" customFormat="1">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -31394,7 +30894,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="32" s="15" customFormat="1" ht="14.5" customHeight="1" spans="1:16">
+    <row r="32" spans="1:16" s="15" customFormat="1" ht="14.5" customHeight="1">
       <c r="A32" s="15" t="s">
         <v>447</v>
       </c>
@@ -31529,35 +31029,33 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P34" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:P34" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="L7" r:id="rId1" display="https://www.bilibili.com/video/BV1MP411h759"/>
-    <hyperlink ref="L13" r:id="rId2" display="https://www.bilibili.com/video/BV1Xg4y1k7GH"/>
-    <hyperlink ref="L14" r:id="rId3" display="https://www.bilibili.com/video/BV1Ai4y167MU"/>
-    <hyperlink ref="L18" r:id="rId4" display="https://www.bilibili.com/video/BV1Cz421e79N"/>
-    <hyperlink ref="L22" r:id="rId5" display="https://www.bilibili.com/video/BV1EvcdenE9h"/>
-    <hyperlink ref="L27" r:id="rId6" display="https://www.bilibili.com/video/BV1RtZmYGE3a"/>
-    <hyperlink ref="L32" r:id="rId7" display="https://www.bilibili.com/video/BV1X58m6AENA"/>
+    <hyperlink ref="L7" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="L13" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="L14" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="L18" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="L22" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="L27" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="L32" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:E193"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="32.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="67.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="27.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="13.5454545454545" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" customWidth="1"/>
+    <col min="3" max="3" width="67.54296875" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31594,7 +31092,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="14.5" customHeight="1">
       <c r="A3" t="s">
         <v>333</v>
       </c>
@@ -31681,7 +31179,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" spans="1:5">
+    <row r="9" spans="1:5" ht="13.5" customHeight="1">
       <c r="A9" t="s">
         <v>239</v>
       </c>
@@ -31891,7 +31389,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" spans="1:5">
+    <row r="24" spans="1:5" ht="18" customHeight="1">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -31905,7 +31403,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:5">
+    <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="A25" t="s">
         <v>306</v>
       </c>
@@ -32003,7 +31501,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:5">
+    <row r="32" spans="1:5" ht="14.5" customHeight="1">
       <c r="A32" t="s">
         <v>319</v>
       </c>
@@ -32020,7 +31518,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:5">
+    <row r="33" spans="1:5" ht="14.5" customHeight="1">
       <c r="A33" t="s">
         <v>326</v>
       </c>
@@ -32037,7 +31535,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:5">
+    <row r="34" spans="1:5" ht="14.5" customHeight="1">
       <c r="A34" t="s">
         <v>342</v>
       </c>
@@ -32054,7 +31552,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="35" ht="15.5" customHeight="1" spans="1:5">
+    <row r="35" spans="1:5" ht="15.5" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -32083,7 +31581,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:5">
+    <row r="37" spans="1:5" ht="15" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -32100,7 +31598,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:5">
+    <row r="38" spans="1:5" ht="15" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -32117,7 +31615,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:5">
+    <row r="39" spans="1:5" ht="14.5" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
@@ -32134,7 +31632,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:5">
+    <row r="40" spans="1:5" ht="15" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>392</v>
       </c>
@@ -32151,7 +31649,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:5">
+    <row r="41" spans="1:5" ht="15" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>401</v>
       </c>
@@ -32168,7 +31666,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:5">
+    <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>409</v>
       </c>
@@ -32720,36 +32218,34 @@
       <c r="C193" s="33"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D51" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:D51" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C14" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="C16" r:id="rId2" display="https://www.animatetimes.com/news/details.php?id=1711341102&amp;p=2"/>
-    <hyperlink ref="C18" r:id="rId3" display="https://www.lisani.jp/0000271996/4/?show_more=1"/>
-    <hyperlink ref="C22" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="B25" r:id="rId4" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n&#10;佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n&#10;高尾：就像剑一样呢。 \n&#10;佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n&#10;高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n&#10;佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n&#10;——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n&#10;佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n&#10;——也是一首很容易入耳的歌呢。\n&#10;高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n&#10;佐佐木： 谢谢——！"/>
-    <hyperlink ref="C25" r:id="rId4" display="https://www.animatetimes.com/news/details.php?id=1711342991&amp;p=2"/>
-    <hyperlink ref="C27" r:id="rId5" display="https://www.lisani.jp/0000256138/?show_more=1"/>
-    <hyperlink ref="C28" r:id="rId6" display="https://www.animatetimes.com/news/details.php?id=1711342991"/>
-    <hyperlink ref="C31" r:id="rId7" display="https://natalie.mu/music/pp/avemujica01/page/2"/>
+    <hyperlink ref="C14" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="C16" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="C18" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="C22" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="B25" r:id="rId5" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n_x000a_佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n_x000a_高尾：就像剑一样呢。 \n_x000a_佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n_x000a_高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n_x000a_佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n_x000a_——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n_x000a_佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n_x000a_——也是一首很容易入耳的歌呢。\n_x000a_高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n_x000a_佐佐木： 谢谢——！" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
+    <hyperlink ref="C25" r:id="rId6" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
+    <hyperlink ref="C27" r:id="rId7" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
+    <hyperlink ref="C28" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
+    <hyperlink ref="C31" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F468"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="12.8181818181818" style="5" customWidth="1"/>
-    <col min="3" max="3" width="49.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="69.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="39.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="29.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" customWidth="1"/>
+    <col min="4" max="4" width="69.26953125" customWidth="1"/>
+    <col min="6" max="6" width="39.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -33017,7 +32513,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" ht="16" customHeight="1">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -33188,7 +32684,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" spans="1:6">
+    <row r="24" spans="1:6" ht="16" customHeight="1">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -33669,7 +33165,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="50" ht="13.5" customHeight="1" spans="1:6">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1">
       <c r="A50" t="s">
         <v>227</v>
       </c>
@@ -34603,7 +34099,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1" spans="1:6">
+    <row r="100" spans="1:6" ht="16" customHeight="1">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -34717,7 +34213,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1" spans="1:6">
+    <row r="106" spans="1:6" ht="16" customHeight="1">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -34925,7 +34421,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1" spans="1:6">
+    <row r="117" spans="1:6" ht="16" customHeight="1">
       <c r="A117" t="s">
         <v>10</v>
       </c>
@@ -35255,7 +34751,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1" spans="1:6">
+    <row r="135" spans="1:6" ht="16" customHeight="1">
       <c r="A135" t="s">
         <v>253</v>
       </c>
@@ -35463,7 +34959,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="146" ht="16" customHeight="1" spans="1:6">
+    <row r="146" spans="1:6" ht="16" customHeight="1">
       <c r="A146" t="s">
         <v>253</v>
       </c>
@@ -35628,7 +35124,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="155" ht="16" customHeight="1" spans="1:6">
+    <row r="155" spans="1:6" ht="16" customHeight="1">
       <c r="A155" t="s">
         <v>58</v>
       </c>
@@ -35918,7 +35414,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="171" ht="16" customHeight="1" spans="1:6">
+    <row r="171" spans="1:6" ht="16" customHeight="1">
       <c r="A171" t="s">
         <v>319</v>
       </c>
@@ -37846,7 +37342,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="274" ht="15" customHeight="1" spans="1:6">
+    <row r="274" spans="1:6" ht="15" customHeight="1">
       <c r="A274" s="1" t="s">
         <v>36</v>
       </c>
@@ -37866,7 +37362,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="275" ht="15" customHeight="1" spans="1:6">
+    <row r="275" spans="1:6" ht="15" customHeight="1">
       <c r="A275" s="1" t="s">
         <v>36</v>
       </c>
@@ -37886,7 +37382,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="276" ht="15" customHeight="1" spans="1:6">
+    <row r="276" spans="1:6" ht="15" customHeight="1">
       <c r="A276" s="1" t="s">
         <v>36</v>
       </c>
@@ -37906,7 +37402,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="277" ht="15" customHeight="1" spans="1:6">
+    <row r="277" spans="1:6" ht="15" customHeight="1">
       <c r="A277" s="1" t="s">
         <v>36</v>
       </c>
@@ -37926,7 +37422,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="278" ht="15" customHeight="1" spans="1:6">
+    <row r="278" spans="1:6" ht="15" customHeight="1">
       <c r="A278" s="1" t="s">
         <v>36</v>
       </c>
@@ -37946,7 +37442,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="279" ht="15" customHeight="1" spans="1:6">
+    <row r="279" spans="1:6" ht="15" customHeight="1">
       <c r="A279" s="1" t="s">
         <v>36</v>
       </c>
@@ -37966,7 +37462,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="280" ht="15" customHeight="1" spans="1:6">
+    <row r="280" spans="1:6" ht="15" customHeight="1">
       <c r="A280" s="1" t="s">
         <v>36</v>
       </c>
@@ -41286,7 +40782,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="458" ht="16" customHeight="1" spans="1:6">
+    <row r="458" spans="1:6" ht="16" customHeight="1">
       <c r="A458" t="s">
         <v>275</v>
       </c>
@@ -41501,258 +40997,256 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F468" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:F468" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.acfun.cn/v/ac47931167" tooltip="https://www.acfun.cn/v/ac47931167"/>
-    <hyperlink ref="F3" r:id="rId2" display="https://www.acfun.cn/v/ac47931167_2"/>
-    <hyperlink ref="F7" r:id="rId3" display="https://www.acfun.cn/v/ac47931167_3"/>
-    <hyperlink ref="F8" r:id="rId4" display="https://www.acfun.cn/v/ac47931167_4"/>
-    <hyperlink ref="F9" r:id="rId5" display="https://www.acfun.cn/v/ac47931167_5"/>
-    <hyperlink ref="F10" r:id="rId6" display="https://www.acfun.cn/v/ac47931167_6"/>
-    <hyperlink ref="F12" r:id="rId7" display="https://www.acfun.cn/v/ac47931167_7"/>
-    <hyperlink ref="F14" r:id="rId8" display="https://www.acfun.cn/v/ac47934758"/>
-    <hyperlink ref="F15" r:id="rId9" display="https://www.acfun.cn/v/ac47934758_2"/>
-    <hyperlink ref="F16" r:id="rId10" display="https://www.acfun.cn/v/ac47934758_3"/>
-    <hyperlink ref="F18" r:id="rId11" display="https://www.acfun.cn/v/ac47934758_4"/>
-    <hyperlink ref="F20" r:id="rId12" display="https://www.acfun.cn/v/ac47934758_5"/>
-    <hyperlink ref="F22" r:id="rId13" display="https://www.acfun.cn/v/ac47934758_6"/>
-    <hyperlink ref="F23" r:id="rId14" display="https://www.acfun.cn/v/ac47934758_7"/>
-    <hyperlink ref="F24" r:id="rId15" display="https://www.acfun.cn/v/ac47934758_8"/>
-    <hyperlink ref="F25" r:id="rId16" display="https://www.acfun.cn/v/ac47934758_9"/>
-    <hyperlink ref="F27" r:id="rId17" display="https://www.acfun.cn/v/ac47934758_10"/>
-    <hyperlink ref="F28" r:id="rId18" display="https://www.acfun.cn/v/ac47934815"/>
-    <hyperlink ref="F29" r:id="rId19" display="https://www.acfun.cn/v/ac47934815_2"/>
-    <hyperlink ref="F31" r:id="rId20" display="https://www.acfun.cn/v/ac47934815_3"/>
-    <hyperlink ref="F32" r:id="rId21" display="https://www.acfun.cn/v/ac47934815_4"/>
-    <hyperlink ref="F33" r:id="rId22" display="https://www.acfun.cn/v/ac47934815_5"/>
-    <hyperlink ref="F34" r:id="rId23" display="https://www.acfun.cn/v/ac47934815_6"/>
-    <hyperlink ref="F39" r:id="rId24" display="https://www.acfun.cn/v/ac47934815_7"/>
-    <hyperlink ref="F69" r:id="rId25" display="https://www.acfun.cn/v/ac47935101_2"/>
-    <hyperlink ref="F71" r:id="rId26" display="https://www.acfun.cn/v/ac47935101_3"/>
-    <hyperlink ref="F73" r:id="rId27" display="https://www.acfun.cn/v/ac47935101_4"/>
-    <hyperlink ref="F74" r:id="rId28" display="https://www.acfun.cn/v/ac47935101_5"/>
-    <hyperlink ref="F75" r:id="rId29" display="https://www.acfun.cn/v/ac47935101_6"/>
-    <hyperlink ref="F76" r:id="rId30" display="https://www.acfun.cn/v/ac47935101_7"/>
-    <hyperlink ref="F77" r:id="rId31" display="https://www.acfun.cn/v/ac47935101_8"/>
-    <hyperlink ref="F78" r:id="rId32" display="https://www.acfun.cn/v/ac47935101_9"/>
-    <hyperlink ref="F80" r:id="rId33" display="https://www.acfun.cn/v/ac47935101_10"/>
-    <hyperlink ref="F87" r:id="rId34" display="https://www.acfun.cn/v/ac48752881_2"/>
-    <hyperlink ref="F101" r:id="rId35" display="https://www.acfun.cn/v/ac47924476_8"/>
-    <hyperlink ref="F105" r:id="rId36" display="https://www.acfun.cn/v/ac47935303"/>
-    <hyperlink ref="F106" r:id="rId37" display="https://www.acfun.cn/v/ac47935303_2"/>
-    <hyperlink ref="F107" r:id="rId38" display="https://www.acfun.cn/v/ac47935303_3"/>
-    <hyperlink ref="F109" r:id="rId39" display="https://www.acfun.cn/v/ac47935303_4"/>
-    <hyperlink ref="F113" r:id="rId40" display="https://www.acfun.cn/v/ac47935303_5"/>
-    <hyperlink ref="F114" r:id="rId41" display="https://www.acfun.cn/v/ac47935303_6"/>
-    <hyperlink ref="F115" r:id="rId42" display="https://www.acfun.cn/v/ac47935303_7"/>
-    <hyperlink ref="F116" r:id="rId43" display="https://www.acfun.cn/v/ac47935303_8"/>
-    <hyperlink ref="F118" r:id="rId44" display="https://www.acfun.cn/v/ac47935303_9"/>
-    <hyperlink ref="F119" r:id="rId45" display="https://www.acfun.cn/v/ac47935303_10"/>
-    <hyperlink ref="F120" r:id="rId46" display="https://www.acfun.cn/v/ac48116488"/>
-    <hyperlink ref="F122" r:id="rId47" display="https://www.acfun.cn/v/ac48116488_2"/>
-    <hyperlink ref="F128" r:id="rId48" display="https://www.acfun.cn/v/ac48116488_3"/>
-    <hyperlink ref="F129" r:id="rId49" display="https://www.acfun.cn/v/ac48116488_4"/>
-    <hyperlink ref="F133" r:id="rId50" display="https://www.acfun.cn/v/ac48116488_5"/>
-    <hyperlink ref="F134" r:id="rId51" display="https://www.acfun.cn/v/ac47934950"/>
-    <hyperlink ref="F135" r:id="rId52" display="https://www.acfun.cn/v/ac47934950_2"/>
-    <hyperlink ref="F136" r:id="rId53" display="https://www.acfun.cn/v/ac47934950_3"/>
-    <hyperlink ref="F138" r:id="rId54" display="https://www.acfun.cn/v/ac47934950_4"/>
-    <hyperlink ref="F140" r:id="rId55" display="https://www.acfun.cn/v/ac47934950_5"/>
-    <hyperlink ref="F141" r:id="rId56" display="https://www.acfun.cn/v/ac47934950_6"/>
-    <hyperlink ref="F142" r:id="rId57" display="https://www.acfun.cn/v/ac47934950_7"/>
-    <hyperlink ref="F143" r:id="rId58" display="https://www.acfun.cn/v/ac47934950_8"/>
-    <hyperlink ref="F149" r:id="rId59" display="https://www.acfun.cn/v/ac47934950_9"/>
-    <hyperlink ref="F167" r:id="rId60" display="https://www.acfun.cn/v/ac48115972_7"/>
-    <hyperlink ref="F168" r:id="rId61" display="https://www.acfun.cn/v/ac47931569" tooltip="https://www.acfun.cn/v/ac47931569"/>
-    <hyperlink ref="F170" r:id="rId62" display="https://www.acfun.cn/v/ac47931569_2"/>
-    <hyperlink ref="F171" r:id="rId63" display="https://www.acfun.cn/v/ac47931569_3"/>
-    <hyperlink ref="F172" r:id="rId64" display="https://www.acfun.cn/v/ac47931569_4"/>
-    <hyperlink ref="F173" r:id="rId65" display="https://www.acfun.cn/v/ac47931569_5"/>
-    <hyperlink ref="F174" r:id="rId66" display="https://www.acfun.cn/v/ac47931569_6"/>
-    <hyperlink ref="F175" r:id="rId67" display="https://www.acfun.cn/v/ac47931569_7"/>
-    <hyperlink ref="F176" r:id="rId68" display="https://www.acfun.cn/v/ac47931569_8"/>
-    <hyperlink ref="F177" r:id="rId69" display="https://www.acfun.cn/v/ac47931569_9"/>
-    <hyperlink ref="F178" r:id="rId70" display="https://www.acfun.cn/v/ac47931569_10"/>
-    <hyperlink ref="F179" r:id="rId71" display="https://www.acfun.cn/v/ac47931603" tooltip="https://www.acfun.cn/v/ac47931603"/>
-    <hyperlink ref="F181" r:id="rId72" display="https://www.acfun.cn/v/ac47931603_2"/>
-    <hyperlink ref="F183" r:id="rId73" display="https://www.acfun.cn/v/ac47931603_3"/>
-    <hyperlink ref="F184" r:id="rId74" display="https://www.acfun.cn/v/ac47931603_4"/>
-    <hyperlink ref="F186" r:id="rId75" display="https://www.acfun.cn/v/ac47931603_5"/>
-    <hyperlink ref="F192" r:id="rId76" display="https://www.acfun.cn/v/ac47931603_6"/>
-    <hyperlink ref="F193" r:id="rId77" display="https://www.acfun.cn/v/ac47931603_7"/>
-    <hyperlink ref="F198" r:id="rId78" display="https://www.acfun.cn/v/ac47931603_8"/>
-    <hyperlink ref="F199" r:id="rId79" display="https://www.acfun.cn/v/ac47933063"/>
-    <hyperlink ref="F201" r:id="rId80" display="https://www.acfun.cn/v/ac47933063_2"/>
-    <hyperlink ref="F202" r:id="rId81" display="https://www.acfun.cn/v/ac47933063_3"/>
-    <hyperlink ref="F203" r:id="rId82" display="https://www.acfun.cn/v/ac47933063_4"/>
-    <hyperlink ref="F204" r:id="rId83" display="https://www.acfun.cn/v/ac47933063_5"/>
-    <hyperlink ref="F206" r:id="rId84" display="https://www.acfun.cn/v/ac47933063_6"/>
-    <hyperlink ref="F207" r:id="rId85" display="https://www.acfun.cn/v/ac47933063_7"/>
-    <hyperlink ref="F208" r:id="rId86" display="https://www.acfun.cn/v/ac47933063_8"/>
-    <hyperlink ref="F209" r:id="rId87" display="https://www.acfun.cn/v/ac47933063_9"/>
-    <hyperlink ref="F211" r:id="rId88" display="https://www.acfun.cn/v/ac47933063_10"/>
-    <hyperlink ref="F213" r:id="rId89" display="https://www.acfun.cn/v/ac48409409_1" tooltip="https://www.acfun.cn/v/ac48409409_1"/>
-    <hyperlink ref="F219" r:id="rId90" display="https://www.acfun.cn/v/ac48409409_2"/>
-    <hyperlink ref="F220" r:id="rId91" display="https://www.acfun.cn/v/ac48409409_3"/>
-    <hyperlink ref="F225" r:id="rId92" display="https://www.acfun.cn/v/ac48409409_4"/>
-    <hyperlink ref="F235" r:id="rId93" display="https://www.acfun.cn/v/ac47931075"/>
-    <hyperlink ref="F236" r:id="rId94" display="https://www.acfun.cn/v/ac47931075_2"/>
-    <hyperlink ref="F238" r:id="rId95" display="https://www.acfun.cn/v/ac47931075_3"/>
-    <hyperlink ref="F240" r:id="rId96" display="https://www.acfun.cn/v/ac47931075_4"/>
-    <hyperlink ref="F241" r:id="rId97" display="https://www.acfun.cn/v/ac47931075_5"/>
-    <hyperlink ref="F242" r:id="rId98" display="https://www.acfun.cn/v/ac47931075_6"/>
-    <hyperlink ref="F244" r:id="rId99" display="https://www.acfun.cn/v/ac47933675"/>
-    <hyperlink ref="F246" r:id="rId100" display="https://www.acfun.cn/v/ac47933675_2"/>
-    <hyperlink ref="F248" r:id="rId101" display="https://www.acfun.cn/v/ac47933675_3"/>
-    <hyperlink ref="F249" r:id="rId102" display="https://www.acfun.cn/v/ac47933675_4"/>
-    <hyperlink ref="F250" r:id="rId103" display="https://www.acfun.cn/v/ac47933675_5"/>
-    <hyperlink ref="F251" r:id="rId104" display="https://www.acfun.cn/v/ac47933675_6"/>
-    <hyperlink ref="F252" r:id="rId105" display="https://www.acfun.cn/v/ac47933675_7"/>
-    <hyperlink ref="F257" r:id="rId106" display="https://www.acfun.cn/v/ac47933675_8"/>
-    <hyperlink ref="F259" r:id="rId107" display="https://www.acfun.cn/v/ac47934854"/>
-    <hyperlink ref="F260" r:id="rId108" display="https://www.acfun.cn/v/ac47934854_2"/>
-    <hyperlink ref="F261" r:id="rId109" display="https://www.acfun.cn/v/ac47934854_3"/>
-    <hyperlink ref="F262" r:id="rId110" display="https://www.acfun.cn/v/ac47934854_4"/>
-    <hyperlink ref="F263" r:id="rId111" display="https://www.acfun.cn/v/ac47934854_5"/>
-    <hyperlink ref="F264" r:id="rId112" display="https://www.acfun.cn/v/ac47934854_6"/>
-    <hyperlink ref="F266" r:id="rId113" display="https://www.acfun.cn/v/ac47934854_7"/>
-    <hyperlink ref="F272" r:id="rId114" display="https://www.acfun.cn/v/ac47934854_8"/>
-    <hyperlink ref="F274" r:id="rId115" display="https://www.acfun.cn/v/ac47933636"/>
-    <hyperlink ref="F275" r:id="rId116" display="https://www.acfun.cn/v/ac47933636_2"/>
-    <hyperlink ref="F276" r:id="rId117" display="https://www.acfun.cn/v/ac47933636_3"/>
-    <hyperlink ref="F277" r:id="rId118" display="https://www.acfun.cn/v/ac47933636_4"/>
-    <hyperlink ref="F278" r:id="rId119" display="https://www.acfun.cn/v/ac47933636_5"/>
-    <hyperlink ref="F279" r:id="rId120" display="https://www.acfun.cn/v/ac47933636_6"/>
-    <hyperlink ref="F281" r:id="rId121" display="https://www.acfun.cn/v/ac47930865"/>
-    <hyperlink ref="F282" r:id="rId122" display="https://www.acfun.cn/v/ac47930865_2"/>
-    <hyperlink ref="F284" r:id="rId123" display="https://www.acfun.cn/v/ac47930865_3"/>
-    <hyperlink ref="F286" r:id="rId124" display="https://www.acfun.cn/v/ac47930865_4"/>
-    <hyperlink ref="F291" r:id="rId125" display="https://www.acfun.cn/v/ac47930865_5"/>
-    <hyperlink ref="F292" r:id="rId126" display="https://www.acfun.cn/v/ac47930865_6"/>
-    <hyperlink ref="F296" r:id="rId127" display="https://www.acfun.cn/v/ac47932379"/>
-    <hyperlink ref="F297" r:id="rId128" display="https://www.acfun.cn/v/ac47932379_2"/>
-    <hyperlink ref="F298" r:id="rId129" display="https://www.acfun.cn/v/ac47932379_3"/>
-    <hyperlink ref="F299" r:id="rId130" display="https://www.acfun.cn/v/ac47932379_4"/>
-    <hyperlink ref="F300" r:id="rId131" display="https://www.acfun.cn/v/ac47932379_5"/>
-    <hyperlink ref="F301" r:id="rId132" display="https://www.acfun.cn/v/ac47932379_6"/>
-    <hyperlink ref="F304" r:id="rId133" display="https://www.acfun.cn/v/ac47932379_7"/>
-    <hyperlink ref="F306" r:id="rId134" display="https://www.acfun.cn/v/ac47932379_8"/>
-    <hyperlink ref="F307" r:id="rId135" display="https://www.acfun.cn/v/ac47932379_9"/>
-    <hyperlink ref="F308" r:id="rId136" display="https://www.acfun.cn/v/ac47932379_10"/>
-    <hyperlink ref="F309" r:id="rId137" display="https://www.acfun.cn/v/ac48055738"/>
-    <hyperlink ref="F310" r:id="rId138" display="https://www.acfun.cn/v/ac48055738_2"/>
-    <hyperlink ref="F311" r:id="rId139" display="https://www.acfun.cn/v/ac48055738_3"/>
-    <hyperlink ref="F312" r:id="rId140" display="https://www.acfun.cn/v/ac48055738_4"/>
-    <hyperlink ref="F313" r:id="rId141" display="https://www.acfun.cn/v/ac48055738_5"/>
-    <hyperlink ref="F314" r:id="rId142" display="https://www.acfun.cn/v/ac48055738_6"/>
-    <hyperlink ref="F316" r:id="rId143" display="https://www.acfun.cn/v/ac48055738_7"/>
-    <hyperlink ref="F317" r:id="rId144" display="https://www.acfun.cn/v/ac48055738_8"/>
-    <hyperlink ref="F319" r:id="rId145" display="https://www.acfun.cn/v/ac48055738_9"/>
-    <hyperlink ref="F325" r:id="rId146" display="https://www.acfun.cn/v/ac48751334"/>
-    <hyperlink ref="F326" r:id="rId147" display="https://www.acfun.cn/v/ac48751334_2"/>
-    <hyperlink ref="F331" r:id="rId148" display="https://www.acfun.cn/v/ac48751334_3" tooltip="https://www.acfun.cn/v/ac48751334_3"/>
-    <hyperlink ref="F332" r:id="rId149" display="https://www.acfun.cn/v/ac47931260"/>
-    <hyperlink ref="F333" r:id="rId150" display="https://www.acfun.cn/v/ac47931260_2"/>
-    <hyperlink ref="F335" r:id="rId151" display="https://www.acfun.cn/v/ac47931260_3"/>
-    <hyperlink ref="F336" r:id="rId152" display="https://www.acfun.cn/v/ac47931260_4"/>
-    <hyperlink ref="F337" r:id="rId153" display="https://www.acfun.cn/v/ac47931260_5"/>
-    <hyperlink ref="F338" r:id="rId154" display="https://www.acfun.cn/v/ac47931260_6"/>
-    <hyperlink ref="F339" r:id="rId155" display="https://www.acfun.cn/v/ac47931260_7"/>
-    <hyperlink ref="F345" r:id="rId156" display="https://www.acfun.cn/v/ac47931260_8"/>
-    <hyperlink ref="F346" r:id="rId157" display="https://www.acfun.cn/v/ac47932208"/>
-    <hyperlink ref="F347" r:id="rId158" display="https://www.acfun.cn/v/ac47932208_2"/>
-    <hyperlink ref="F348" r:id="rId159" display="https://www.acfun.cn/v/ac47932208_3"/>
-    <hyperlink ref="F349" r:id="rId160" display="https://www.acfun.cn/v/ac47932208_4"/>
-    <hyperlink ref="F350" r:id="rId161" display="https://www.acfun.cn/v/ac47932208_5"/>
-    <hyperlink ref="F351" r:id="rId162" display="https://www.acfun.cn/v/ac47932208_6"/>
-    <hyperlink ref="F352" r:id="rId163" display="https://www.acfun.cn/v/ac47932208_7"/>
-    <hyperlink ref="F358" r:id="rId164" display="https://www.acfun.cn/v/ac47932208_8"/>
-    <hyperlink ref="F359" r:id="rId165" display="https://www.acfun.cn/v/ac47932208_9"/>
-    <hyperlink ref="F363" r:id="rId166" display="https://www.acfun.cn/v/ac47932208_10"/>
-    <hyperlink ref="F364" r:id="rId167" display="https://www.acfun.cn/v/ac47931830"/>
-    <hyperlink ref="F365" r:id="rId168" display="https://www.acfun.cn/v/ac47931830_2"/>
-    <hyperlink ref="F368" r:id="rId169" display="https://www.acfun.cn/v/ac47931830_3"/>
-    <hyperlink ref="F369" r:id="rId170" display="https://www.acfun.cn/v/ac47931830_4"/>
-    <hyperlink ref="F370" r:id="rId171" display="https://www.acfun.cn/v/ac47931830_5"/>
-    <hyperlink ref="F372" r:id="rId172" display="https://www.acfun.cn/v/ac47931830_6"/>
-    <hyperlink ref="F373" r:id="rId173" display="https://www.acfun.cn/v/ac47931830_7"/>
-    <hyperlink ref="F374" r:id="rId174" display="https://www.acfun.cn/v/ac47931830_8"/>
-    <hyperlink ref="F376" r:id="rId175" display="https://www.acfun.cn/v/ac47931830_9"/>
-    <hyperlink ref="F378" r:id="rId176" display="https://www.acfun.cn/v/ac47931830_10"/>
-    <hyperlink ref="F384" r:id="rId177" display="https://www.acfun.cn/v/ac48751840"/>
-    <hyperlink ref="F385" r:id="rId178" display="https://www.acfun.cn/v/ac48751840_2"/>
-    <hyperlink ref="F389" r:id="rId179" display="https://www.acfun.cn/v/ac48751840_3"/>
-    <hyperlink ref="F390" r:id="rId180" display="https://www.acfun.cn/v/ac47931318"/>
-    <hyperlink ref="F391" r:id="rId181" display="https://www.acfun.cn/v/ac47931318_2"/>
-    <hyperlink ref="F395" r:id="rId182" display="https://www.acfun.cn/v/ac47931318_3"/>
-    <hyperlink ref="F396" r:id="rId183" display="https://www.acfun.cn/v/ac47931318_4"/>
-    <hyperlink ref="F397" r:id="rId184" display="https://www.acfun.cn/v/ac47931318_5"/>
-    <hyperlink ref="F398" r:id="rId185" display="https://www.acfun.cn/v/ac47931318_6"/>
-    <hyperlink ref="F399" r:id="rId186" display="https://www.acfun.cn/v/ac47931318_7"/>
-    <hyperlink ref="F400" r:id="rId187" display="https://www.acfun.cn/v/ac47931318_8"/>
-    <hyperlink ref="F401" r:id="rId188" display="https://www.acfun.cn/v/ac47931318_9"/>
-    <hyperlink ref="F402" r:id="rId189" display="https://www.acfun.cn/v/ac47931318_10"/>
-    <hyperlink ref="F403" r:id="rId190" display="https://www.acfun.cn/v/ac48311717"/>
-    <hyperlink ref="F405" r:id="rId191" display="https://www.acfun.cn/v/ac48311717_2"/>
-    <hyperlink ref="F406" r:id="rId192" display="https://www.acfun.cn/v/ac48311717_3"/>
-    <hyperlink ref="F408" r:id="rId193" display="https://www.acfun.cn/v/ac48311717_4"/>
-    <hyperlink ref="F414" r:id="rId194" display="https://www.acfun.cn/v/ac48311717_5"/>
-    <hyperlink ref="F415" r:id="rId195" display="https://www.acfun.cn/v/ac48311717_6"/>
-    <hyperlink ref="F420" r:id="rId196" display="https://www.acfun.cn/v/ac48311717_7"/>
-    <hyperlink ref="F421" r:id="rId197" display="https://www.acfun.cn/v/ac47932123"/>
-    <hyperlink ref="F422" r:id="rId198" display="https://www.acfun.cn/v/ac47932123_2"/>
-    <hyperlink ref="F424" r:id="rId199" display="https://www.acfun.cn/v/ac47932123_3"/>
-    <hyperlink ref="F425" r:id="rId200" display="https://www.acfun.cn/v/ac47932123_4" tooltip="https://www.acfun.cn/v/ac47932123_4"/>
-    <hyperlink ref="F426" r:id="rId201" display="https://www.acfun.cn/v/ac47932123_5"/>
-    <hyperlink ref="F427" r:id="rId202" display="https://www.acfun.cn/v/ac47932123_6"/>
-    <hyperlink ref="F428" r:id="rId203" display="https://www.acfun.cn/v/ac47932123_7"/>
-    <hyperlink ref="F430" r:id="rId204" display="https://www.acfun.cn/v/ac47932123_8"/>
-    <hyperlink ref="F434" r:id="rId205" display="https://www.acfun.cn/v/ac47930836"/>
-    <hyperlink ref="F435" r:id="rId206" display="https://www.acfun.cn/v/ac47930836_2"/>
-    <hyperlink ref="F436" r:id="rId207" display="https://www.acfun.cn/v/ac47930836_3"/>
-    <hyperlink ref="F438" r:id="rId208" display="https://www.acfun.cn/v/ac47930836_4"/>
-    <hyperlink ref="F440" r:id="rId209" display="https://www.acfun.cn/v/ac47930836_5"/>
-    <hyperlink ref="F441" r:id="rId210" display="https://www.acfun.cn/v/ac47930836_6"/>
-    <hyperlink ref="F447" r:id="rId211" display="https://www.acfun.cn/v/ac47930836_7"/>
-    <hyperlink ref="F448" r:id="rId212" display="https://www.acfun.cn/v/ac47930836_8"/>
-    <hyperlink ref="F451" r:id="rId213" display="https://www.acfun.cn/v/ac47935835"/>
-    <hyperlink ref="F452" r:id="rId214" display="https://www.acfun.cn/v/ac47935862" tooltip="https://www.acfun.cn/v/ac47935862"/>
-    <hyperlink ref="F453" r:id="rId215" display="https://www.acfun.cn/v/ac47932937" tooltip="https://www.acfun.cn/v/ac47932937"/>
-    <hyperlink ref="F454" r:id="rId216" display="https://www.acfun.cn/v/ac47932937_2"/>
-    <hyperlink ref="F455" r:id="rId217" display="https://www.acfun.cn/v/ac47932937_3"/>
-    <hyperlink ref="F457" r:id="rId218" display="https://www.acfun.cn/v/ac47932937_4"/>
-    <hyperlink ref="F458" r:id="rId219" display="https://www.acfun.cn/v/ac47932937_5"/>
-    <hyperlink ref="F459" r:id="rId220" display="https://www.acfun.cn/v/ac47932763" tooltip="https://www.acfun.cn/v/ac47932763"/>
-    <hyperlink ref="F460" r:id="rId221" display="https://www.acfun.cn/v/ac47932763_2"/>
-    <hyperlink ref="F461" r:id="rId222" display="https://www.acfun.cn/v/ac47932763_3"/>
-    <hyperlink ref="F463" r:id="rId223" display="https://www.acfun.cn/v/ac47932763_4"/>
-    <hyperlink ref="F464" r:id="rId224" display="https://www.acfun.cn/v/ac47931710" tooltip="https://www.acfun.cn/v/ac47931710"/>
-    <hyperlink ref="F465" r:id="rId225" display="https://www.acfun.cn/v/ac47931710_2"/>
-    <hyperlink ref="F466" r:id="rId226" display="https://www.acfun.cn/v/ac47931710_3"/>
-    <hyperlink ref="F468" r:id="rId227" display="https://www.acfun.cn/v/ac47931710_4"/>
+    <hyperlink ref="F2" r:id="rId1" tooltip="https://www.acfun.cn/v/ac47931167" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
+    <hyperlink ref="F14" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
+    <hyperlink ref="F16" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
+    <hyperlink ref="F18" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
+    <hyperlink ref="F20" r:id="rId12" xr:uid="{00000000-0004-0000-0600-00000B000000}"/>
+    <hyperlink ref="F22" r:id="rId13" xr:uid="{00000000-0004-0000-0600-00000C000000}"/>
+    <hyperlink ref="F23" r:id="rId14" xr:uid="{00000000-0004-0000-0600-00000D000000}"/>
+    <hyperlink ref="F24" r:id="rId15" xr:uid="{00000000-0004-0000-0600-00000E000000}"/>
+    <hyperlink ref="F25" r:id="rId16" xr:uid="{00000000-0004-0000-0600-00000F000000}"/>
+    <hyperlink ref="F27" r:id="rId17" xr:uid="{00000000-0004-0000-0600-000010000000}"/>
+    <hyperlink ref="F28" r:id="rId18" xr:uid="{00000000-0004-0000-0600-000011000000}"/>
+    <hyperlink ref="F29" r:id="rId19" xr:uid="{00000000-0004-0000-0600-000012000000}"/>
+    <hyperlink ref="F31" r:id="rId20" xr:uid="{00000000-0004-0000-0600-000013000000}"/>
+    <hyperlink ref="F32" r:id="rId21" xr:uid="{00000000-0004-0000-0600-000014000000}"/>
+    <hyperlink ref="F33" r:id="rId22" xr:uid="{00000000-0004-0000-0600-000015000000}"/>
+    <hyperlink ref="F34" r:id="rId23" xr:uid="{00000000-0004-0000-0600-000016000000}"/>
+    <hyperlink ref="F39" r:id="rId24" xr:uid="{00000000-0004-0000-0600-000017000000}"/>
+    <hyperlink ref="F69" r:id="rId25" xr:uid="{00000000-0004-0000-0600-000018000000}"/>
+    <hyperlink ref="F71" r:id="rId26" xr:uid="{00000000-0004-0000-0600-000019000000}"/>
+    <hyperlink ref="F73" r:id="rId27" xr:uid="{00000000-0004-0000-0600-00001A000000}"/>
+    <hyperlink ref="F74" r:id="rId28" xr:uid="{00000000-0004-0000-0600-00001B000000}"/>
+    <hyperlink ref="F75" r:id="rId29" xr:uid="{00000000-0004-0000-0600-00001C000000}"/>
+    <hyperlink ref="F76" r:id="rId30" xr:uid="{00000000-0004-0000-0600-00001D000000}"/>
+    <hyperlink ref="F77" r:id="rId31" xr:uid="{00000000-0004-0000-0600-00001E000000}"/>
+    <hyperlink ref="F78" r:id="rId32" xr:uid="{00000000-0004-0000-0600-00001F000000}"/>
+    <hyperlink ref="F80" r:id="rId33" xr:uid="{00000000-0004-0000-0600-000020000000}"/>
+    <hyperlink ref="F87" r:id="rId34" xr:uid="{00000000-0004-0000-0600-000021000000}"/>
+    <hyperlink ref="F101" r:id="rId35" xr:uid="{00000000-0004-0000-0600-000022000000}"/>
+    <hyperlink ref="F105" r:id="rId36" xr:uid="{00000000-0004-0000-0600-000023000000}"/>
+    <hyperlink ref="F106" r:id="rId37" xr:uid="{00000000-0004-0000-0600-000024000000}"/>
+    <hyperlink ref="F107" r:id="rId38" xr:uid="{00000000-0004-0000-0600-000025000000}"/>
+    <hyperlink ref="F109" r:id="rId39" xr:uid="{00000000-0004-0000-0600-000026000000}"/>
+    <hyperlink ref="F113" r:id="rId40" xr:uid="{00000000-0004-0000-0600-000027000000}"/>
+    <hyperlink ref="F114" r:id="rId41" xr:uid="{00000000-0004-0000-0600-000028000000}"/>
+    <hyperlink ref="F115" r:id="rId42" xr:uid="{00000000-0004-0000-0600-000029000000}"/>
+    <hyperlink ref="F116" r:id="rId43" xr:uid="{00000000-0004-0000-0600-00002A000000}"/>
+    <hyperlink ref="F118" r:id="rId44" xr:uid="{00000000-0004-0000-0600-00002B000000}"/>
+    <hyperlink ref="F119" r:id="rId45" xr:uid="{00000000-0004-0000-0600-00002C000000}"/>
+    <hyperlink ref="F120" r:id="rId46" xr:uid="{00000000-0004-0000-0600-00002D000000}"/>
+    <hyperlink ref="F122" r:id="rId47" xr:uid="{00000000-0004-0000-0600-00002E000000}"/>
+    <hyperlink ref="F128" r:id="rId48" xr:uid="{00000000-0004-0000-0600-00002F000000}"/>
+    <hyperlink ref="F129" r:id="rId49" xr:uid="{00000000-0004-0000-0600-000030000000}"/>
+    <hyperlink ref="F133" r:id="rId50" xr:uid="{00000000-0004-0000-0600-000031000000}"/>
+    <hyperlink ref="F134" r:id="rId51" xr:uid="{00000000-0004-0000-0600-000032000000}"/>
+    <hyperlink ref="F135" r:id="rId52" xr:uid="{00000000-0004-0000-0600-000033000000}"/>
+    <hyperlink ref="F136" r:id="rId53" xr:uid="{00000000-0004-0000-0600-000034000000}"/>
+    <hyperlink ref="F138" r:id="rId54" xr:uid="{00000000-0004-0000-0600-000035000000}"/>
+    <hyperlink ref="F140" r:id="rId55" xr:uid="{00000000-0004-0000-0600-000036000000}"/>
+    <hyperlink ref="F141" r:id="rId56" xr:uid="{00000000-0004-0000-0600-000037000000}"/>
+    <hyperlink ref="F142" r:id="rId57" xr:uid="{00000000-0004-0000-0600-000038000000}"/>
+    <hyperlink ref="F143" r:id="rId58" xr:uid="{00000000-0004-0000-0600-000039000000}"/>
+    <hyperlink ref="F149" r:id="rId59" xr:uid="{00000000-0004-0000-0600-00003A000000}"/>
+    <hyperlink ref="F167" r:id="rId60" xr:uid="{00000000-0004-0000-0600-00003B000000}"/>
+    <hyperlink ref="F168" r:id="rId61" tooltip="https://www.acfun.cn/v/ac47931569" xr:uid="{00000000-0004-0000-0600-00003C000000}"/>
+    <hyperlink ref="F170" r:id="rId62" xr:uid="{00000000-0004-0000-0600-00003D000000}"/>
+    <hyperlink ref="F171" r:id="rId63" xr:uid="{00000000-0004-0000-0600-00003E000000}"/>
+    <hyperlink ref="F172" r:id="rId64" xr:uid="{00000000-0004-0000-0600-00003F000000}"/>
+    <hyperlink ref="F173" r:id="rId65" xr:uid="{00000000-0004-0000-0600-000040000000}"/>
+    <hyperlink ref="F174" r:id="rId66" xr:uid="{00000000-0004-0000-0600-000041000000}"/>
+    <hyperlink ref="F175" r:id="rId67" xr:uid="{00000000-0004-0000-0600-000042000000}"/>
+    <hyperlink ref="F176" r:id="rId68" xr:uid="{00000000-0004-0000-0600-000043000000}"/>
+    <hyperlink ref="F177" r:id="rId69" xr:uid="{00000000-0004-0000-0600-000044000000}"/>
+    <hyperlink ref="F178" r:id="rId70" xr:uid="{00000000-0004-0000-0600-000045000000}"/>
+    <hyperlink ref="F179" r:id="rId71" tooltip="https://www.acfun.cn/v/ac47931603" xr:uid="{00000000-0004-0000-0600-000046000000}"/>
+    <hyperlink ref="F181" r:id="rId72" xr:uid="{00000000-0004-0000-0600-000047000000}"/>
+    <hyperlink ref="F183" r:id="rId73" xr:uid="{00000000-0004-0000-0600-000048000000}"/>
+    <hyperlink ref="F184" r:id="rId74" xr:uid="{00000000-0004-0000-0600-000049000000}"/>
+    <hyperlink ref="F186" r:id="rId75" xr:uid="{00000000-0004-0000-0600-00004A000000}"/>
+    <hyperlink ref="F192" r:id="rId76" xr:uid="{00000000-0004-0000-0600-00004B000000}"/>
+    <hyperlink ref="F193" r:id="rId77" xr:uid="{00000000-0004-0000-0600-00004C000000}"/>
+    <hyperlink ref="F198" r:id="rId78" xr:uid="{00000000-0004-0000-0600-00004D000000}"/>
+    <hyperlink ref="F199" r:id="rId79" xr:uid="{00000000-0004-0000-0600-00004E000000}"/>
+    <hyperlink ref="F201" r:id="rId80" xr:uid="{00000000-0004-0000-0600-00004F000000}"/>
+    <hyperlink ref="F202" r:id="rId81" xr:uid="{00000000-0004-0000-0600-000050000000}"/>
+    <hyperlink ref="F203" r:id="rId82" xr:uid="{00000000-0004-0000-0600-000051000000}"/>
+    <hyperlink ref="F204" r:id="rId83" xr:uid="{00000000-0004-0000-0600-000052000000}"/>
+    <hyperlink ref="F206" r:id="rId84" xr:uid="{00000000-0004-0000-0600-000053000000}"/>
+    <hyperlink ref="F207" r:id="rId85" xr:uid="{00000000-0004-0000-0600-000054000000}"/>
+    <hyperlink ref="F208" r:id="rId86" xr:uid="{00000000-0004-0000-0600-000055000000}"/>
+    <hyperlink ref="F209" r:id="rId87" xr:uid="{00000000-0004-0000-0600-000056000000}"/>
+    <hyperlink ref="F211" r:id="rId88" xr:uid="{00000000-0004-0000-0600-000057000000}"/>
+    <hyperlink ref="F213" r:id="rId89" tooltip="https://www.acfun.cn/v/ac48409409_1" xr:uid="{00000000-0004-0000-0600-000058000000}"/>
+    <hyperlink ref="F219" r:id="rId90" xr:uid="{00000000-0004-0000-0600-000059000000}"/>
+    <hyperlink ref="F220" r:id="rId91" xr:uid="{00000000-0004-0000-0600-00005A000000}"/>
+    <hyperlink ref="F225" r:id="rId92" xr:uid="{00000000-0004-0000-0600-00005B000000}"/>
+    <hyperlink ref="F235" r:id="rId93" xr:uid="{00000000-0004-0000-0600-00005C000000}"/>
+    <hyperlink ref="F236" r:id="rId94" xr:uid="{00000000-0004-0000-0600-00005D000000}"/>
+    <hyperlink ref="F238" r:id="rId95" xr:uid="{00000000-0004-0000-0600-00005E000000}"/>
+    <hyperlink ref="F240" r:id="rId96" xr:uid="{00000000-0004-0000-0600-00005F000000}"/>
+    <hyperlink ref="F241" r:id="rId97" xr:uid="{00000000-0004-0000-0600-000060000000}"/>
+    <hyperlink ref="F242" r:id="rId98" xr:uid="{00000000-0004-0000-0600-000061000000}"/>
+    <hyperlink ref="F244" r:id="rId99" xr:uid="{00000000-0004-0000-0600-000062000000}"/>
+    <hyperlink ref="F246" r:id="rId100" xr:uid="{00000000-0004-0000-0600-000063000000}"/>
+    <hyperlink ref="F248" r:id="rId101" xr:uid="{00000000-0004-0000-0600-000064000000}"/>
+    <hyperlink ref="F249" r:id="rId102" xr:uid="{00000000-0004-0000-0600-000065000000}"/>
+    <hyperlink ref="F250" r:id="rId103" xr:uid="{00000000-0004-0000-0600-000066000000}"/>
+    <hyperlink ref="F251" r:id="rId104" xr:uid="{00000000-0004-0000-0600-000067000000}"/>
+    <hyperlink ref="F252" r:id="rId105" xr:uid="{00000000-0004-0000-0600-000068000000}"/>
+    <hyperlink ref="F257" r:id="rId106" xr:uid="{00000000-0004-0000-0600-000069000000}"/>
+    <hyperlink ref="F259" r:id="rId107" xr:uid="{00000000-0004-0000-0600-00006A000000}"/>
+    <hyperlink ref="F260" r:id="rId108" xr:uid="{00000000-0004-0000-0600-00006B000000}"/>
+    <hyperlink ref="F261" r:id="rId109" xr:uid="{00000000-0004-0000-0600-00006C000000}"/>
+    <hyperlink ref="F262" r:id="rId110" xr:uid="{00000000-0004-0000-0600-00006D000000}"/>
+    <hyperlink ref="F263" r:id="rId111" xr:uid="{00000000-0004-0000-0600-00006E000000}"/>
+    <hyperlink ref="F264" r:id="rId112" xr:uid="{00000000-0004-0000-0600-00006F000000}"/>
+    <hyperlink ref="F266" r:id="rId113" xr:uid="{00000000-0004-0000-0600-000070000000}"/>
+    <hyperlink ref="F272" r:id="rId114" xr:uid="{00000000-0004-0000-0600-000071000000}"/>
+    <hyperlink ref="F274" r:id="rId115" xr:uid="{00000000-0004-0000-0600-000072000000}"/>
+    <hyperlink ref="F275" r:id="rId116" xr:uid="{00000000-0004-0000-0600-000073000000}"/>
+    <hyperlink ref="F276" r:id="rId117" xr:uid="{00000000-0004-0000-0600-000074000000}"/>
+    <hyperlink ref="F277" r:id="rId118" xr:uid="{00000000-0004-0000-0600-000075000000}"/>
+    <hyperlink ref="F278" r:id="rId119" xr:uid="{00000000-0004-0000-0600-000076000000}"/>
+    <hyperlink ref="F279" r:id="rId120" xr:uid="{00000000-0004-0000-0600-000077000000}"/>
+    <hyperlink ref="F281" r:id="rId121" xr:uid="{00000000-0004-0000-0600-000078000000}"/>
+    <hyperlink ref="F282" r:id="rId122" xr:uid="{00000000-0004-0000-0600-000079000000}"/>
+    <hyperlink ref="F284" r:id="rId123" xr:uid="{00000000-0004-0000-0600-00007A000000}"/>
+    <hyperlink ref="F286" r:id="rId124" xr:uid="{00000000-0004-0000-0600-00007B000000}"/>
+    <hyperlink ref="F291" r:id="rId125" xr:uid="{00000000-0004-0000-0600-00007C000000}"/>
+    <hyperlink ref="F292" r:id="rId126" xr:uid="{00000000-0004-0000-0600-00007D000000}"/>
+    <hyperlink ref="F296" r:id="rId127" xr:uid="{00000000-0004-0000-0600-00007E000000}"/>
+    <hyperlink ref="F297" r:id="rId128" xr:uid="{00000000-0004-0000-0600-00007F000000}"/>
+    <hyperlink ref="F298" r:id="rId129" xr:uid="{00000000-0004-0000-0600-000080000000}"/>
+    <hyperlink ref="F299" r:id="rId130" xr:uid="{00000000-0004-0000-0600-000081000000}"/>
+    <hyperlink ref="F300" r:id="rId131" xr:uid="{00000000-0004-0000-0600-000082000000}"/>
+    <hyperlink ref="F301" r:id="rId132" xr:uid="{00000000-0004-0000-0600-000083000000}"/>
+    <hyperlink ref="F304" r:id="rId133" xr:uid="{00000000-0004-0000-0600-000084000000}"/>
+    <hyperlink ref="F306" r:id="rId134" xr:uid="{00000000-0004-0000-0600-000085000000}"/>
+    <hyperlink ref="F307" r:id="rId135" xr:uid="{00000000-0004-0000-0600-000086000000}"/>
+    <hyperlink ref="F308" r:id="rId136" xr:uid="{00000000-0004-0000-0600-000087000000}"/>
+    <hyperlink ref="F309" r:id="rId137" xr:uid="{00000000-0004-0000-0600-000088000000}"/>
+    <hyperlink ref="F310" r:id="rId138" xr:uid="{00000000-0004-0000-0600-000089000000}"/>
+    <hyperlink ref="F311" r:id="rId139" xr:uid="{00000000-0004-0000-0600-00008A000000}"/>
+    <hyperlink ref="F312" r:id="rId140" xr:uid="{00000000-0004-0000-0600-00008B000000}"/>
+    <hyperlink ref="F313" r:id="rId141" xr:uid="{00000000-0004-0000-0600-00008C000000}"/>
+    <hyperlink ref="F314" r:id="rId142" xr:uid="{00000000-0004-0000-0600-00008D000000}"/>
+    <hyperlink ref="F316" r:id="rId143" xr:uid="{00000000-0004-0000-0600-00008E000000}"/>
+    <hyperlink ref="F317" r:id="rId144" xr:uid="{00000000-0004-0000-0600-00008F000000}"/>
+    <hyperlink ref="F319" r:id="rId145" xr:uid="{00000000-0004-0000-0600-000090000000}"/>
+    <hyperlink ref="F325" r:id="rId146" xr:uid="{00000000-0004-0000-0600-000091000000}"/>
+    <hyperlink ref="F326" r:id="rId147" xr:uid="{00000000-0004-0000-0600-000092000000}"/>
+    <hyperlink ref="F331" r:id="rId148" tooltip="https://www.acfun.cn/v/ac48751334_3" xr:uid="{00000000-0004-0000-0600-000093000000}"/>
+    <hyperlink ref="F332" r:id="rId149" xr:uid="{00000000-0004-0000-0600-000094000000}"/>
+    <hyperlink ref="F333" r:id="rId150" xr:uid="{00000000-0004-0000-0600-000095000000}"/>
+    <hyperlink ref="F335" r:id="rId151" xr:uid="{00000000-0004-0000-0600-000096000000}"/>
+    <hyperlink ref="F336" r:id="rId152" xr:uid="{00000000-0004-0000-0600-000097000000}"/>
+    <hyperlink ref="F337" r:id="rId153" xr:uid="{00000000-0004-0000-0600-000098000000}"/>
+    <hyperlink ref="F338" r:id="rId154" xr:uid="{00000000-0004-0000-0600-000099000000}"/>
+    <hyperlink ref="F339" r:id="rId155" xr:uid="{00000000-0004-0000-0600-00009A000000}"/>
+    <hyperlink ref="F345" r:id="rId156" xr:uid="{00000000-0004-0000-0600-00009B000000}"/>
+    <hyperlink ref="F346" r:id="rId157" xr:uid="{00000000-0004-0000-0600-00009C000000}"/>
+    <hyperlink ref="F347" r:id="rId158" xr:uid="{00000000-0004-0000-0600-00009D000000}"/>
+    <hyperlink ref="F348" r:id="rId159" xr:uid="{00000000-0004-0000-0600-00009E000000}"/>
+    <hyperlink ref="F349" r:id="rId160" xr:uid="{00000000-0004-0000-0600-00009F000000}"/>
+    <hyperlink ref="F350" r:id="rId161" xr:uid="{00000000-0004-0000-0600-0000A0000000}"/>
+    <hyperlink ref="F351" r:id="rId162" xr:uid="{00000000-0004-0000-0600-0000A1000000}"/>
+    <hyperlink ref="F352" r:id="rId163" xr:uid="{00000000-0004-0000-0600-0000A2000000}"/>
+    <hyperlink ref="F358" r:id="rId164" xr:uid="{00000000-0004-0000-0600-0000A3000000}"/>
+    <hyperlink ref="F359" r:id="rId165" xr:uid="{00000000-0004-0000-0600-0000A4000000}"/>
+    <hyperlink ref="F363" r:id="rId166" xr:uid="{00000000-0004-0000-0600-0000A5000000}"/>
+    <hyperlink ref="F364" r:id="rId167" xr:uid="{00000000-0004-0000-0600-0000A6000000}"/>
+    <hyperlink ref="F365" r:id="rId168" xr:uid="{00000000-0004-0000-0600-0000A7000000}"/>
+    <hyperlink ref="F368" r:id="rId169" xr:uid="{00000000-0004-0000-0600-0000A8000000}"/>
+    <hyperlink ref="F369" r:id="rId170" xr:uid="{00000000-0004-0000-0600-0000A9000000}"/>
+    <hyperlink ref="F370" r:id="rId171" xr:uid="{00000000-0004-0000-0600-0000AA000000}"/>
+    <hyperlink ref="F372" r:id="rId172" xr:uid="{00000000-0004-0000-0600-0000AB000000}"/>
+    <hyperlink ref="F373" r:id="rId173" xr:uid="{00000000-0004-0000-0600-0000AC000000}"/>
+    <hyperlink ref="F374" r:id="rId174" xr:uid="{00000000-0004-0000-0600-0000AD000000}"/>
+    <hyperlink ref="F376" r:id="rId175" xr:uid="{00000000-0004-0000-0600-0000AE000000}"/>
+    <hyperlink ref="F378" r:id="rId176" xr:uid="{00000000-0004-0000-0600-0000AF000000}"/>
+    <hyperlink ref="F384" r:id="rId177" xr:uid="{00000000-0004-0000-0600-0000B0000000}"/>
+    <hyperlink ref="F385" r:id="rId178" xr:uid="{00000000-0004-0000-0600-0000B1000000}"/>
+    <hyperlink ref="F389" r:id="rId179" xr:uid="{00000000-0004-0000-0600-0000B2000000}"/>
+    <hyperlink ref="F390" r:id="rId180" xr:uid="{00000000-0004-0000-0600-0000B3000000}"/>
+    <hyperlink ref="F391" r:id="rId181" xr:uid="{00000000-0004-0000-0600-0000B4000000}"/>
+    <hyperlink ref="F395" r:id="rId182" xr:uid="{00000000-0004-0000-0600-0000B5000000}"/>
+    <hyperlink ref="F396" r:id="rId183" xr:uid="{00000000-0004-0000-0600-0000B6000000}"/>
+    <hyperlink ref="F397" r:id="rId184" xr:uid="{00000000-0004-0000-0600-0000B7000000}"/>
+    <hyperlink ref="F398" r:id="rId185" xr:uid="{00000000-0004-0000-0600-0000B8000000}"/>
+    <hyperlink ref="F399" r:id="rId186" xr:uid="{00000000-0004-0000-0600-0000B9000000}"/>
+    <hyperlink ref="F400" r:id="rId187" xr:uid="{00000000-0004-0000-0600-0000BA000000}"/>
+    <hyperlink ref="F401" r:id="rId188" xr:uid="{00000000-0004-0000-0600-0000BB000000}"/>
+    <hyperlink ref="F402" r:id="rId189" xr:uid="{00000000-0004-0000-0600-0000BC000000}"/>
+    <hyperlink ref="F403" r:id="rId190" xr:uid="{00000000-0004-0000-0600-0000BD000000}"/>
+    <hyperlink ref="F405" r:id="rId191" xr:uid="{00000000-0004-0000-0600-0000BE000000}"/>
+    <hyperlink ref="F406" r:id="rId192" xr:uid="{00000000-0004-0000-0600-0000BF000000}"/>
+    <hyperlink ref="F408" r:id="rId193" xr:uid="{00000000-0004-0000-0600-0000C0000000}"/>
+    <hyperlink ref="F414" r:id="rId194" xr:uid="{00000000-0004-0000-0600-0000C1000000}"/>
+    <hyperlink ref="F415" r:id="rId195" xr:uid="{00000000-0004-0000-0600-0000C2000000}"/>
+    <hyperlink ref="F420" r:id="rId196" xr:uid="{00000000-0004-0000-0600-0000C3000000}"/>
+    <hyperlink ref="F421" r:id="rId197" xr:uid="{00000000-0004-0000-0600-0000C4000000}"/>
+    <hyperlink ref="F422" r:id="rId198" xr:uid="{00000000-0004-0000-0600-0000C5000000}"/>
+    <hyperlink ref="F424" r:id="rId199" xr:uid="{00000000-0004-0000-0600-0000C6000000}"/>
+    <hyperlink ref="F425" r:id="rId200" tooltip="https://www.acfun.cn/v/ac47932123_4" xr:uid="{00000000-0004-0000-0600-0000C7000000}"/>
+    <hyperlink ref="F426" r:id="rId201" xr:uid="{00000000-0004-0000-0600-0000C8000000}"/>
+    <hyperlink ref="F427" r:id="rId202" xr:uid="{00000000-0004-0000-0600-0000C9000000}"/>
+    <hyperlink ref="F428" r:id="rId203" xr:uid="{00000000-0004-0000-0600-0000CA000000}"/>
+    <hyperlink ref="F430" r:id="rId204" xr:uid="{00000000-0004-0000-0600-0000CB000000}"/>
+    <hyperlink ref="F434" r:id="rId205" xr:uid="{00000000-0004-0000-0600-0000CC000000}"/>
+    <hyperlink ref="F435" r:id="rId206" xr:uid="{00000000-0004-0000-0600-0000CD000000}"/>
+    <hyperlink ref="F436" r:id="rId207" xr:uid="{00000000-0004-0000-0600-0000CE000000}"/>
+    <hyperlink ref="F438" r:id="rId208" xr:uid="{00000000-0004-0000-0600-0000CF000000}"/>
+    <hyperlink ref="F440" r:id="rId209" xr:uid="{00000000-0004-0000-0600-0000D0000000}"/>
+    <hyperlink ref="F441" r:id="rId210" xr:uid="{00000000-0004-0000-0600-0000D1000000}"/>
+    <hyperlink ref="F447" r:id="rId211" xr:uid="{00000000-0004-0000-0600-0000D2000000}"/>
+    <hyperlink ref="F448" r:id="rId212" xr:uid="{00000000-0004-0000-0600-0000D3000000}"/>
+    <hyperlink ref="F451" r:id="rId213" xr:uid="{00000000-0004-0000-0600-0000D4000000}"/>
+    <hyperlink ref="F452" r:id="rId214" tooltip="https://www.acfun.cn/v/ac47935862" xr:uid="{00000000-0004-0000-0600-0000D5000000}"/>
+    <hyperlink ref="F453" r:id="rId215" tooltip="https://www.acfun.cn/v/ac47932937" xr:uid="{00000000-0004-0000-0600-0000D6000000}"/>
+    <hyperlink ref="F454" r:id="rId216" xr:uid="{00000000-0004-0000-0600-0000D7000000}"/>
+    <hyperlink ref="F455" r:id="rId217" xr:uid="{00000000-0004-0000-0600-0000D8000000}"/>
+    <hyperlink ref="F457" r:id="rId218" xr:uid="{00000000-0004-0000-0600-0000D9000000}"/>
+    <hyperlink ref="F458" r:id="rId219" xr:uid="{00000000-0004-0000-0600-0000DA000000}"/>
+    <hyperlink ref="F459" r:id="rId220" tooltip="https://www.acfun.cn/v/ac47932763" xr:uid="{00000000-0004-0000-0600-0000DB000000}"/>
+    <hyperlink ref="F460" r:id="rId221" xr:uid="{00000000-0004-0000-0600-0000DC000000}"/>
+    <hyperlink ref="F461" r:id="rId222" xr:uid="{00000000-0004-0000-0600-0000DD000000}"/>
+    <hyperlink ref="F463" r:id="rId223" xr:uid="{00000000-0004-0000-0600-0000DE000000}"/>
+    <hyperlink ref="F464" r:id="rId224" tooltip="https://www.acfun.cn/v/ac47931710" xr:uid="{00000000-0004-0000-0600-0000DF000000}"/>
+    <hyperlink ref="F465" r:id="rId225" xr:uid="{00000000-0004-0000-0600-0000E0000000}"/>
+    <hyperlink ref="F466" r:id="rId226" xr:uid="{00000000-0004-0000-0600-0000E1000000}"/>
+    <hyperlink ref="F468" r:id="rId227" xr:uid="{00000000-0004-0000-0600-0000E2000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="52.4545454545455" style="3" customWidth="1"/>
+    <col min="1" max="1" width="52.453125" style="3" customWidth="1"/>
     <col min="2" max="2" width="20" style="19" customWidth="1"/>
-    <col min="3" max="3" width="38.4545454545455" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.8181818181818" style="3" customWidth="1"/>
-    <col min="5" max="5" width="28.6363636363636" style="3" customWidth="1"/>
-    <col min="6" max="6" width="48.0909090909091" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.5454545454545" style="3" customWidth="1"/>
+    <col min="3" max="3" width="38.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="28.6328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="48.08984375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" style="3" customWidth="1"/>
     <col min="8" max="8" width="14" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.4545454545455" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" style="3" customWidth="1"/>
     <col min="10" max="10" width="9" style="3" customWidth="1"/>
     <col min="11" max="16384" width="9" style="3"/>
   </cols>
@@ -41815,7 +41309,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:9">
+    <row r="3" spans="1:9" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -41925,7 +41419,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" spans="1:9">
+    <row r="7" spans="1:9" ht="16" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -43108,44 +42602,111 @@
         <v>1046</v>
       </c>
     </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="49" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B51" s="25">
+        <v>46357</v>
+      </c>
+      <c r="C51" s="50" t="s">
+        <v>2521</v>
+      </c>
+      <c r="D51" s="50" t="s">
+        <v>2529</v>
+      </c>
+      <c r="E51" s="50" t="s">
+        <v>2532</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="I51" s="50" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="49" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B52" s="25">
+        <v>46358</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D52" s="50" t="s">
+        <v>2530</v>
+      </c>
+      <c r="E52" s="50" t="s">
+        <v>2532</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="I52" s="50" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="49" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B53" s="25">
+        <v>46360</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D53" s="50" t="s">
+        <v>2531</v>
+      </c>
+      <c r="E53" s="50" t="s">
+        <v>2532</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="I53" s="50" t="s">
+        <v>2525</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H48" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:H48" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.acfun.cn/v/ac48837138"/>
-    <hyperlink ref="F10" r:id="rId2" display="https://www.acfun.cn/v/ac48796276"/>
-    <hyperlink ref="F15" r:id="rId3" display="https://www.bilibili.com/video/BV1aAZYYAEEQ"/>
-    <hyperlink ref="F17" r:id="rId4" display="https://www.bilibili.com/video/BV1RV2eBeEAd"/>
-    <hyperlink ref="F19" r:id="rId5" display="https://www.bilibili.com/video/BV1pB3izpExm"/>
-    <hyperlink ref="F24" r:id="rId6" display="https://www.acfun.cn/v/ac48737511"/>
-    <hyperlink ref="F28" r:id="rId7" display="https://www.acfun.cn/v/ac48832641" tooltip="https://www.acfun.cn/v/ac48832641"/>
-    <hyperlink ref="F29" r:id="rId8" display="https://www.acfun.cn/v/ac48832628" tooltip="https://www.acfun.cn/v/ac48832628"/>
-    <hyperlink ref="F30" r:id="rId9" display="https://www.acfun.cn/v/ac48691288" tooltip="https://www.acfun.cn/v/ac48691288"/>
-    <hyperlink ref="F33" r:id="rId10" display="https://www.acfun.cn/v/ac48832656"/>
-    <hyperlink ref="F34" r:id="rId11" display="https://www.bilibili.com/video/BV1TFJW6FEeP"/>
-    <hyperlink ref="F36" r:id="rId12" display="https://www.bilibili.com/video/BV18RdHBnELz"/>
-    <hyperlink ref="F42" r:id="rId13" display="https://www.acfun.cn/v/ac48645465" tooltip="https://www.acfun.cn/v/ac48645465"/>
-    <hyperlink ref="F43" r:id="rId14" display="https://www.acfun.cn/v/ac48644820" tooltip="https://www.acfun.cn/v/ac48644820"/>
-    <hyperlink ref="F48" r:id="rId15" display="https://www.bilibili.com/video/BV17iYj6bE6G" tooltip="https://www.bilibili.com/video/BV17iYj6bE6G"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="F10" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
+    <hyperlink ref="F15" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
+    <hyperlink ref="F17" r:id="rId4" xr:uid="{00000000-0004-0000-0700-000003000000}"/>
+    <hyperlink ref="F19" r:id="rId5" xr:uid="{00000000-0004-0000-0700-000004000000}"/>
+    <hyperlink ref="F24" r:id="rId6" xr:uid="{00000000-0004-0000-0700-000005000000}"/>
+    <hyperlink ref="F28" r:id="rId7" tooltip="https://www.acfun.cn/v/ac48832641" xr:uid="{00000000-0004-0000-0700-000006000000}"/>
+    <hyperlink ref="F29" r:id="rId8" tooltip="https://www.acfun.cn/v/ac48832628" xr:uid="{00000000-0004-0000-0700-000007000000}"/>
+    <hyperlink ref="F30" r:id="rId9" tooltip="https://www.acfun.cn/v/ac48691288" xr:uid="{00000000-0004-0000-0700-000008000000}"/>
+    <hyperlink ref="F33" r:id="rId10" xr:uid="{00000000-0004-0000-0700-000009000000}"/>
+    <hyperlink ref="F34" r:id="rId11" xr:uid="{00000000-0004-0000-0700-00000A000000}"/>
+    <hyperlink ref="F36" r:id="rId12" xr:uid="{00000000-0004-0000-0700-00000B000000}"/>
+    <hyperlink ref="F42" r:id="rId13" tooltip="https://www.acfun.cn/v/ac48645465" xr:uid="{00000000-0004-0000-0700-00000C000000}"/>
+    <hyperlink ref="F43" r:id="rId14" tooltip="https://www.acfun.cn/v/ac48644820" xr:uid="{00000000-0004-0000-0700-00000D000000}"/>
+    <hyperlink ref="F48" r:id="rId15" tooltip="https://www.bilibili.com/video/BV17iYj6bE6G" xr:uid="{00000000-0004-0000-0700-00000E000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:G554"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="83.2727272727273" customWidth="1"/>
-    <col min="2" max="2" width="10.2727272727273" customWidth="1"/>
-    <col min="3" max="3" width="39.7272727272727" customWidth="1"/>
-    <col min="4" max="4" width="16.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="45.9090909090909" customWidth="1"/>
-    <col min="6" max="6" width="15.7272727272727" customWidth="1"/>
+    <col min="1" max="1" width="83.26953125" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
+    <col min="5" max="5" width="45.90625" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -43763,7 +43324,7 @@
       </c>
       <c r="G43" s="19"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:7">
+    <row r="44" spans="1:7" ht="15" customHeight="1">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -45023,7 +44584,7 @@
       </c>
       <c r="G136" s="19"/>
     </row>
-    <row r="137" ht="15" customHeight="1" spans="1:7">
+    <row r="137" spans="1:7" ht="15" customHeight="1">
       <c r="A137" s="3" t="s">
         <v>21</v>
       </c>
@@ -45326,7 +44887,7 @@
       </c>
       <c r="G159" s="19"/>
     </row>
-    <row r="160" ht="15" customHeight="1" spans="1:7">
+    <row r="160" spans="1:7" ht="15" customHeight="1">
       <c r="A160" s="3" t="s">
         <v>27</v>
       </c>
@@ -46167,7 +45728,7 @@
       </c>
       <c r="G222" s="19"/>
     </row>
-    <row r="223" ht="18" customHeight="1" spans="1:7">
+    <row r="223" spans="1:7" ht="18" customHeight="1">
       <c r="A223" t="s">
         <v>45</v>
       </c>
@@ -46239,7 +45800,7 @@
       </c>
       <c r="G226" s="19"/>
     </row>
-    <row r="227" ht="15" customHeight="1" spans="1:7">
+    <row r="227" spans="1:7" ht="15" customHeight="1">
       <c r="A227" t="s">
         <v>45</v>
       </c>
@@ -46476,7 +46037,7 @@
       </c>
       <c r="G242" s="19"/>
     </row>
-    <row r="243" ht="18" customHeight="1" spans="1:7">
+    <row r="243" spans="1:7" ht="18" customHeight="1">
       <c r="A243" t="s">
         <v>47</v>
       </c>
@@ -46548,7 +46109,7 @@
       </c>
       <c r="G246" s="19"/>
     </row>
-    <row r="247" ht="15" customHeight="1" spans="1:7">
+    <row r="247" spans="1:7" ht="15" customHeight="1">
       <c r="A247" t="s">
         <v>47</v>
       </c>
@@ -46785,7 +46346,7 @@
       </c>
       <c r="G262" s="19"/>
     </row>
-    <row r="263" ht="13.5" customHeight="1" spans="1:7">
+    <row r="263" spans="1:7" ht="13.5" customHeight="1">
       <c r="A263" t="s">
         <v>49</v>
       </c>
@@ -50600,15 +50161,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G554" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:G554" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G163" r:id="rId3" display="https://www.acfun.cn/v/ac47932379_3"/>
-    <hyperlink ref="G177" r:id="rId4" display="https://www.acfun.cn/v/ac47932379_4"/>
+    <hyperlink ref="G163" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="G177" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A142DBB-0A29-458F-9E49-B01A99AD8D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772F2466-CC49-4857-9282-D25B7AE38A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="名字规范！！！" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10549" uniqueCount="2535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10575" uniqueCount="2550">
   <si>
     <t>SONG</t>
   </si>
@@ -8134,15 +8134,98 @@
     <t>1.live样式优化 2.live新增即将到来的演出展示</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
+  <si>
+    <t>2026.09.19</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增全局搜索</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>../images/横k鸡狗1场刊02.webp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>../images/lisani2025_am10.webp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>リスアニ!LIVE 2025 SATURDAY STAGE</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>「わかれ道の、その先へ」 CONCEPT PHOTOBOOK访谈 Ave Mujica部分</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>mc/lisani2025场刊.md</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>リスアニ!LIVE 2025 场刊 Ave Mujica部分</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>../images/202408113p对谈01.webp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>斋藤光二 x 绪方航贵 x 松本拓辉</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>『Anisama 2024』斋藤P x “MyGO!!!!!”P 绪方航贵 x “Ave Mujica”P 松本拓辉 三方对谈</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>mc/202408113p对谈.md</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>../images/20241211lisani全员访谈01.webp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>mc/20241211lisani全员访谈.md</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「リスパレ！チョイス」选出艺人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ave Mujica 访谈</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
+    <numFmt numFmtId="176" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8281,6 +8364,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -8340,7 +8430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -20494,7 +20584,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="43.26953125" customWidth="1"/>
@@ -20701,7 +20791,7 @@
         <v>2182</v>
       </c>
       <c r="F10" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -20721,7 +20811,7 @@
         <v>2184</v>
       </c>
       <c r="F11" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -20741,7 +20831,7 @@
         <v>2186</v>
       </c>
       <c r="F12" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -20805,8 +20895,8 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>1679</v>
+      <c r="A16" s="49" t="s">
+        <v>2537</v>
       </c>
       <c r="B16" s="5">
         <v>45773</v>
@@ -20814,13 +20904,73 @@
       <c r="C16" t="s">
         <v>12</v>
       </c>
-      <c r="D16" t="s">
-        <v>199</v>
+      <c r="D16" s="49" t="s">
+        <v>2540</v>
       </c>
       <c r="E16" t="s">
         <v>2193</v>
       </c>
       <c r="F16" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="49" t="s">
+        <v>2538</v>
+      </c>
+      <c r="B17" s="5">
+        <v>45682</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>2542</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>2541</v>
+      </c>
+      <c r="F17" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="49" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B18" s="5">
+        <v>45515</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>2544</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>2545</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>2546</v>
+      </c>
+      <c r="F18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16.5">
+      <c r="A19" s="49" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B19" s="5">
+        <v>45637</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>2549</v>
+      </c>
+      <c r="E19" s="49" t="s">
+        <v>2548</v>
+      </c>
+      <c r="F19" t="s">
         <v>194</v>
       </c>
     </row>
@@ -28824,7 +28974,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
@@ -29080,6 +29230,17 @@
       </c>
       <c r="B23" s="49" t="s">
         <v>2534</v>
+      </c>
+      <c r="C23" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="49" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>2536</v>
       </c>
     </row>
   </sheetData>
@@ -29093,7 +29254,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16.6328125" customWidth="1"/>
@@ -29309,7 +29470,7 @@
         <v>46279</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -29326,13 +29487,55 @@
         <v>209</v>
       </c>
     </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C17" s="5">
+        <v>46284</v>
+      </c>
+      <c r="D17" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C18" s="5">
+        <v>46284</v>
+      </c>
+      <c r="D18" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C19" s="5">
+        <v>46284</v>
+      </c>
+      <c r="D19" t="s">
+        <v>209</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16 A18:A1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"song,live,interview,discography"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D18:D1000 D2:D16" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1000" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -41637,8 +41840,8 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="3" t="s">
-        <v>29</v>
+      <c r="A15" s="50" t="s">
+        <v>2539</v>
       </c>
       <c r="B15" s="25">
         <v>45682</v>

--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF3432D-390D-4E82-9675-B98410859E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5748BE60-0907-496F-B67B-137E063268DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="名字规范！！！" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">song_comments!$A$1:$D$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">song_live_history!$A$1:$F$468</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">songs!$A$1:$P$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">timeline!$A$1:$J$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">timeline!$A$1:$J$348</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -14671,7 +14671,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" hidden="1">
       <c r="A2" s="11">
         <v>45081</v>
       </c>
@@ -14697,7 +14697,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" hidden="1">
       <c r="A3" s="11" t="s">
         <v>1735</v>
       </c>
@@ -14723,7 +14723,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" hidden="1">
       <c r="A4" s="11" t="s">
         <v>1739</v>
       </c>
@@ -14749,7 +14749,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" hidden="1">
       <c r="A5" s="11" t="s">
         <v>1739</v>
       </c>
@@ -14775,7 +14775,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" hidden="1">
       <c r="A6" s="11" t="s">
         <v>1739</v>
       </c>
@@ -14801,7 +14801,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1">
+    <row r="7" spans="1:10">
       <c r="A7" s="10" t="s">
         <v>1745</v>
       </c>
@@ -14827,7 +14827,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1">
+    <row r="8" spans="1:10">
       <c r="A8" s="10" t="s">
         <v>1745</v>
       </c>
@@ -14853,7 +14853,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1">
+    <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
         <v>1751</v>
       </c>
@@ -14879,7 +14879,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1">
+    <row r="10" spans="1:10">
       <c r="A10" s="10" t="s">
         <v>1751</v>
       </c>
@@ -14905,7 +14905,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1">
+    <row r="11" spans="1:10">
       <c r="A11" s="10" t="s">
         <v>1756</v>
       </c>
@@ -14931,7 +14931,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1">
+    <row r="12" spans="1:10">
       <c r="A12" s="10" t="s">
         <v>1756</v>
       </c>
@@ -14957,7 +14957,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1">
+    <row r="13" spans="1:10">
       <c r="A13" s="10" t="s">
         <v>1761</v>
       </c>
@@ -14983,7 +14983,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1">
+    <row r="14" spans="1:10">
       <c r="A14" s="10" t="s">
         <v>1761</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1">
+    <row r="15" spans="1:10">
       <c r="A15" s="10" t="s">
         <v>1766</v>
       </c>
@@ -15035,7 +15035,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1">
+    <row r="16" spans="1:10">
       <c r="A16" s="10" t="s">
         <v>1766</v>
       </c>
@@ -16797,7 +16797,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1">
+    <row r="89" spans="1:10">
       <c r="A89" s="10">
         <v>45290</v>
       </c>
@@ -16823,7 +16823,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1">
+    <row r="90" spans="1:10">
       <c r="A90" s="10">
         <v>45290</v>
       </c>
@@ -16846,7 +16846,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1">
+    <row r="91" spans="1:10">
       <c r="A91" s="10">
         <v>45298</v>
       </c>
@@ -16872,7 +16872,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1">
+    <row r="92" spans="1:10">
       <c r="A92" s="10">
         <v>45298</v>
       </c>
@@ -16970,7 +16970,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" s="11">
         <v>45451</v>
       </c>
@@ -16996,7 +16996,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" hidden="1">
       <c r="A97" s="11">
         <v>45451</v>
       </c>
@@ -17022,7 +17022,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" hidden="1">
       <c r="A98" s="11">
         <v>45451</v>
       </c>
@@ -17045,7 +17045,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" hidden="1">
       <c r="A99" s="11">
         <v>45480</v>
       </c>
@@ -17071,7 +17071,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" hidden="1">
       <c r="A100" s="11">
         <v>45578</v>
       </c>
@@ -17097,7 +17097,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" hidden="1">
       <c r="A101" s="11">
         <v>45578</v>
       </c>
@@ -17123,7 +17123,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" hidden="1">
       <c r="A102" s="11">
         <v>45578</v>
       </c>
@@ -17146,7 +17146,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" hidden="1">
       <c r="A103" s="11">
         <v>45360</v>
       </c>
@@ -17169,7 +17169,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" hidden="1">
       <c r="A104" s="11">
         <v>45486</v>
       </c>
@@ -17195,7 +17195,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" hidden="1">
       <c r="A105" s="11">
         <v>45486</v>
       </c>
@@ -17218,7 +17218,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" hidden="1">
       <c r="A106" s="11">
         <v>45487</v>
       </c>
@@ -17235,7 +17235,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" hidden="1">
       <c r="A107" s="11">
         <v>45534</v>
       </c>
@@ -17261,7 +17261,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" hidden="1">
       <c r="A108" s="11">
         <v>45534</v>
       </c>
@@ -17284,7 +17284,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" hidden="1">
       <c r="A109" s="11">
         <v>45186</v>
       </c>
@@ -17310,7 +17310,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" hidden="1">
       <c r="A110" s="11">
         <v>45186</v>
       </c>
@@ -17333,7 +17333,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1">
+    <row r="111" spans="1:10">
       <c r="A111" s="10">
         <v>45389</v>
       </c>
@@ -17359,7 +17359,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1">
+    <row r="112" spans="1:10">
       <c r="A112" s="10">
         <v>45389</v>
       </c>
@@ -17382,7 +17382,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1">
+    <row r="113" spans="1:10">
       <c r="A113" s="10">
         <v>45430</v>
       </c>
@@ -17408,7 +17408,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1">
+    <row r="114" spans="1:10">
       <c r="A114" s="10">
         <v>45430</v>
       </c>
@@ -17431,7 +17431,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1">
+    <row r="115" spans="1:10">
       <c r="A115" s="10">
         <v>45458</v>
       </c>
@@ -17457,7 +17457,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1">
+    <row r="116" spans="1:10">
       <c r="A116" s="10">
         <v>45458</v>
       </c>
@@ -17480,7 +17480,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1">
+    <row r="117" spans="1:10">
       <c r="A117" s="10">
         <v>45481</v>
       </c>
@@ -17506,7 +17506,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1">
+    <row r="118" spans="1:10">
       <c r="A118" s="10">
         <v>45481</v>
       </c>
@@ -17529,7 +17529,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1">
+    <row r="119" spans="1:10">
       <c r="A119" s="10">
         <v>45534</v>
       </c>
@@ -17555,7 +17555,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1">
+    <row r="120" spans="1:10">
       <c r="A120" s="10">
         <v>45534</v>
       </c>
@@ -17783,7 +17783,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" hidden="1">
       <c r="A129" s="11">
         <v>45640</v>
       </c>
@@ -17809,7 +17809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" hidden="1">
       <c r="A130" s="11">
         <v>45640</v>
       </c>
@@ -17832,7 +17832,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" hidden="1">
       <c r="A131" s="11">
         <v>45641</v>
       </c>
@@ -17858,7 +17858,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" hidden="1">
       <c r="A132" s="11">
         <v>45641</v>
       </c>
@@ -17884,7 +17884,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" hidden="1">
       <c r="A133" s="11">
         <v>45641</v>
       </c>
@@ -17907,7 +17907,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" hidden="1">
       <c r="A134" s="11">
         <v>45619</v>
       </c>
@@ -17930,7 +17930,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" hidden="1">
       <c r="A135" s="11">
         <v>45619</v>
       </c>
@@ -22213,7 +22213,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="310" spans="1:10" hidden="1">
+    <row r="310" spans="1:10">
       <c r="A310" s="10">
         <v>45674</v>
       </c>
@@ -22236,7 +22236,7 @@
         <v>2651</v>
       </c>
     </row>
-    <row r="311" spans="1:10" hidden="1">
+    <row r="311" spans="1:10">
       <c r="A311" s="10">
         <v>45674</v>
       </c>
@@ -22262,7 +22262,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="312" spans="1:10" hidden="1">
+    <row r="312" spans="1:10">
       <c r="A312" s="10">
         <v>45873</v>
       </c>
@@ -22288,7 +22288,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="313" spans="1:10" hidden="1">
+    <row r="313" spans="1:10">
       <c r="A313" s="10">
         <v>45722</v>
       </c>
@@ -22314,7 +22314,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="314" spans="1:10" hidden="1">
+    <row r="314" spans="1:10">
       <c r="A314" s="10">
         <v>45722</v>
       </c>
@@ -22340,7 +22340,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="315" spans="1:10" hidden="1">
+    <row r="315" spans="1:10">
       <c r="A315" s="10">
         <v>45722</v>
       </c>
@@ -22366,7 +22366,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="316" spans="1:10" hidden="1">
+    <row r="316" spans="1:10">
       <c r="A316" s="10">
         <v>45722</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="317" spans="1:10" hidden="1">
+    <row r="317" spans="1:10">
       <c r="A317" s="10">
         <v>45750</v>
       </c>
@@ -22418,7 +22418,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="318" spans="1:10" hidden="1">
+    <row r="318" spans="1:10">
       <c r="A318" s="10">
         <v>45750</v>
       </c>
@@ -22444,7 +22444,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="319" spans="1:10" hidden="1">
+    <row r="319" spans="1:10">
       <c r="A319" s="10">
         <v>45764</v>
       </c>
@@ -22470,7 +22470,7 @@
         <v>2262</v>
       </c>
     </row>
-    <row r="320" spans="1:10" hidden="1">
+    <row r="320" spans="1:10">
       <c r="A320" s="10">
         <v>45764</v>
       </c>
@@ -22496,7 +22496,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="321" spans="1:10" hidden="1">
+    <row r="321" spans="1:10">
       <c r="A321" s="10">
         <v>45904</v>
       </c>
@@ -22522,7 +22522,7 @@
         <v>2643</v>
       </c>
     </row>
-    <row r="322" spans="1:10" hidden="1">
+    <row r="322" spans="1:10">
       <c r="A322" s="10">
         <v>45904</v>
       </c>
@@ -22548,7 +22548,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="323" spans="1:10" hidden="1">
+    <row r="323" spans="1:10">
       <c r="A323" s="10">
         <v>45927</v>
       </c>
@@ -22571,7 +22571,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="324" spans="1:10" hidden="1">
+    <row r="324" spans="1:10">
       <c r="A324" s="10">
         <v>45927</v>
       </c>
@@ -22597,7 +22597,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="325" spans="1:10" hidden="1">
+    <row r="325" spans="1:10">
       <c r="A325" s="10">
         <v>46279</v>
       </c>
@@ -23092,7 +23092,7 @@
         <v>2701</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" hidden="1">
       <c r="A344" s="10">
         <v>45682</v>
       </c>
@@ -23115,7 +23115,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" hidden="1">
       <c r="A345" s="10">
         <v>45682</v>
       </c>
@@ -23138,7 +23138,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" hidden="1">
       <c r="A346" s="10">
         <v>45690</v>
       </c>
@@ -23161,7 +23161,7 @@
         <v>2710</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" hidden="1">
       <c r="A347" s="10">
         <v>45690</v>
       </c>
@@ -23184,7 +23184,7 @@
         <v>2711</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" hidden="1">
       <c r="A348" s="10">
         <v>45690</v>
       </c>
@@ -23211,7 +23211,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J343" xr:uid="{00000000-0009-0000-0000-00000B000000}">
+  <autoFilter ref="A1:J348" xr:uid="{00000000-0009-0000-0000-00000B000000}">
     <filterColumn colId="2">
       <filters>
         <filter val="organization"/>
@@ -23219,9 +23219,7 @@
     </filterColumn>
     <filterColumn colId="4">
       <filters>
-        <filter val="bandori_fes"/>
-        <filter val="fes"/>
-        <filter val="oml"/>
+        <filter val="single"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8172D903-41BE-487B-B570-2375A7CEAA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF71C170-3920-4CBB-881D-ECB2B03B2E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="名字规范！！！" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11275" uniqueCount="2741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11278" uniqueCount="2742">
   <si>
     <t>SONG</t>
   </si>
@@ -8832,6 +8832,10 @@
   </si>
   <si>
     <t>images/骰子通常.webp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fatal</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -23891,7 +23895,7 @@
         <v>2381</v>
       </c>
       <c r="F13" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -32414,7 +32418,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16.6328125" customWidth="1"/>
@@ -32610,7 +32614,7 @@
         <v>216</v>
       </c>
       <c r="B14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C14" s="5">
         <v>46279</v>
@@ -32621,13 +32625,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C15" s="5">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="D15" t="s">
         <v>203</v>
@@ -32638,10 +32642,10 @@
         <v>205</v>
       </c>
       <c r="B16" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C16" s="5">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="D16" t="s">
         <v>203</v>
@@ -32652,7 +32656,7 @@
         <v>205</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C17" s="5">
         <v>46284</v>
@@ -32666,7 +32670,7 @@
         <v>205</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C18" s="5">
         <v>46284</v>
@@ -32675,43 +32679,43 @@
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" ht="16.5">
       <c r="A19" t="s">
         <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C19" s="5">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="D19" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="16.5">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>205</v>
       </c>
       <c r="B20" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C20" s="5">
         <v>46287</v>
       </c>
       <c r="D20" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s">
-        <v>224</v>
+        <v>481</v>
       </c>
       <c r="C21" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D21" t="s">
         <v>223</v>
@@ -32721,13 +32725,27 @@
       <c r="A22" t="s">
         <v>216</v>
       </c>
-      <c r="B22" t="s">
-        <v>481</v>
+      <c r="B22" s="48" t="s">
+        <v>2741</v>
       </c>
       <c r="C22" s="5">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="D22" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C23" s="5">
+        <v>46292</v>
+      </c>
+      <c r="D23" t="s">
         <v>223</v>
       </c>
     </row>
@@ -32737,7 +32755,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"song,live,interview,discography"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1000" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D999" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480" firstSheet="9" activeTab="11"/>
+    <workbookView windowWidth="25600" windowHeight="11480" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="名字规范！！！" sheetId="1" r:id="rId1"/>
@@ -1957,10 +1957,192 @@
     <t>Diggy-MO’</t>
   </si>
   <si>
-    <t>ざわめく海  哀しい幻\n堕ちるように昇ってゆく愛  still burnin’\n鮮やかな闇を描くこの天(そら)に\nまた わたしの吐息を許すのなら\n巡り巡る星よ\n時代(とき)の波間に来て\n生まれ変わって もういちど\nさあ わたしの傷口にキスをして\nloneliness, loneliness,  baby, let me hear you\nso, let me hear you sing ‘A Song Of Romance’\nloneliness,  baby, let me hear you\nplease, let me hear you sing ‘A Song Of Romance’\nキスをして  さあ 癒して  キスをして\n甦れば\n真実に近づけると believe\nまた自由に 自由になれると  still dreamin’\n追憶の君を辿れば わたしも同じなの\n理解(わか)ってあげられたはずなのに\n揺れる揺れる星を\nそっと 抱き寄せて\n孤独をただ分け合うように\nそうね きっとみんな寂しいのね\nwho am i…\noh, who am i…\nalienation, emptiness,\nfrom despair to where…\nhappiness, loneliness,\nbeyond,  beyond,\n巡り巡る星よ\n時代(とき)の波間に来て\n生まれ変わって もういちど\n君に出逢えたなら\n傷だらけの星を\nそっと 抱き寄せて\n孤独をただ分け合うように\n赤裸々に\n…sing ‘A Song Of Romance’\nloneliness,  baby, let me hear you\nplease, let me hear you sing ‘A Song Of Romance’</t>
-  </si>
-  <si>
-    <t>喧嚣翻涌的海 悲伤的幻影\n如坠落般不断升腾的爱 still burnin’\n描绘鲜明黑暗的这片天空中\n若能再次容许我的呼吸\n轮回运转的星啊\n来到时光的波涛间\n重获新生 再一次\n来吧 亲吻我的伤口\nloneliness, loneliness, baby, let me hear you\nso, let me hear you sing ‘A Song Of Romance’\nloneliness, baby, let me hear you\nplease, let me hear you sing ‘A Song Of Romance’\n亲吻我 来吧 治愈我 亲吻我\n若能复苏\n就能接近真实 believe\n就能再次自由 变得自由 still dreamin’\n追寻记忆中的你 我也是一样啊\n明明本应能理解你\n将那摇曳不定的星\n轻轻地拥入怀中\n仿佛只是在彼此分担孤独\n是啊 想必大家都很寂寞\nwho am i…\noh, who am i…\nalienation, emptiness,\nfrom despair to where…\nhappiness, loneliness,\nbeyond, beyond,\n轮回运转的星啊\n来到时光的波涛间\n重获新生 再一次\n若能与你相遇\n将那伤痕累累的星\n轻轻地拥入怀中\n仿佛只是在彼此分担孤独\n无遮无掩地\n…sing ‘A Song Of Romance’\nloneliness, baby, let me hear you\nplease, let me hear you sing ‘A Song Of Romance’</t>
+    <r>
+      <t>ざわめく海</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>哀しい幻\n堕ちるように昇ってゆく愛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>still burnin’\n \n鮮やかな闇を描くこの天(そら)に\nまた わたしの吐息を許すのなら\n \n巡り巡る星よ\n時代(とき)の波間に来て\n生まれ変わって もういちど\nさあ わたしの傷口にキスをして\n \nloneliness, loneliness,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>baby, let me hear you\nso, let me hear you sing ‘A Song Of Romance’\nloneliness,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>baby, let me hear you\nplease, let me hear you sing ‘A Song Of Romance’\n \nキスをして</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>さあ 癒して</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>キスをして\n甦れば\n \n \n \n真実に近づけると believe\nまた自由に 自由になれると</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>still dreamin’\n \n追憶の君を辿れば わたしも同じなの\n理解(わか)ってあげられたはずなのに\n揺れる揺れる星を\nそっと 抱き寄せて\n孤独をただ分け合うように\nそうね きっとみんな寂しいのね\n \n \n \nwho am i…\noh, who am i…\nalienation, emptiness,\nfrom despair to where…\nhappiness, loneliness,\nbeyond,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>beyond,\n \n \n \n巡り巡る星よ\n時代(とき)の波間に来て\n生まれ変わって もういちど\n君に出逢えたなら\n \n傷だらけの星を\nそっと 抱き寄せて\n孤独をただ分け合うように\n赤裸々に\n \n…sing ‘A Song Of Romance’\nloneliness,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>baby, let me hear you\nplease, let me hear you sing ‘A Song Of Romance’</t>
+    </r>
+  </si>
+  <si>
+    <t>喧嚣翻涌的海 悲伤的幻影\n如坠落般不断升腾的爱 still burnin’\n \n描绘鲜明黑暗的这片天空中\n若能再次容许我的呼吸\n \n轮回运转的星啊\n来到时光的波涛间\n重获新生 再一次\n来吧 亲吻我的伤口\n \nloneliness, loneliness, baby, let me hear you\nso, let me hear you sing ‘A Song Of Romance’\nloneliness, baby, let me hear you\nplease, let me hear you sing ‘A Song Of Romance’\n \n亲吻我 来吧 治愈我 亲吻我\n若能复苏\n \n \n \n就能接近真实 believe\n就能再次自由 变得自由 still dreamin’\n \n追寻记忆中的你 我也是一样啊\n明明本应能理解你\n将那摇曳不定的星\n轻轻地拥入怀中\n仿佛只是在彼此分担孤独\n是啊 想必大家都很寂寞\n \n \n \nwho am i…\noh, who am i…\nalienation, emptiness,\nfrom despair to where…\nhappiness, loneliness,\nbeyond, beyond,\n \n \n \n轮回运转的星啊\n来到时光的波涛间\n重获新生 再一次\n若能与你相遇\n \n将那伤痕累累的星\n轻轻地拥入怀中\n仿佛只是在彼此分担孤独\n无遮无掩地\n \n…sing ‘A Song Of Romance’\nloneliness, baby, let me hear you\nplease, let me hear you sing ‘A Song Of Romance’</t>
   </si>
   <si>
     <t>神の名を</t>
@@ -15981,7 +16163,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -16096,6 +16278,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -16688,7 +16873,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="64" t="s">
+      <c r="A28" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B28" t="s">
@@ -17894,7 +18079,7 @@
       <c r="B47" t="s">
         <v>1322</v>
       </c>
-      <c r="C47" s="64" t="s">
+      <c r="C47" s="65" t="s">
         <v>1323</v>
       </c>
       <c r="D47" t="s">
@@ -17914,7 +18099,7 @@
       <c r="B48" t="s">
         <v>1326</v>
       </c>
-      <c r="C48" s="64" t="s">
+      <c r="C48" s="65" t="s">
         <v>1327</v>
       </c>
       <c r="D48" t="s">
@@ -17937,7 +18122,7 @@
       <c r="B49" t="s">
         <v>1331</v>
       </c>
-      <c r="C49" s="64" t="s">
+      <c r="C49" s="65" t="s">
         <v>1327</v>
       </c>
       <c r="D49" t="s">
@@ -18434,7 +18619,7 @@
       <c r="B71" t="s">
         <v>1375</v>
       </c>
-      <c r="C71" s="64" t="s">
+      <c r="C71" s="65" t="s">
         <v>1376</v>
       </c>
       <c r="D71" s="16" t="s">
@@ -18454,7 +18639,7 @@
       <c r="B72" t="s">
         <v>1379</v>
       </c>
-      <c r="C72" s="64" t="s">
+      <c r="C72" s="65" t="s">
         <v>1380</v>
       </c>
       <c r="D72" s="16" t="s">
@@ -18474,7 +18659,7 @@
       <c r="B73" t="s">
         <v>1383</v>
       </c>
-      <c r="C73" s="64" t="s">
+      <c r="C73" s="65" t="s">
         <v>1376</v>
       </c>
       <c r="D73" s="16" t="s">
@@ -18497,7 +18682,7 @@
       <c r="B74" t="s">
         <v>1386</v>
       </c>
-      <c r="C74" s="64" t="s">
+      <c r="C74" s="65" t="s">
         <v>1376</v>
       </c>
       <c r="D74" s="16" t="s">
@@ -18520,7 +18705,7 @@
       <c r="B75" t="s">
         <v>1387</v>
       </c>
-      <c r="C75" s="64" t="s">
+      <c r="C75" s="65" t="s">
         <v>1376</v>
       </c>
       <c r="D75" s="16" t="s">
@@ -18543,7 +18728,7 @@
       <c r="B76" t="s">
         <v>1388</v>
       </c>
-      <c r="C76" s="64" t="s">
+      <c r="C76" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D76" s="16" t="s">
@@ -18566,7 +18751,7 @@
       <c r="B77" t="s">
         <v>1393</v>
       </c>
-      <c r="C77" s="64" t="s">
+      <c r="C77" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D77" s="16" t="s">
@@ -18589,7 +18774,7 @@
       <c r="B78" t="s">
         <v>1394</v>
       </c>
-      <c r="C78" s="64" t="s">
+      <c r="C78" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D78" s="16" t="s">
@@ -18612,7 +18797,7 @@
       <c r="B79" t="s">
         <v>1395</v>
       </c>
-      <c r="C79" s="64" t="s">
+      <c r="C79" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D79" s="16" t="s">
@@ -18635,7 +18820,7 @@
       <c r="B80" t="s">
         <v>1396</v>
       </c>
-      <c r="C80" s="64" t="s">
+      <c r="C80" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D80" s="16" t="s">
@@ -18658,7 +18843,7 @@
       <c r="B81" t="s">
         <v>1397</v>
       </c>
-      <c r="C81" s="64" t="s">
+      <c r="C81" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D81" s="16" t="s">
@@ -18681,7 +18866,7 @@
       <c r="B82" t="s">
         <v>1398</v>
       </c>
-      <c r="C82" s="64" t="s">
+      <c r="C82" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D82" s="16" t="s">
@@ -18704,7 +18889,7 @@
       <c r="B83" t="s">
         <v>1399</v>
       </c>
-      <c r="C83" s="64" t="s">
+      <c r="C83" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D83" s="16" t="s">
@@ -18727,7 +18912,7 @@
       <c r="B84" t="s">
         <v>961</v>
       </c>
-      <c r="C84" s="64" t="s">
+      <c r="C84" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D84" s="16" t="s">
@@ -18750,7 +18935,7 @@
       <c r="B85" t="s">
         <v>1403</v>
       </c>
-      <c r="C85" s="64" t="s">
+      <c r="C85" s="65" t="s">
         <v>1389</v>
       </c>
       <c r="D85" s="16" t="s">
@@ -42892,14 +43077,14 @@
     <extLst/>
   </autoFilter>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请选择列表中的时间轴 tag" sqref="E280 E281 E282 E283 E589 E590 E2:E279 E284:E588 E591:E728 E733:E734 E739:E1048576">
-      <formula1>"oml,bandori_fes,fes,single,album,anime,game,book,program,offline,private,business_mjc,business_others"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" promptTitle="媒体类型" prompt="请选择媒体类型" sqref="I669 F743 F592:F594 F603:F607 F612:F741">
       <formula1>"image,video,link"</formula1>
     </dataValidation>
     <dataValidation type="list" errorTitle="无效分类" error="请选择 organization 或 personal" sqref="C603:C741">
       <formula1>"organization,personal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请选择列表中的时间轴 tag" sqref="E2:E728 E733:E734 E739:E1048576">
+      <formula1>"oml,bandori_fes,fes,single,album,anime,game,book,program,offline,private,business_mjc,business_others"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -45970,7 +46155,7 @@
       <c r="D7" t="s">
         <v>3308</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="G7" t="s">
@@ -46190,7 +46375,7 @@
       <c r="D18" t="s">
         <v>3308</v>
       </c>
-      <c r="E18" s="64" t="s">
+      <c r="E18" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="G18" t="s">
@@ -46322,7 +46507,7 @@
       <c r="D24" t="s">
         <v>3367</v>
       </c>
-      <c r="E24" s="64" t="s">
+      <c r="E24" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F24" t="s">
@@ -46345,7 +46530,7 @@
       <c r="D25" t="s">
         <v>3367</v>
       </c>
-      <c r="E25" s="64" t="s">
+      <c r="E25" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F25" t="s">
@@ -46362,7 +46547,7 @@
       <c r="B26" t="s">
         <v>3406</v>
       </c>
-      <c r="C26" s="64" t="s">
+      <c r="C26" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D26" t="s">
@@ -46382,13 +46567,13 @@
       <c r="B27" t="s">
         <v>3406</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D27" t="s">
         <v>3308</v>
       </c>
-      <c r="E27" s="64" t="s">
+      <c r="E27" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="G27" t="s">
@@ -46402,13 +46587,13 @@
       <c r="B28" t="s">
         <v>3406</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D28" t="s">
         <v>3308</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="65" t="s">
         <v>3500</v>
       </c>
       <c r="G28" t="s">
@@ -46520,7 +46705,7 @@
       <c r="D33" t="s">
         <v>3367</v>
       </c>
-      <c r="E33" s="64" t="s">
+      <c r="E33" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F33" t="s">
@@ -46543,7 +46728,7 @@
       <c r="D34" t="s">
         <v>3367</v>
       </c>
-      <c r="E34" s="64" t="s">
+      <c r="E34" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F34" t="s">
@@ -46612,7 +46797,7 @@
       <c r="D37" t="s">
         <v>3367</v>
       </c>
-      <c r="E37" s="64" t="s">
+      <c r="E37" s="65" t="s">
         <v>3500</v>
       </c>
       <c r="F37" t="s">
@@ -46635,7 +46820,7 @@
       <c r="D38" t="s">
         <v>3367</v>
       </c>
-      <c r="E38" s="64" t="s">
+      <c r="E38" s="65" t="s">
         <v>3501</v>
       </c>
       <c r="F38" t="s">
@@ -46652,7 +46837,7 @@
       <c r="B39" t="s">
         <v>3406</v>
       </c>
-      <c r="C39" s="64" t="s">
+      <c r="C39" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D39" t="s">
@@ -46724,7 +46909,7 @@
       <c r="D42" t="s">
         <v>3367</v>
       </c>
-      <c r="E42" s="64" t="s">
+      <c r="E42" s="65" t="s">
         <v>3500</v>
       </c>
       <c r="F42" t="s">
@@ -46747,7 +46932,7 @@
       <c r="D43" t="s">
         <v>3367</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>3501</v>
       </c>
       <c r="F43" t="s">
@@ -46862,7 +47047,7 @@
       <c r="D48" t="s">
         <v>3367</v>
       </c>
-      <c r="E48" s="64" t="s">
+      <c r="E48" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F48" t="s">
@@ -46885,7 +47070,7 @@
       <c r="D49" t="s">
         <v>3367</v>
       </c>
-      <c r="E49" s="64" t="s">
+      <c r="E49" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F49" t="s">
@@ -46902,7 +47087,7 @@
       <c r="B50" t="s">
         <v>3406</v>
       </c>
-      <c r="C50" s="64" t="s">
+      <c r="C50" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D50" t="s">
@@ -46925,7 +47110,7 @@
       <c r="B51" t="s">
         <v>3406</v>
       </c>
-      <c r="C51" s="64" t="s">
+      <c r="C51" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D51" t="s">
@@ -47046,7 +47231,7 @@
       <c r="D56" t="s">
         <v>3367</v>
       </c>
-      <c r="E56" s="64" t="s">
+      <c r="E56" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F56" t="s">
@@ -47069,7 +47254,7 @@
       <c r="D57" t="s">
         <v>3367</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F57" t="s">
@@ -47184,7 +47369,7 @@
       <c r="D62" t="s">
         <v>3367</v>
       </c>
-      <c r="E62" s="64" t="s">
+      <c r="E62" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F62" s="4" t="s">
@@ -47201,7 +47386,7 @@
       <c r="B63" t="s">
         <v>3438</v>
       </c>
-      <c r="C63" s="64" t="s">
+      <c r="C63" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D63" t="s">
@@ -47319,7 +47504,7 @@
       <c r="D68" t="s">
         <v>3367</v>
       </c>
-      <c r="E68" s="64" t="s">
+      <c r="E68" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F68" s="4" t="s">
@@ -47336,7 +47521,7 @@
       <c r="B69" t="s">
         <v>3406</v>
       </c>
-      <c r="C69" s="64" t="s">
+      <c r="C69" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D69" t="s">
@@ -47454,7 +47639,7 @@
       <c r="D74" t="s">
         <v>3367</v>
       </c>
-      <c r="E74" s="64" t="s">
+      <c r="E74" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F74" s="4" t="s">
@@ -47563,7 +47748,7 @@
       <c r="B79" t="s">
         <v>3406</v>
       </c>
-      <c r="C79" s="64" t="s">
+      <c r="C79" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D79" t="s">
@@ -47773,7 +47958,7 @@
       <c r="D88" t="s">
         <v>3367</v>
       </c>
-      <c r="E88" s="64" t="s">
+      <c r="E88" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F88" t="s">
@@ -47796,7 +47981,7 @@
       <c r="D89" t="s">
         <v>3367</v>
       </c>
-      <c r="E89" s="64" t="s">
+      <c r="E89" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F89" t="s">
@@ -47819,7 +48004,7 @@
       <c r="D90" t="s">
         <v>3367</v>
       </c>
-      <c r="E90" s="64" t="s">
+      <c r="E90" s="65" t="s">
         <v>3516</v>
       </c>
       <c r="F90" t="s">
@@ -47836,7 +48021,7 @@
       <c r="B91" t="s">
         <v>3399</v>
       </c>
-      <c r="C91" s="64" t="s">
+      <c r="C91" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D91" t="s">
@@ -47954,7 +48139,7 @@
       <c r="D96" t="s">
         <v>3367</v>
       </c>
-      <c r="E96" s="64" t="s">
+      <c r="E96" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F96" t="s">
@@ -47977,7 +48162,7 @@
       <c r="D97" t="s">
         <v>3367</v>
       </c>
-      <c r="E97" s="64" t="s">
+      <c r="E97" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F97" t="s">
@@ -48000,7 +48185,7 @@
       <c r="D98" t="s">
         <v>3367</v>
       </c>
-      <c r="E98" s="64" t="s">
+      <c r="E98" s="65" t="s">
         <v>3516</v>
       </c>
       <c r="F98" t="s">
@@ -48017,7 +48202,7 @@
       <c r="B99" t="s">
         <v>3406</v>
       </c>
-      <c r="C99" s="64" t="s">
+      <c r="C99" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D99" t="s">
@@ -48135,7 +48320,7 @@
       <c r="D104" t="s">
         <v>3367</v>
       </c>
-      <c r="E104" s="64" t="s">
+      <c r="E104" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F104" t="s">
@@ -48158,7 +48343,7 @@
       <c r="D105" t="s">
         <v>3367</v>
       </c>
-      <c r="E105" s="64" t="s">
+      <c r="E105" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F105" t="s">
@@ -48181,7 +48366,7 @@
       <c r="D106" t="s">
         <v>3367</v>
       </c>
-      <c r="E106" s="64" t="s">
+      <c r="E106" s="65" t="s">
         <v>3516</v>
       </c>
       <c r="F106" t="s">
@@ -48258,7 +48443,7 @@
       <c r="B110" t="s">
         <v>3414</v>
       </c>
-      <c r="C110" s="64" t="s">
+      <c r="C110" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D110" t="s">
@@ -48278,7 +48463,7 @@
       <c r="B111" t="s">
         <v>3414</v>
       </c>
-      <c r="C111" s="64" t="s">
+      <c r="C111" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D111" t="s">
@@ -48298,7 +48483,7 @@
       <c r="B112" t="s">
         <v>3414</v>
       </c>
-      <c r="C112" s="64" t="s">
+      <c r="C112" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D112" t="s">
@@ -48378,7 +48563,7 @@
       <c r="B116" t="s">
         <v>3414</v>
       </c>
-      <c r="C116" s="64" t="s">
+      <c r="C116" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D116" t="s">
@@ -48398,7 +48583,7 @@
       <c r="B117" t="s">
         <v>3414</v>
       </c>
-      <c r="C117" s="64" t="s">
+      <c r="C117" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D117" t="s">
@@ -48418,7 +48603,7 @@
       <c r="B118" t="s">
         <v>3414</v>
       </c>
-      <c r="C118" s="64" t="s">
+      <c r="C118" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D118" t="s">
@@ -48438,7 +48623,7 @@
       <c r="B119" t="s">
         <v>3414</v>
       </c>
-      <c r="C119" s="64" t="s">
+      <c r="C119" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="D119" t="s">
@@ -48659,7 +48844,7 @@
       <c r="E129" t="s">
         <v>3497</v>
       </c>
-      <c r="F129" s="64" t="s">
+      <c r="F129" s="65" t="s">
         <v>54</v>
       </c>
       <c r="H129" s="5">
@@ -48831,7 +49016,7 @@
       <c r="E137" t="s">
         <v>3497</v>
       </c>
-      <c r="F137" s="64" t="s">
+      <c r="F137" s="65" t="s">
         <v>54</v>
       </c>
       <c r="H137" s="5">
@@ -48963,7 +49148,7 @@
       <c r="E143" t="s">
         <v>3497</v>
       </c>
-      <c r="F143" s="64" t="s">
+      <c r="F143" s="65" t="s">
         <v>54</v>
       </c>
       <c r="H143" s="5">
@@ -49144,7 +49329,7 @@
       <c r="D151" t="s">
         <v>3367</v>
       </c>
-      <c r="E151" s="64" t="s">
+      <c r="E151" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F151" t="s">
@@ -49299,7 +49484,7 @@
       <c r="D158" t="s">
         <v>3367</v>
       </c>
-      <c r="E158" s="64" t="s">
+      <c r="E158" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="F158" t="s">
@@ -49322,7 +49507,7 @@
       <c r="D159" t="s">
         <v>3367</v>
       </c>
-      <c r="E159" s="64" t="s">
+      <c r="E159" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="F159" t="s">
@@ -49345,7 +49530,7 @@
       <c r="D160" t="s">
         <v>3367</v>
       </c>
-      <c r="E160" s="64" t="s">
+      <c r="E160" s="65" t="s">
         <v>3500</v>
       </c>
       <c r="F160" t="s">
@@ -49368,7 +49553,7 @@
       <c r="D161" t="s">
         <v>3367</v>
       </c>
-      <c r="E161" s="64" t="s">
+      <c r="E161" s="65" t="s">
         <v>3501</v>
       </c>
       <c r="F161" t="s">
@@ -49391,7 +49576,7 @@
       <c r="D162" t="s">
         <v>3367</v>
       </c>
-      <c r="E162" s="64" t="s">
+      <c r="E162" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F162" t="s">
@@ -49414,7 +49599,7 @@
       <c r="D163" t="s">
         <v>3367</v>
       </c>
-      <c r="E163" s="64" t="s">
+      <c r="E163" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F163" t="s">
@@ -49437,7 +49622,7 @@
       <c r="D164" t="s">
         <v>3367</v>
       </c>
-      <c r="E164" s="64" t="s">
+      <c r="E164" s="65" t="s">
         <v>3516</v>
       </c>
       <c r="F164" t="s">
@@ -49460,7 +49645,7 @@
       <c r="D165" t="s">
         <v>3367</v>
       </c>
-      <c r="E165" s="64" t="s">
+      <c r="E165" s="65" t="s">
         <v>3541</v>
       </c>
       <c r="F165" t="s">
@@ -49483,7 +49668,7 @@
       <c r="D166" t="s">
         <v>3367</v>
       </c>
-      <c r="E166" s="64" t="s">
+      <c r="E166" s="65" t="s">
         <v>3542</v>
       </c>
       <c r="F166" t="s">
@@ -49506,7 +49691,7 @@
       <c r="D167" t="s">
         <v>3367</v>
       </c>
-      <c r="E167" s="64" t="s">
+      <c r="E167" s="65" t="s">
         <v>3543</v>
       </c>
       <c r="F167" t="s">
@@ -49529,7 +49714,7 @@
       <c r="D168" t="s">
         <v>3367</v>
       </c>
-      <c r="E168" s="64" t="s">
+      <c r="E168" s="65" t="s">
         <v>3544</v>
       </c>
       <c r="F168" t="s">
@@ -49552,7 +49737,7 @@
       <c r="D169" t="s">
         <v>3367</v>
       </c>
-      <c r="E169" s="64" t="s">
+      <c r="E169" s="65" t="s">
         <v>3545</v>
       </c>
       <c r="F169" t="s">
@@ -49575,7 +49760,7 @@
       <c r="D170" t="s">
         <v>3367</v>
       </c>
-      <c r="E170" s="64" t="s">
+      <c r="E170" s="65" t="s">
         <v>3546</v>
       </c>
       <c r="F170" t="s">
@@ -49598,7 +49783,7 @@
       <c r="D171" t="s">
         <v>3367</v>
       </c>
-      <c r="E171" s="64" t="s">
+      <c r="E171" s="65" t="s">
         <v>3547</v>
       </c>
       <c r="F171" t="s">
@@ -49621,7 +49806,7 @@
       <c r="D172" t="s">
         <v>3367</v>
       </c>
-      <c r="E172" s="64" t="s">
+      <c r="E172" s="65" t="s">
         <v>3548</v>
       </c>
       <c r="F172" s="4" t="s">
@@ -49684,7 +49869,7 @@
       <c r="D175" t="s">
         <v>3367</v>
       </c>
-      <c r="E175" s="64" t="s">
+      <c r="E175" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="F175" t="s">
@@ -49707,7 +49892,7 @@
       <c r="D176" t="s">
         <v>3367</v>
       </c>
-      <c r="E176" s="64" t="s">
+      <c r="E176" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="F176" t="s">
@@ -49730,7 +49915,7 @@
       <c r="D177" t="s">
         <v>3367</v>
       </c>
-      <c r="E177" s="64" t="s">
+      <c r="E177" s="65" t="s">
         <v>3500</v>
       </c>
       <c r="F177" t="s">
@@ -49753,7 +49938,7 @@
       <c r="D178" t="s">
         <v>3367</v>
       </c>
-      <c r="E178" s="64" t="s">
+      <c r="E178" s="65" t="s">
         <v>3501</v>
       </c>
       <c r="F178" t="s">
@@ -49776,7 +49961,7 @@
       <c r="D179" t="s">
         <v>3367</v>
       </c>
-      <c r="E179" s="64" t="s">
+      <c r="E179" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F179" t="s">
@@ -49799,7 +49984,7 @@
       <c r="D180" t="s">
         <v>3367</v>
       </c>
-      <c r="E180" s="64" t="s">
+      <c r="E180" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F180" t="s">
@@ -49822,7 +50007,7 @@
       <c r="D181" t="s">
         <v>3367</v>
       </c>
-      <c r="E181" s="64" t="s">
+      <c r="E181" s="65" t="s">
         <v>3516</v>
       </c>
       <c r="F181" t="s">
@@ -49845,7 +50030,7 @@
       <c r="D182" t="s">
         <v>3367</v>
       </c>
-      <c r="E182" s="64" t="s">
+      <c r="E182" s="65" t="s">
         <v>3541</v>
       </c>
       <c r="F182" t="s">
@@ -49868,7 +50053,7 @@
       <c r="D183" t="s">
         <v>3367</v>
       </c>
-      <c r="E183" s="64" t="s">
+      <c r="E183" s="65" t="s">
         <v>3542</v>
       </c>
       <c r="F183" t="s">
@@ -49891,7 +50076,7 @@
       <c r="D184" t="s">
         <v>3367</v>
       </c>
-      <c r="E184" s="64" t="s">
+      <c r="E184" s="65" t="s">
         <v>3543</v>
       </c>
       <c r="F184" t="s">
@@ -49914,7 +50099,7 @@
       <c r="D185" t="s">
         <v>3367</v>
       </c>
-      <c r="E185" s="64" t="s">
+      <c r="E185" s="65" t="s">
         <v>3544</v>
       </c>
       <c r="F185" t="s">
@@ -49937,7 +50122,7 @@
       <c r="D186" t="s">
         <v>3367</v>
       </c>
-      <c r="E186" s="64" t="s">
+      <c r="E186" s="65" t="s">
         <v>3545</v>
       </c>
       <c r="F186" t="s">
@@ -49960,7 +50145,7 @@
       <c r="D187" t="s">
         <v>3367</v>
       </c>
-      <c r="E187" s="64" t="s">
+      <c r="E187" s="65" t="s">
         <v>3546</v>
       </c>
       <c r="F187" t="s">
@@ -49983,7 +50168,7 @@
       <c r="D188" t="s">
         <v>3367</v>
       </c>
-      <c r="E188" s="64" t="s">
+      <c r="E188" s="65" t="s">
         <v>3547</v>
       </c>
       <c r="F188" t="s">
@@ -50006,7 +50191,7 @@
       <c r="D189" t="s">
         <v>3367</v>
       </c>
-      <c r="E189" s="64" t="s">
+      <c r="E189" s="65" t="s">
         <v>3548</v>
       </c>
       <c r="F189" s="4" t="s">
@@ -50049,7 +50234,7 @@
       <c r="D191" t="s">
         <v>3367</v>
       </c>
-      <c r="E191" s="64" t="s">
+      <c r="E191" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="F191" t="s">
@@ -50072,7 +50257,7 @@
       <c r="D192" t="s">
         <v>3367</v>
       </c>
-      <c r="E192" s="64" t="s">
+      <c r="E192" s="65" t="s">
         <v>3499</v>
       </c>
       <c r="F192" t="s">
@@ -50095,7 +50280,7 @@
       <c r="D193" t="s">
         <v>3367</v>
       </c>
-      <c r="E193" s="64" t="s">
+      <c r="E193" s="65" t="s">
         <v>3500</v>
       </c>
       <c r="F193" t="s">
@@ -50118,7 +50303,7 @@
       <c r="D194" t="s">
         <v>3367</v>
       </c>
-      <c r="E194" s="64" t="s">
+      <c r="E194" s="65" t="s">
         <v>3501</v>
       </c>
       <c r="F194" t="s">
@@ -50141,7 +50326,7 @@
       <c r="D195" t="s">
         <v>3367</v>
       </c>
-      <c r="E195" s="64" t="s">
+      <c r="E195" s="65" t="s">
         <v>3503</v>
       </c>
       <c r="F195" t="s">
@@ -50164,7 +50349,7 @@
       <c r="D196" t="s">
         <v>3367</v>
       </c>
-      <c r="E196" s="64" t="s">
+      <c r="E196" s="65" t="s">
         <v>3504</v>
       </c>
       <c r="F196" t="s">
@@ -50187,7 +50372,7 @@
       <c r="D197" t="s">
         <v>3367</v>
       </c>
-      <c r="E197" s="64" t="s">
+      <c r="E197" s="65" t="s">
         <v>3516</v>
       </c>
       <c r="F197" t="s">
@@ -50210,7 +50395,7 @@
       <c r="D198" t="s">
         <v>3367</v>
       </c>
-      <c r="E198" s="64" t="s">
+      <c r="E198" s="65" t="s">
         <v>3541</v>
       </c>
       <c r="F198" t="s">
@@ -50233,7 +50418,7 @@
       <c r="D199" t="s">
         <v>3367</v>
       </c>
-      <c r="E199" s="64" t="s">
+      <c r="E199" s="65" t="s">
         <v>3542</v>
       </c>
       <c r="F199" t="s">
@@ -50256,7 +50441,7 @@
       <c r="D200" t="s">
         <v>3367</v>
       </c>
-      <c r="E200" s="64" t="s">
+      <c r="E200" s="65" t="s">
         <v>3543</v>
       </c>
       <c r="F200" t="s">
@@ -50279,7 +50464,7 @@
       <c r="D201" t="s">
         <v>3367</v>
       </c>
-      <c r="E201" s="64" t="s">
+      <c r="E201" s="65" t="s">
         <v>3544</v>
       </c>
       <c r="F201" t="s">
@@ -50302,7 +50487,7 @@
       <c r="D202" t="s">
         <v>3367</v>
       </c>
-      <c r="E202" s="64" t="s">
+      <c r="E202" s="65" t="s">
         <v>3545</v>
       </c>
       <c r="F202" t="s">
@@ -50325,7 +50510,7 @@
       <c r="D203" t="s">
         <v>3367</v>
       </c>
-      <c r="E203" s="64" t="s">
+      <c r="E203" s="65" t="s">
         <v>3546</v>
       </c>
       <c r="F203" t="s">
@@ -50348,7 +50533,7 @@
       <c r="D204" t="s">
         <v>3367</v>
       </c>
-      <c r="E204" s="64" t="s">
+      <c r="E204" s="65" t="s">
         <v>3547</v>
       </c>
       <c r="F204" t="s">
@@ -50371,7 +50556,7 @@
       <c r="D205" t="s">
         <v>3367</v>
       </c>
-      <c r="E205" s="64" t="s">
+      <c r="E205" s="65" t="s">
         <v>3548</v>
       </c>
       <c r="F205" s="4" t="s">
@@ -50430,7 +50615,7 @@
       <c r="C2" t="s">
         <v>3553</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E2" t="s">
@@ -50447,7 +50632,7 @@
       <c r="C3" t="s">
         <v>3555</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E3" t="s">
@@ -50464,7 +50649,7 @@
       <c r="C4" t="s">
         <v>3557</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E4" t="s">
@@ -50481,7 +50666,7 @@
       <c r="C5" t="s">
         <v>3559</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E5" t="s">
@@ -50498,7 +50683,7 @@
       <c r="C6" t="s">
         <v>3561</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E6" t="s">
@@ -50515,7 +50700,7 @@
       <c r="C7" t="s">
         <v>3564</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E7" t="s">
@@ -50535,7 +50720,7 @@
       <c r="C8" t="s">
         <v>3553</v>
       </c>
-      <c r="D8" s="64" t="s">
+      <c r="D8" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E8" t="s">
@@ -50552,7 +50737,7 @@
       <c r="C9" t="s">
         <v>3555</v>
       </c>
-      <c r="D9" s="64" t="s">
+      <c r="D9" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -50569,7 +50754,7 @@
       <c r="C10" t="s">
         <v>3557</v>
       </c>
-      <c r="D10" s="64" t="s">
+      <c r="D10" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E10" t="s">
@@ -50586,7 +50771,7 @@
       <c r="C11" t="s">
         <v>3559</v>
       </c>
-      <c r="D11" s="64" t="s">
+      <c r="D11" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E11" t="s">
@@ -50603,7 +50788,7 @@
       <c r="C12" t="s">
         <v>3561</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E12" t="s">
@@ -50722,7 +50907,7 @@
       <c r="C19" t="s">
         <v>3586</v>
       </c>
-      <c r="D19" s="64" t="s">
+      <c r="D19" s="65" t="s">
         <v>3587</v>
       </c>
       <c r="E19" t="s">
@@ -50739,7 +50924,7 @@
       <c r="C20" t="s">
         <v>3586</v>
       </c>
-      <c r="D20" s="64" t="s">
+      <c r="D20" s="65" t="s">
         <v>3589</v>
       </c>
       <c r="E20" t="s">
@@ -50756,7 +50941,7 @@
       <c r="C21" t="s">
         <v>3586</v>
       </c>
-      <c r="D21" s="64" t="s">
+      <c r="D21" s="65" t="s">
         <v>3591</v>
       </c>
       <c r="E21" t="s">
@@ -50773,7 +50958,7 @@
       <c r="C22" t="s">
         <v>3586</v>
       </c>
-      <c r="D22" s="64" t="s">
+      <c r="D22" s="65" t="s">
         <v>3593</v>
       </c>
       <c r="E22" t="s">
@@ -50807,7 +50992,7 @@
       <c r="C24" t="s">
         <v>3586</v>
       </c>
-      <c r="D24" s="64" t="s">
+      <c r="D24" s="65" t="s">
         <v>3587</v>
       </c>
       <c r="E24" t="s">
@@ -50824,7 +51009,7 @@
       <c r="C25" t="s">
         <v>3586</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="65" t="s">
         <v>3589</v>
       </c>
       <c r="E25" t="s">
@@ -50841,7 +51026,7 @@
       <c r="C26" t="s">
         <v>3586</v>
       </c>
-      <c r="D26" s="64" t="s">
+      <c r="D26" s="65" t="s">
         <v>3591</v>
       </c>
       <c r="E26" t="s">
@@ -50858,7 +51043,7 @@
       <c r="C27" t="s">
         <v>3586</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="D27" s="65" t="s">
         <v>3593</v>
       </c>
       <c r="E27" t="s">
@@ -50892,7 +51077,7 @@
       <c r="C29" t="s">
         <v>3553</v>
       </c>
-      <c r="D29" s="64" t="s">
+      <c r="D29" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E29" t="s">
@@ -50909,7 +51094,7 @@
       <c r="C30" t="s">
         <v>3555</v>
       </c>
-      <c r="D30" s="64" t="s">
+      <c r="D30" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E30" t="s">
@@ -50926,7 +51111,7 @@
       <c r="C31" t="s">
         <v>3557</v>
       </c>
-      <c r="D31" s="64" t="s">
+      <c r="D31" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E31" t="s">
@@ -50943,7 +51128,7 @@
       <c r="C32" t="s">
         <v>3559</v>
       </c>
-      <c r="D32" s="64" t="s">
+      <c r="D32" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E32" t="s">
@@ -50960,7 +51145,7 @@
       <c r="C33" t="s">
         <v>3561</v>
       </c>
-      <c r="D33" s="64" t="s">
+      <c r="D33" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E33" t="s">
@@ -50977,7 +51162,7 @@
       <c r="C34" t="s">
         <v>3553</v>
       </c>
-      <c r="D34" s="64" t="s">
+      <c r="D34" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E34" t="s">
@@ -50994,7 +51179,7 @@
       <c r="C35" t="s">
         <v>3555</v>
       </c>
-      <c r="D35" s="64" t="s">
+      <c r="D35" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E35" t="s">
@@ -51011,7 +51196,7 @@
       <c r="C36" t="s">
         <v>3557</v>
       </c>
-      <c r="D36" s="64" t="s">
+      <c r="D36" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E36" t="s">
@@ -51028,7 +51213,7 @@
       <c r="C37" t="s">
         <v>3559</v>
       </c>
-      <c r="D37" s="64" t="s">
+      <c r="D37" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E37" t="s">
@@ -51045,7 +51230,7 @@
       <c r="C38" t="s">
         <v>3561</v>
       </c>
-      <c r="D38" s="64" t="s">
+      <c r="D38" s="65" t="s">
         <v>3497</v>
       </c>
       <c r="E38" t="s">
@@ -57489,16 +57674,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="64" t="s">
         <v>88</v>
       </c>
     </row>
@@ -58311,16 +58496,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="63" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="63" t="s">
         <v>206</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="63" t="s">
         <v>207</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="63" t="s">
         <v>208</v>
       </c>
     </row>
@@ -60099,10 +60284,10 @@
       </c>
     </row>
     <row r="28" s="52" customFormat="1" spans="1:16">
-      <c r="A28" s="64" t="s">
+      <c r="A28" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="64" t="s">
+      <c r="B28" s="65" t="s">
         <v>54</v>
       </c>
       <c r="C28" t="s">
@@ -60417,10 +60602,10 @@
       <c r="K34" t="s">
         <v>469</v>
       </c>
-      <c r="M34" s="41" t="s">
+      <c r="M34" s="62" t="s">
         <v>494</v>
       </c>
-      <c r="N34" s="41" t="s">
+      <c r="N34" s="62" t="s">
         <v>495</v>
       </c>
       <c r="O34" t="s">
@@ -61133,7 +61318,7 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="64" t="s">
+      <c r="A43" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B43" t="s">
@@ -69794,7 +69979,7 @@
       </c>
     </row>
     <row r="434" spans="1:6">
-      <c r="A434" s="64" t="s">
+      <c r="A434" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B434" s="8">
@@ -69814,7 +69999,7 @@
       </c>
     </row>
     <row r="435" spans="1:6">
-      <c r="A435" s="64" t="s">
+      <c r="A435" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B435" s="8">
@@ -69834,7 +70019,7 @@
       </c>
     </row>
     <row r="436" spans="1:6">
-      <c r="A436" s="64" t="s">
+      <c r="A436" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B436" s="8">
@@ -69854,7 +70039,7 @@
       </c>
     </row>
     <row r="437" spans="1:6">
-      <c r="A437" s="64" t="s">
+      <c r="A437" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B437" s="8">
@@ -69871,7 +70056,7 @@
       </c>
     </row>
     <row r="438" spans="1:6">
-      <c r="A438" s="64" t="s">
+      <c r="A438" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B438" s="8">
@@ -69891,7 +70076,7 @@
       </c>
     </row>
     <row r="439" spans="1:6">
-      <c r="A439" s="64" t="s">
+      <c r="A439" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B439" s="8">
@@ -69908,7 +70093,7 @@
       </c>
     </row>
     <row r="440" spans="1:6">
-      <c r="A440" s="64" t="s">
+      <c r="A440" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B440" s="8">
@@ -69928,7 +70113,7 @@
       </c>
     </row>
     <row r="441" spans="1:6">
-      <c r="A441" s="64" t="s">
+      <c r="A441" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B441" s="8">
@@ -69948,7 +70133,7 @@
       </c>
     </row>
     <row r="442" spans="1:6">
-      <c r="A442" s="64" t="s">
+      <c r="A442" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B442" s="8">
@@ -69965,7 +70150,7 @@
       </c>
     </row>
     <row r="443" spans="1:6">
-      <c r="A443" s="64" t="s">
+      <c r="A443" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B443" s="8">
@@ -69982,7 +70167,7 @@
       </c>
     </row>
     <row r="444" spans="1:6">
-      <c r="A444" s="64" t="s">
+      <c r="A444" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B444" s="8">
@@ -69999,7 +70184,7 @@
       </c>
     </row>
     <row r="445" spans="1:6">
-      <c r="A445" s="64" t="s">
+      <c r="A445" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B445" s="8">
@@ -70016,7 +70201,7 @@
       </c>
     </row>
     <row r="446" spans="1:6">
-      <c r="A446" s="64" t="s">
+      <c r="A446" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B446" s="8">
@@ -70033,7 +70218,7 @@
       </c>
     </row>
     <row r="447" spans="1:6">
-      <c r="A447" s="64" t="s">
+      <c r="A447" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B447" s="8">
@@ -70053,7 +70238,7 @@
       </c>
     </row>
     <row r="448" spans="1:6">
-      <c r="A448" s="64" t="s">
+      <c r="A448" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B448" s="8">
@@ -70073,7 +70258,7 @@
       </c>
     </row>
     <row r="449" spans="1:6">
-      <c r="A449" s="64" t="s">
+      <c r="A449" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B449" s="8">
@@ -70090,7 +70275,7 @@
       </c>
     </row>
     <row r="450" spans="1:6">
-      <c r="A450" s="64" t="s">
+      <c r="A450" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B450" s="8">
@@ -75449,7 +75634,7 @@
       <c r="B239" t="s">
         <v>1147</v>
       </c>
-      <c r="C239" s="64" t="s">
+      <c r="C239" s="65" t="s">
         <v>54</v>
       </c>
       <c r="D239" t="s">
@@ -75758,7 +75943,7 @@
       <c r="B259" t="s">
         <v>1147</v>
       </c>
-      <c r="C259" s="64" t="s">
+      <c r="C259" s="65" t="s">
         <v>54</v>
       </c>
       <c r="D259" t="s">
@@ -75839,7 +76024,7 @@
       <c r="B264" t="s">
         <v>1098</v>
       </c>
-      <c r="C264" s="64" t="s">
+      <c r="C264" s="65" t="s">
         <v>54</v>
       </c>
       <c r="D264" t="s">
@@ -76052,7 +76237,7 @@
       <c r="B278" t="s">
         <v>1107</v>
       </c>
-      <c r="C278" s="64" t="s">
+      <c r="C278" s="65" t="s">
         <v>54</v>
       </c>
       <c r="D278" t="s">
@@ -76718,7 +76903,7 @@
       <c r="B326" t="s">
         <v>1145</v>
       </c>
-      <c r="C326" s="64" t="s">
+      <c r="C326" s="65" t="s">
         <v>54</v>
       </c>
       <c r="D326" t="s">
@@ -77009,7 +77194,7 @@
       <c r="B347" t="s">
         <v>1145</v>
       </c>
-      <c r="C347" s="64" t="s">
+      <c r="C347" s="65" t="s">
         <v>54</v>
       </c>
       <c r="G347" s="13"/>
@@ -77225,7 +77410,7 @@
       <c r="B363" t="s">
         <v>1118</v>
       </c>
-      <c r="C363" s="64" t="s">
+      <c r="C363" s="65" t="s">
         <v>54</v>
       </c>
       <c r="D363" t="s">
@@ -77411,7 +77596,7 @@
       <c r="B377" t="s">
         <v>1107</v>
       </c>
-      <c r="C377" s="64" t="s">
+      <c r="C377" s="65" t="s">
         <v>54</v>
       </c>
       <c r="G377" s="13"/>
@@ -77579,7 +77764,7 @@
       <c r="B391" t="s">
         <v>1118</v>
       </c>
-      <c r="C391" s="64" t="s">
+      <c r="C391" s="65" t="s">
         <v>54</v>
       </c>
       <c r="G391" s="13"/>
@@ -77810,7 +77995,7 @@
       <c r="B410" t="s">
         <v>1145</v>
       </c>
-      <c r="C410" s="64" t="s">
+      <c r="C410" s="65" t="s">
         <v>54</v>
       </c>
       <c r="E410" s="42"/>
@@ -78040,7 +78225,7 @@
       <c r="B429" t="s">
         <v>1145</v>
       </c>
-      <c r="C429" s="64" t="s">
+      <c r="C429" s="65" t="s">
         <v>54</v>
       </c>
       <c r="E429" s="42"/>
@@ -78270,7 +78455,7 @@
       <c r="B448" t="s">
         <v>1145</v>
       </c>
-      <c r="C448" s="64" t="s">
+      <c r="C448" s="65" t="s">
         <v>54</v>
       </c>
       <c r="E448" s="42"/>
@@ -78500,7 +78685,7 @@
       <c r="B467" t="s">
         <v>1145</v>
       </c>
-      <c r="C467" s="64" t="s">
+      <c r="C467" s="65" t="s">
         <v>54</v>
       </c>
       <c r="E467" s="42"/>
@@ -78771,7 +78956,7 @@
       <c r="B486" t="s">
         <v>1145</v>
       </c>
-      <c r="C486" s="64" t="s">
+      <c r="C486" s="65" t="s">
         <v>54</v>
       </c>
       <c r="E486" s="42"/>
@@ -79081,7 +79266,7 @@
       <c r="B508" t="s">
         <v>1147</v>
       </c>
-      <c r="C508" s="64" t="s">
+      <c r="C508" s="65" t="s">
         <v>54</v>
       </c>
     </row>
@@ -79389,7 +79574,7 @@
       <c r="B534" t="s">
         <v>1145</v>
       </c>
-      <c r="C534" s="64" t="s">
+      <c r="C534" s="65" t="s">
         <v>54</v>
       </c>
       <c r="E534" s="42"/>
@@ -79605,7 +79790,7 @@
       <c r="B552" t="s">
         <v>1147</v>
       </c>
-      <c r="C552" s="64" t="s">
+      <c r="C552" s="65" t="s">
         <v>54</v>
       </c>
     </row>

--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yumin\web\MujicaTimeLineWeb\_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CABF242-CBD1-454C-86C7-4B6E7057D1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="名字规范！！！" sheetId="1" r:id="rId1"/>
@@ -35,14 +36,14 @@
     <externalReference r:id="rId19"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">lives!$A$1:$H$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">lyrics_atlas_rules!$A$1:$D$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">songs!$A$1:$P$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">programs!$A$1:$L$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">setlist!$A$1:$G$554</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">song_comments!$A$1:$D$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">song_live_history!$A$1:$F$468</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">lives!$A$1:$H$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">setlist!$A$1:$G$554</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">songs!$A$1:$P$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">timeline!$A$1:$J$855</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">programs!$A$1:$L$152</definedName>
     <definedName name="organization">[1]Lists!$A$1:$A$5</definedName>
     <definedName name="personal">[1]Lists!$B$1:$B$2</definedName>
   </definedNames>
@@ -55,8 +56,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -64,17 +63,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wijipedia</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>手动填写链接优先；留空时，生成器按演出名和曲名自动查找 song_live_history 的 video_url。</t>
@@ -86,317 +86,343 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wijipedia</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>稳定标识，由脚本自动填写；生成后不要修改。</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>节目系列，如 バンドリ！TV LIVE；特别节目也可另填系列名。</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>期数，如 #199；不定期节目可留空。</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000004000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>播出日期，YYYY/MM/DD。原表的日期原样保留。</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000005000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>可选：开播时间 HH:MM。没有可靠来源时留空，不能把日期中的 00:00 当作开播时间。</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000006000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>时间对应时区，如 +09:00 日本、+08:00 中国；未填时间时可留空。</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000007000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>本期标题；普通期目可留空，特别节目填写完整名称。</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000008000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>出演者姓名，用半角 | 分隔；名字与 N 列或 Q 列别名一致。</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000009000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>字幕组切片链接，用半角 | 分隔。可写 URL 或 标题=&gt;URL；不需要另建表。</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-00000A000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>完整节目链接。脚本只自动填入唯一匹配项；也可手动粘贴 YouTube 链接。</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-00000B000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>本地封面路径，脚本自动填写，如 images/programs/bdtv-0199.webp。</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-00000C000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>可选备注。</t>
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-00000D000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>出演者标准名。N:Q 为独立字典，与左侧同一行的节目没有对应关系。只需为新人加一次。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-00000E000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该出演者所属乐队。未知先留空；多个乐队用 | 分隔。</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-00000F000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>从原表颜色提取的网页色值，如 #881144；不用给单元格涂色。多乐队色值按顺序用 | 分隔。</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000010000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>同一个人的其他写法，用 | 分隔，统计时归到 N 列标准名。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O63" authorId="0">
+    <comment ref="O63" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000011000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O64" authorId="0">
+    <comment ref="O64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000012000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O65" authorId="0">
+    <comment ref="O65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000013000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O66" authorId="0">
+    <comment ref="O66" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000014000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O67" authorId="0">
+    <comment ref="O67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000015000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O68" authorId="0">
+    <comment ref="O68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000016000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O69" authorId="0">
+    <comment ref="O69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000017000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O70" authorId="0">
+    <comment ref="O70" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000018000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O71" authorId="0">
+    <comment ref="O71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000019000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
         </r>
       </text>
     </comment>
-    <comment ref="O72" authorId="0">
+    <comment ref="O72" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-00001A000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>原表 N:O 中没有此名字，请填写归属或在标准名的 aliases 中添加此写法。</t>
@@ -408,7 +434,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17320" uniqueCount="4839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17323" uniqueCount="4839">
   <si>
     <t>SONG</t>
   </si>
@@ -15695,15 +15721,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15731,7 +15753,7 @@
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -15753,13 +15775,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Emoji"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -15798,7 +15820,7 @@
       <sz val="9.75"/>
       <color rgb="FF9599A6"/>
       <name val="Courier New"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="9.35"/>
@@ -15810,18 +15832,19 @@
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="initial"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF131313"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF131313"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -15829,152 +15852,25 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -16017,194 +15913,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -16212,263 +15922,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -16487,15 +15958,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -16505,9 +15976,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -16541,7 +16012,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -16564,68 +16035,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="时间轴数据"/>
@@ -16918,19 +16346,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="33.2727272727273" customWidth="1"/>
+    <col min="2" max="2" width="33.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -17077,7 +16506,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:2">
+    <row r="19" spans="1:2" ht="15" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
@@ -17313,24 +16742,24 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G194"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="45.9090909090909" customWidth="1"/>
-    <col min="2" max="2" width="46.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="17.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="55.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="47.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="14.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="17.9090909090909" customWidth="1"/>
+    <col min="1" max="1" width="45.90625" customWidth="1"/>
+    <col min="2" max="2" width="46.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="55.08984375" customWidth="1"/>
+    <col min="5" max="5" width="47.6328125" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -17859,7 +17288,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" spans="1:7">
+    <row r="24" spans="1:7" ht="16.5" customHeight="1">
       <c r="A24" t="s">
         <v>84</v>
       </c>
@@ -17928,7 +17357,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:7">
+    <row r="27" spans="1:7" ht="16.5" customHeight="1">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -17951,7 +17380,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1" spans="1:7">
+    <row r="28" spans="1:7" ht="28" customHeight="1">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -17974,7 +17403,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="29" s="11" customFormat="1" ht="42" customHeight="1" spans="1:7">
+    <row r="29" spans="1:7" s="11" customFormat="1" ht="42" customHeight="1">
       <c r="A29" s="11" t="s">
         <v>84</v>
       </c>
@@ -18020,7 +17449,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="31" ht="47" customHeight="1" spans="1:7">
+    <row r="31" spans="1:7" ht="47" customHeight="1">
       <c r="A31" t="s">
         <v>84</v>
       </c>
@@ -18178,7 +17607,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="38" ht="33" customHeight="1" spans="1:7">
+    <row r="38" spans="1:7" ht="33" customHeight="1">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -18201,7 +17630,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="39" ht="30.5" customHeight="1" spans="1:7">
+    <row r="39" spans="1:7" ht="30.5" customHeight="1">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -18224,7 +17653,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="40" ht="47" customHeight="1" spans="1:7">
+    <row r="40" spans="1:7" ht="47" customHeight="1">
       <c r="A40" t="s">
         <v>84</v>
       </c>
@@ -18347,7 +17776,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="46" s="11" customFormat="1" spans="1:7">
+    <row r="46" spans="1:7" s="11" customFormat="1">
       <c r="A46" s="11" t="s">
         <v>85</v>
       </c>
@@ -18686,7 +18115,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="61" ht="28" customHeight="1" spans="1:7">
+    <row r="61" spans="1:7" ht="28" customHeight="1">
       <c r="A61" t="s">
         <v>85</v>
       </c>
@@ -18732,7 +18161,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="63" ht="44.5" customHeight="1" spans="1:7">
+    <row r="63" spans="1:7" ht="44.5" customHeight="1">
       <c r="A63" t="s">
         <v>85</v>
       </c>
@@ -18752,7 +18181,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="64" ht="22.5" customHeight="1" spans="1:7">
+    <row r="64" spans="1:7" ht="22.5" customHeight="1">
       <c r="A64" t="s">
         <v>85</v>
       </c>
@@ -18838,7 +18267,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="68" ht="49.5" customHeight="1" spans="1:7">
+    <row r="68" spans="1:7" ht="49.5" customHeight="1">
       <c r="A68" t="s">
         <v>85</v>
       </c>
@@ -18861,7 +18290,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="69" ht="49.5" customHeight="1" spans="1:7">
+    <row r="69" spans="1:7" ht="49.5" customHeight="1">
       <c r="A69" t="s">
         <v>85</v>
       </c>
@@ -18884,7 +18313,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="70" ht="30.5" customHeight="1" spans="1:7">
+    <row r="70" spans="1:7" ht="30.5" customHeight="1">
       <c r="A70" t="s">
         <v>85</v>
       </c>
@@ -19246,7 +18675,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="86" ht="16.5" customHeight="1" spans="1:7">
+    <row r="86" spans="1:7" ht="16.5" customHeight="1">
       <c r="A86" s="11" t="s">
         <v>82</v>
       </c>
@@ -19269,7 +18698,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="87" ht="30.5" customHeight="1" spans="1:7">
+    <row r="87" spans="1:7" ht="30.5" customHeight="1">
       <c r="A87" t="s">
         <v>82</v>
       </c>
@@ -19292,7 +18721,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="88" ht="33" customHeight="1" spans="1:7">
+    <row r="88" spans="1:7" ht="33" customHeight="1">
       <c r="A88" t="s">
         <v>82</v>
       </c>
@@ -19315,7 +18744,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="89" ht="63.5" customHeight="1" spans="1:7">
+    <row r="89" spans="1:7" ht="63.5" customHeight="1">
       <c r="A89" t="s">
         <v>82</v>
       </c>
@@ -19338,7 +18767,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="90" ht="63.5" customHeight="1" spans="1:7">
+    <row r="90" spans="1:7" ht="63.5" customHeight="1">
       <c r="A90" t="s">
         <v>82</v>
       </c>
@@ -19361,7 +18790,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="91" ht="30.5" customHeight="1" spans="1:7">
+    <row r="91" spans="1:7" ht="30.5" customHeight="1">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -19384,7 +18813,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="92" ht="30.5" customHeight="1" spans="1:7">
+    <row r="92" spans="1:7" ht="30.5" customHeight="1">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -19407,7 +18836,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="93" ht="30.5" customHeight="1" spans="1:7">
+    <row r="93" spans="1:7" ht="30.5" customHeight="1">
       <c r="A93" t="s">
         <v>82</v>
       </c>
@@ -19430,7 +18859,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="94" ht="30.5" customHeight="1" spans="1:7">
+    <row r="94" spans="1:7" ht="30.5" customHeight="1">
       <c r="A94" t="s">
         <v>82</v>
       </c>
@@ -19453,7 +18882,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="95" ht="30.5" customHeight="1" spans="1:7">
+    <row r="95" spans="1:7" ht="30.5" customHeight="1">
       <c r="A95" t="s">
         <v>82</v>
       </c>
@@ -19499,7 +18928,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="97" ht="42" customHeight="1" spans="1:7">
+    <row r="97" spans="1:7" ht="42" customHeight="1">
       <c r="A97" t="s">
         <v>82</v>
       </c>
@@ -19522,7 +18951,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="98" ht="44.5" customHeight="1" spans="1:7">
+    <row r="98" spans="1:7" ht="44.5" customHeight="1">
       <c r="A98" t="s">
         <v>82</v>
       </c>
@@ -19545,7 +18974,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="99" ht="47" customHeight="1" spans="1:7">
+    <row r="99" spans="1:7" ht="47" customHeight="1">
       <c r="A99" t="s">
         <v>82</v>
       </c>
@@ -20051,7 +19480,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="121" ht="16.5" customHeight="1" spans="1:7">
+    <row r="121" spans="1:7" ht="16.5" customHeight="1">
       <c r="A121" s="11" t="s">
         <v>83</v>
       </c>
@@ -20074,7 +19503,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="122" ht="44.5" customHeight="1" spans="1:7">
+    <row r="122" spans="1:7" ht="44.5" customHeight="1">
       <c r="A122" t="s">
         <v>83</v>
       </c>
@@ -20120,7 +19549,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="124" ht="89" customHeight="1" spans="1:7">
+    <row r="124" spans="1:7" ht="89" customHeight="1">
       <c r="A124" t="s">
         <v>83</v>
       </c>
@@ -20143,7 +19572,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="125" ht="16.5" customHeight="1" spans="1:7">
+    <row r="125" spans="1:7" ht="16.5" customHeight="1">
       <c r="A125" t="s">
         <v>83</v>
       </c>
@@ -20166,7 +19595,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="126" ht="30.5" customHeight="1" spans="1:7">
+    <row r="126" spans="1:7" ht="30.5" customHeight="1">
       <c r="A126" t="s">
         <v>83</v>
       </c>
@@ -20189,7 +19618,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="127" ht="30.5" customHeight="1" spans="1:7">
+    <row r="127" spans="1:7" ht="30.5" customHeight="1">
       <c r="A127" t="s">
         <v>83</v>
       </c>
@@ -20235,7 +19664,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="129" ht="58.5" customHeight="1" spans="1:7">
+    <row r="129" spans="1:7" ht="58.5" customHeight="1">
       <c r="A129" t="s">
         <v>83</v>
       </c>
@@ -20258,7 +19687,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="130" ht="58.5" customHeight="1" spans="1:7">
+    <row r="130" spans="1:7" ht="58.5" customHeight="1">
       <c r="A130" t="s">
         <v>83</v>
       </c>
@@ -20304,7 +19733,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="132" ht="70" customHeight="1" spans="1:7">
+    <row r="132" spans="1:7" ht="70" customHeight="1">
       <c r="A132" t="s">
         <v>83</v>
       </c>
@@ -20327,7 +19756,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="133" ht="70" customHeight="1" spans="1:7">
+    <row r="133" spans="1:7" ht="70" customHeight="1">
       <c r="A133" t="s">
         <v>83</v>
       </c>
@@ -20373,7 +19802,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="135" ht="28" customHeight="1" spans="1:7">
+    <row r="135" spans="1:7" ht="28" customHeight="1">
       <c r="A135" t="s">
         <v>83</v>
       </c>
@@ -20787,7 +20216,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="153" ht="33" customHeight="1" spans="1:7">
+    <row r="153" spans="1:7" ht="33" customHeight="1">
       <c r="A153" t="s">
         <v>85</v>
       </c>
@@ -20810,7 +20239,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="154" ht="33" customHeight="1" spans="1:7">
+    <row r="154" spans="1:7" ht="33" customHeight="1">
       <c r="A154" t="s">
         <v>85</v>
       </c>
@@ -20833,7 +20262,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="155" ht="33" customHeight="1" spans="1:7">
+    <row r="155" spans="1:7" ht="33" customHeight="1">
       <c r="A155" t="s">
         <v>85</v>
       </c>
@@ -20856,7 +20285,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="156" ht="33" customHeight="1" spans="1:7">
+    <row r="156" spans="1:7" ht="33" customHeight="1">
       <c r="A156" t="s">
         <v>85</v>
       </c>
@@ -20879,7 +20308,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="157" ht="33" customHeight="1" spans="1:7">
+    <row r="157" spans="1:7" ht="33" customHeight="1">
       <c r="A157" t="s">
         <v>85</v>
       </c>
@@ -20902,7 +20331,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="158" s="11" customFormat="1" ht="89" customHeight="1" spans="1:7">
+    <row r="158" spans="1:7" s="11" customFormat="1" ht="89" customHeight="1">
       <c r="A158" s="11" t="s">
         <v>81</v>
       </c>
@@ -20925,7 +20354,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="159" ht="16.5" customHeight="1" spans="1:7">
+    <row r="159" spans="1:7" ht="16.5" customHeight="1">
       <c r="A159" t="s">
         <v>81</v>
       </c>
@@ -20948,7 +20377,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="160" ht="409.5" customHeight="1" spans="1:7">
+    <row r="160" spans="1:7" ht="409.5" customHeight="1">
       <c r="A160" t="s">
         <v>81</v>
       </c>
@@ -20971,7 +20400,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="161" ht="409.5" customHeight="1" spans="1:7">
+    <row r="161" spans="1:7" ht="409.5" customHeight="1">
       <c r="A161" t="s">
         <v>81</v>
       </c>
@@ -20994,7 +20423,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="162" ht="119.5" customHeight="1" spans="1:7">
+    <row r="162" spans="1:7" ht="119.5" customHeight="1">
       <c r="A162" t="s">
         <v>81</v>
       </c>
@@ -21017,7 +20446,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="163" ht="33" customHeight="1" spans="1:7">
+    <row r="163" spans="1:7" ht="33" customHeight="1">
       <c r="A163" t="s">
         <v>81</v>
       </c>
@@ -21040,7 +20469,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="164" ht="82.5" customHeight="1" spans="1:7">
+    <row r="164" spans="1:7" ht="82.5" customHeight="1">
       <c r="A164" t="s">
         <v>81</v>
       </c>
@@ -21063,7 +20492,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="165" ht="127.5" customHeight="1" spans="1:7">
+    <row r="165" spans="1:7" ht="127.5" customHeight="1">
       <c r="A165" t="s">
         <v>81</v>
       </c>
@@ -21086,7 +20515,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="166" ht="127.5" customHeight="1" spans="1:7">
+    <row r="166" spans="1:7" ht="127.5" customHeight="1">
       <c r="A166" t="s">
         <v>81</v>
       </c>
@@ -21109,7 +20538,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="167" ht="127.5" customHeight="1" spans="1:7">
+    <row r="167" spans="1:7" ht="127.5" customHeight="1">
       <c r="A167" t="s">
         <v>81</v>
       </c>
@@ -21132,7 +20561,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="168" ht="94" customHeight="1" spans="1:7">
+    <row r="168" spans="1:7" ht="94" customHeight="1">
       <c r="A168" t="s">
         <v>81</v>
       </c>
@@ -21155,7 +20584,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="169" ht="94" customHeight="1" spans="1:7">
+    <row r="169" spans="1:7" ht="94" customHeight="1">
       <c r="A169" t="s">
         <v>81</v>
       </c>
@@ -21178,7 +20607,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="170" ht="16.5" customHeight="1" spans="1:7">
+    <row r="170" spans="1:7" ht="16.5" customHeight="1">
       <c r="A170" t="s">
         <v>81</v>
       </c>
@@ -21201,7 +20630,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="171" ht="409.5" customHeight="1" spans="1:7">
+    <row r="171" spans="1:7" ht="409.5" customHeight="1">
       <c r="A171" t="s">
         <v>81</v>
       </c>
@@ -21224,7 +20653,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="172" ht="409.5" customHeight="1" spans="1:7">
+    <row r="172" spans="1:7" ht="409.5" customHeight="1">
       <c r="A172" t="s">
         <v>81</v>
       </c>
@@ -21247,7 +20676,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="173" ht="92.5" customHeight="1" spans="1:7">
+    <row r="173" spans="1:7" ht="92.5" customHeight="1">
       <c r="A173" t="s">
         <v>81</v>
       </c>
@@ -21270,7 +20699,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="174" ht="92.5" customHeight="1" spans="1:7">
+    <row r="174" spans="1:7" ht="92.5" customHeight="1">
       <c r="A174" t="s">
         <v>81</v>
       </c>
@@ -21293,7 +20722,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="175" ht="409.5" customHeight="1" spans="1:7">
+    <row r="175" spans="1:7" ht="409.5" customHeight="1">
       <c r="A175" t="s">
         <v>81</v>
       </c>
@@ -21339,7 +20768,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="177" ht="409.5" customHeight="1" spans="1:7">
+    <row r="177" spans="1:7" ht="409.5" customHeight="1">
       <c r="A177" t="s">
         <v>81</v>
       </c>
@@ -21362,7 +20791,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="178" ht="409.5" customHeight="1" spans="1:7">
+    <row r="178" spans="1:7" ht="409.5" customHeight="1">
       <c r="A178" t="s">
         <v>81</v>
       </c>
@@ -21385,7 +20814,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="179" ht="409.5" customHeight="1" spans="1:7">
+    <row r="179" spans="1:7" ht="409.5" customHeight="1">
       <c r="A179" t="s">
         <v>81</v>
       </c>
@@ -21408,7 +20837,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="180" ht="409.5" customHeight="1" spans="1:7">
+    <row r="180" spans="1:7" ht="409.5" customHeight="1">
       <c r="A180" t="s">
         <v>81</v>
       </c>
@@ -21431,7 +20860,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="181" ht="409.5" customHeight="1" spans="1:7">
+    <row r="181" spans="1:7" ht="409.5" customHeight="1">
       <c r="A181" t="s">
         <v>81</v>
       </c>
@@ -21454,7 +20883,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="182" ht="409.5" customHeight="1" spans="1:7">
+    <row r="182" spans="1:7" ht="409.5" customHeight="1">
       <c r="A182" t="s">
         <v>81</v>
       </c>
@@ -21477,7 +20906,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="183" ht="409.5" customHeight="1" spans="1:7">
+    <row r="183" spans="1:7" ht="409.5" customHeight="1">
       <c r="A183" t="s">
         <v>81</v>
       </c>
@@ -21500,7 +20929,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="184" ht="409.5" customHeight="1" spans="1:7">
+    <row r="184" spans="1:7" ht="409.5" customHeight="1">
       <c r="A184" t="s">
         <v>81</v>
       </c>
@@ -21523,7 +20952,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="185" ht="28" customHeight="1" spans="1:7">
+    <row r="185" spans="1:7" ht="28" customHeight="1">
       <c r="A185" t="s">
         <v>81</v>
       </c>
@@ -21546,7 +20975,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="186" ht="77.5" customHeight="1" spans="1:7">
+    <row r="186" spans="1:7" ht="77.5" customHeight="1">
       <c r="A186" t="s">
         <v>81</v>
       </c>
@@ -21592,7 +21021,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="188" ht="56" customHeight="1" spans="1:7">
+    <row r="188" spans="1:7" ht="56" customHeight="1">
       <c r="A188" t="s">
         <v>81</v>
       </c>
@@ -21707,7 +21136,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="193" ht="16.5" customHeight="1" spans="1:7">
+    <row r="193" spans="1:7" ht="16.5" customHeight="1">
       <c r="A193" t="s">
         <v>83</v>
       </c>
@@ -21730,7 +21159,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="194" ht="16.5" customHeight="1" spans="1:7">
+    <row r="194" spans="1:7" ht="16.5" customHeight="1">
       <c r="A194" t="s">
         <v>83</v>
       </c>
@@ -21754,151 +21183,151 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E11" r:id="rId1" display="https://x.com/bang_dream_info/status/2088182616268910792?s=20"/>
-    <hyperlink ref="E23" r:id="rId2" display="https://x.com/Watase_Yuzuki/status/2088065379088347150?s=20"/>
-    <hyperlink ref="E24" r:id="rId3" display="https://x.com/Watase_Yuzuki/status/2088179201157537898?s=20"/>
-    <hyperlink ref="E25" r:id="rId4" display="https://x.com/Watase_Yuzuki/status/2088786673832538180?s=20"/>
-    <hyperlink ref="E26" r:id="rId5" display="https://x.com/sasakirico/status/2087837294204240082?s=20"/>
-    <hyperlink ref="E27" r:id="rId6" display="https://x.com/sasakirico/status/2088071499219644718?s=20"/>
-    <hyperlink ref="E28" r:id="rId7" display="https://x.com/sasakirico/status/2088175045470458281?s=20"/>
-    <hyperlink ref="E29" r:id="rId8" display="https://x.com/sasakirico/status/2088789235675627903?s=20"/>
-    <hyperlink ref="E39" r:id="rId9" display="https://x.com/Kanon_Takao/status/2088627188316930108?s=20"/>
-    <hyperlink ref="E40" r:id="rId10" display="https://x.com/Kanon_Takao/status/2088823105057853755?s=20"/>
-    <hyperlink ref="E41" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E42" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E43" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E44" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E45" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E47" r:id="rId12" display="https://x.com/BABYMETAL_JAPAN/status/2089290445172125822?s=20"/>
-    <hyperlink ref="E61" r:id="rId13" display="https://x.com/Watase_Yuzuki/status/2088894872896061845?s=20"/>
-    <hyperlink ref="E62" r:id="rId14" display="https://x.com/Watase_Yuzuki/status/2089309227349320029?s=20"/>
-    <hyperlink ref="E63" r:id="rId15" display="https://x.com/sasakirico/status/2088912851788599553?s=20"/>
-    <hyperlink ref="E71" r:id="rId16" display="https://spice.eplus.jp/articles/331632"/>
-    <hyperlink ref="E72" r:id="rId17" display="https://natalie.mu/comic/gallery/news/588794/2400212"/>
-    <hyperlink ref="E86" r:id="rId18" display="https://x.com/sasakirico/status/2085925716089266183"/>
-    <hyperlink ref="E87" r:id="rId19" display="https://x.com/sasakirico/status/2086079486609776694"/>
-    <hyperlink ref="E88" r:id="rId20" display="https://x.com/Kanon_Takao/status/2085903933365731590"/>
-    <hyperlink ref="E89" r:id="rId21" display="https://x.com/Kanon_Takao/status/2086081558285602907"/>
-    <hyperlink ref="E90" r:id="rId21" display="https://x.com/Kanon_Takao/status/2086081558285602907"/>
-    <hyperlink ref="E91" r:id="rId22" display="https://www.instagram.com/p/DcD0UQRD0tz/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E92" r:id="rId22" display="https://www.instagram.com/p/DcD0UQRD0tz/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E93" r:id="rId22" display="https://www.instagram.com/p/DcD0UQRD0tz/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E94" r:id="rId23" display="https://x.com/Watase_Yuzuki/status/2085916849448059315"/>
-    <hyperlink ref="E95" r:id="rId24" display="https://x.com/Watase_Yuzuki/status/2086090508334752142"/>
-    <hyperlink ref="E96" r:id="rId25" display="https://x.com/okada_mei0519/status/2085921577095590287"/>
-    <hyperlink ref="E97" r:id="rId26" display="https://x.com/okada_mei0519/status/2086096996683911327"/>
-    <hyperlink ref="E98" r:id="rId27" display="https://x.com/AkaneY_banu/status/2085916706606911998"/>
-    <hyperlink ref="E99" r:id="rId28" display="https://x.com/AkaneY_banu/status/2086085630350823855"/>
-    <hyperlink ref="E100" r:id="rId29" display="https://x.com/diggymo04/status/2086756637206106514"/>
-    <hyperlink ref="E101" r:id="rId30" display="https://x.com/bang_dream_info/status/2086087629016293644?s=20"/>
-    <hyperlink ref="E102" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E103" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E104" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E105" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E106" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E107" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E108" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E109" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E110" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E111" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E112" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E113" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E114" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E115" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E116" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E117" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E118" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E119" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E120" r:id="rId31" display="https://www.instagram.com/p/Db8HQwXDwvq/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E121" r:id="rId32" display="https://x.com/sasakirico/status/2086296289487262100"/>
-    <hyperlink ref="E122" r:id="rId33" display="https://x.com/sasakirico/status/2086433629853643156"/>
-    <hyperlink ref="E123" r:id="rId34" display="https://x.com/Kanon_Takao/status/2086296285284557287"/>
-    <hyperlink ref="E124" r:id="rId35" display="https://x.com/Kanon_Takao/status/2086426948163797373"/>
-    <hyperlink ref="E125" r:id="rId36" display="https://x.com/Kanon_Takao/status/2086439530366951649"/>
-    <hyperlink ref="E126" r:id="rId22" display="https://www.instagram.com/p/DcD0UQRD0tz/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E127" r:id="rId22" display="https://www.instagram.com/p/DcD0UQRD0tz/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E128" r:id="rId37" display="https://x.com/Watase_Yuzuki/status/2086296286849064968"/>
-    <hyperlink ref="E129" r:id="rId38" display="https://x.com/Watase_Yuzuki/status/2086443973284069484"/>
-    <hyperlink ref="E130" r:id="rId38" display="https://x.com/Watase_Yuzuki/status/2086443973284069484"/>
-    <hyperlink ref="E131" r:id="rId39" display="https://x.com/okada_mei0519/status/2086296291844456895"/>
-    <hyperlink ref="E132" r:id="rId40" display="https://x.com/okada_mei0519/status/2086441274924732840"/>
-    <hyperlink ref="E133" r:id="rId40" display="https://x.com/okada_mei0519/status/2086441274924732840"/>
-    <hyperlink ref="E134" r:id="rId41" display="https://x.com/AkaneY_banu/status/2086296289579565468"/>
-    <hyperlink ref="E135" r:id="rId42" display="https://x.com/AkaneY_banu/status/2086445450429927514"/>
-    <hyperlink ref="E136" r:id="rId29" display="https://x.com/diggymo04/status/2086756637206106514"/>
-    <hyperlink ref="E137" r:id="rId43" display="https://x.com/bang_dream_info/status/2086423862389158120"/>
-    <hyperlink ref="E138" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E139" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E140" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E141" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E142" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E143" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E144" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E145" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E146" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E147" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E148" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E149" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E150" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E151" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E152" r:id="rId44" display="https://www.instagram.com/p/DcDn5VLkWq9/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E153" r:id="rId45" display="https://www.instagram.com/p/DeKH76-E51m/?utm_source=ig_web_copy_link&amp;stkn=NTc4MTIwNjQ2YQ=="/>
-    <hyperlink ref="E154" r:id="rId45" display="https://www.instagram.com/p/DeKH76-E51m/?utm_source=ig_web_copy_link&amp;stkn=NTc4MTIwNjQ2YQ=="/>
-    <hyperlink ref="E155" r:id="rId45" display="https://www.instagram.com/p/DeKH76-E51m/?utm_source=ig_web_copy_link&amp;stkn=NTc4MTIwNjQ2YQ=="/>
-    <hyperlink ref="E156" r:id="rId45" display="https://www.instagram.com/p/DeKH76-E51m/?utm_source=ig_web_copy_link&amp;stkn=NTc4MTIwNjQ2YQ=="/>
-    <hyperlink ref="E157" r:id="rId45" display="https://www.instagram.com/p/DeKH76-E51m/?utm_source=ig_web_copy_link&amp;stkn=NTc4MTIwNjQ2YQ=="/>
-    <hyperlink ref="E158" r:id="rId46" display="https://x.com/sasakirico/status/2075939269416522069"/>
-    <hyperlink ref="E159" r:id="rId47" display="https://x.com/sasakirico/status/2076204903970820468"/>
-    <hyperlink ref="E160" r:id="rId48" display="https://x.com/sasakirico/status/2076254262343221681"/>
-    <hyperlink ref="E161" r:id="rId48" display="https://x.com/sasakirico/status/2076254262343221681"/>
-    <hyperlink ref="E162" r:id="rId49" display="https://x.com/sasakirico/status/2076277886252957889"/>
-    <hyperlink ref="E163" r:id="rId50" display="https://x.com/sasakirico/status/2076463436008182016"/>
-    <hyperlink ref="E164" r:id="rId51" display="https://x.com/Kanon_Takao/status/2075924288931287290"/>
-    <hyperlink ref="E165" r:id="rId52" display="https://x.com/Kanon_Takao/status/2076254009778913475"/>
-    <hyperlink ref="E166" r:id="rId52" display="https://x.com/Kanon_Takao/status/2076254009778913475"/>
-    <hyperlink ref="E167" r:id="rId52" display="https://x.com/Kanon_Takao/status/2076254009778913475"/>
-    <hyperlink ref="E168" r:id="rId53" display="https://x.com/Kanon_Takao/status/2076266941216690258"/>
-    <hyperlink ref="E169" r:id="rId53" display="https://x.com/Kanon_Takao/status/2076266941216690258"/>
-    <hyperlink ref="E170" r:id="rId54" display="https://x.com/Kanon_Takao/status/2076625979414564999"/>
-    <hyperlink ref="E171" r:id="rId55" display="https://x.com/Watase_Yuzuki/status/2058857794137391385"/>
-    <hyperlink ref="E172" r:id="rId56" display="https://x.com/Watase_Yuzuki/status/2075938975647473985"/>
-    <hyperlink ref="E173" r:id="rId57" display="https://x.com/Watase_Yuzuki/status/2076261984497275169"/>
-    <hyperlink ref="E174" r:id="rId57" display="https://x.com/Watase_Yuzuki/status/2076261984497275169"/>
-    <hyperlink ref="E175" r:id="rId58" display="https://x.com/okada_mei0519/status/2075941193553485996"/>
-    <hyperlink ref="E176" r:id="rId59" display="https://x.com/okada_mei0519/status/2076107095494246870"/>
-    <hyperlink ref="E177" r:id="rId60" display="https://x.com/okada_mei0519/status/2076262462589120870"/>
-    <hyperlink ref="E178" r:id="rId61" display="https://www.instagram.com/p/Dau7ooBgci_/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E179" r:id="rId61" display="https://www.instagram.com/p/Dau7ooBgci_/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E180" r:id="rId61" display="https://www.instagram.com/p/Dau7ooBgci_/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E181" r:id="rId61" display="https://www.instagram.com/p/Dau7ooBgci_/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E182" r:id="rId61" display="https://www.instagram.com/p/Dau7ooBgci_/?utm_source=ig_web_copy_link&amp;stkn=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E183" r:id="rId62" display="https://x.com/AkaneY_banu/status/2076108394826781127"/>
-    <hyperlink ref="E184" r:id="rId63" display="https://x.com/AkaneY_banu/status/2076263634339315928"/>
-    <hyperlink ref="E185" r:id="rId64" display="https://x.com/nananananachume/status/2076311484976824767"/>
-    <hyperlink ref="E186" r:id="rId65" display="https://x.com/AkaneY_banu/status/2076323039730671747"/>
-    <hyperlink ref="E187" r:id="rId66" display="https://x.com/AkaneY_banu/status/2076526436589199755"/>
-    <hyperlink ref="E188" r:id="rId67" display="https://x.com/diggymo04/status/2076313991958446573"/>
-    <hyperlink ref="E189" r:id="rId68" display="https://x.com/bang_dream_info/status/2070141621300326743"/>
-    <hyperlink ref="E190" r:id="rId69" display="https://x.com/bang_dream_info/status/2076264406523191448"/>
-    <hyperlink ref="E191" r:id="rId70" display="https://x.com/bang_dream_info/status/2076265291689115979"/>
-    <hyperlink ref="E192" r:id="rId71" display="https://x.com/AkaneY_banu/status/2108008985614016963"/>
-    <hyperlink ref="E193" r:id="rId72" display="https://www.instagram.com/p/DeN_u45IFHx/?utm_source=ig_web_copy_link&amp;cplk=MzRlODBiNWFlZA==&amp;srtk=MzRlODBiNWFlZA=="/>
-    <hyperlink ref="E194" r:id="rId72" display="https://www.instagram.com/p/DeN_u45IFHx/?utm_source=ig_web_copy_link&amp;cplk=MzRlODBiNWFlZA==&amp;srtk=MzRlODBiNWFlZA=="/>
+    <hyperlink ref="E11" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="E23" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
+    <hyperlink ref="E24" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
+    <hyperlink ref="E25" r:id="rId4" xr:uid="{00000000-0004-0000-0900-000003000000}"/>
+    <hyperlink ref="E26" r:id="rId5" xr:uid="{00000000-0004-0000-0900-000004000000}"/>
+    <hyperlink ref="E27" r:id="rId6" xr:uid="{00000000-0004-0000-0900-000005000000}"/>
+    <hyperlink ref="E28" r:id="rId7" xr:uid="{00000000-0004-0000-0900-000006000000}"/>
+    <hyperlink ref="E29" r:id="rId8" xr:uid="{00000000-0004-0000-0900-000007000000}"/>
+    <hyperlink ref="E39" r:id="rId9" xr:uid="{00000000-0004-0000-0900-000008000000}"/>
+    <hyperlink ref="E40" r:id="rId10" xr:uid="{00000000-0004-0000-0900-000009000000}"/>
+    <hyperlink ref="E41" r:id="rId11" xr:uid="{00000000-0004-0000-0900-00000A000000}"/>
+    <hyperlink ref="E42" r:id="rId12" xr:uid="{00000000-0004-0000-0900-00000B000000}"/>
+    <hyperlink ref="E43" r:id="rId13" xr:uid="{00000000-0004-0000-0900-00000C000000}"/>
+    <hyperlink ref="E44" r:id="rId14" xr:uid="{00000000-0004-0000-0900-00000D000000}"/>
+    <hyperlink ref="E45" r:id="rId15" xr:uid="{00000000-0004-0000-0900-00000E000000}"/>
+    <hyperlink ref="E47" r:id="rId16" xr:uid="{00000000-0004-0000-0900-00000F000000}"/>
+    <hyperlink ref="E61" r:id="rId17" xr:uid="{00000000-0004-0000-0900-000010000000}"/>
+    <hyperlink ref="E62" r:id="rId18" xr:uid="{00000000-0004-0000-0900-000011000000}"/>
+    <hyperlink ref="E63" r:id="rId19" xr:uid="{00000000-0004-0000-0900-000012000000}"/>
+    <hyperlink ref="E71" r:id="rId20" xr:uid="{00000000-0004-0000-0900-000013000000}"/>
+    <hyperlink ref="E72" r:id="rId21" xr:uid="{00000000-0004-0000-0900-000014000000}"/>
+    <hyperlink ref="E86" r:id="rId22" xr:uid="{00000000-0004-0000-0900-000015000000}"/>
+    <hyperlink ref="E87" r:id="rId23" xr:uid="{00000000-0004-0000-0900-000016000000}"/>
+    <hyperlink ref="E88" r:id="rId24" xr:uid="{00000000-0004-0000-0900-000017000000}"/>
+    <hyperlink ref="E89" r:id="rId25" xr:uid="{00000000-0004-0000-0900-000018000000}"/>
+    <hyperlink ref="E90" r:id="rId26" xr:uid="{00000000-0004-0000-0900-000019000000}"/>
+    <hyperlink ref="E91" r:id="rId27" xr:uid="{00000000-0004-0000-0900-00001A000000}"/>
+    <hyperlink ref="E92" r:id="rId28" xr:uid="{00000000-0004-0000-0900-00001B000000}"/>
+    <hyperlink ref="E93" r:id="rId29" xr:uid="{00000000-0004-0000-0900-00001C000000}"/>
+    <hyperlink ref="E94" r:id="rId30" xr:uid="{00000000-0004-0000-0900-00001D000000}"/>
+    <hyperlink ref="E95" r:id="rId31" xr:uid="{00000000-0004-0000-0900-00001E000000}"/>
+    <hyperlink ref="E96" r:id="rId32" xr:uid="{00000000-0004-0000-0900-00001F000000}"/>
+    <hyperlink ref="E97" r:id="rId33" xr:uid="{00000000-0004-0000-0900-000020000000}"/>
+    <hyperlink ref="E98" r:id="rId34" xr:uid="{00000000-0004-0000-0900-000021000000}"/>
+    <hyperlink ref="E99" r:id="rId35" xr:uid="{00000000-0004-0000-0900-000022000000}"/>
+    <hyperlink ref="E100" r:id="rId36" xr:uid="{00000000-0004-0000-0900-000023000000}"/>
+    <hyperlink ref="E101" r:id="rId37" xr:uid="{00000000-0004-0000-0900-000024000000}"/>
+    <hyperlink ref="E102" r:id="rId38" xr:uid="{00000000-0004-0000-0900-000025000000}"/>
+    <hyperlink ref="E103" r:id="rId39" xr:uid="{00000000-0004-0000-0900-000026000000}"/>
+    <hyperlink ref="E104" r:id="rId40" xr:uid="{00000000-0004-0000-0900-000027000000}"/>
+    <hyperlink ref="E105" r:id="rId41" xr:uid="{00000000-0004-0000-0900-000028000000}"/>
+    <hyperlink ref="E106" r:id="rId42" xr:uid="{00000000-0004-0000-0900-000029000000}"/>
+    <hyperlink ref="E107" r:id="rId43" xr:uid="{00000000-0004-0000-0900-00002A000000}"/>
+    <hyperlink ref="E108" r:id="rId44" xr:uid="{00000000-0004-0000-0900-00002B000000}"/>
+    <hyperlink ref="E109" r:id="rId45" xr:uid="{00000000-0004-0000-0900-00002C000000}"/>
+    <hyperlink ref="E110" r:id="rId46" xr:uid="{00000000-0004-0000-0900-00002D000000}"/>
+    <hyperlink ref="E111" r:id="rId47" xr:uid="{00000000-0004-0000-0900-00002E000000}"/>
+    <hyperlink ref="E112" r:id="rId48" xr:uid="{00000000-0004-0000-0900-00002F000000}"/>
+    <hyperlink ref="E113" r:id="rId49" xr:uid="{00000000-0004-0000-0900-000030000000}"/>
+    <hyperlink ref="E114" r:id="rId50" xr:uid="{00000000-0004-0000-0900-000031000000}"/>
+    <hyperlink ref="E115" r:id="rId51" xr:uid="{00000000-0004-0000-0900-000032000000}"/>
+    <hyperlink ref="E116" r:id="rId52" xr:uid="{00000000-0004-0000-0900-000033000000}"/>
+    <hyperlink ref="E117" r:id="rId53" xr:uid="{00000000-0004-0000-0900-000034000000}"/>
+    <hyperlink ref="E118" r:id="rId54" xr:uid="{00000000-0004-0000-0900-000035000000}"/>
+    <hyperlink ref="E119" r:id="rId55" xr:uid="{00000000-0004-0000-0900-000036000000}"/>
+    <hyperlink ref="E120" r:id="rId56" xr:uid="{00000000-0004-0000-0900-000037000000}"/>
+    <hyperlink ref="E121" r:id="rId57" xr:uid="{00000000-0004-0000-0900-000038000000}"/>
+    <hyperlink ref="E122" r:id="rId58" xr:uid="{00000000-0004-0000-0900-000039000000}"/>
+    <hyperlink ref="E123" r:id="rId59" xr:uid="{00000000-0004-0000-0900-00003A000000}"/>
+    <hyperlink ref="E124" r:id="rId60" xr:uid="{00000000-0004-0000-0900-00003B000000}"/>
+    <hyperlink ref="E125" r:id="rId61" xr:uid="{00000000-0004-0000-0900-00003C000000}"/>
+    <hyperlink ref="E126" r:id="rId62" xr:uid="{00000000-0004-0000-0900-00003D000000}"/>
+    <hyperlink ref="E127" r:id="rId63" xr:uid="{00000000-0004-0000-0900-00003E000000}"/>
+    <hyperlink ref="E128" r:id="rId64" xr:uid="{00000000-0004-0000-0900-00003F000000}"/>
+    <hyperlink ref="E129" r:id="rId65" xr:uid="{00000000-0004-0000-0900-000040000000}"/>
+    <hyperlink ref="E130" r:id="rId66" xr:uid="{00000000-0004-0000-0900-000041000000}"/>
+    <hyperlink ref="E131" r:id="rId67" xr:uid="{00000000-0004-0000-0900-000042000000}"/>
+    <hyperlink ref="E132" r:id="rId68" xr:uid="{00000000-0004-0000-0900-000043000000}"/>
+    <hyperlink ref="E133" r:id="rId69" xr:uid="{00000000-0004-0000-0900-000044000000}"/>
+    <hyperlink ref="E134" r:id="rId70" xr:uid="{00000000-0004-0000-0900-000045000000}"/>
+    <hyperlink ref="E135" r:id="rId71" xr:uid="{00000000-0004-0000-0900-000046000000}"/>
+    <hyperlink ref="E136" r:id="rId72" xr:uid="{00000000-0004-0000-0900-000047000000}"/>
+    <hyperlink ref="E137" r:id="rId73" xr:uid="{00000000-0004-0000-0900-000048000000}"/>
+    <hyperlink ref="E138" r:id="rId74" xr:uid="{00000000-0004-0000-0900-000049000000}"/>
+    <hyperlink ref="E139" r:id="rId75" xr:uid="{00000000-0004-0000-0900-00004A000000}"/>
+    <hyperlink ref="E140" r:id="rId76" xr:uid="{00000000-0004-0000-0900-00004B000000}"/>
+    <hyperlink ref="E141" r:id="rId77" xr:uid="{00000000-0004-0000-0900-00004C000000}"/>
+    <hyperlink ref="E142" r:id="rId78" xr:uid="{00000000-0004-0000-0900-00004D000000}"/>
+    <hyperlink ref="E143" r:id="rId79" xr:uid="{00000000-0004-0000-0900-00004E000000}"/>
+    <hyperlink ref="E144" r:id="rId80" xr:uid="{00000000-0004-0000-0900-00004F000000}"/>
+    <hyperlink ref="E145" r:id="rId81" xr:uid="{00000000-0004-0000-0900-000050000000}"/>
+    <hyperlink ref="E146" r:id="rId82" xr:uid="{00000000-0004-0000-0900-000051000000}"/>
+    <hyperlink ref="E147" r:id="rId83" xr:uid="{00000000-0004-0000-0900-000052000000}"/>
+    <hyperlink ref="E148" r:id="rId84" xr:uid="{00000000-0004-0000-0900-000053000000}"/>
+    <hyperlink ref="E149" r:id="rId85" xr:uid="{00000000-0004-0000-0900-000054000000}"/>
+    <hyperlink ref="E150" r:id="rId86" xr:uid="{00000000-0004-0000-0900-000055000000}"/>
+    <hyperlink ref="E151" r:id="rId87" xr:uid="{00000000-0004-0000-0900-000056000000}"/>
+    <hyperlink ref="E152" r:id="rId88" xr:uid="{00000000-0004-0000-0900-000057000000}"/>
+    <hyperlink ref="E153" r:id="rId89" xr:uid="{00000000-0004-0000-0900-000058000000}"/>
+    <hyperlink ref="E154" r:id="rId90" xr:uid="{00000000-0004-0000-0900-000059000000}"/>
+    <hyperlink ref="E155" r:id="rId91" xr:uid="{00000000-0004-0000-0900-00005A000000}"/>
+    <hyperlink ref="E156" r:id="rId92" xr:uid="{00000000-0004-0000-0900-00005B000000}"/>
+    <hyperlink ref="E157" r:id="rId93" xr:uid="{00000000-0004-0000-0900-00005C000000}"/>
+    <hyperlink ref="E158" r:id="rId94" xr:uid="{00000000-0004-0000-0900-00005D000000}"/>
+    <hyperlink ref="E159" r:id="rId95" xr:uid="{00000000-0004-0000-0900-00005E000000}"/>
+    <hyperlink ref="E160" r:id="rId96" xr:uid="{00000000-0004-0000-0900-00005F000000}"/>
+    <hyperlink ref="E161" r:id="rId97" xr:uid="{00000000-0004-0000-0900-000060000000}"/>
+    <hyperlink ref="E162" r:id="rId98" xr:uid="{00000000-0004-0000-0900-000061000000}"/>
+    <hyperlink ref="E163" r:id="rId99" xr:uid="{00000000-0004-0000-0900-000062000000}"/>
+    <hyperlink ref="E164" r:id="rId100" xr:uid="{00000000-0004-0000-0900-000063000000}"/>
+    <hyperlink ref="E165" r:id="rId101" xr:uid="{00000000-0004-0000-0900-000064000000}"/>
+    <hyperlink ref="E166" r:id="rId102" xr:uid="{00000000-0004-0000-0900-000065000000}"/>
+    <hyperlink ref="E167" r:id="rId103" xr:uid="{00000000-0004-0000-0900-000066000000}"/>
+    <hyperlink ref="E168" r:id="rId104" xr:uid="{00000000-0004-0000-0900-000067000000}"/>
+    <hyperlink ref="E169" r:id="rId105" xr:uid="{00000000-0004-0000-0900-000068000000}"/>
+    <hyperlink ref="E170" r:id="rId106" xr:uid="{00000000-0004-0000-0900-000069000000}"/>
+    <hyperlink ref="E171" r:id="rId107" xr:uid="{00000000-0004-0000-0900-00006A000000}"/>
+    <hyperlink ref="E172" r:id="rId108" xr:uid="{00000000-0004-0000-0900-00006B000000}"/>
+    <hyperlink ref="E173" r:id="rId109" xr:uid="{00000000-0004-0000-0900-00006C000000}"/>
+    <hyperlink ref="E174" r:id="rId110" xr:uid="{00000000-0004-0000-0900-00006D000000}"/>
+    <hyperlink ref="E175" r:id="rId111" xr:uid="{00000000-0004-0000-0900-00006E000000}"/>
+    <hyperlink ref="E176" r:id="rId112" xr:uid="{00000000-0004-0000-0900-00006F000000}"/>
+    <hyperlink ref="E177" r:id="rId113" xr:uid="{00000000-0004-0000-0900-000070000000}"/>
+    <hyperlink ref="E178" r:id="rId114" xr:uid="{00000000-0004-0000-0900-000071000000}"/>
+    <hyperlink ref="E179" r:id="rId115" xr:uid="{00000000-0004-0000-0900-000072000000}"/>
+    <hyperlink ref="E180" r:id="rId116" xr:uid="{00000000-0004-0000-0900-000073000000}"/>
+    <hyperlink ref="E181" r:id="rId117" xr:uid="{00000000-0004-0000-0900-000074000000}"/>
+    <hyperlink ref="E182" r:id="rId118" xr:uid="{00000000-0004-0000-0900-000075000000}"/>
+    <hyperlink ref="E183" r:id="rId119" xr:uid="{00000000-0004-0000-0900-000076000000}"/>
+    <hyperlink ref="E184" r:id="rId120" xr:uid="{00000000-0004-0000-0900-000077000000}"/>
+    <hyperlink ref="E185" r:id="rId121" xr:uid="{00000000-0004-0000-0900-000078000000}"/>
+    <hyperlink ref="E186" r:id="rId122" xr:uid="{00000000-0004-0000-0900-000079000000}"/>
+    <hyperlink ref="E187" r:id="rId123" xr:uid="{00000000-0004-0000-0900-00007A000000}"/>
+    <hyperlink ref="E188" r:id="rId124" xr:uid="{00000000-0004-0000-0900-00007B000000}"/>
+    <hyperlink ref="E189" r:id="rId125" xr:uid="{00000000-0004-0000-0900-00007C000000}"/>
+    <hyperlink ref="E190" r:id="rId126" xr:uid="{00000000-0004-0000-0900-00007D000000}"/>
+    <hyperlink ref="E191" r:id="rId127" xr:uid="{00000000-0004-0000-0900-00007E000000}"/>
+    <hyperlink ref="E192" r:id="rId128" xr:uid="{00000000-0004-0000-0900-00007F000000}"/>
+    <hyperlink ref="E193" r:id="rId129" xr:uid="{00000000-0004-0000-0900-000080000000}"/>
+    <hyperlink ref="E194" r:id="rId130" xr:uid="{00000000-0004-0000-0900-000081000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:E560"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="31.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="16.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -24726,25 +24155,24 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:K857"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.8181818181818" style="12" customWidth="1"/>
-    <col min="2" max="2" width="92.8181818181818" customWidth="1"/>
-    <col min="4" max="4" width="62.7272727272727" customWidth="1"/>
-    <col min="6" max="6" width="7.18181818181818" customWidth="1"/>
-    <col min="7" max="7" width="22.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="12.7272727272727" customWidth="1"/>
-    <col min="9" max="9" width="111.818181818182" customWidth="1"/>
-    <col min="10" max="10" width="21.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="92.81640625" customWidth="1"/>
+    <col min="4" max="4" width="62.7265625" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" customWidth="1"/>
+    <col min="7" max="7" width="22.81640625" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="9" width="111.81640625" customWidth="1"/>
+    <col min="10" max="10" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -25250,7 +24678,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="20" ht="98" customHeight="1" spans="1:10">
+    <row r="20" spans="1:10" ht="98" customHeight="1">
       <c r="A20" s="8">
         <v>45301</v>
       </c>
@@ -25273,7 +24701,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="21" ht="98" customHeight="1" spans="1:10">
+    <row r="21" spans="1:10" ht="98" customHeight="1">
       <c r="A21" s="8">
         <v>45301</v>
       </c>
@@ -25296,7 +24724,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="22" ht="98" customHeight="1" spans="1:10">
+    <row r="22" spans="1:10" ht="98" customHeight="1">
       <c r="A22" s="8">
         <v>45301</v>
       </c>
@@ -25322,7 +24750,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="23" ht="98" customHeight="1" spans="1:10">
+    <row r="23" spans="1:10" ht="98" customHeight="1">
       <c r="A23" s="8">
         <v>45301</v>
       </c>
@@ -25348,7 +24776,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="24" ht="124" customHeight="1" spans="1:10">
+    <row r="24" spans="1:10" ht="124" customHeight="1">
       <c r="A24" s="8">
         <v>45323</v>
       </c>
@@ -25371,7 +24799,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="25" ht="124" customHeight="1" spans="1:10">
+    <row r="25" spans="1:10" ht="124" customHeight="1">
       <c r="A25" s="8">
         <v>45323</v>
       </c>
@@ -25394,7 +24822,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="26" ht="124" customHeight="1" spans="1:10">
+    <row r="26" spans="1:10" ht="124" customHeight="1">
       <c r="A26" s="8">
         <v>45323</v>
       </c>
@@ -25417,7 +24845,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="27" ht="124" customHeight="1" spans="1:10">
+    <row r="27" spans="1:10" ht="124" customHeight="1">
       <c r="A27" s="8">
         <v>45323</v>
       </c>
@@ -25440,7 +24868,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="28" ht="124" customHeight="1" spans="1:10">
+    <row r="28" spans="1:10" ht="124" customHeight="1">
       <c r="A28" s="8">
         <v>45323</v>
       </c>
@@ -25463,7 +24891,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="29" ht="124" customHeight="1" spans="1:10">
+    <row r="29" spans="1:10" ht="124" customHeight="1">
       <c r="A29" s="8">
         <v>45323</v>
       </c>
@@ -25486,7 +24914,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="30" ht="124" customHeight="1" spans="1:10">
+    <row r="30" spans="1:10" ht="124" customHeight="1">
       <c r="A30" s="8">
         <v>45323</v>
       </c>
@@ -25509,7 +24937,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="31" ht="124" customHeight="1" spans="1:10">
+    <row r="31" spans="1:10" ht="124" customHeight="1">
       <c r="A31" s="8">
         <v>45323</v>
       </c>
@@ -25533,7 +24961,7 @@
       </c>
       <c r="H31" s="15"/>
     </row>
-    <row r="32" ht="124" customHeight="1" spans="1:10">
+    <row r="32" spans="1:10" ht="124" customHeight="1">
       <c r="A32" s="8">
         <v>45323</v>
       </c>
@@ -25560,7 +24988,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="33" ht="197.5" customHeight="1" spans="1:10">
+    <row r="33" spans="1:10" ht="197.5" customHeight="1">
       <c r="A33" s="8">
         <v>45323</v>
       </c>
@@ -25586,7 +25014,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="34" ht="197.5" customHeight="1" spans="1:10">
+    <row r="34" spans="1:10" ht="197.5" customHeight="1">
       <c r="A34" s="8">
         <v>45336</v>
       </c>
@@ -25609,7 +25037,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="35" ht="197.5" customHeight="1" spans="1:10">
+    <row r="35" spans="1:10" ht="197.5" customHeight="1">
       <c r="A35" s="8">
         <v>45336</v>
       </c>
@@ -25633,7 +25061,7 @@
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" ht="197.5" customHeight="1" spans="1:10">
+    <row r="36" spans="1:10" ht="197.5" customHeight="1">
       <c r="A36" s="8">
         <v>45336</v>
       </c>
@@ -25656,7 +25084,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="37" ht="197.5" customHeight="1" spans="1:10">
+    <row r="37" spans="1:10" ht="197.5" customHeight="1">
       <c r="A37" s="8">
         <v>45336</v>
       </c>
@@ -25679,7 +25107,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="38" ht="197.5" customHeight="1" spans="1:10">
+    <row r="38" spans="1:10" ht="197.5" customHeight="1">
       <c r="A38" s="8">
         <v>45336</v>
       </c>
@@ -25705,7 +25133,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="39" ht="197.5" customHeight="1" spans="1:10">
+    <row r="39" spans="1:10" ht="197.5" customHeight="1">
       <c r="A39" s="8">
         <v>45336</v>
       </c>
@@ -25732,7 +25160,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="40" ht="197.5" customHeight="1" spans="1:10">
+    <row r="40" spans="1:10" ht="197.5" customHeight="1">
       <c r="A40" s="8">
         <v>45342</v>
       </c>
@@ -25755,7 +25183,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="41" ht="197.5" customHeight="1" spans="1:10">
+    <row r="41" spans="1:10" ht="197.5" customHeight="1">
       <c r="A41" s="8">
         <v>45342</v>
       </c>
@@ -25778,7 +25206,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="42" ht="58.5" customHeight="1" spans="1:10">
+    <row r="42" spans="1:10" ht="58.5" customHeight="1">
       <c r="A42" s="8">
         <v>45342</v>
       </c>
@@ -25801,7 +25229,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="43" ht="58.5" customHeight="1" spans="1:10">
+    <row r="43" spans="1:10" ht="58.5" customHeight="1">
       <c r="A43" s="8">
         <v>45342</v>
       </c>
@@ -25828,7 +25256,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="44" ht="84" customHeight="1" spans="1:10">
+    <row r="44" spans="1:10" ht="84" customHeight="1">
       <c r="A44" s="8">
         <v>45342</v>
       </c>
@@ -25851,7 +25279,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="45" ht="84" customHeight="1" spans="1:10">
+    <row r="45" spans="1:10" ht="84" customHeight="1">
       <c r="A45" s="8">
         <v>45342</v>
       </c>
@@ -25874,7 +25302,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="46" ht="84" customHeight="1" spans="1:10">
+    <row r="46" spans="1:10" ht="84" customHeight="1">
       <c r="A46" s="8">
         <v>45342</v>
       </c>
@@ -25897,7 +25325,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="47" ht="84" customHeight="1" spans="1:10">
+    <row r="47" spans="1:10" ht="84" customHeight="1">
       <c r="A47" s="8">
         <v>45342</v>
       </c>
@@ -25920,7 +25348,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="48" ht="84" customHeight="1" spans="1:10">
+    <row r="48" spans="1:10" ht="84" customHeight="1">
       <c r="A48" s="8">
         <v>45342</v>
       </c>
@@ -25943,7 +25371,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="49" ht="84" customHeight="1" spans="1:10">
+    <row r="49" spans="1:10" ht="84" customHeight="1">
       <c r="A49" s="8">
         <v>45342</v>
       </c>
@@ -25966,7 +25394,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="50" ht="105.5" customHeight="1" spans="1:10">
+    <row r="50" spans="1:10" ht="105.5" customHeight="1">
       <c r="A50" s="8">
         <v>45342</v>
       </c>
@@ -25989,7 +25417,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="51" ht="105.5" customHeight="1" spans="1:10">
+    <row r="51" spans="1:10" ht="105.5" customHeight="1">
       <c r="A51" s="8">
         <v>45342</v>
       </c>
@@ -26012,7 +25440,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="52" ht="105.5" customHeight="1" spans="1:10">
+    <row r="52" spans="1:10" ht="105.5" customHeight="1">
       <c r="A52" s="8">
         <v>45342</v>
       </c>
@@ -26035,7 +25463,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="53" ht="126" customHeight="1" spans="1:10">
+    <row r="53" spans="1:10" ht="126" customHeight="1">
       <c r="A53" s="8">
         <v>45342</v>
       </c>
@@ -26058,7 +25486,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="54" ht="126" customHeight="1" spans="1:10">
+    <row r="54" spans="1:10" ht="126" customHeight="1">
       <c r="A54" s="8">
         <v>45342</v>
       </c>
@@ -26081,7 +25509,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="55" ht="126" customHeight="1" spans="1:10">
+    <row r="55" spans="1:10" ht="126" customHeight="1">
       <c r="A55" s="8">
         <v>45342</v>
       </c>
@@ -26104,7 +25532,7 @@
         <v>2106</v>
       </c>
     </row>
-    <row r="56" ht="126" customHeight="1" spans="1:10">
+    <row r="56" spans="1:10" ht="126" customHeight="1">
       <c r="A56" s="8">
         <v>45342</v>
       </c>
@@ -26127,7 +25555,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="57" ht="126" customHeight="1" spans="1:10">
+    <row r="57" spans="1:10" ht="126" customHeight="1">
       <c r="A57" s="8">
         <v>45342</v>
       </c>
@@ -26153,7 +25581,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="58" ht="47" customHeight="1" spans="1:10">
+    <row r="58" spans="1:10" ht="47" customHeight="1">
       <c r="A58" s="8">
         <v>45342</v>
       </c>
@@ -26179,7 +25607,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="59" ht="47" customHeight="1" spans="1:10">
+    <row r="59" spans="1:10" ht="47" customHeight="1">
       <c r="A59" s="8">
         <v>45342</v>
       </c>
@@ -26205,7 +25633,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="60" ht="47" customHeight="1" spans="1:10">
+    <row r="60" spans="1:10" ht="47" customHeight="1">
       <c r="A60" s="8">
         <v>45342</v>
       </c>
@@ -26231,7 +25659,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="61" ht="84" customHeight="1" spans="1:10">
+    <row r="61" spans="1:10" ht="84" customHeight="1">
       <c r="A61" s="8">
         <v>45343</v>
       </c>
@@ -26254,7 +25682,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="62" ht="84" customHeight="1" spans="1:10">
+    <row r="62" spans="1:10" ht="84" customHeight="1">
       <c r="A62" s="8">
         <v>45343</v>
       </c>
@@ -26277,7 +25705,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="63" ht="84" customHeight="1" spans="1:10">
+    <row r="63" spans="1:10" ht="84" customHeight="1">
       <c r="A63" s="8">
         <v>45343</v>
       </c>
@@ -26349,7 +25777,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="66" ht="84" customHeight="1" spans="1:10">
+    <row r="66" spans="1:10" ht="84" customHeight="1">
       <c r="A66" s="8">
         <v>45352</v>
       </c>
@@ -26372,7 +25800,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="67" ht="84" customHeight="1" spans="1:10">
+    <row r="67" spans="1:10" ht="84" customHeight="1">
       <c r="A67" s="8">
         <v>45352</v>
       </c>
@@ -26395,7 +25823,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="68" ht="84" customHeight="1" spans="1:10">
+    <row r="68" spans="1:10" ht="84" customHeight="1">
       <c r="A68" s="8">
         <v>45352</v>
       </c>
@@ -26418,7 +25846,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="69" ht="84" customHeight="1" spans="1:10">
+    <row r="69" spans="1:10" ht="84" customHeight="1">
       <c r="A69" s="8">
         <v>45352</v>
       </c>
@@ -26441,7 +25869,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="70" ht="84" customHeight="1" spans="1:10">
+    <row r="70" spans="1:10" ht="84" customHeight="1">
       <c r="A70" s="8">
         <v>45352</v>
       </c>
@@ -26464,7 +25892,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="71" ht="154" customHeight="1" spans="1:10">
+    <row r="71" spans="1:10" ht="154" customHeight="1">
       <c r="A71" s="8">
         <v>45352</v>
       </c>
@@ -26487,7 +25915,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="72" ht="154" customHeight="1" spans="1:10">
+    <row r="72" spans="1:10" ht="154" customHeight="1">
       <c r="A72" s="8">
         <v>45352</v>
       </c>
@@ -26510,7 +25938,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="73" ht="154" customHeight="1" spans="1:10">
+    <row r="73" spans="1:10" ht="154" customHeight="1">
       <c r="A73" s="8">
         <v>45352</v>
       </c>
@@ -26533,7 +25961,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="74" ht="154" customHeight="1" spans="1:10">
+    <row r="74" spans="1:10" ht="154" customHeight="1">
       <c r="A74" s="8">
         <v>45352</v>
       </c>
@@ -26556,7 +25984,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="75" ht="154" customHeight="1" spans="1:10">
+    <row r="75" spans="1:10" ht="154" customHeight="1">
       <c r="A75" s="8">
         <v>45352</v>
       </c>
@@ -26579,7 +26007,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="76" ht="154" customHeight="1" spans="1:10">
+    <row r="76" spans="1:10" ht="154" customHeight="1">
       <c r="A76" s="8">
         <v>45352</v>
       </c>
@@ -26602,7 +26030,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="77" ht="154" customHeight="1" spans="1:10">
+    <row r="77" spans="1:10" ht="154" customHeight="1">
       <c r="A77" s="8">
         <v>45352</v>
       </c>
@@ -26628,7 +26056,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="78" ht="154" customHeight="1" spans="1:10">
+    <row r="78" spans="1:10" ht="154" customHeight="1">
       <c r="A78" s="8">
         <v>45352</v>
       </c>
@@ -26654,7 +26082,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="79" ht="140" customHeight="1" spans="1:10">
+    <row r="79" spans="1:10" ht="140" customHeight="1">
       <c r="A79" s="8">
         <v>45352</v>
       </c>
@@ -26680,7 +26108,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="80" ht="140" customHeight="1" spans="1:10">
+    <row r="80" spans="1:10" ht="140" customHeight="1">
       <c r="A80" s="8">
         <v>45352</v>
       </c>
@@ -26706,7 +26134,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="81" ht="70" customHeight="1" spans="1:10">
+    <row r="81" spans="1:10" ht="70" customHeight="1">
       <c r="A81" s="8">
         <v>45360</v>
       </c>
@@ -26730,7 +26158,7 @@
       </c>
       <c r="H81" s="15"/>
     </row>
-    <row r="82" ht="70" customHeight="1" spans="1:10">
+    <row r="82" spans="1:10" ht="70" customHeight="1">
       <c r="A82" s="8">
         <v>45360</v>
       </c>
@@ -26808,7 +26236,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="85" ht="98" customHeight="1" spans="1:10">
+    <row r="85" spans="1:10" ht="98" customHeight="1">
       <c r="A85" s="8">
         <v>45374</v>
       </c>
@@ -26834,7 +26262,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="86" ht="98" customHeight="1" spans="1:10">
+    <row r="86" spans="1:10" ht="98" customHeight="1">
       <c r="A86" s="8">
         <v>45374</v>
       </c>
@@ -26860,7 +26288,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="87" ht="98" customHeight="1" spans="1:10">
+    <row r="87" spans="1:10" ht="98" customHeight="1">
       <c r="A87" s="8">
         <v>45374</v>
       </c>
@@ -26883,7 +26311,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="88" ht="98" customHeight="1" spans="1:10">
+    <row r="88" spans="1:10" ht="98" customHeight="1">
       <c r="A88" s="8">
         <v>45374</v>
       </c>
@@ -28094,7 +27522,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="137" ht="196" customHeight="1" spans="1:10">
+    <row r="137" spans="1:10" ht="196" customHeight="1">
       <c r="A137" s="8">
         <v>45374</v>
       </c>
@@ -28117,7 +27545,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="138" ht="196" customHeight="1" spans="1:10">
+    <row r="138" spans="1:10" ht="196" customHeight="1">
       <c r="A138" s="8">
         <v>45374</v>
       </c>
@@ -28140,7 +27568,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="139" ht="196" customHeight="1" spans="1:10">
+    <row r="139" spans="1:10" ht="196" customHeight="1">
       <c r="A139" s="8">
         <v>45374</v>
       </c>
@@ -28163,7 +27591,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="140" ht="196" customHeight="1" spans="1:10">
+    <row r="140" spans="1:10" ht="196" customHeight="1">
       <c r="A140" s="8">
         <v>45374</v>
       </c>
@@ -28186,7 +27614,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="141" ht="196" customHeight="1" spans="1:10">
+    <row r="141" spans="1:10" ht="196" customHeight="1">
       <c r="A141" s="8">
         <v>45374</v>
       </c>
@@ -28209,7 +27637,7 @@
         <v>2256</v>
       </c>
     </row>
-    <row r="142" ht="196" customHeight="1" spans="1:10">
+    <row r="142" spans="1:10" ht="196" customHeight="1">
       <c r="A142" s="8">
         <v>45374</v>
       </c>
@@ -28232,7 +27660,7 @@
         <v>2257</v>
       </c>
     </row>
-    <row r="143" ht="196" customHeight="1" spans="1:10">
+    <row r="143" spans="1:10" ht="196" customHeight="1">
       <c r="A143" s="8">
         <v>45374</v>
       </c>
@@ -28255,7 +27683,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="144" ht="196" customHeight="1" spans="1:10">
+    <row r="144" spans="1:10" ht="196" customHeight="1">
       <c r="A144" s="8">
         <v>45374</v>
       </c>
@@ -28278,7 +27706,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="145" ht="196" customHeight="1" spans="1:10">
+    <row r="145" spans="1:10" ht="196" customHeight="1">
       <c r="A145" s="8">
         <v>45374</v>
       </c>
@@ -28301,7 +27729,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="146" ht="196" customHeight="1" spans="1:10">
+    <row r="146" spans="1:10" ht="196" customHeight="1">
       <c r="A146" s="8">
         <v>45374</v>
       </c>
@@ -28324,7 +27752,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="147" ht="84" customHeight="1" spans="1:10">
+    <row r="147" spans="1:10" ht="84" customHeight="1">
       <c r="A147" s="8">
         <v>45374</v>
       </c>
@@ -28347,7 +27775,7 @@
         <v>2262</v>
       </c>
     </row>
-    <row r="148" ht="84" customHeight="1" spans="1:10">
+    <row r="148" spans="1:10" ht="84" customHeight="1">
       <c r="A148" s="8">
         <v>45374</v>
       </c>
@@ -28370,7 +27798,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="149" ht="84" customHeight="1" spans="1:10">
+    <row r="149" spans="1:10" ht="84" customHeight="1">
       <c r="A149" s="8">
         <v>45409</v>
       </c>
@@ -28393,7 +27821,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="150" ht="84" customHeight="1" spans="1:10">
+    <row r="150" spans="1:10" ht="84" customHeight="1">
       <c r="A150" s="8">
         <v>45409</v>
       </c>
@@ -28416,7 +27844,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="151" ht="84" customHeight="1" spans="1:10">
+    <row r="151" spans="1:10" ht="84" customHeight="1">
       <c r="A151" s="8">
         <v>45409</v>
       </c>
@@ -28442,7 +27870,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="152" ht="84" customHeight="1" spans="1:10">
+    <row r="152" spans="1:10" ht="84" customHeight="1">
       <c r="A152" s="8">
         <v>45457</v>
       </c>
@@ -28466,7 +27894,7 @@
       </c>
       <c r="H152" s="3"/>
     </row>
-    <row r="153" ht="126" customHeight="1" spans="1:10">
+    <row r="153" spans="1:10" ht="126" customHeight="1">
       <c r="A153" s="8">
         <v>45457</v>
       </c>
@@ -28492,7 +27920,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="154" ht="126" customHeight="1" spans="1:10">
+    <row r="154" spans="1:10" ht="126" customHeight="1">
       <c r="A154" s="8">
         <v>45457</v>
       </c>
@@ -28518,7 +27946,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="155" ht="70" customHeight="1" spans="1:10">
+    <row r="155" spans="1:10" ht="70" customHeight="1">
       <c r="A155" s="8">
         <v>45469</v>
       </c>
@@ -28542,7 +27970,7 @@
       </c>
       <c r="H155" s="3"/>
     </row>
-    <row r="156" ht="70" customHeight="1" spans="1:10">
+    <row r="156" spans="1:10" ht="70" customHeight="1">
       <c r="A156" s="8">
         <v>45469</v>
       </c>
@@ -28566,7 +27994,7 @@
       </c>
       <c r="H156" s="3"/>
     </row>
-    <row r="157" ht="70" customHeight="1" spans="1:10">
+    <row r="157" spans="1:10" ht="70" customHeight="1">
       <c r="A157" s="8">
         <v>45469</v>
       </c>
@@ -28592,7 +28020,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="158" ht="42" customHeight="1" spans="1:10">
+    <row r="158" spans="1:10" ht="42" customHeight="1">
       <c r="A158" s="8">
         <v>45481</v>
       </c>
@@ -28615,7 +28043,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="159" ht="42" customHeight="1" spans="1:10">
+    <row r="159" spans="1:10" ht="42" customHeight="1">
       <c r="A159" s="8">
         <v>45481</v>
       </c>
@@ -28638,7 +28066,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="160" ht="42" customHeight="1" spans="1:10">
+    <row r="160" spans="1:10" ht="42" customHeight="1">
       <c r="A160" s="8">
         <v>45481</v>
       </c>
@@ -28664,7 +28092,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="161" ht="42" customHeight="1" spans="1:10">
+    <row r="161" spans="1:10" ht="42" customHeight="1">
       <c r="A161" s="8">
         <v>45481</v>
       </c>
@@ -28690,7 +28118,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="162" ht="28" customHeight="1" spans="1:10">
+    <row r="162" spans="1:10" ht="28" customHeight="1">
       <c r="A162" s="8">
         <v>45517</v>
       </c>
@@ -28716,7 +28144,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="163" ht="28" customHeight="1" spans="1:10">
+    <row r="163" spans="1:10" ht="28" customHeight="1">
       <c r="A163" s="8">
         <v>45517</v>
       </c>
@@ -28739,7 +28167,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="164" ht="98" customHeight="1" spans="1:10">
+    <row r="164" spans="1:10" ht="98" customHeight="1">
       <c r="A164" s="8">
         <v>45545</v>
       </c>
@@ -28762,7 +28190,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="165" ht="98" customHeight="1" spans="1:10">
+    <row r="165" spans="1:10" ht="98" customHeight="1">
       <c r="A165" s="8">
         <v>45545</v>
       </c>
@@ -28785,7 +28213,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="166" ht="98" customHeight="1" spans="1:10">
+    <row r="166" spans="1:10" ht="98" customHeight="1">
       <c r="A166" s="8">
         <v>45545</v>
       </c>
@@ -28982,7 +28410,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="174" ht="84" customHeight="1" spans="1:10">
+    <row r="174" spans="1:10" ht="84" customHeight="1">
       <c r="A174" s="8">
         <v>45568</v>
       </c>
@@ -29008,7 +28436,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="175" ht="84" customHeight="1" spans="1:10">
+    <row r="175" spans="1:10" ht="84" customHeight="1">
       <c r="A175" s="8">
         <v>45569</v>
       </c>
@@ -29032,7 +28460,7 @@
       </c>
       <c r="I175" s="3"/>
     </row>
-    <row r="176" ht="84" customHeight="1" spans="1:10">
+    <row r="176" spans="1:10" ht="84" customHeight="1">
       <c r="A176" s="8">
         <v>45569</v>
       </c>
@@ -29058,7 +28486,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="177" ht="28" customHeight="1" spans="1:10">
+    <row r="177" spans="1:10" ht="28" customHeight="1">
       <c r="A177" s="8">
         <v>45593</v>
       </c>
@@ -29084,7 +28512,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="178" ht="28" customHeight="1" spans="1:10">
+    <row r="178" spans="1:10" ht="28" customHeight="1">
       <c r="A178" s="8">
         <v>45593</v>
       </c>
@@ -29107,7 +28535,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="179" ht="28" customHeight="1" spans="1:10">
+    <row r="179" spans="1:10" ht="28" customHeight="1">
       <c r="A179" s="8">
         <v>45593</v>
       </c>
@@ -29130,7 +28558,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="180" ht="98" customHeight="1" spans="1:10">
+    <row r="180" spans="1:10" ht="98" customHeight="1">
       <c r="A180" s="8">
         <v>45598</v>
       </c>
@@ -29153,7 +28581,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="181" ht="98" customHeight="1" spans="1:10">
+    <row r="181" spans="1:10" ht="98" customHeight="1">
       <c r="A181" s="8">
         <v>45598</v>
       </c>
@@ -29176,7 +28604,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="182" ht="98" customHeight="1" spans="1:10">
+    <row r="182" spans="1:10" ht="98" customHeight="1">
       <c r="A182" s="8">
         <v>45598</v>
       </c>
@@ -29199,7 +28627,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="183" ht="98" customHeight="1" spans="1:10">
+    <row r="183" spans="1:10" ht="98" customHeight="1">
       <c r="A183" s="8">
         <v>45598</v>
       </c>
@@ -29225,7 +28653,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="184" ht="98" customHeight="1" spans="1:10">
+    <row r="184" spans="1:10" ht="98" customHeight="1">
       <c r="A184" s="8">
         <v>45598</v>
       </c>
@@ -29251,7 +28679,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="185" ht="126" customHeight="1" spans="1:10">
+    <row r="185" spans="1:10" ht="126" customHeight="1">
       <c r="A185" s="8">
         <v>45606</v>
       </c>
@@ -29274,7 +28702,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="186" ht="126" customHeight="1" spans="1:10">
+    <row r="186" spans="1:10" ht="126" customHeight="1">
       <c r="A186" s="8">
         <v>45606</v>
       </c>
@@ -29297,7 +28725,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="187" ht="126" customHeight="1" spans="1:10">
+    <row r="187" spans="1:10" ht="126" customHeight="1">
       <c r="A187" s="8">
         <v>45606</v>
       </c>
@@ -29476,7 +28904,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="194" ht="70" customHeight="1" spans="1:10">
+    <row r="194" spans="1:10" ht="70" customHeight="1">
       <c r="A194" s="8">
         <v>45652</v>
       </c>
@@ -29499,7 +28927,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="195" ht="70" customHeight="1" spans="1:10">
+    <row r="195" spans="1:10" ht="70" customHeight="1">
       <c r="A195" s="8">
         <v>45652</v>
       </c>
@@ -29617,7 +29045,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="200" ht="15.5" customHeight="1" spans="1:10">
+    <row r="200" spans="1:10" ht="15.5" customHeight="1">
       <c r="A200" s="8">
         <v>45652</v>
       </c>
@@ -29643,7 +29071,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="201" ht="70" customHeight="1" spans="1:10">
+    <row r="201" spans="1:10" ht="70" customHeight="1">
       <c r="A201" s="8">
         <v>45655</v>
       </c>
@@ -29667,7 +29095,7 @@
       </c>
       <c r="I201" s="3"/>
     </row>
-    <row r="202" ht="70" customHeight="1" spans="1:10">
+    <row r="202" spans="1:10" ht="70" customHeight="1">
       <c r="A202" s="8">
         <v>45655</v>
       </c>
@@ -29690,7 +29118,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="203" ht="70" customHeight="1" spans="1:10">
+    <row r="203" spans="1:10" ht="70" customHeight="1">
       <c r="A203" s="8">
         <v>45655</v>
       </c>
@@ -29713,7 +29141,7 @@
         <v>2351</v>
       </c>
     </row>
-    <row r="204" ht="70" customHeight="1" spans="1:10">
+    <row r="204" spans="1:10" ht="70" customHeight="1">
       <c r="A204" s="8">
         <v>45655</v>
       </c>
@@ -29736,7 +29164,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="205" ht="70" customHeight="1" spans="1:10">
+    <row r="205" spans="1:10" ht="70" customHeight="1">
       <c r="A205" s="8">
         <v>45655</v>
       </c>
@@ -29759,7 +29187,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="206" ht="70" customHeight="1" spans="1:10">
+    <row r="206" spans="1:10" ht="70" customHeight="1">
       <c r="A206" s="8">
         <v>45655</v>
       </c>
@@ -29984,7 +29412,7 @@
         <v>2368</v>
       </c>
     </row>
-    <row r="216" ht="56" customHeight="1" spans="1:10">
+    <row r="216" spans="1:10" ht="56" customHeight="1">
       <c r="A216" s="8">
         <v>45666</v>
       </c>
@@ -30007,7 +29435,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="217" ht="126" customHeight="1" spans="1:10">
+    <row r="217" spans="1:10" ht="126" customHeight="1">
       <c r="A217" s="8">
         <v>45666</v>
       </c>
@@ -30030,7 +29458,7 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="218" ht="126" customHeight="1" spans="1:10">
+    <row r="218" spans="1:10" ht="126" customHeight="1">
       <c r="A218" s="8">
         <v>45666</v>
       </c>
@@ -30056,7 +29484,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="219" ht="126" customHeight="1" spans="1:10">
+    <row r="219" spans="1:10" ht="126" customHeight="1">
       <c r="A219" s="8">
         <v>45676</v>
       </c>
@@ -30079,7 +29507,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="220" ht="70" customHeight="1" spans="1:10">
+    <row r="220" spans="1:10" ht="70" customHeight="1">
       <c r="A220" s="8">
         <v>45676</v>
       </c>
@@ -30102,7 +29530,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="221" ht="70" customHeight="1" spans="1:10">
+    <row r="221" spans="1:10" ht="70" customHeight="1">
       <c r="A221" s="8">
         <v>45676</v>
       </c>
@@ -30128,7 +29556,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="222" ht="70" customHeight="1" spans="1:10">
+    <row r="222" spans="1:10" ht="70" customHeight="1">
       <c r="A222" s="8">
         <v>45679</v>
       </c>
@@ -30149,7 +29577,7 @@
       </c>
       <c r="I222" s="19"/>
     </row>
-    <row r="223" ht="42" customHeight="1" spans="1:10">
+    <row r="223" spans="1:10" ht="42" customHeight="1">
       <c r="A223" s="8">
         <v>45679</v>
       </c>
@@ -30170,7 +29598,7 @@
       </c>
       <c r="I223" s="19"/>
     </row>
-    <row r="224" ht="42" customHeight="1" spans="1:10">
+    <row r="224" spans="1:10" ht="42" customHeight="1">
       <c r="A224" s="8">
         <v>45679</v>
       </c>
@@ -30194,7 +29622,7 @@
       </c>
       <c r="I224" s="19"/>
     </row>
-    <row r="225" ht="42" customHeight="1" spans="1:10">
+    <row r="225" spans="1:10" ht="42" customHeight="1">
       <c r="A225" s="8">
         <v>45679</v>
       </c>
@@ -30218,7 +29646,7 @@
       </c>
       <c r="I225" s="19"/>
     </row>
-    <row r="226" ht="42" customHeight="1" spans="1:10">
+    <row r="226" spans="1:10" ht="42" customHeight="1">
       <c r="A226" s="8">
         <v>45679</v>
       </c>
@@ -30242,7 +29670,7 @@
       </c>
       <c r="I226" s="19"/>
     </row>
-    <row r="227" ht="28" customHeight="1" spans="1:10">
+    <row r="227" spans="1:10" ht="28" customHeight="1">
       <c r="A227" s="8">
         <v>45679</v>
       </c>
@@ -30266,7 +29694,7 @@
       </c>
       <c r="I227" s="19"/>
     </row>
-    <row r="228" ht="28" customHeight="1" spans="1:10">
+    <row r="228" spans="1:10" ht="28" customHeight="1">
       <c r="A228" s="8">
         <v>45679</v>
       </c>
@@ -30289,7 +29717,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="229" ht="98" customHeight="1" spans="1:10">
+    <row r="229" spans="1:10" ht="98" customHeight="1">
       <c r="A229" s="8">
         <v>45679</v>
       </c>
@@ -30313,7 +29741,7 @@
       </c>
       <c r="I229" s="19"/>
     </row>
-    <row r="230" ht="98" customHeight="1" spans="1:10">
+    <row r="230" spans="1:10" ht="98" customHeight="1">
       <c r="A230" s="8">
         <v>45679</v>
       </c>
@@ -30337,7 +29765,7 @@
       </c>
       <c r="I230" s="19"/>
     </row>
-    <row r="231" ht="98" customHeight="1" spans="1:10">
+    <row r="231" spans="1:10" ht="98" customHeight="1">
       <c r="A231" s="8">
         <v>45679</v>
       </c>
@@ -30407,7 +29835,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="234" ht="84" customHeight="1" spans="1:10">
+    <row r="234" spans="1:10" ht="84" customHeight="1">
       <c r="A234" s="8">
         <v>45702</v>
       </c>
@@ -30433,7 +29861,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="235" ht="84" customHeight="1" spans="1:10">
+    <row r="235" spans="1:10" ht="84" customHeight="1">
       <c r="A235" s="8">
         <v>45702</v>
       </c>
@@ -30457,7 +29885,7 @@
       </c>
       <c r="I235" s="19"/>
     </row>
-    <row r="236" ht="84" customHeight="1" spans="1:10">
+    <row r="236" spans="1:10" ht="84" customHeight="1">
       <c r="A236" s="8">
         <v>45702</v>
       </c>
@@ -30481,7 +29909,7 @@
       </c>
       <c r="I236" s="19"/>
     </row>
-    <row r="237" ht="84" customHeight="1" spans="1:10">
+    <row r="237" spans="1:10" ht="84" customHeight="1">
       <c r="A237" s="8">
         <v>45717</v>
       </c>
@@ -30504,7 +29932,7 @@
         <v>2406</v>
       </c>
     </row>
-    <row r="238" ht="84" customHeight="1" spans="1:10">
+    <row r="238" spans="1:10" ht="84" customHeight="1">
       <c r="A238" s="8">
         <v>45717</v>
       </c>
@@ -30527,7 +29955,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="239" ht="84" customHeight="1" spans="1:10">
+    <row r="239" spans="1:10" ht="84" customHeight="1">
       <c r="A239" s="8">
         <v>45717</v>
       </c>
@@ -30553,7 +29981,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="240" ht="28" customHeight="1" spans="1:10">
+    <row r="240" spans="1:10" ht="28" customHeight="1">
       <c r="A240" s="8">
         <v>45722</v>
       </c>
@@ -30576,7 +30004,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="241" ht="28" customHeight="1" spans="1:10">
+    <row r="241" spans="1:10" ht="28" customHeight="1">
       <c r="A241" s="8">
         <v>45722</v>
       </c>
@@ -30596,7 +30024,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="242" ht="30.5" customHeight="1" spans="1:10">
+    <row r="242" spans="1:10" ht="30.5" customHeight="1">
       <c r="A242" s="8">
         <v>45729</v>
       </c>
@@ -30619,7 +30047,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="243" ht="30.5" customHeight="1" spans="1:10">
+    <row r="243" spans="1:10" ht="30.5" customHeight="1">
       <c r="A243" s="8">
         <v>45729</v>
       </c>
@@ -30645,7 +30073,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="244" ht="109.5" customHeight="1" spans="1:10">
+    <row r="244" spans="1:10" ht="109.5" customHeight="1">
       <c r="A244" s="8">
         <v>45729</v>
       </c>
@@ -30668,7 +30096,7 @@
         <v>2416</v>
       </c>
     </row>
-    <row r="245" ht="109.5" customHeight="1" spans="1:10">
+    <row r="245" spans="1:10" ht="109.5" customHeight="1">
       <c r="A245" s="8">
         <v>45729</v>
       </c>
@@ -30691,7 +30119,7 @@
         <v>2417</v>
       </c>
     </row>
-    <row r="246" ht="109.5" customHeight="1" spans="1:10">
+    <row r="246" spans="1:10" ht="109.5" customHeight="1">
       <c r="A246" s="8">
         <v>45729</v>
       </c>
@@ -30717,7 +30145,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="247" ht="109.5" customHeight="1" spans="1:10">
+    <row r="247" spans="1:10" ht="109.5" customHeight="1">
       <c r="A247" s="8">
         <v>45729</v>
       </c>
@@ -30741,7 +30169,7 @@
       </c>
       <c r="I247" s="3"/>
     </row>
-    <row r="248" ht="109.5" customHeight="1" spans="1:10">
+    <row r="248" spans="1:10" ht="109.5" customHeight="1">
       <c r="A248" s="8">
         <v>45730</v>
       </c>
@@ -30767,7 +30195,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="249" ht="109.5" customHeight="1" spans="1:10">
+    <row r="249" spans="1:10" ht="109.5" customHeight="1">
       <c r="A249" s="8">
         <v>45730</v>
       </c>
@@ -30790,7 +30218,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="250" ht="109.5" customHeight="1" spans="1:10">
+    <row r="250" spans="1:10" ht="109.5" customHeight="1">
       <c r="A250" s="8">
         <v>45730</v>
       </c>
@@ -30813,7 +30241,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="251" ht="109.5" customHeight="1" spans="1:10">
+    <row r="251" spans="1:10" ht="109.5" customHeight="1">
       <c r="A251" s="8">
         <v>45729</v>
       </c>
@@ -30836,7 +30264,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="252" ht="136" customHeight="1" spans="1:10">
+    <row r="252" spans="1:10" ht="136" customHeight="1">
       <c r="A252" s="8">
         <v>45729</v>
       </c>
@@ -30859,7 +30287,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="253" ht="136" customHeight="1" spans="1:10">
+    <row r="253" spans="1:10" ht="136" customHeight="1">
       <c r="A253" s="8">
         <v>45729</v>
       </c>
@@ -30882,7 +30310,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="254" ht="136" customHeight="1" spans="1:10">
+    <row r="254" spans="1:10" ht="136" customHeight="1">
       <c r="A254" s="8">
         <v>45729</v>
       </c>
@@ -30905,7 +30333,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="255" ht="136" customHeight="1" spans="1:10">
+    <row r="255" spans="1:10" ht="136" customHeight="1">
       <c r="A255" s="8">
         <v>45729</v>
       </c>
@@ -30931,7 +30359,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="256" ht="136" customHeight="1" spans="1:10">
+    <row r="256" spans="1:10" ht="136" customHeight="1">
       <c r="A256" s="8">
         <v>45729</v>
       </c>
@@ -30957,7 +30385,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="257" ht="136" customHeight="1" spans="1:10">
+    <row r="257" spans="1:10" ht="136" customHeight="1">
       <c r="A257" s="8">
         <v>45729</v>
       </c>
@@ -30984,7 +30412,7 @@
       </c>
       <c r="I257" s="3"/>
     </row>
-    <row r="258" ht="136" customHeight="1" spans="1:10">
+    <row r="258" spans="1:10" ht="136" customHeight="1">
       <c r="A258" s="8">
         <v>45729</v>
       </c>
@@ -31011,7 +30439,7 @@
       </c>
       <c r="I258" s="3"/>
     </row>
-    <row r="259" ht="136" customHeight="1" spans="1:10">
+    <row r="259" spans="1:10" ht="136" customHeight="1">
       <c r="A259" s="8">
         <v>45729</v>
       </c>
@@ -31038,7 +30466,7 @@
       </c>
       <c r="I259" s="3"/>
     </row>
-    <row r="260" ht="136" customHeight="1" spans="1:10">
+    <row r="260" spans="1:10" ht="136" customHeight="1">
       <c r="A260" s="8">
         <v>45729</v>
       </c>
@@ -31065,7 +30493,7 @@
       </c>
       <c r="I260" s="3"/>
     </row>
-    <row r="261" ht="136" customHeight="1" spans="1:10">
+    <row r="261" spans="1:10" ht="136" customHeight="1">
       <c r="A261" s="8">
         <v>45729</v>
       </c>
@@ -31092,7 +30520,7 @@
       </c>
       <c r="I261" s="3"/>
     </row>
-    <row r="262" ht="136" customHeight="1" spans="1:10">
+    <row r="262" spans="1:10" ht="136" customHeight="1">
       <c r="A262" s="8">
         <v>45729</v>
       </c>
@@ -31119,7 +30547,7 @@
       </c>
       <c r="I262" s="3"/>
     </row>
-    <row r="263" ht="136" customHeight="1" spans="1:10">
+    <row r="263" spans="1:10" ht="136" customHeight="1">
       <c r="A263" s="8">
         <v>45729</v>
       </c>
@@ -31146,7 +30574,7 @@
       </c>
       <c r="I263" s="3"/>
     </row>
-    <row r="264" ht="136" customHeight="1" spans="1:10">
+    <row r="264" spans="1:10" ht="136" customHeight="1">
       <c r="A264" s="8">
         <v>45729</v>
       </c>
@@ -31173,7 +30601,7 @@
       </c>
       <c r="I264" s="3"/>
     </row>
-    <row r="265" ht="136" customHeight="1" spans="1:10">
+    <row r="265" spans="1:10" ht="136" customHeight="1">
       <c r="A265" s="8">
         <v>45736</v>
       </c>
@@ -31196,7 +30624,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="266" ht="16.5" customHeight="1" spans="1:10">
+    <row r="266" spans="1:10" ht="16.5" customHeight="1">
       <c r="A266" s="8">
         <v>45736</v>
       </c>
@@ -31219,7 +30647,7 @@
         <v>2452</v>
       </c>
     </row>
-    <row r="267" ht="16.5" customHeight="1" spans="1:10">
+    <row r="267" spans="1:10" ht="16.5" customHeight="1">
       <c r="A267" s="8">
         <v>45736</v>
       </c>
@@ -31242,7 +30670,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="268" ht="126" customHeight="1" spans="1:10">
+    <row r="268" spans="1:10" ht="126" customHeight="1">
       <c r="A268" s="8">
         <v>45736</v>
       </c>
@@ -31265,7 +30693,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="269" ht="126" customHeight="1" spans="1:10">
+    <row r="269" spans="1:10" ht="126" customHeight="1">
       <c r="A269" s="8">
         <v>45736</v>
       </c>
@@ -31291,7 +30719,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="270" ht="126" customHeight="1" spans="1:10">
+    <row r="270" spans="1:10" ht="126" customHeight="1">
       <c r="A270" s="8">
         <v>45736</v>
       </c>
@@ -31314,7 +30742,7 @@
         <v>2456</v>
       </c>
     </row>
-    <row r="271" ht="126" customHeight="1" spans="1:10">
+    <row r="271" spans="1:10" ht="126" customHeight="1">
       <c r="A271" s="8">
         <v>45736</v>
       </c>
@@ -31337,7 +30765,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="272" ht="126" customHeight="1" spans="1:10">
+    <row r="272" spans="1:10" ht="126" customHeight="1">
       <c r="A272" s="8">
         <v>45736</v>
       </c>
@@ -31360,7 +30788,7 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="273" ht="126" customHeight="1" spans="1:10">
+    <row r="273" spans="1:10" ht="126" customHeight="1">
       <c r="A273" s="8">
         <v>45736</v>
       </c>
@@ -31383,7 +30811,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="274" ht="77.5" customHeight="1" spans="1:10">
+    <row r="274" spans="1:10" ht="77.5" customHeight="1">
       <c r="A274" s="8">
         <v>45736</v>
       </c>
@@ -31409,7 +30837,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="275" ht="77.5" customHeight="1" spans="1:10">
+    <row r="275" spans="1:10" ht="77.5" customHeight="1">
       <c r="A275" s="8">
         <v>45736</v>
       </c>
@@ -31435,7 +30863,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="276" ht="77.5" customHeight="1" spans="1:10">
+    <row r="276" spans="1:10" ht="77.5" customHeight="1">
       <c r="A276" s="8">
         <v>45736</v>
       </c>
@@ -31461,7 +30889,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="277" ht="77.5" customHeight="1" spans="1:10">
+    <row r="277" spans="1:10" ht="77.5" customHeight="1">
       <c r="A277" s="8">
         <v>45736</v>
       </c>
@@ -31488,7 +30916,7 @@
       </c>
       <c r="I277" s="3"/>
     </row>
-    <row r="278" ht="77.5" customHeight="1" spans="1:10">
+    <row r="278" spans="1:10" ht="77.5" customHeight="1">
       <c r="A278" s="8">
         <v>45736</v>
       </c>
@@ -31515,7 +30943,7 @@
       </c>
       <c r="I278" s="3"/>
     </row>
-    <row r="279" ht="77.5" customHeight="1" spans="1:10">
+    <row r="279" spans="1:10" ht="77.5" customHeight="1">
       <c r="A279" s="8">
         <v>45736</v>
       </c>
@@ -31538,7 +30966,7 @@
         <v>2471</v>
       </c>
     </row>
-    <row r="280" ht="77.5" customHeight="1" spans="1:10">
+    <row r="280" spans="1:10" ht="77.5" customHeight="1">
       <c r="A280" s="8">
         <v>45736</v>
       </c>
@@ -31561,7 +30989,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="281" ht="77.5" customHeight="1" spans="1:10">
+    <row r="281" spans="1:10" ht="77.5" customHeight="1">
       <c r="A281" s="8">
         <v>45736</v>
       </c>
@@ -31584,7 +31012,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="282" ht="196" customHeight="1" spans="1:10">
+    <row r="282" spans="1:10" ht="196" customHeight="1">
       <c r="A282" s="8">
         <v>45736</v>
       </c>
@@ -31610,7 +31038,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="283" ht="197.5" customHeight="1" spans="1:10">
+    <row r="283" spans="1:10" ht="197.5" customHeight="1">
       <c r="A283" s="8">
         <v>45736</v>
       </c>
@@ -31682,7 +31110,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="286" ht="84" customHeight="1" spans="1:10">
+    <row r="286" spans="1:10" ht="84" customHeight="1">
       <c r="A286" s="14">
         <v>45659</v>
       </c>
@@ -31708,7 +31136,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="287" ht="84" customHeight="1" spans="1:10">
+    <row r="287" spans="1:10" ht="84" customHeight="1">
       <c r="A287" s="14">
         <v>45659</v>
       </c>
@@ -31734,7 +31162,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="288" ht="84" customHeight="1" spans="1:10">
+    <row r="288" spans="1:10" ht="84" customHeight="1">
       <c r="A288" s="14">
         <v>45659</v>
       </c>
@@ -31760,7 +31188,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="289" ht="70" customHeight="1" spans="1:8">
+    <row r="289" spans="1:8" ht="70" customHeight="1">
       <c r="A289" s="14">
         <v>45666</v>
       </c>
@@ -31786,7 +31214,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="290" ht="70" customHeight="1" spans="1:8">
+    <row r="290" spans="1:8" ht="70" customHeight="1">
       <c r="A290" s="14">
         <v>45666</v>
       </c>
@@ -31812,7 +31240,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="291" ht="70" customHeight="1" spans="1:8">
+    <row r="291" spans="1:8" ht="70" customHeight="1">
       <c r="A291" s="14">
         <v>45666</v>
       </c>
@@ -31838,7 +31266,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="292" ht="70" customHeight="1" spans="1:8">
+    <row r="292" spans="1:8" ht="70" customHeight="1">
       <c r="A292" s="14">
         <v>45673</v>
       </c>
@@ -31864,7 +31292,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="293" ht="70" customHeight="1" spans="1:8">
+    <row r="293" spans="1:8" ht="70" customHeight="1">
       <c r="A293" s="14">
         <v>45673</v>
       </c>
@@ -31890,7 +31318,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="294" ht="70" customHeight="1" spans="1:8">
+    <row r="294" spans="1:8" ht="70" customHeight="1">
       <c r="A294" s="14">
         <v>45673</v>
       </c>
@@ -31916,7 +31344,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="295" ht="70" customHeight="1" spans="1:8">
+    <row r="295" spans="1:8" ht="70" customHeight="1">
       <c r="A295" s="14">
         <v>45680</v>
       </c>
@@ -31942,7 +31370,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="296" ht="70" customHeight="1" spans="1:8">
+    <row r="296" spans="1:8" ht="70" customHeight="1">
       <c r="A296" s="14">
         <v>45680</v>
       </c>
@@ -31968,7 +31396,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="297" ht="70" customHeight="1" spans="1:8">
+    <row r="297" spans="1:8" ht="70" customHeight="1">
       <c r="A297" s="14">
         <v>45680</v>
       </c>
@@ -31994,7 +31422,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="298" ht="42" customHeight="1" spans="1:8">
+    <row r="298" spans="1:8" ht="42" customHeight="1">
       <c r="A298" s="14">
         <v>45687</v>
       </c>
@@ -32020,7 +31448,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="299" ht="42" customHeight="1" spans="1:8">
+    <row r="299" spans="1:8" ht="42" customHeight="1">
       <c r="A299" s="14">
         <v>45687</v>
       </c>
@@ -32046,7 +31474,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="300" ht="42" customHeight="1" spans="1:8">
+    <row r="300" spans="1:8" ht="42" customHeight="1">
       <c r="A300" s="14">
         <v>45687</v>
       </c>
@@ -32072,7 +31500,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="301" ht="42" customHeight="1" spans="1:8">
+    <row r="301" spans="1:8" ht="42" customHeight="1">
       <c r="A301" s="14">
         <v>45687</v>
       </c>
@@ -32098,7 +31526,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="302" ht="42" customHeight="1" spans="1:8">
+    <row r="302" spans="1:8" ht="42" customHeight="1">
       <c r="A302" s="14">
         <v>45687</v>
       </c>
@@ -32124,7 +31552,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="303" ht="56" customHeight="1" spans="1:8">
+    <row r="303" spans="1:8" ht="56" customHeight="1">
       <c r="A303" s="14">
         <v>45694</v>
       </c>
@@ -32150,7 +31578,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="304" ht="56" customHeight="1" spans="1:8">
+    <row r="304" spans="1:8" ht="56" customHeight="1">
       <c r="A304" s="14">
         <v>45694</v>
       </c>
@@ -32176,7 +31604,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="305" ht="56" customHeight="1" spans="1:8">
+    <row r="305" spans="1:8" ht="56" customHeight="1">
       <c r="A305" s="14">
         <v>45694</v>
       </c>
@@ -32202,7 +31630,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="306" ht="70" customHeight="1" spans="1:8">
+    <row r="306" spans="1:8" ht="70" customHeight="1">
       <c r="A306" s="14">
         <v>45701</v>
       </c>
@@ -32228,7 +31656,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="307" ht="70" customHeight="1" spans="1:8">
+    <row r="307" spans="1:8" ht="70" customHeight="1">
       <c r="A307" s="14">
         <v>45701</v>
       </c>
@@ -32254,7 +31682,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="308" ht="70" customHeight="1" spans="1:8">
+    <row r="308" spans="1:8" ht="70" customHeight="1">
       <c r="A308" s="14">
         <v>45701</v>
       </c>
@@ -32280,7 +31708,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="309" ht="56" customHeight="1" spans="1:8">
+    <row r="309" spans="1:8" ht="56" customHeight="1">
       <c r="A309" s="14">
         <v>45708</v>
       </c>
@@ -32306,7 +31734,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="310" ht="56" customHeight="1" spans="1:8">
+    <row r="310" spans="1:8" ht="56" customHeight="1">
       <c r="A310" s="14">
         <v>45708</v>
       </c>
@@ -32332,7 +31760,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="311" ht="56" customHeight="1" spans="1:8">
+    <row r="311" spans="1:8" ht="56" customHeight="1">
       <c r="A311" s="14">
         <v>45708</v>
       </c>
@@ -32358,7 +31786,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="312" ht="56" customHeight="1" spans="1:8">
+    <row r="312" spans="1:8" ht="56" customHeight="1">
       <c r="A312" s="14">
         <v>45715</v>
       </c>
@@ -32384,7 +31812,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="313" ht="56" customHeight="1" spans="1:8">
+    <row r="313" spans="1:8" ht="56" customHeight="1">
       <c r="A313" s="14">
         <v>45715</v>
       </c>
@@ -32410,7 +31838,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="314" ht="56" customHeight="1" spans="1:8">
+    <row r="314" spans="1:8" ht="56" customHeight="1">
       <c r="A314" s="14">
         <v>45715</v>
       </c>
@@ -32436,7 +31864,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="315" ht="28" customHeight="1" spans="1:8">
+    <row r="315" spans="1:8" ht="28" customHeight="1">
       <c r="A315" s="14">
         <v>45722</v>
       </c>
@@ -32462,7 +31890,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="316" ht="28" customHeight="1" spans="1:8">
+    <row r="316" spans="1:8" ht="28" customHeight="1">
       <c r="A316" s="14">
         <v>45722</v>
       </c>
@@ -32488,7 +31916,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="317" ht="28" customHeight="1" spans="1:8">
+    <row r="317" spans="1:8" ht="28" customHeight="1">
       <c r="A317" s="14">
         <v>45722</v>
       </c>
@@ -32514,7 +31942,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="318" ht="28" customHeight="1" spans="1:8">
+    <row r="318" spans="1:8" ht="28" customHeight="1">
       <c r="A318" s="14">
         <v>45729</v>
       </c>
@@ -32540,7 +31968,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="319" ht="42" customHeight="1" spans="1:8">
+    <row r="319" spans="1:8" ht="42" customHeight="1">
       <c r="A319" s="14">
         <v>45736</v>
       </c>
@@ -32566,7 +31994,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="320" ht="42" customHeight="1" spans="1:8">
+    <row r="320" spans="1:8" ht="42" customHeight="1">
       <c r="A320" s="14">
         <v>45736</v>
       </c>
@@ -32592,7 +32020,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="321" ht="42" customHeight="1" spans="1:10">
+    <row r="321" spans="1:10" ht="42" customHeight="1">
       <c r="A321" s="14">
         <v>45736</v>
       </c>
@@ -32618,7 +32046,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="322" ht="42" customHeight="1" spans="1:10">
+    <row r="322" spans="1:10" ht="42" customHeight="1">
       <c r="A322" s="14">
         <v>45743</v>
       </c>
@@ -32644,7 +32072,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="323" ht="42" customHeight="1" spans="1:10">
+    <row r="323" spans="1:10" ht="42" customHeight="1">
       <c r="A323" s="14">
         <v>45743</v>
       </c>
@@ -32670,7 +32098,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="324" ht="42" customHeight="1" spans="1:10">
+    <row r="324" spans="1:10" ht="42" customHeight="1">
       <c r="A324" s="14">
         <v>45743</v>
       </c>
@@ -32696,7 +32124,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="325" ht="42" customHeight="1" spans="1:10">
+    <row r="325" spans="1:10" ht="42" customHeight="1">
       <c r="A325" s="14">
         <v>45743</v>
       </c>
@@ -32722,7 +32150,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="326" ht="42" customHeight="1" spans="1:10">
+    <row r="326" spans="1:10" ht="42" customHeight="1">
       <c r="A326" s="14">
         <v>45743</v>
       </c>
@@ -35396,7 +34824,7 @@
         <v>2719</v>
       </c>
     </row>
-    <row r="432" ht="42" customHeight="1" spans="1:11">
+    <row r="432" spans="1:11" ht="42" customHeight="1">
       <c r="A432" s="13">
         <v>45183</v>
       </c>
@@ -35422,7 +34850,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="433" ht="42" customHeight="1" spans="1:10">
+    <row r="433" spans="1:10" ht="42" customHeight="1">
       <c r="A433" s="13">
         <v>45183</v>
       </c>
@@ -36557,7 +35985,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="480" ht="126" customHeight="1" spans="1:11">
+    <row r="480" spans="1:11" ht="126" customHeight="1">
       <c r="A480" s="13">
         <v>45932</v>
       </c>
@@ -36583,7 +36011,7 @@
         <v>2837</v>
       </c>
     </row>
-    <row r="481" ht="126" customHeight="1" spans="1:10">
+    <row r="481" spans="1:10" ht="126" customHeight="1">
       <c r="A481" s="13">
         <v>45932</v>
       </c>
@@ -36609,7 +36037,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="482" ht="126" customHeight="1" spans="1:10">
+    <row r="482" spans="1:10" ht="126" customHeight="1">
       <c r="A482" s="13">
         <v>45932</v>
       </c>
@@ -36635,7 +36063,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="483" ht="126" customHeight="1" spans="1:10">
+    <row r="483" spans="1:10" ht="126" customHeight="1">
       <c r="A483" s="13">
         <v>45932</v>
       </c>
@@ -36661,7 +36089,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="484" ht="126" customHeight="1" spans="1:10">
+    <row r="484" spans="1:10" ht="126" customHeight="1">
       <c r="A484" s="13">
         <v>45932</v>
       </c>
@@ -36688,7 +36116,7 @@
         <v>2845</v>
       </c>
     </row>
-    <row r="485" ht="28" customHeight="1" spans="1:10">
+    <row r="485" spans="1:10" ht="28" customHeight="1">
       <c r="A485" s="13">
         <v>45933</v>
       </c>
@@ -36711,7 +36139,7 @@
         <v>2848</v>
       </c>
     </row>
-    <row r="486" ht="28" customHeight="1" spans="1:10">
+    <row r="486" spans="1:10" ht="28" customHeight="1">
       <c r="A486" s="13">
         <v>45933</v>
       </c>
@@ -36737,7 +36165,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="487" ht="56" customHeight="1" spans="1:10">
+    <row r="487" spans="1:10" ht="56" customHeight="1">
       <c r="A487" s="13">
         <v>45995</v>
       </c>
@@ -36763,7 +36191,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="488" ht="56" customHeight="1" spans="1:10">
+    <row r="488" spans="1:10" ht="56" customHeight="1">
       <c r="A488" s="13">
         <v>45995</v>
       </c>
@@ -36789,7 +36217,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="489" ht="56" customHeight="1" spans="1:10">
+    <row r="489" spans="1:10" ht="56" customHeight="1">
       <c r="A489" s="13">
         <v>45995</v>
       </c>
@@ -36815,7 +36243,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="490" ht="56" customHeight="1" spans="1:10">
+    <row r="490" spans="1:10" ht="56" customHeight="1">
       <c r="A490" s="13">
         <v>45995</v>
       </c>
@@ -36841,7 +36269,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="491" ht="56" customHeight="1" spans="1:10">
+    <row r="491" spans="1:10" ht="56" customHeight="1">
       <c r="A491" s="13">
         <v>45995</v>
       </c>
@@ -36867,7 +36295,7 @@
         <v>2859</v>
       </c>
     </row>
-    <row r="492" ht="70" customHeight="1" spans="1:10">
+    <row r="492" spans="1:10" ht="70" customHeight="1">
       <c r="A492" s="13">
         <v>46009</v>
       </c>
@@ -36893,7 +36321,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="493" ht="70" customHeight="1" spans="1:10">
+    <row r="493" spans="1:10" ht="70" customHeight="1">
       <c r="A493" s="13">
         <v>46009</v>
       </c>
@@ -36919,7 +36347,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="494" ht="70" customHeight="1" spans="1:10">
+    <row r="494" spans="1:10" ht="70" customHeight="1">
       <c r="A494" s="13">
         <v>46009</v>
       </c>
@@ -36945,7 +36373,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="495" ht="70" customHeight="1" spans="1:10">
+    <row r="495" spans="1:10" ht="70" customHeight="1">
       <c r="A495" s="13">
         <v>46009</v>
       </c>
@@ -36971,7 +36399,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="496" ht="70" customHeight="1" spans="1:10">
+    <row r="496" spans="1:10" ht="70" customHeight="1">
       <c r="A496" s="13">
         <v>46009</v>
       </c>
@@ -36997,7 +36425,7 @@
         <v>2867</v>
       </c>
     </row>
-    <row r="497" ht="98" customHeight="1" spans="1:10">
+    <row r="497" spans="1:10" ht="98" customHeight="1">
       <c r="A497" s="13">
         <v>46058</v>
       </c>
@@ -37023,7 +36451,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="498" ht="98" customHeight="1" spans="1:10">
+    <row r="498" spans="1:10" ht="98" customHeight="1">
       <c r="A498" s="13">
         <v>46058</v>
       </c>
@@ -37049,7 +36477,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="499" ht="98" customHeight="1" spans="1:10">
+    <row r="499" spans="1:10" ht="98" customHeight="1">
       <c r="A499" s="13">
         <v>46058</v>
       </c>
@@ -37075,7 +36503,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="500" ht="98" customHeight="1" spans="1:10">
+    <row r="500" spans="1:10" ht="98" customHeight="1">
       <c r="A500" s="13">
         <v>46058</v>
       </c>
@@ -37101,7 +36529,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="501" ht="98" customHeight="1" spans="1:10">
+    <row r="501" spans="1:10" ht="98" customHeight="1">
       <c r="A501" s="13">
         <v>46058</v>
       </c>
@@ -37127,7 +36555,7 @@
         <v>2875</v>
       </c>
     </row>
-    <row r="502" ht="112" customHeight="1" spans="1:10">
+    <row r="502" spans="1:10" ht="112" customHeight="1">
       <c r="A502" s="13">
         <v>46065</v>
       </c>
@@ -37153,7 +36581,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="503" ht="112" customHeight="1" spans="1:10">
+    <row r="503" spans="1:10" ht="112" customHeight="1">
       <c r="A503" s="13">
         <v>46065</v>
       </c>
@@ -37179,7 +36607,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="504" ht="112" customHeight="1" spans="1:10">
+    <row r="504" spans="1:10" ht="112" customHeight="1">
       <c r="A504" s="13">
         <v>46065</v>
       </c>
@@ -37205,7 +36633,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="505" ht="112" customHeight="1" spans="1:10">
+    <row r="505" spans="1:10" ht="112" customHeight="1">
       <c r="A505" s="13">
         <v>46065</v>
       </c>
@@ -37231,7 +36659,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="506" ht="112" customHeight="1" spans="1:10">
+    <row r="506" spans="1:10" ht="112" customHeight="1">
       <c r="A506" s="13">
         <v>46065</v>
       </c>
@@ -37257,7 +36685,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="507" ht="98" customHeight="1" spans="1:10">
+    <row r="507" spans="1:10" ht="98" customHeight="1">
       <c r="A507" s="13">
         <v>46079</v>
       </c>
@@ -37283,7 +36711,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="508" ht="98" customHeight="1" spans="1:10">
+    <row r="508" spans="1:10" ht="98" customHeight="1">
       <c r="A508" s="13">
         <v>46079</v>
       </c>
@@ -37309,7 +36737,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="509" ht="98" customHeight="1" spans="1:10">
+    <row r="509" spans="1:10" ht="98" customHeight="1">
       <c r="A509" s="13">
         <v>46079</v>
       </c>
@@ -37335,7 +36763,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="510" ht="98" customHeight="1" spans="1:10">
+    <row r="510" spans="1:10" ht="98" customHeight="1">
       <c r="A510" s="13">
         <v>46079</v>
       </c>
@@ -37361,7 +36789,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="511" ht="98" customHeight="1" spans="1:10">
+    <row r="511" spans="1:10" ht="98" customHeight="1">
       <c r="A511" s="13">
         <v>46079</v>
       </c>
@@ -37387,7 +36815,7 @@
         <v>2891</v>
       </c>
     </row>
-    <row r="512" ht="56" customHeight="1" spans="1:10">
+    <row r="512" spans="1:10" ht="56" customHeight="1">
       <c r="A512" s="13">
         <v>46093</v>
       </c>
@@ -37413,7 +36841,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="513" ht="56" customHeight="1" spans="1:10">
+    <row r="513" spans="1:10" ht="56" customHeight="1">
       <c r="A513" s="13">
         <v>46093</v>
       </c>
@@ -37439,7 +36867,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="514" ht="56" customHeight="1" spans="1:10">
+    <row r="514" spans="1:10" ht="56" customHeight="1">
       <c r="A514" s="13">
         <v>46093</v>
       </c>
@@ -37465,7 +36893,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="515" ht="56" customHeight="1" spans="1:10">
+    <row r="515" spans="1:10" ht="56" customHeight="1">
       <c r="A515" s="13">
         <v>46093</v>
       </c>
@@ -37491,7 +36919,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="516" ht="56" customHeight="1" spans="1:10">
+    <row r="516" spans="1:10" ht="56" customHeight="1">
       <c r="A516" s="13">
         <v>46093</v>
       </c>
@@ -37517,7 +36945,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="517" ht="112" customHeight="1" spans="1:10">
+    <row r="517" spans="1:10" ht="112" customHeight="1">
       <c r="A517" s="13">
         <v>46100</v>
       </c>
@@ -37543,7 +36971,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="518" ht="112" customHeight="1" spans="1:10">
+    <row r="518" spans="1:10" ht="112" customHeight="1">
       <c r="A518" s="13">
         <v>46100</v>
       </c>
@@ -37569,7 +36997,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="519" ht="112" customHeight="1" spans="1:10">
+    <row r="519" spans="1:10" ht="112" customHeight="1">
       <c r="A519" s="13">
         <v>46100</v>
       </c>
@@ -37595,7 +37023,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="520" ht="112" customHeight="1" spans="1:10">
+    <row r="520" spans="1:10" ht="112" customHeight="1">
       <c r="A520" s="13">
         <v>46100</v>
       </c>
@@ -37621,7 +37049,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="521" ht="112" customHeight="1" spans="1:10">
+    <row r="521" spans="1:10" ht="112" customHeight="1">
       <c r="A521" s="13">
         <v>46100</v>
       </c>
@@ -37647,7 +37075,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="522" ht="112" customHeight="1" spans="1:10">
+    <row r="522" spans="1:10" ht="112" customHeight="1">
       <c r="A522" s="13">
         <v>46100</v>
       </c>
@@ -37673,7 +37101,7 @@
         <v>2908</v>
       </c>
     </row>
-    <row r="523" ht="168" customHeight="1" spans="1:10">
+    <row r="523" spans="1:10" ht="168" customHeight="1">
       <c r="A523" s="13">
         <v>46114</v>
       </c>
@@ -37699,7 +37127,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="524" ht="168" customHeight="1" spans="1:10">
+    <row r="524" spans="1:10" ht="168" customHeight="1">
       <c r="A524" s="13">
         <v>46114</v>
       </c>
@@ -37725,7 +37153,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="525" ht="168" customHeight="1" spans="1:10">
+    <row r="525" spans="1:10" ht="168" customHeight="1">
       <c r="A525" s="13">
         <v>46114</v>
       </c>
@@ -37751,7 +37179,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="526" ht="168" customHeight="1" spans="1:10">
+    <row r="526" spans="1:10" ht="168" customHeight="1">
       <c r="A526" s="13">
         <v>46114</v>
       </c>
@@ -37777,7 +37205,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="527" ht="168" customHeight="1" spans="1:10">
+    <row r="527" spans="1:10" ht="168" customHeight="1">
       <c r="A527" s="13">
         <v>46114</v>
       </c>
@@ -37803,7 +37231,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="528" ht="168" customHeight="1" spans="1:10">
+    <row r="528" spans="1:10" ht="168" customHeight="1">
       <c r="A528" s="13">
         <v>46114</v>
       </c>
@@ -37829,7 +37257,7 @@
         <v>2917</v>
       </c>
     </row>
-    <row r="529" ht="224" customHeight="1" spans="1:10">
+    <row r="529" spans="1:10" ht="224" customHeight="1">
       <c r="A529" s="13">
         <v>46135</v>
       </c>
@@ -37855,7 +37283,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="530" ht="224" customHeight="1" spans="1:10">
+    <row r="530" spans="1:10" ht="224" customHeight="1">
       <c r="A530" s="13">
         <v>46135</v>
       </c>
@@ -37881,7 +37309,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="531" ht="224" customHeight="1" spans="1:10">
+    <row r="531" spans="1:10" ht="224" customHeight="1">
       <c r="A531" s="13">
         <v>46135</v>
       </c>
@@ -37907,7 +37335,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="532" ht="224" customHeight="1" spans="1:10">
+    <row r="532" spans="1:10" ht="224" customHeight="1">
       <c r="A532" s="13">
         <v>46135</v>
       </c>
@@ -37933,7 +37361,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="533" ht="224" customHeight="1" spans="1:10">
+    <row r="533" spans="1:10" ht="224" customHeight="1">
       <c r="A533" s="13">
         <v>46135</v>
       </c>
@@ -37959,7 +37387,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="534" ht="60" customHeight="1" spans="1:10">
+    <row r="534" spans="1:10" ht="60" customHeight="1">
       <c r="A534" s="13">
         <v>46184</v>
       </c>
@@ -37985,7 +37413,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="535" ht="60" customHeight="1" spans="1:10">
+    <row r="535" spans="1:10" ht="60" customHeight="1">
       <c r="A535" s="13">
         <v>46184</v>
       </c>
@@ -38011,7 +37439,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="536" ht="60" customHeight="1" spans="1:10">
+    <row r="536" spans="1:10" ht="60" customHeight="1">
       <c r="A536" s="13">
         <v>46184</v>
       </c>
@@ -38037,7 +37465,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="537" ht="60" customHeight="1" spans="1:10">
+    <row r="537" spans="1:10" ht="60" customHeight="1">
       <c r="A537" s="13">
         <v>46184</v>
       </c>
@@ -38063,7 +37491,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="538" ht="60" customHeight="1" spans="1:10">
+    <row r="538" spans="1:10" ht="60" customHeight="1">
       <c r="A538" s="13">
         <v>46184</v>
       </c>
@@ -38089,7 +37517,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="539" ht="60" customHeight="1" spans="1:10">
+    <row r="539" spans="1:10" ht="60" customHeight="1">
       <c r="A539" s="13">
         <v>46184</v>
       </c>
@@ -38115,7 +37543,7 @@
         <v>2934</v>
       </c>
     </row>
-    <row r="540" ht="84" customHeight="1" spans="1:10">
+    <row r="540" spans="1:10" ht="84" customHeight="1">
       <c r="A540" s="13">
         <v>46205</v>
       </c>
@@ -38141,7 +37569,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="541" ht="84" customHeight="1" spans="1:10">
+    <row r="541" spans="1:10" ht="84" customHeight="1">
       <c r="A541" s="13">
         <v>46205</v>
       </c>
@@ -38167,7 +37595,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="542" ht="84" customHeight="1" spans="1:10">
+    <row r="542" spans="1:10" ht="84" customHeight="1">
       <c r="A542" s="13">
         <v>46205</v>
       </c>
@@ -38193,7 +37621,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="543" ht="84" customHeight="1" spans="1:10">
+    <row r="543" spans="1:10" ht="84" customHeight="1">
       <c r="A543" s="13">
         <v>46205</v>
       </c>
@@ -38219,7 +37647,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="544" ht="84" customHeight="1" spans="1:10">
+    <row r="544" spans="1:10" ht="84" customHeight="1">
       <c r="A544" s="13">
         <v>46205</v>
       </c>
@@ -38245,7 +37673,7 @@
         <v>2942</v>
       </c>
     </row>
-    <row r="545" ht="112" customHeight="1" spans="1:10">
+    <row r="545" spans="1:10" ht="112" customHeight="1">
       <c r="A545" s="13">
         <v>46212</v>
       </c>
@@ -38271,7 +37699,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="546" ht="112" customHeight="1" spans="1:10">
+    <row r="546" spans="1:10" ht="112" customHeight="1">
       <c r="A546" s="13">
         <v>46212</v>
       </c>
@@ -38297,7 +37725,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="547" ht="112" customHeight="1" spans="1:10">
+    <row r="547" spans="1:10" ht="112" customHeight="1">
       <c r="A547" s="13">
         <v>46212</v>
       </c>
@@ -38323,7 +37751,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="548" ht="112" customHeight="1" spans="1:10">
+    <row r="548" spans="1:10" ht="112" customHeight="1">
       <c r="A548" s="13">
         <v>46212</v>
       </c>
@@ -38349,7 +37777,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="549" ht="112" customHeight="1" spans="1:10">
+    <row r="549" spans="1:10" ht="112" customHeight="1">
       <c r="A549" s="13">
         <v>46212</v>
       </c>
@@ -38375,7 +37803,7 @@
         <v>2950</v>
       </c>
     </row>
-    <row r="550" ht="168" customHeight="1" spans="1:10">
+    <row r="550" spans="1:10" ht="168" customHeight="1">
       <c r="A550" s="13">
         <v>46226</v>
       </c>
@@ -38401,7 +37829,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="551" ht="168" customHeight="1" spans="1:10">
+    <row r="551" spans="1:10" ht="168" customHeight="1">
       <c r="A551" s="13">
         <v>46226</v>
       </c>
@@ -38427,7 +37855,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="552" ht="168" customHeight="1" spans="1:10">
+    <row r="552" spans="1:10" ht="168" customHeight="1">
       <c r="A552" s="13">
         <v>46226</v>
       </c>
@@ -38453,7 +37881,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="553" ht="168" customHeight="1" spans="1:10">
+    <row r="553" spans="1:10" ht="168" customHeight="1">
       <c r="A553" s="13">
         <v>46226</v>
       </c>
@@ -38479,7 +37907,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="554" ht="168" customHeight="1" spans="1:10">
+    <row r="554" spans="1:10" ht="168" customHeight="1">
       <c r="A554" s="13">
         <v>46226</v>
       </c>
@@ -38505,7 +37933,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="555" ht="168" customHeight="1" spans="1:10">
+    <row r="555" spans="1:10" ht="168" customHeight="1">
       <c r="A555" s="13">
         <v>46226</v>
       </c>
@@ -38531,7 +37959,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="556" ht="84" customHeight="1" spans="1:10">
+    <row r="556" spans="1:10" ht="84" customHeight="1">
       <c r="A556" s="13">
         <v>46240</v>
       </c>
@@ -38557,7 +37985,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="557" ht="84" customHeight="1" spans="1:10">
+    <row r="557" spans="1:10" ht="84" customHeight="1">
       <c r="A557" s="13">
         <v>46240</v>
       </c>
@@ -38583,7 +38011,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="558" ht="84" customHeight="1" spans="1:10">
+    <row r="558" spans="1:10" ht="84" customHeight="1">
       <c r="A558" s="13">
         <v>46240</v>
       </c>
@@ -38609,7 +38037,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="559" ht="84" customHeight="1" spans="1:10">
+    <row r="559" spans="1:10" ht="84" customHeight="1">
       <c r="A559" s="13">
         <v>46240</v>
       </c>
@@ -38635,7 +38063,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="560" ht="84" customHeight="1" spans="1:10">
+    <row r="560" spans="1:10" ht="84" customHeight="1">
       <c r="A560" s="13">
         <v>46240</v>
       </c>
@@ -38661,7 +38089,7 @@
         <v>2967</v>
       </c>
     </row>
-    <row r="561" ht="98" customHeight="1" spans="1:10">
+    <row r="561" spans="1:10" ht="98" customHeight="1">
       <c r="A561" s="13">
         <v>46261</v>
       </c>
@@ -38687,7 +38115,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="562" ht="98" customHeight="1" spans="1:10">
+    <row r="562" spans="1:10" ht="98" customHeight="1">
       <c r="A562" s="13">
         <v>46261</v>
       </c>
@@ -38713,7 +38141,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="563" ht="98" customHeight="1" spans="1:10">
+    <row r="563" spans="1:10" ht="98" customHeight="1">
       <c r="A563" s="13">
         <v>46261</v>
       </c>
@@ -38739,7 +38167,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="564" ht="98" customHeight="1" spans="1:10">
+    <row r="564" spans="1:10" ht="98" customHeight="1">
       <c r="A564" s="13">
         <v>46261</v>
       </c>
@@ -38765,7 +38193,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="565" ht="98" customHeight="1" spans="1:10">
+    <row r="565" spans="1:10" ht="98" customHeight="1">
       <c r="A565" s="13">
         <v>46261</v>
       </c>
@@ -38791,7 +38219,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="566" ht="126" customHeight="1" spans="1:10">
+    <row r="566" spans="1:10" ht="126" customHeight="1">
       <c r="A566" s="13">
         <v>46282</v>
       </c>
@@ -38817,7 +38245,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="567" ht="126" customHeight="1" spans="1:10">
+    <row r="567" spans="1:10" ht="126" customHeight="1">
       <c r="A567" s="13">
         <v>46282</v>
       </c>
@@ -38843,7 +38271,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="568" ht="126" customHeight="1" spans="1:10">
+    <row r="568" spans="1:10" ht="126" customHeight="1">
       <c r="A568" s="13">
         <v>46282</v>
       </c>
@@ -38869,7 +38297,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="569" ht="126" customHeight="1" spans="1:10">
+    <row r="569" spans="1:10" ht="126" customHeight="1">
       <c r="A569" s="13">
         <v>46282</v>
       </c>
@@ -38895,7 +38323,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="570" ht="126" customHeight="1" spans="1:10">
+    <row r="570" spans="1:10" ht="126" customHeight="1">
       <c r="A570" s="13">
         <v>46282</v>
       </c>
@@ -38921,7 +38349,7 @@
         <v>2983</v>
       </c>
     </row>
-    <row r="571" ht="112" customHeight="1" spans="1:10">
+    <row r="571" spans="1:10" ht="112" customHeight="1">
       <c r="A571" s="13">
         <v>46289</v>
       </c>
@@ -38947,7 +38375,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="572" ht="112" customHeight="1" spans="1:10">
+    <row r="572" spans="1:10" ht="112" customHeight="1">
       <c r="A572" s="13">
         <v>46289</v>
       </c>
@@ -38973,7 +38401,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="573" ht="112" customHeight="1" spans="1:10">
+    <row r="573" spans="1:10" ht="112" customHeight="1">
       <c r="A573" s="13">
         <v>46289</v>
       </c>
@@ -38999,7 +38427,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="574" ht="112" customHeight="1" spans="1:10">
+    <row r="574" spans="1:10" ht="112" customHeight="1">
       <c r="A574" s="13">
         <v>46289</v>
       </c>
@@ -39025,7 +38453,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="575" ht="112" customHeight="1" spans="1:10">
+    <row r="575" spans="1:10" ht="112" customHeight="1">
       <c r="A575" s="13">
         <v>46289</v>
       </c>
@@ -39051,7 +38479,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="576" ht="112" customHeight="1" spans="1:10">
+    <row r="576" spans="1:10" ht="112" customHeight="1">
       <c r="A576" s="13">
         <v>46289</v>
       </c>
@@ -39077,7 +38505,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="577" ht="140" customHeight="1" spans="1:10">
+    <row r="577" spans="1:10" ht="140" customHeight="1">
       <c r="A577" s="13">
         <v>46296</v>
       </c>
@@ -39103,7 +38531,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="578" ht="140" customHeight="1" spans="1:10">
+    <row r="578" spans="1:10" ht="140" customHeight="1">
       <c r="A578" s="13">
         <v>46296</v>
       </c>
@@ -39129,7 +38557,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="579" ht="140" customHeight="1" spans="1:10">
+    <row r="579" spans="1:10" ht="140" customHeight="1">
       <c r="A579" s="13">
         <v>46296</v>
       </c>
@@ -39155,7 +38583,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="580" ht="140" customHeight="1" spans="1:10">
+    <row r="580" spans="1:10" ht="140" customHeight="1">
       <c r="A580" s="13">
         <v>46296</v>
       </c>
@@ -39181,7 +38609,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="581" ht="140" customHeight="1" spans="1:10">
+    <row r="581" spans="1:10" ht="140" customHeight="1">
       <c r="A581" s="13">
         <v>46296</v>
       </c>
@@ -39377,7 +38805,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="589" ht="196" customHeight="1" spans="1:10">
+    <row r="589" spans="1:10" ht="196" customHeight="1">
       <c r="A589" s="8">
         <v>45736</v>
       </c>
@@ -39400,7 +38828,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="590" ht="196" customHeight="1" spans="1:10">
+    <row r="590" spans="1:10" ht="196" customHeight="1">
       <c r="A590" s="8">
         <v>45736</v>
       </c>
@@ -39449,7 +38877,7 @@
         <v>3018</v>
       </c>
     </row>
-    <row r="592" ht="28" customHeight="1" spans="1:10">
+    <row r="592" spans="1:10" ht="28" customHeight="1">
       <c r="A592" s="21">
         <v>46312</v>
       </c>
@@ -39472,7 +38900,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="593" ht="28" customHeight="1" spans="1:10">
+    <row r="593" spans="1:10" ht="28" customHeight="1">
       <c r="A593" s="21">
         <v>46328</v>
       </c>
@@ -39495,7 +38923,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="594" ht="28" customHeight="1" spans="1:10">
+    <row r="594" spans="1:10" ht="28" customHeight="1">
       <c r="A594" s="21">
         <v>46329</v>
       </c>
@@ -39518,7 +38946,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="595" ht="42" customHeight="1" spans="1:10">
+    <row r="595" spans="1:10" ht="42" customHeight="1">
       <c r="A595" s="13">
         <v>45949</v>
       </c>
@@ -39541,7 +38969,7 @@
         <v>3028</v>
       </c>
     </row>
-    <row r="596" ht="42" customHeight="1" spans="1:10">
+    <row r="596" spans="1:10" ht="42" customHeight="1">
       <c r="A596" s="13">
         <v>45949</v>
       </c>
@@ -39564,7 +38992,7 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="597" ht="42" customHeight="1" spans="1:10">
+    <row r="597" spans="1:10" ht="42" customHeight="1">
       <c r="A597" s="13">
         <v>45949</v>
       </c>
@@ -39591,7 +39019,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="598" ht="42" customHeight="1" spans="1:10">
+    <row r="598" spans="1:10" ht="42" customHeight="1">
       <c r="A598" s="13">
         <v>46061</v>
       </c>
@@ -39614,7 +39042,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="599" ht="42" customHeight="1" spans="1:10">
+    <row r="599" spans="1:10" ht="42" customHeight="1">
       <c r="A599" s="13">
         <v>46016</v>
       </c>
@@ -39637,7 +39065,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="600" ht="42" customHeight="1" spans="1:10">
+    <row r="600" spans="1:10" ht="42" customHeight="1">
       <c r="A600" s="13">
         <v>46016</v>
       </c>
@@ -39660,7 +39088,7 @@
         <v>3038</v>
       </c>
     </row>
-    <row r="601" ht="42" customHeight="1" spans="1:10">
+    <row r="601" spans="1:10" ht="42" customHeight="1">
       <c r="A601" s="13">
         <v>46016</v>
       </c>
@@ -39758,7 +39186,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="606" ht="98" customHeight="1" spans="1:10">
+    <row r="606" spans="1:10" ht="98" customHeight="1">
       <c r="A606" s="8">
         <v>45740</v>
       </c>
@@ -39784,7 +39212,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="607" ht="98" customHeight="1" spans="1:10">
+    <row r="607" spans="1:10" ht="98" customHeight="1">
       <c r="A607" s="8">
         <v>45740</v>
       </c>
@@ -39810,7 +39238,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="608" ht="98" customHeight="1" spans="1:10">
+    <row r="608" spans="1:10" ht="98" customHeight="1">
       <c r="A608" s="8">
         <v>45740</v>
       </c>
@@ -39837,7 +39265,7 @@
       </c>
       <c r="I608" s="19"/>
     </row>
-    <row r="609" ht="98" customHeight="1" spans="1:10">
+    <row r="609" spans="1:10" ht="98" customHeight="1">
       <c r="A609" s="8">
         <v>45740</v>
       </c>
@@ -39864,7 +39292,7 @@
       </c>
       <c r="I609" s="19"/>
     </row>
-    <row r="610" ht="98" customHeight="1" spans="1:10">
+    <row r="610" spans="1:10" ht="98" customHeight="1">
       <c r="A610" s="8">
         <v>45740</v>
       </c>
@@ -40565,7 +39993,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="638" ht="16.5" customHeight="1" spans="1:10">
+    <row r="638" spans="1:10" ht="16.5" customHeight="1">
       <c r="A638" s="23">
         <v>45854</v>
       </c>
@@ -40593,7 +40021,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="639" ht="16.5" customHeight="1" spans="1:10">
+    <row r="639" spans="1:10" ht="16.5" customHeight="1">
       <c r="A639" s="23">
         <v>45854</v>
       </c>
@@ -40621,7 +40049,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="640" s="11" customFormat="1" spans="1:10">
+    <row r="640" spans="1:10" s="11" customFormat="1">
       <c r="A640" s="23">
         <v>45854</v>
       </c>
@@ -40647,7 +40075,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="641" s="11" customFormat="1" spans="1:10">
+    <row r="641" spans="1:10" s="11" customFormat="1">
       <c r="A641" s="23">
         <v>45866</v>
       </c>
@@ -40670,7 +40098,7 @@
         <v>3096</v>
       </c>
     </row>
-    <row r="642" s="11" customFormat="1" spans="1:10">
+    <row r="642" spans="1:10" s="11" customFormat="1">
       <c r="A642" s="23">
         <v>45866</v>
       </c>
@@ -40696,7 +40124,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="643" s="11" customFormat="1" spans="1:10">
+    <row r="643" spans="1:10" s="11" customFormat="1">
       <c r="A643" s="23">
         <v>45866</v>
       </c>
@@ -40719,7 +40147,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="644" s="11" customFormat="1" spans="1:10">
+    <row r="644" spans="1:10" s="11" customFormat="1">
       <c r="A644" s="23">
         <v>45866</v>
       </c>
@@ -40745,7 +40173,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="645" s="11" customFormat="1" spans="1:10">
+    <row r="645" spans="1:10" s="11" customFormat="1">
       <c r="A645" s="23">
         <v>45866</v>
       </c>
@@ -40768,7 +40196,7 @@
         <v>3104</v>
       </c>
     </row>
-    <row r="646" s="11" customFormat="1" spans="1:10">
+    <row r="646" spans="1:10" s="11" customFormat="1">
       <c r="A646" s="23">
         <v>45866</v>
       </c>
@@ -40791,7 +40219,7 @@
         <v>3105</v>
       </c>
     </row>
-    <row r="647" s="11" customFormat="1" spans="1:10">
+    <row r="647" spans="1:10" s="11" customFormat="1">
       <c r="A647" s="23">
         <v>45866</v>
       </c>
@@ -40814,7 +40242,7 @@
         <v>3106</v>
       </c>
     </row>
-    <row r="648" s="11" customFormat="1" spans="1:10">
+    <row r="648" spans="1:10" s="11" customFormat="1">
       <c r="A648" s="23">
         <v>45866</v>
       </c>
@@ -40837,7 +40265,7 @@
         <v>3107</v>
       </c>
     </row>
-    <row r="649" s="11" customFormat="1" spans="1:10">
+    <row r="649" spans="1:10" s="11" customFormat="1">
       <c r="A649" s="23">
         <v>45866</v>
       </c>
@@ -40863,7 +40291,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="650" s="11" customFormat="1" spans="1:10">
+    <row r="650" spans="1:10" s="11" customFormat="1">
       <c r="A650" s="23">
         <v>45866</v>
       </c>
@@ -40886,7 +40314,7 @@
         <v>3111</v>
       </c>
     </row>
-    <row r="651" s="11" customFormat="1" spans="1:10">
+    <row r="651" spans="1:10" s="11" customFormat="1">
       <c r="A651" s="23">
         <v>45866</v>
       </c>
@@ -40909,7 +40337,7 @@
         <v>3112</v>
       </c>
     </row>
-    <row r="652" s="11" customFormat="1" spans="1:10">
+    <row r="652" spans="1:10" s="11" customFormat="1">
       <c r="A652" s="23">
         <v>45866</v>
       </c>
@@ -40935,7 +40363,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="653" s="11" customFormat="1" spans="1:10">
+    <row r="653" spans="1:10" s="11" customFormat="1">
       <c r="A653" s="23">
         <v>45892</v>
       </c>
@@ -40958,7 +40386,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="654" s="11" customFormat="1" spans="1:10">
+    <row r="654" spans="1:10" s="11" customFormat="1">
       <c r="A654" s="23">
         <v>45892</v>
       </c>
@@ -40984,7 +40412,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="655" s="11" customFormat="1" spans="1:10">
+    <row r="655" spans="1:10" s="11" customFormat="1">
       <c r="A655" s="23">
         <v>45892</v>
       </c>
@@ -41010,7 +40438,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="656" s="11" customFormat="1" spans="1:10">
+    <row r="656" spans="1:10" s="11" customFormat="1">
       <c r="A656" s="23">
         <v>45892</v>
       </c>
@@ -41036,7 +40464,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="657" s="11" customFormat="1" spans="1:10">
+    <row r="657" spans="1:10" s="11" customFormat="1">
       <c r="A657" s="23">
         <v>45902</v>
       </c>
@@ -41056,7 +40484,7 @@
         <v>3121</v>
       </c>
     </row>
-    <row r="658" s="11" customFormat="1" spans="1:10">
+    <row r="658" spans="1:10" s="11" customFormat="1">
       <c r="A658" s="23">
         <v>45902</v>
       </c>
@@ -41076,7 +40504,7 @@
         <v>3122</v>
       </c>
     </row>
-    <row r="659" s="11" customFormat="1" spans="1:10">
+    <row r="659" spans="1:10" s="11" customFormat="1">
       <c r="A659" s="23">
         <v>45902</v>
       </c>
@@ -41099,7 +40527,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="660" s="11" customFormat="1" spans="1:10">
+    <row r="660" spans="1:10" s="11" customFormat="1">
       <c r="A660" s="23">
         <v>45902</v>
       </c>
@@ -41122,7 +40550,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="661" s="11" customFormat="1" spans="1:10">
+    <row r="661" spans="1:10" s="11" customFormat="1">
       <c r="A661" s="23">
         <v>45910</v>
       </c>
@@ -41145,7 +40573,7 @@
         <v>3126</v>
       </c>
     </row>
-    <row r="662" s="11" customFormat="1" spans="1:10">
+    <row r="662" spans="1:10" s="11" customFormat="1">
       <c r="A662" s="23">
         <v>45910</v>
       </c>
@@ -41171,7 +40599,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="663" s="11" customFormat="1" spans="1:10">
+    <row r="663" spans="1:10" s="11" customFormat="1">
       <c r="A663" s="23">
         <v>45910</v>
       </c>
@@ -41197,7 +40625,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="664" s="11" customFormat="1" spans="1:10">
+    <row r="664" spans="1:10" s="11" customFormat="1">
       <c r="A664" s="23">
         <v>45917</v>
       </c>
@@ -41217,7 +40645,7 @@
         <v>3130</v>
       </c>
     </row>
-    <row r="665" s="11" customFormat="1" spans="1:10">
+    <row r="665" spans="1:10" s="11" customFormat="1">
       <c r="A665" s="23">
         <v>45917</v>
       </c>
@@ -41240,7 +40668,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="666" s="11" customFormat="1" spans="1:10">
+    <row r="666" spans="1:10" s="11" customFormat="1">
       <c r="A666" s="23">
         <v>45971</v>
       </c>
@@ -41263,7 +40691,7 @@
         <v>3133</v>
       </c>
     </row>
-    <row r="667" s="11" customFormat="1" spans="1:10">
+    <row r="667" spans="1:10" s="11" customFormat="1">
       <c r="A667" s="23">
         <v>45971</v>
       </c>
@@ -41289,7 +40717,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="668" s="11" customFormat="1" spans="1:10">
+    <row r="668" spans="1:10" s="11" customFormat="1">
       <c r="A668" s="23">
         <v>45971</v>
       </c>
@@ -41315,7 +40743,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="669" s="11" customFormat="1" spans="1:10">
+    <row r="669" spans="1:10" s="11" customFormat="1">
       <c r="A669" s="23">
         <v>45971</v>
       </c>
@@ -41341,7 +40769,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="670" s="11" customFormat="1" ht="20" customHeight="1" spans="1:10">
+    <row r="670" spans="1:10" s="11" customFormat="1" ht="20" customHeight="1">
       <c r="A670" s="23">
         <v>45992</v>
       </c>
@@ -41364,7 +40792,7 @@
         <v>3139</v>
       </c>
     </row>
-    <row r="671" s="11" customFormat="1" ht="20" customHeight="1" spans="1:10">
+    <row r="671" spans="1:10" s="11" customFormat="1" ht="20" customHeight="1">
       <c r="A671" s="23">
         <v>45992</v>
       </c>
@@ -41387,7 +40815,7 @@
         <v>3140</v>
       </c>
     </row>
-    <row r="672" s="11" customFormat="1" ht="20" customHeight="1" spans="1:10">
+    <row r="672" spans="1:10" s="11" customFormat="1" ht="20" customHeight="1">
       <c r="A672" s="23">
         <v>45992</v>
       </c>
@@ -41410,7 +40838,7 @@
         <v>3141</v>
       </c>
     </row>
-    <row r="673" s="11" customFormat="1" spans="1:10">
+    <row r="673" spans="1:10" s="11" customFormat="1">
       <c r="A673" s="23">
         <v>45992</v>
       </c>
@@ -41436,7 +40864,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="674" s="11" customFormat="1" spans="1:10">
+    <row r="674" spans="1:10" s="11" customFormat="1">
       <c r="A674" s="23">
         <v>46022</v>
       </c>
@@ -41462,7 +40890,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="675" s="11" customFormat="1" spans="1:10">
+    <row r="675" spans="1:10" s="11" customFormat="1">
       <c r="A675" s="23">
         <v>46022</v>
       </c>
@@ -41488,7 +40916,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="676" s="11" customFormat="1" spans="1:10">
+    <row r="676" spans="1:10" s="11" customFormat="1">
       <c r="A676" s="23">
         <v>46022</v>
       </c>
@@ -41514,7 +40942,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="677" s="11" customFormat="1" spans="1:10">
+    <row r="677" spans="1:10" s="11" customFormat="1">
       <c r="A677" s="13">
         <v>46304</v>
       </c>
@@ -41537,7 +40965,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="678" s="11" customFormat="1" spans="1:10">
+    <row r="678" spans="1:10" s="11" customFormat="1">
       <c r="A678" s="13">
         <v>46304</v>
       </c>
@@ -41560,7 +40988,7 @@
         <v>3151</v>
       </c>
     </row>
-    <row r="679" s="11" customFormat="1" spans="1:10">
+    <row r="679" spans="1:10" s="11" customFormat="1">
       <c r="A679" s="13">
         <v>46311</v>
       </c>
@@ -41583,7 +41011,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="680" s="11" customFormat="1" spans="1:10">
+    <row r="680" spans="1:10" s="11" customFormat="1">
       <c r="A680" s="13">
         <v>46333</v>
       </c>
@@ -41606,7 +41034,7 @@
         <v>3155</v>
       </c>
     </row>
-    <row r="681" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="681" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A681" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41629,7 +41057,7 @@
         <v>3159</v>
       </c>
     </row>
-    <row r="682" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="682" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A682" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41652,7 +41080,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="683" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="683" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A683" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41675,7 +41103,7 @@
         <v>3161</v>
       </c>
     </row>
-    <row r="684" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="684" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A684" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41698,7 +41126,7 @@
         <v>3162</v>
       </c>
     </row>
-    <row r="685" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="685" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A685" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41721,7 +41149,7 @@
         <v>3163</v>
       </c>
     </row>
-    <row r="686" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="686" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A686" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41744,7 +41172,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="687" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="687" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A687" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41767,7 +41195,7 @@
         <v>3165</v>
       </c>
     </row>
-    <row r="688" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="688" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A688" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41790,7 +41218,7 @@
         <v>3166</v>
       </c>
     </row>
-    <row r="689" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="689" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A689" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41816,7 +41244,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="690" s="11" customFormat="1" ht="182" customHeight="1" spans="1:10">
+    <row r="690" spans="1:10" s="11" customFormat="1" ht="182" customHeight="1">
       <c r="A690" s="14" t="s">
         <v>3156</v>
       </c>
@@ -41842,7 +41270,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="691" s="11" customFormat="1" ht="98" customHeight="1" spans="1:10">
+    <row r="691" spans="1:10" s="11" customFormat="1" ht="98" customHeight="1">
       <c r="A691" s="14" t="s">
         <v>3169</v>
       </c>
@@ -41865,7 +41293,7 @@
         <v>3172</v>
       </c>
     </row>
-    <row r="692" s="11" customFormat="1" ht="98" customHeight="1" spans="1:10">
+    <row r="692" spans="1:10" s="11" customFormat="1" ht="98" customHeight="1">
       <c r="A692" s="14" t="s">
         <v>3169</v>
       </c>
@@ -41888,7 +41316,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="693" s="11" customFormat="1" ht="98" customHeight="1" spans="1:10">
+    <row r="693" spans="1:10" s="11" customFormat="1" ht="98" customHeight="1">
       <c r="A693" s="14" t="s">
         <v>3169</v>
       </c>
@@ -41914,7 +41342,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="694" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="694" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A694" s="14" t="s">
         <v>3175</v>
       </c>
@@ -41937,7 +41365,7 @@
         <v>3178</v>
       </c>
     </row>
-    <row r="695" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="695" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A695" s="14" t="s">
         <v>3175</v>
       </c>
@@ -41960,7 +41388,7 @@
         <v>3179</v>
       </c>
     </row>
-    <row r="696" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="696" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A696" s="14" t="s">
         <v>3175</v>
       </c>
@@ -41983,7 +41411,7 @@
         <v>3180</v>
       </c>
     </row>
-    <row r="697" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="697" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A697" s="14" t="s">
         <v>3175</v>
       </c>
@@ -42006,7 +41434,7 @@
         <v>3181</v>
       </c>
     </row>
-    <row r="698" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="698" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A698" s="14" t="s">
         <v>3175</v>
       </c>
@@ -42032,7 +41460,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="699" s="11" customFormat="1" ht="42" customHeight="1" spans="1:10">
+    <row r="699" spans="1:10" s="11" customFormat="1" ht="42" customHeight="1">
       <c r="A699" s="14" t="s">
         <v>3183</v>
       </c>
@@ -42055,7 +41483,7 @@
         <v>3186</v>
       </c>
     </row>
-    <row r="700" s="11" customFormat="1" ht="42" customHeight="1" spans="1:10">
+    <row r="700" spans="1:10" s="11" customFormat="1" ht="42" customHeight="1">
       <c r="A700" s="14" t="s">
         <v>3183</v>
       </c>
@@ -42078,7 +41506,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="701" s="11" customFormat="1" ht="42" customHeight="1" spans="1:10">
+    <row r="701" spans="1:10" s="11" customFormat="1" ht="42" customHeight="1">
       <c r="A701" s="14" t="s">
         <v>3183</v>
       </c>
@@ -42104,7 +41532,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="702" s="11" customFormat="1" ht="56" customHeight="1" spans="1:10">
+    <row r="702" spans="1:10" s="11" customFormat="1" ht="56" customHeight="1">
       <c r="A702" s="14" t="s">
         <v>3189</v>
       </c>
@@ -42127,7 +41555,7 @@
         <v>3192</v>
       </c>
     </row>
-    <row r="703" s="11" customFormat="1" ht="56" customHeight="1" spans="1:10">
+    <row r="703" spans="1:10" s="11" customFormat="1" ht="56" customHeight="1">
       <c r="A703" s="14" t="s">
         <v>3189</v>
       </c>
@@ -42153,7 +41581,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="704" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="704" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A704" s="14" t="s">
         <v>3193</v>
       </c>
@@ -42176,7 +41604,7 @@
         <v>3196</v>
       </c>
     </row>
-    <row r="705" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="705" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A705" s="14" t="s">
         <v>3193</v>
       </c>
@@ -42199,7 +41627,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="706" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="706" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A706" s="14" t="s">
         <v>3193</v>
       </c>
@@ -42222,7 +41650,7 @@
         <v>3198</v>
       </c>
     </row>
-    <row r="707" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="707" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A707" s="14" t="s">
         <v>3193</v>
       </c>
@@ -42245,7 +41673,7 @@
         <v>3199</v>
       </c>
     </row>
-    <row r="708" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="708" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A708" s="14" t="s">
         <v>3193</v>
       </c>
@@ -42271,7 +41699,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="709" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="709" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A709" s="14" t="s">
         <v>3193</v>
       </c>
@@ -42297,7 +41725,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="710" s="11" customFormat="1" spans="1:10">
+    <row r="710" spans="1:10" s="11" customFormat="1">
       <c r="A710" s="14" t="s">
         <v>3202</v>
       </c>
@@ -42320,7 +41748,7 @@
         <v>3205</v>
       </c>
     </row>
-    <row r="711" s="11" customFormat="1" spans="1:10">
+    <row r="711" spans="1:10" s="11" customFormat="1">
       <c r="A711" s="14" t="s">
         <v>3202</v>
       </c>
@@ -42343,7 +41771,7 @@
         <v>3206</v>
       </c>
     </row>
-    <row r="712" s="11" customFormat="1" spans="1:10">
+    <row r="712" spans="1:10" s="11" customFormat="1">
       <c r="A712" s="14" t="s">
         <v>3202</v>
       </c>
@@ -42366,7 +41794,7 @@
         <v>3207</v>
       </c>
     </row>
-    <row r="713" s="11" customFormat="1" spans="1:10">
+    <row r="713" spans="1:10" s="11" customFormat="1">
       <c r="A713" s="14" t="s">
         <v>3202</v>
       </c>
@@ -42392,7 +41820,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="714" s="11" customFormat="1" spans="1:10">
+    <row r="714" spans="1:10" s="11" customFormat="1">
       <c r="A714" s="14" t="s">
         <v>3202</v>
       </c>
@@ -42418,7 +41846,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="715" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="715" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A715" s="14" t="s">
         <v>3210</v>
       </c>
@@ -42441,7 +41869,7 @@
         <v>3213</v>
       </c>
     </row>
-    <row r="716" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="716" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A716" s="14" t="s">
         <v>3210</v>
       </c>
@@ -42464,7 +41892,7 @@
         <v>3214</v>
       </c>
     </row>
-    <row r="717" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="717" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A717" s="14" t="s">
         <v>3210</v>
       </c>
@@ -42487,7 +41915,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="718" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="718" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A718" s="14" t="s">
         <v>3210</v>
       </c>
@@ -42510,7 +41938,7 @@
         <v>3216</v>
       </c>
     </row>
-    <row r="719" s="11" customFormat="1" ht="84" customHeight="1" spans="1:10">
+    <row r="719" spans="1:10" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A719" s="14" t="s">
         <v>3210</v>
       </c>
@@ -42536,7 +41964,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="720" s="11" customFormat="1" ht="154" customHeight="1" spans="1:10">
+    <row r="720" spans="1:10" s="11" customFormat="1" ht="154" customHeight="1">
       <c r="A720" s="14" t="s">
         <v>3218</v>
       </c>
@@ -42559,7 +41987,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="721" s="11" customFormat="1" ht="154" customHeight="1" spans="1:10">
+    <row r="721" spans="1:10" s="11" customFormat="1" ht="154" customHeight="1">
       <c r="A721" s="14" t="s">
         <v>3218</v>
       </c>
@@ -42582,7 +42010,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="722" s="11" customFormat="1" ht="154" customHeight="1" spans="1:10">
+    <row r="722" spans="1:10" s="11" customFormat="1" ht="154" customHeight="1">
       <c r="A722" s="14" t="s">
         <v>3218</v>
       </c>
@@ -42605,7 +42033,7 @@
         <v>3223</v>
       </c>
     </row>
-    <row r="723" s="11" customFormat="1" ht="154" customHeight="1" spans="1:10">
+    <row r="723" spans="1:10" s="11" customFormat="1" ht="154" customHeight="1">
       <c r="A723" s="14" t="s">
         <v>3218</v>
       </c>
@@ -42628,7 +42056,7 @@
         <v>3224</v>
       </c>
     </row>
-    <row r="724" s="11" customFormat="1" ht="154" customHeight="1" spans="1:10">
+    <row r="724" spans="1:10" s="11" customFormat="1" ht="154" customHeight="1">
       <c r="A724" s="14" t="s">
         <v>3218</v>
       </c>
@@ -42651,7 +42079,7 @@
         <v>3225</v>
       </c>
     </row>
-    <row r="725" s="11" customFormat="1" ht="154" customHeight="1" spans="1:10">
+    <row r="725" spans="1:10" s="11" customFormat="1" ht="154" customHeight="1">
       <c r="A725" s="14" t="s">
         <v>3218</v>
       </c>
@@ -42674,7 +42102,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="726" s="11" customFormat="1" ht="154" customHeight="1" spans="1:10">
+    <row r="726" spans="1:10" s="11" customFormat="1" ht="154" customHeight="1">
       <c r="A726" s="14" t="s">
         <v>3218</v>
       </c>
@@ -42700,7 +42128,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="727" s="11" customFormat="1" ht="154" customHeight="1" spans="1:10">
+    <row r="727" spans="1:10" s="11" customFormat="1" ht="154" customHeight="1">
       <c r="A727" s="14" t="s">
         <v>3218</v>
       </c>
@@ -42726,7 +42154,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="728" s="11" customFormat="1" ht="140" customHeight="1" spans="1:10">
+    <row r="728" spans="1:10" s="11" customFormat="1" ht="140" customHeight="1">
       <c r="A728" t="s">
         <v>3218</v>
       </c>
@@ -42750,7 +42178,7 @@
       </c>
       <c r="I728" s="3"/>
     </row>
-    <row r="729" s="11" customFormat="1" ht="140" customHeight="1" spans="1:10">
+    <row r="729" spans="1:10" s="11" customFormat="1" ht="140" customHeight="1">
       <c r="A729" t="s">
         <v>3218</v>
       </c>
@@ -42777,7 +42205,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="730" s="11" customFormat="1" spans="1:10">
+    <row r="730" spans="1:10" s="11" customFormat="1">
       <c r="A730" s="14" t="s">
         <v>3233</v>
       </c>
@@ -42800,7 +42228,7 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="731" s="11" customFormat="1" spans="1:10">
+    <row r="731" spans="1:10" s="11" customFormat="1">
       <c r="A731" s="14" t="s">
         <v>3233</v>
       </c>
@@ -42823,7 +42251,7 @@
         <v>3237</v>
       </c>
     </row>
-    <row r="732" s="11" customFormat="1" spans="1:10">
+    <row r="732" spans="1:10" s="11" customFormat="1">
       <c r="A732" s="14" t="s">
         <v>3233</v>
       </c>
@@ -42849,7 +42277,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="733" s="11" customFormat="1" spans="1:10">
+    <row r="733" spans="1:10" s="11" customFormat="1">
       <c r="A733" s="14" t="s">
         <v>3233</v>
       </c>
@@ -42875,7 +42303,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="734" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="734" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A734" s="14" t="s">
         <v>3240</v>
       </c>
@@ -42898,7 +42326,7 @@
         <v>3243</v>
       </c>
     </row>
-    <row r="735" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="735" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A735" s="14" t="s">
         <v>3240</v>
       </c>
@@ -42921,7 +42349,7 @@
         <v>3244</v>
       </c>
     </row>
-    <row r="736" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="736" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A736" s="14" t="s">
         <v>3240</v>
       </c>
@@ -42944,7 +42372,7 @@
         <v>3245</v>
       </c>
     </row>
-    <row r="737" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="737" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A737" s="14" t="s">
         <v>3240</v>
       </c>
@@ -42967,7 +42395,7 @@
         <v>3246</v>
       </c>
     </row>
-    <row r="738" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="738" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A738" s="14" t="s">
         <v>3240</v>
       </c>
@@ -42990,7 +42418,7 @@
         <v>3247</v>
       </c>
     </row>
-    <row r="739" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="739" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A739" s="14" t="s">
         <v>3240</v>
       </c>
@@ -43013,7 +42441,7 @@
         <v>3248</v>
       </c>
     </row>
-    <row r="740" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="740" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A740" s="14" t="s">
         <v>3240</v>
       </c>
@@ -43036,7 +42464,7 @@
         <v>3249</v>
       </c>
     </row>
-    <row r="741" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="741" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A741" s="14" t="s">
         <v>3240</v>
       </c>
@@ -43062,7 +42490,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="742" s="11" customFormat="1" ht="112" customHeight="1" spans="1:10">
+    <row r="742" spans="1:10" s="11" customFormat="1" ht="112" customHeight="1">
       <c r="A742" s="14" t="s">
         <v>3240</v>
       </c>
@@ -43102,7 +42530,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="744" ht="28" customHeight="1" spans="1:10">
+    <row r="744" spans="1:10" ht="28" customHeight="1">
       <c r="A744" s="21">
         <v>46347</v>
       </c>
@@ -44149,7 +43577,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="792" s="11" customFormat="1" spans="1:10">
+    <row r="792" spans="1:10" s="11" customFormat="1">
       <c r="A792" s="13">
         <v>45484</v>
       </c>
@@ -45571,117 +44999,115 @@
       <c r="A857" s="13"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J855" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:J855" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" promptTitle="媒体类型" prompt="请选择媒体类型" sqref="I669 F592:F594 F603:F607 F612:F677 F679:F742 F744:F855">
+    <dataValidation type="list" allowBlank="1" promptTitle="媒体类型" prompt="请选择媒体类型" sqref="I669 F592:F594 F603:F607 F612:F677 F679:F742 F744:F855" xr:uid="{00000000-0002-0000-0B00-000000000000}">
       <formula1>"image,video,link"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorTitle="无效分类" error="请选择 organization 或 personal" sqref="C603:C742">
+    <dataValidation type="list" errorTitle="无效分类" error="请选择 organization 或 personal" sqref="C603:C742" xr:uid="{00000000-0002-0000-0B00-000001000000}">
       <formula1>"organization,personal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请选择列表中的时间轴 tag" sqref="E2:E729 E734:E735 E740:E1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请选择列表中的时间轴 tag" sqref="E2:E729 E734:E735 E740:E1048576" xr:uid="{00000000-0002-0000-0B00-000002000000}">
       <formula1>"oml,bandori_fes,fes,single,album,anime,game,book,program,offline,private,business_mjc,business_others"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I128" r:id="rId1" location="/album?id=198675493" display="https://music.163.com/#/album?id=198675493"/>
-    <hyperlink ref="I210" r:id="rId2" display="https://x.com/Kanon_Takao/status/1876884572278784227"/>
-    <hyperlink ref="G212" r:id="rId3" display="https://player.bilibili.com/player.html?bvid=BV1BmBEB2E1E"/>
-    <hyperlink ref="G213" r:id="rId4" display="https://player.bilibili.com/player.html?bvid=BV1QnBEBNE1b"/>
-    <hyperlink ref="G214" r:id="rId5" display="https://player.bilibili.com/player.html?bvid=BV1nCBTBDErk"/>
-    <hyperlink ref="G215" r:id="rId6" display="https://player.bilibili.com/player.html?bvid=BV1FiBvBFEVN" tooltip="https://player.bilibili.com/player.html?bvid=BV1FiBvBFEVN"/>
-    <hyperlink ref="G224" r:id="rId7" display="https://player.bilibili.com/player.html?bvid=BV1C1viBcEeP" tooltip="https://player.bilibili.com/player.html?bvid=BV1C1viBcEeP"/>
-    <hyperlink ref="G225" r:id="rId8" display="https://player.bilibili.com/player.html?bvid=BV1N7qwBgELv" tooltip="https://player.bilibili.com/player.html?bvid=BV1N7qwBgELv"/>
-    <hyperlink ref="G226" r:id="rId9" display="https://player.bilibili.com/player.html?bvid=BV1NzihB9E9P" tooltip="https://player.bilibili.com/player.html?bvid=BV1NzihB9E9P"/>
-    <hyperlink ref="G227" r:id="rId10" display="https://player.bilibili.com/player.html?bvid=BV1QGB2B5Eay" tooltip="https://player.bilibili.com/player.html?bvid=BV1QGB2B5Eay"/>
-    <hyperlink ref="I228" r:id="rId11" display="https://x.com/Kanon_Takao/status/1881913308317691905"/>
-    <hyperlink ref="I233" r:id="rId12" display="https://x.com/Kanon_Takao/status/1885705318468096355"/>
-    <hyperlink ref="I234" r:id="rId13" display="https://x.com/Kanon_Takao/status/1890053441181143405"/>
-    <hyperlink ref="G236" r:id="rId14" display="https://player.bilibili.com/player.html?bvid=BV18LKFesEYL" tooltip="https://player.bilibili.com/player.html?bvid=BV18LKFesEYL"/>
-    <hyperlink ref="I243" r:id="rId15" display="https://x.com/sasakirico/status/1900154861234381115"/>
-    <hyperlink ref="I246" r:id="rId16" display="https://x.com/Kanon_Takao/status/1900138654317895759"/>
-    <hyperlink ref="G250" r:id="rId17" display="https://player.bilibili.com/player.html?bvid=BV1ihQ5YzESq" tooltip="https://player.bilibili.com/player.html?bvid=BV1ihQ5YzESq"/>
-    <hyperlink ref="I256" r:id="rId18" display="https://x.com/Kanon_Takao/status/1900197144524407076"/>
-    <hyperlink ref="G257" r:id="rId19" display="https://player.bilibili.com/player.html?bvid=BV1dYGE61EPQ" tooltip="https://player.bilibili.com/player.html?bvid=BV1dYGE61EPQ"/>
-    <hyperlink ref="G258" r:id="rId20" display="https://player.bilibili.com/player.html?bvid=BV1JDVN6DE14" tooltip="https://player.bilibili.com/player.html?bvid=BV1JDVN6DE14"/>
-    <hyperlink ref="G259" r:id="rId21" display="https://player.bilibili.com/player.html?bvid=BV1QhV866EaJ" tooltip="https://player.bilibili.com/player.html?bvid=BV1QhV866EaJ"/>
-    <hyperlink ref="G260" r:id="rId22" display="https://player.bilibili.com/player.html?bvid=BV1gX7y64EkW" tooltip="https://player.bilibili.com/player.html?bvid=BV1gX7y64EkW"/>
-    <hyperlink ref="G261" r:id="rId23" display="https://player.bilibili.com/player.html?bvid=BV1bqMM6bEGw" tooltip="https://player.bilibili.com/player.html?bvid=BV1bqMM6bEGw"/>
-    <hyperlink ref="G262" r:id="rId24" display="https://player.bilibili.com/player.html?bvid=BV13qNx6rEcr" tooltip="https://player.bilibili.com/player.html?bvid=BV13qNx6rEcr"/>
-    <hyperlink ref="G263" r:id="rId25" display="https://player.bilibili.com/player.html?bvid=BV1KEKB6TEgq" tooltip="https://player.bilibili.com/player.html?bvid=BV1KEKB6TEgq"/>
-    <hyperlink ref="G264" r:id="rId26" display="https://player.bilibili.com/player.html?bvid=BV1XRKH6iEf6" tooltip="https://player.bilibili.com/player.html?bvid=BV1XRKH6iEf6"/>
-    <hyperlink ref="I269" r:id="rId27" display="https://x.com/sasakirico/status/1902740705275240514"/>
-    <hyperlink ref="I274" r:id="rId28" display="https://x.com/Kanon_Takao/status/1902728244434190745"/>
-    <hyperlink ref="I276" r:id="rId29" display="https://x.com/sasakirico/status/1902730571341840390"/>
-    <hyperlink ref="G277" r:id="rId30" display="https://player.bilibili.com/player.html?bvid=BV1RZXYYoEDi" tooltip="https://player.bilibili.com/player.html?bvid=BV1RZXYYoEDi"/>
-    <hyperlink ref="G278" r:id="rId31" display="https://player.bilibili.com/player.html?bvid=BV1vZXYYoEgd" tooltip="https://player.bilibili.com/player.html?bvid=BV1vZXYYoEgd"/>
-    <hyperlink ref="I328" r:id="rId32" display="https://www.bilibili.com/video/BV1EvcdenE9h"/>
-    <hyperlink ref="I335" r:id="rId33" display="https://www.bilibili.com/video/BV1RtZmYGE3a"/>
-    <hyperlink ref="I368" r:id="rId34" display="https://www.bilibili.com/video/BV1RV2eBeEAd"/>
-    <hyperlink ref="I379" r:id="rId35" display="https://www.acfun.cn/v/ac48737511"/>
-    <hyperlink ref="I388" r:id="rId36" display="https://www.acfun.cn/v/ac48832641" tooltip="https://www.acfun.cn/v/ac48832641"/>
-    <hyperlink ref="I389" r:id="rId37" display="https://www.acfun.cn/v/ac48832628" tooltip="https://www.acfun.cn/v/ac48832628"/>
-    <hyperlink ref="I400" r:id="rId38" display="https://www.acfun.cn/v/ac48832656"/>
-    <hyperlink ref="I403" r:id="rId39" display="https://www.bilibili.com/video/BV1TFJW6FEeP"/>
-    <hyperlink ref="I406" r:id="rId40" display="https://www.bilibili.com/video/BV18RdHBnELz"/>
-    <hyperlink ref="I423" r:id="rId41" display="https://www.acfun.cn/v/ac48645465" tooltip="https://www.acfun.cn/v/ac48645465"/>
-    <hyperlink ref="I424" r:id="rId42" display="https://www.acfun.cn/v/ac48644820" tooltip="https://www.acfun.cn/v/ac48644820"/>
-    <hyperlink ref="I430" r:id="rId43" display="https://www.bilibili.com/video/BV17iYj6bE6G" tooltip="https://www.bilibili.com/video/BV17iYj6bE6G"/>
-    <hyperlink ref="I588" r:id="rId44" display="https://www.bilibili.com/video/BV1QcKs6gECv"/>
-    <hyperlink ref="I590" r:id="rId45" display="https://x.com/sasakirico/status/1902729137560899747"/>
-    <hyperlink ref="I605" r:id="rId46" display="https://x.com/sasakirico/status/1903291256802791627"/>
-    <hyperlink ref="I607" r:id="rId47" display="https://x.com/sasakirico/status/1904171422273925132" tooltip="https://x.com/sasakirico/status/1904171422273925132"/>
-    <hyperlink ref="G608" r:id="rId48" display="https://player.bilibili.com/player.html?bvid=BV1WBo2YXEjd" tooltip="https://player.bilibili.com/player.html?bvid=BV1WBo2YXEjd"/>
-    <hyperlink ref="G609" r:id="rId49" display="https://player.bilibili.com/player.html?bvid=BV1GEo2YiEfY" tooltip="https://player.bilibili.com/player.html?bvid=BV1GEo2YiEfY"/>
-    <hyperlink ref="G611" r:id="rId50" display="https://player.bilibili.com/player.html?bvid=BV19WZ3YuEaV" tooltip="https://player.bilibili.com/player.html?bvid=BV19WZ3YuEaV"/>
-    <hyperlink ref="I638" r:id="rId51" display="https://x.com/Kanon_Takao/status/1945307259149426993"/>
-    <hyperlink ref="G678" r:id="rId52" display="https://player.bilibili.com/player.html?bvid=BV1SRpn6vE7X" tooltip="https://player.bilibili.com/player.html?bvid=BV1SRpn6vE7X"/>
-    <hyperlink ref="I689" r:id="rId53" display="https://x.com/Kanon_Takao/status/1719212653686788414"/>
-    <hyperlink ref="I732" r:id="rId54" display="https://x.com/Kanon_Takao/status/1695354653582746087&#10;"/>
-    <hyperlink ref="I742" r:id="rId55" display="https://x.com/Kanon_Takao/status/1706878641228190181"/>
-    <hyperlink ref="I748" r:id="rId56" display="https://x.com/Kanon_Takao/status/1778435557825425791"/>
-    <hyperlink ref="I756" r:id="rId57" display="https://x.com/Watase_Yuzuki/status/1788583833375519131"/>
-    <hyperlink ref="I757" r:id="rId58" display="https://x.com/sasakirico/status/1788580361351705013"/>
-    <hyperlink ref="I762" r:id="rId59" display="https://x.com/sasakirico/status/1808862866583531792"/>
-    <hyperlink ref="I787" r:id="rId60" display="https://x.com/sasakirico/status/1811401646020391283"/>
-    <hyperlink ref="I788" r:id="rId61" display="https://x.com/Watase_Yuzuki/status/1811409554087039215"/>
-    <hyperlink ref="I789" r:id="rId62" display="https://x.com/okada_mei0519/status/1811423552492675263" tooltip="https://x.com/okada_mei0519/status/1811423552492675263"/>
-    <hyperlink ref="I790" r:id="rId63" display="https://x.com/AkaneY_banu/status/1811410459964424285"/>
-    <hyperlink ref="I791" r:id="rId64" display="https://x.com/Kanon_Takao/status/1811400298591932472"/>
-    <hyperlink ref="G792" r:id="rId65" display="https://player.bilibili.com/player.html?bvid=BV1c2Jk66EHo" tooltip="https://player.bilibili.com/player.html?bvid=BV1c2Jk66EHo"/>
-    <hyperlink ref="I794" r:id="rId66" display="https://x.com/Watase_Yuzuki/status/1826629108803272815"/>
-    <hyperlink ref="I802" r:id="rId67" display="https://x.com/okada_mei0519/status/1834253894966542442" tooltip="https://x.com/okada_mei0519/status/1834253894966542442"/>
-    <hyperlink ref="I806" r:id="rId68" display="https://x.com/Kanon_Takao/status/1844390783706898776"/>
-    <hyperlink ref="I808" r:id="rId69" display="https://x.com/AkaneY_banu/status/1859603864254808243"/>
-    <hyperlink ref="I812" r:id="rId70" display="https://x.com/AkaneY_banu/status/1867221048850338259" tooltip="https://x.com/AkaneY_banu/status/1867221048850338259"/>
-    <hyperlink ref="I823" r:id="rId71" display="https://x.com/sasakirico/status/1869755372573212914"/>
-    <hyperlink ref="I824" r:id="rId72" display="https://x.com/okada_mei0519/status/1869758235194069298" tooltip="https://x.com/okada_mei0519/status/1869758235194069298"/>
-    <hyperlink ref="I834" r:id="rId73" display="https://x.com/sasakirico/status/1877375815219863979"/>
-    <hyperlink ref="I835" r:id="rId74" display="https://x.com/okada_mei0519/status/1877385990429352204"/>
-    <hyperlink ref="I836" r:id="rId75" display="https://x.com/AkaneY_banu/status/1877390219382501409" tooltip="https://x.com/AkaneY_banu/status/1877390219382501409"/>
-    <hyperlink ref="I837" r:id="rId76" display="https://x.com/Kanon_Takao/status/1877362746188058860"/>
-    <hyperlink ref="I852" r:id="rId77" display="https://x.com/sasakirico/status/1878772746802639241"/>
-    <hyperlink ref="I853" r:id="rId78" display="https://x.com/Watase_Yuzuki/status/1878770156786372624"/>
-    <hyperlink ref="I854" r:id="rId79" display="https://x.com/AkaneY_banu/status/1878772273953533955"/>
+    <hyperlink ref="I128" r:id="rId1" location="/album?id=198675493" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
+    <hyperlink ref="I210" r:id="rId2" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
+    <hyperlink ref="G212" r:id="rId3" xr:uid="{00000000-0004-0000-0B00-000002000000}"/>
+    <hyperlink ref="G213" r:id="rId4" xr:uid="{00000000-0004-0000-0B00-000003000000}"/>
+    <hyperlink ref="G214" r:id="rId5" xr:uid="{00000000-0004-0000-0B00-000004000000}"/>
+    <hyperlink ref="G215" r:id="rId6" tooltip="https://player.bilibili.com/player.html?bvid=BV1FiBvBFEVN" xr:uid="{00000000-0004-0000-0B00-000005000000}"/>
+    <hyperlink ref="G224" r:id="rId7" tooltip="https://player.bilibili.com/player.html?bvid=BV1C1viBcEeP" xr:uid="{00000000-0004-0000-0B00-000006000000}"/>
+    <hyperlink ref="G225" r:id="rId8" tooltip="https://player.bilibili.com/player.html?bvid=BV1N7qwBgELv" xr:uid="{00000000-0004-0000-0B00-000007000000}"/>
+    <hyperlink ref="G226" r:id="rId9" tooltip="https://player.bilibili.com/player.html?bvid=BV1NzihB9E9P" xr:uid="{00000000-0004-0000-0B00-000008000000}"/>
+    <hyperlink ref="G227" r:id="rId10" tooltip="https://player.bilibili.com/player.html?bvid=BV1QGB2B5Eay" xr:uid="{00000000-0004-0000-0B00-000009000000}"/>
+    <hyperlink ref="I228" r:id="rId11" xr:uid="{00000000-0004-0000-0B00-00000A000000}"/>
+    <hyperlink ref="I233" r:id="rId12" xr:uid="{00000000-0004-0000-0B00-00000B000000}"/>
+    <hyperlink ref="I234" r:id="rId13" xr:uid="{00000000-0004-0000-0B00-00000C000000}"/>
+    <hyperlink ref="G236" r:id="rId14" tooltip="https://player.bilibili.com/player.html?bvid=BV18LKFesEYL" xr:uid="{00000000-0004-0000-0B00-00000D000000}"/>
+    <hyperlink ref="I243" r:id="rId15" xr:uid="{00000000-0004-0000-0B00-00000E000000}"/>
+    <hyperlink ref="I246" r:id="rId16" xr:uid="{00000000-0004-0000-0B00-00000F000000}"/>
+    <hyperlink ref="G250" r:id="rId17" tooltip="https://player.bilibili.com/player.html?bvid=BV1ihQ5YzESq" xr:uid="{00000000-0004-0000-0B00-000010000000}"/>
+    <hyperlink ref="I256" r:id="rId18" xr:uid="{00000000-0004-0000-0B00-000011000000}"/>
+    <hyperlink ref="G257" r:id="rId19" tooltip="https://player.bilibili.com/player.html?bvid=BV1dYGE61EPQ" xr:uid="{00000000-0004-0000-0B00-000012000000}"/>
+    <hyperlink ref="G258" r:id="rId20" tooltip="https://player.bilibili.com/player.html?bvid=BV1JDVN6DE14" xr:uid="{00000000-0004-0000-0B00-000013000000}"/>
+    <hyperlink ref="G259" r:id="rId21" tooltip="https://player.bilibili.com/player.html?bvid=BV1QhV866EaJ" xr:uid="{00000000-0004-0000-0B00-000014000000}"/>
+    <hyperlink ref="G260" r:id="rId22" tooltip="https://player.bilibili.com/player.html?bvid=BV1gX7y64EkW" xr:uid="{00000000-0004-0000-0B00-000015000000}"/>
+    <hyperlink ref="G261" r:id="rId23" tooltip="https://player.bilibili.com/player.html?bvid=BV1bqMM6bEGw" xr:uid="{00000000-0004-0000-0B00-000016000000}"/>
+    <hyperlink ref="G262" r:id="rId24" tooltip="https://player.bilibili.com/player.html?bvid=BV13qNx6rEcr" xr:uid="{00000000-0004-0000-0B00-000017000000}"/>
+    <hyperlink ref="G263" r:id="rId25" tooltip="https://player.bilibili.com/player.html?bvid=BV1KEKB6TEgq" xr:uid="{00000000-0004-0000-0B00-000018000000}"/>
+    <hyperlink ref="G264" r:id="rId26" tooltip="https://player.bilibili.com/player.html?bvid=BV1XRKH6iEf6" xr:uid="{00000000-0004-0000-0B00-000019000000}"/>
+    <hyperlink ref="I269" r:id="rId27" xr:uid="{00000000-0004-0000-0B00-00001A000000}"/>
+    <hyperlink ref="I274" r:id="rId28" xr:uid="{00000000-0004-0000-0B00-00001B000000}"/>
+    <hyperlink ref="I276" r:id="rId29" xr:uid="{00000000-0004-0000-0B00-00001C000000}"/>
+    <hyperlink ref="G277" r:id="rId30" tooltip="https://player.bilibili.com/player.html?bvid=BV1RZXYYoEDi" xr:uid="{00000000-0004-0000-0B00-00001D000000}"/>
+    <hyperlink ref="G278" r:id="rId31" tooltip="https://player.bilibili.com/player.html?bvid=BV1vZXYYoEgd" xr:uid="{00000000-0004-0000-0B00-00001E000000}"/>
+    <hyperlink ref="I328" r:id="rId32" xr:uid="{00000000-0004-0000-0B00-00001F000000}"/>
+    <hyperlink ref="I335" r:id="rId33" xr:uid="{00000000-0004-0000-0B00-000020000000}"/>
+    <hyperlink ref="I368" r:id="rId34" xr:uid="{00000000-0004-0000-0B00-000021000000}"/>
+    <hyperlink ref="I379" r:id="rId35" xr:uid="{00000000-0004-0000-0B00-000022000000}"/>
+    <hyperlink ref="I388" r:id="rId36" tooltip="https://www.acfun.cn/v/ac48832641" xr:uid="{00000000-0004-0000-0B00-000023000000}"/>
+    <hyperlink ref="I389" r:id="rId37" tooltip="https://www.acfun.cn/v/ac48832628" xr:uid="{00000000-0004-0000-0B00-000024000000}"/>
+    <hyperlink ref="I400" r:id="rId38" xr:uid="{00000000-0004-0000-0B00-000025000000}"/>
+    <hyperlink ref="I403" r:id="rId39" xr:uid="{00000000-0004-0000-0B00-000026000000}"/>
+    <hyperlink ref="I406" r:id="rId40" xr:uid="{00000000-0004-0000-0B00-000027000000}"/>
+    <hyperlink ref="I423" r:id="rId41" tooltip="https://www.acfun.cn/v/ac48645465" xr:uid="{00000000-0004-0000-0B00-000028000000}"/>
+    <hyperlink ref="I424" r:id="rId42" tooltip="https://www.acfun.cn/v/ac48644820" xr:uid="{00000000-0004-0000-0B00-000029000000}"/>
+    <hyperlink ref="I430" r:id="rId43" tooltip="https://www.bilibili.com/video/BV17iYj6bE6G" xr:uid="{00000000-0004-0000-0B00-00002A000000}"/>
+    <hyperlink ref="I588" r:id="rId44" xr:uid="{00000000-0004-0000-0B00-00002B000000}"/>
+    <hyperlink ref="I590" r:id="rId45" xr:uid="{00000000-0004-0000-0B00-00002C000000}"/>
+    <hyperlink ref="I605" r:id="rId46" xr:uid="{00000000-0004-0000-0B00-00002D000000}"/>
+    <hyperlink ref="I607" r:id="rId47" tooltip="https://x.com/sasakirico/status/1904171422273925132" xr:uid="{00000000-0004-0000-0B00-00002E000000}"/>
+    <hyperlink ref="G608" r:id="rId48" tooltip="https://player.bilibili.com/player.html?bvid=BV1WBo2YXEjd" xr:uid="{00000000-0004-0000-0B00-00002F000000}"/>
+    <hyperlink ref="G609" r:id="rId49" tooltip="https://player.bilibili.com/player.html?bvid=BV1GEo2YiEfY" xr:uid="{00000000-0004-0000-0B00-000030000000}"/>
+    <hyperlink ref="G611" r:id="rId50" tooltip="https://player.bilibili.com/player.html?bvid=BV19WZ3YuEaV" xr:uid="{00000000-0004-0000-0B00-000031000000}"/>
+    <hyperlink ref="I638" r:id="rId51" xr:uid="{00000000-0004-0000-0B00-000032000000}"/>
+    <hyperlink ref="G678" r:id="rId52" tooltip="https://player.bilibili.com/player.html?bvid=BV1SRpn6vE7X" xr:uid="{00000000-0004-0000-0B00-000033000000}"/>
+    <hyperlink ref="I689" r:id="rId53" xr:uid="{00000000-0004-0000-0B00-000034000000}"/>
+    <hyperlink ref="I732" r:id="rId54" xr:uid="{00000000-0004-0000-0B00-000035000000}"/>
+    <hyperlink ref="I742" r:id="rId55" xr:uid="{00000000-0004-0000-0B00-000036000000}"/>
+    <hyperlink ref="I748" r:id="rId56" xr:uid="{00000000-0004-0000-0B00-000037000000}"/>
+    <hyperlink ref="I756" r:id="rId57" xr:uid="{00000000-0004-0000-0B00-000038000000}"/>
+    <hyperlink ref="I757" r:id="rId58" xr:uid="{00000000-0004-0000-0B00-000039000000}"/>
+    <hyperlink ref="I762" r:id="rId59" xr:uid="{00000000-0004-0000-0B00-00003A000000}"/>
+    <hyperlink ref="I787" r:id="rId60" xr:uid="{00000000-0004-0000-0B00-00003B000000}"/>
+    <hyperlink ref="I788" r:id="rId61" xr:uid="{00000000-0004-0000-0B00-00003C000000}"/>
+    <hyperlink ref="I789" r:id="rId62" tooltip="https://x.com/okada_mei0519/status/1811423552492675263" xr:uid="{00000000-0004-0000-0B00-00003D000000}"/>
+    <hyperlink ref="I790" r:id="rId63" xr:uid="{00000000-0004-0000-0B00-00003E000000}"/>
+    <hyperlink ref="I791" r:id="rId64" xr:uid="{00000000-0004-0000-0B00-00003F000000}"/>
+    <hyperlink ref="G792" r:id="rId65" tooltip="https://player.bilibili.com/player.html?bvid=BV1c2Jk66EHo" xr:uid="{00000000-0004-0000-0B00-000040000000}"/>
+    <hyperlink ref="I794" r:id="rId66" xr:uid="{00000000-0004-0000-0B00-000041000000}"/>
+    <hyperlink ref="I802" r:id="rId67" tooltip="https://x.com/okada_mei0519/status/1834253894966542442" xr:uid="{00000000-0004-0000-0B00-000042000000}"/>
+    <hyperlink ref="I806" r:id="rId68" xr:uid="{00000000-0004-0000-0B00-000043000000}"/>
+    <hyperlink ref="I808" r:id="rId69" xr:uid="{00000000-0004-0000-0B00-000044000000}"/>
+    <hyperlink ref="I812" r:id="rId70" tooltip="https://x.com/AkaneY_banu/status/1867221048850338259" xr:uid="{00000000-0004-0000-0B00-000045000000}"/>
+    <hyperlink ref="I823" r:id="rId71" xr:uid="{00000000-0004-0000-0B00-000046000000}"/>
+    <hyperlink ref="I824" r:id="rId72" tooltip="https://x.com/okada_mei0519/status/1869758235194069298" xr:uid="{00000000-0004-0000-0B00-000047000000}"/>
+    <hyperlink ref="I834" r:id="rId73" xr:uid="{00000000-0004-0000-0B00-000048000000}"/>
+    <hyperlink ref="I835" r:id="rId74" xr:uid="{00000000-0004-0000-0B00-000049000000}"/>
+    <hyperlink ref="I836" r:id="rId75" tooltip="https://x.com/AkaneY_banu/status/1877390219382501409" xr:uid="{00000000-0004-0000-0B00-00004A000000}"/>
+    <hyperlink ref="I837" r:id="rId76" xr:uid="{00000000-0004-0000-0B00-00004B000000}"/>
+    <hyperlink ref="I852" r:id="rId77" xr:uid="{00000000-0004-0000-0B00-00004C000000}"/>
+    <hyperlink ref="I853" r:id="rId78" xr:uid="{00000000-0004-0000-0B00-00004D000000}"/>
+    <hyperlink ref="I854" r:id="rId79" xr:uid="{00000000-0004-0000-0B00-00004E000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="43.2727272727273" customWidth="1"/>
-    <col min="2" max="2" width="24.9090909090909" customWidth="1"/>
-    <col min="3" max="3" width="23.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="43.26953125" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" customWidth="1"/>
     <col min="4" max="4" width="74" customWidth="1"/>
-    <col min="5" max="5" width="27.6363636363636" customWidth="1"/>
+    <col min="5" max="5" width="27.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -46044,7 +45470,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" spans="1:6">
+    <row r="19" spans="1:6" ht="16.5" customHeight="1">
       <c r="A19" t="s">
         <v>3427</v>
       </c>
@@ -46064,7 +45490,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" spans="1:6">
+    <row r="20" spans="1:6" ht="16.5" customHeight="1">
       <c r="A20" t="s">
         <v>3427</v>
       </c>
@@ -46225,27 +45651,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="28.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="29.4545454545455" customWidth="1"/>
-    <col min="3" max="3" width="50.2727272727273" customWidth="1"/>
-    <col min="4" max="4" width="13.5454545454545" customWidth="1"/>
-    <col min="5" max="5" width="14.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="11.3636363636364" customWidth="1"/>
-    <col min="7" max="7" width="16.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="37.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="28.6363636363636" customWidth="1"/>
-    <col min="10" max="10" width="23.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" customWidth="1"/>
+    <col min="8" max="8" width="37.26953125" customWidth="1"/>
+    <col min="9" max="9" width="28.6328125" customWidth="1"/>
+    <col min="10" max="10" width="23.26953125" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -47045,27 +46470,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:O40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="22.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="13.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="11.3636363636364" customWidth="1"/>
-    <col min="6" max="6" width="28.6363636363636" customWidth="1"/>
-    <col min="7" max="7" width="22.1818181818182" customWidth="1"/>
-    <col min="8" max="8" width="34.0909090909091" customWidth="1"/>
-    <col min="9" max="9" width="13.5454545454545" customWidth="1"/>
-    <col min="10" max="10" width="51.1818181818182" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
+    <col min="6" max="6" width="28.6328125" customWidth="1"/>
+    <col min="7" max="7" width="22.1796875" customWidth="1"/>
+    <col min="8" max="8" width="34.08984375" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" customWidth="1"/>
+    <col min="10" max="10" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -48560,20 +47984,19 @@
       <c r="E40" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:I205"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="22.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="55.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="6" max="6" width="55.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -48625,7 +48048,7 @@
         <v>70</v>
       </c>
       <c r="H2" s="5">
-        <v>0.209027777777778</v>
+        <v>0.20902777777777801</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -48671,7 +48094,7 @@
         <v>74</v>
       </c>
       <c r="H4" s="5">
-        <v>0.188888888888889</v>
+        <v>0.18888888888888899</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -48757,7 +48180,7 @@
         <v>70</v>
       </c>
       <c r="H8" s="5">
-        <v>0.209027777777778</v>
+        <v>0.20902777777777801</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -48803,7 +48226,7 @@
         <v>74</v>
       </c>
       <c r="H10" s="5">
-        <v>0.188888888888889</v>
+        <v>0.18888888888888899</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -48869,7 +48292,7 @@
         <v>70</v>
       </c>
       <c r="H13" s="5">
-        <v>0.209027777777778</v>
+        <v>0.20902777777777801</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -48915,7 +48338,7 @@
         <v>74</v>
       </c>
       <c r="H15" s="5">
-        <v>0.188888888888889</v>
+        <v>0.18888888888888899</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -49044,7 +48467,7 @@
         <v>4</v>
       </c>
       <c r="H21" s="5">
-        <v>0.205555555555555</v>
+        <v>0.20555555555555499</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -49067,7 +48490,7 @@
         <v>6</v>
       </c>
       <c r="H22" s="5">
-        <v>0.193055555555556</v>
+        <v>0.19305555555555601</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -49113,7 +48536,7 @@
         <v>10</v>
       </c>
       <c r="H24" s="5">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -49136,7 +48559,7 @@
         <v>12</v>
       </c>
       <c r="H25" s="5">
-        <v>0.177083333333333</v>
+        <v>0.17708333333333301</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -49242,7 +48665,7 @@
         <v>4</v>
       </c>
       <c r="H30" s="5">
-        <v>0.205555555555555</v>
+        <v>0.20555555555555499</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -49265,7 +48688,7 @@
         <v>6</v>
       </c>
       <c r="H31" s="5">
-        <v>0.193055555555556</v>
+        <v>0.19305555555555601</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -49311,7 +48734,7 @@
         <v>10</v>
       </c>
       <c r="H33" s="5">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -49334,7 +48757,7 @@
         <v>12</v>
       </c>
       <c r="H34" s="5">
-        <v>0.177083333333333</v>
+        <v>0.17708333333333301</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -49357,7 +48780,7 @@
         <v>24</v>
       </c>
       <c r="H35" s="5">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -49380,7 +48803,7 @@
         <v>26</v>
       </c>
       <c r="H36" s="5">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -49403,7 +48826,7 @@
         <v>3668</v>
       </c>
       <c r="H37" s="5">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -49426,7 +48849,7 @@
         <v>3669</v>
       </c>
       <c r="H38" s="5">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -49469,7 +48892,7 @@
         <v>24</v>
       </c>
       <c r="H40" s="5">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -49492,7 +48915,7 @@
         <v>26</v>
       </c>
       <c r="H41" s="5">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -49515,7 +48938,7 @@
         <v>3668</v>
       </c>
       <c r="H42" s="5">
-        <v>0.186111111111111</v>
+        <v>0.18611111111111101</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -49538,7 +48961,7 @@
         <v>3669</v>
       </c>
       <c r="H43" s="5">
-        <v>0.190972222222222</v>
+        <v>0.19097222222222199</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -49584,7 +49007,7 @@
         <v>3671</v>
       </c>
       <c r="H45" s="5">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -49607,7 +49030,7 @@
         <v>3672</v>
       </c>
       <c r="H46" s="5">
-        <v>0.176388888888889</v>
+        <v>0.17638888888888901</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -49630,7 +49053,7 @@
         <v>14</v>
       </c>
       <c r="H47" s="5">
-        <v>0.184027777777778</v>
+        <v>0.18402777777777801</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -49653,7 +49076,7 @@
         <v>16</v>
       </c>
       <c r="H48" s="5">
-        <v>0.127083333333333</v>
+        <v>0.12708333333333299</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -49676,7 +49099,7 @@
         <v>18</v>
       </c>
       <c r="H49" s="5">
-        <v>0.220138888888889</v>
+        <v>0.22013888888888899</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -49768,7 +49191,7 @@
         <v>3671</v>
       </c>
       <c r="H53" s="5">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -49791,7 +49214,7 @@
         <v>3672</v>
       </c>
       <c r="H54" s="5">
-        <v>0.176388888888889</v>
+        <v>0.17638888888888901</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -49814,7 +49237,7 @@
         <v>14</v>
       </c>
       <c r="H55" s="5">
-        <v>0.184027777777778</v>
+        <v>0.18402777777777801</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -49837,7 +49260,7 @@
         <v>16</v>
       </c>
       <c r="H56" s="5">
-        <v>0.127083333333333</v>
+        <v>0.12708333333333299</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -49860,7 +49283,7 @@
         <v>18</v>
       </c>
       <c r="H57" s="5">
-        <v>0.220138888888889</v>
+        <v>0.22013888888888899</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -49883,7 +49306,7 @@
         <v>28</v>
       </c>
       <c r="H58" s="5">
-        <v>0.217361111111111</v>
+        <v>0.21736111111111101</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -49952,10 +49375,10 @@
         <v>34</v>
       </c>
       <c r="H61" s="5">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" spans="1:9">
+        <v>0.16666666666666699</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15" customHeight="1">
       <c r="A62" t="s">
         <v>3495</v>
       </c>
@@ -49975,7 +49398,7 @@
         <v>36</v>
       </c>
       <c r="H62" s="5">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -50018,7 +49441,7 @@
         <v>28</v>
       </c>
       <c r="H64" s="5">
-        <v>0.217361111111111</v>
+        <v>0.21736111111111101</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -50087,10 +49510,10 @@
         <v>34</v>
       </c>
       <c r="H67" s="5">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1" spans="1:8">
+        <v>0.16666666666666699</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15" customHeight="1">
       <c r="A68" t="s">
         <v>3495</v>
       </c>
@@ -50110,7 +49533,7 @@
         <v>36</v>
       </c>
       <c r="H68" s="5">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -50153,7 +49576,7 @@
         <v>28</v>
       </c>
       <c r="H70" s="5">
-        <v>0.217361111111111</v>
+        <v>0.21736111111111101</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -50222,10 +49645,10 @@
         <v>34</v>
       </c>
       <c r="H73" s="5">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" spans="1:8">
+        <v>0.16666666666666699</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15" customHeight="1">
       <c r="A74" t="s">
         <v>3495</v>
       </c>
@@ -50245,7 +49668,7 @@
         <v>36</v>
       </c>
       <c r="H74" s="5">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -50268,7 +49691,7 @@
         <v>38</v>
       </c>
       <c r="H75" s="5">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -50314,7 +49737,7 @@
         <v>3676</v>
       </c>
       <c r="H77" s="5">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -50337,7 +49760,7 @@
         <v>3677</v>
       </c>
       <c r="H78" s="5">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -50380,7 +49803,7 @@
         <v>38</v>
       </c>
       <c r="H80" s="5">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -50426,7 +49849,7 @@
         <v>3676</v>
       </c>
       <c r="H82" s="5">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -50449,7 +49872,7 @@
         <v>3677</v>
       </c>
       <c r="H83" s="5">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -50472,7 +49895,7 @@
         <v>38</v>
       </c>
       <c r="H84" s="5">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -50495,7 +49918,7 @@
         <v>40</v>
       </c>
       <c r="H85" s="5">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -50518,7 +49941,7 @@
         <v>44</v>
       </c>
       <c r="H86" s="5">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -50541,7 +49964,7 @@
         <v>46</v>
       </c>
       <c r="H87" s="5">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -50564,7 +49987,7 @@
         <v>48</v>
       </c>
       <c r="H88" s="5">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -50587,7 +50010,7 @@
         <v>50</v>
       </c>
       <c r="H89" s="5">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -50610,7 +50033,7 @@
         <v>52</v>
       </c>
       <c r="H90" s="5">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -50653,7 +50076,7 @@
         <v>38</v>
       </c>
       <c r="H92" s="5">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -50676,7 +50099,7 @@
         <v>40</v>
       </c>
       <c r="H93" s="5">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -50699,7 +50122,7 @@
         <v>44</v>
       </c>
       <c r="H94" s="5">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -50722,7 +50145,7 @@
         <v>46</v>
       </c>
       <c r="H95" s="5">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -50745,7 +50168,7 @@
         <v>48</v>
       </c>
       <c r="H96" s="5">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -50768,7 +50191,7 @@
         <v>50</v>
       </c>
       <c r="H97" s="5">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -50791,7 +50214,7 @@
         <v>52</v>
       </c>
       <c r="H98" s="5">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -50834,7 +50257,7 @@
         <v>38</v>
       </c>
       <c r="H100" s="5">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -50857,7 +50280,7 @@
         <v>40</v>
       </c>
       <c r="H101" s="5">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -50880,7 +50303,7 @@
         <v>44</v>
       </c>
       <c r="H102" s="5">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -50903,7 +50326,7 @@
         <v>46</v>
       </c>
       <c r="H103" s="5">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -50926,7 +50349,7 @@
         <v>48</v>
       </c>
       <c r="H104" s="5">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -50949,7 +50372,7 @@
         <v>50</v>
       </c>
       <c r="H105" s="5">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -50972,7 +50395,7 @@
         <v>52</v>
       </c>
       <c r="H106" s="5">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -51315,7 +50738,7 @@
         <v>3693</v>
       </c>
       <c r="H123" s="5">
-        <v>0.229861111111111</v>
+        <v>0.22986111111111099</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -51338,7 +50761,7 @@
         <v>3694</v>
       </c>
       <c r="H124" s="5">
-        <v>0.205555555555555</v>
+        <v>0.20555555555555499</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -51361,7 +50784,7 @@
         <v>3695</v>
       </c>
       <c r="H125" s="5">
-        <v>0.272222222222222</v>
+        <v>0.27222222222222198</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -51384,7 +50807,7 @@
         <v>3696</v>
       </c>
       <c r="H126" s="5">
-        <v>0.2125</v>
+        <v>0.21249999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -51447,7 +50870,7 @@
         <v>54</v>
       </c>
       <c r="H129" s="5">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -51470,7 +50893,7 @@
         <v>58</v>
       </c>
       <c r="H130" s="5">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -51493,7 +50916,7 @@
         <v>3697</v>
       </c>
       <c r="H131" s="5">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -51516,7 +50939,7 @@
         <v>3698</v>
       </c>
       <c r="H132" s="5">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -51619,7 +51042,7 @@
         <v>54</v>
       </c>
       <c r="H137" s="5">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -51642,7 +51065,7 @@
         <v>58</v>
       </c>
       <c r="H138" s="5">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -51665,7 +51088,7 @@
         <v>3697</v>
       </c>
       <c r="H139" s="5">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -51688,7 +51111,7 @@
         <v>3698</v>
       </c>
       <c r="H140" s="5">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -51751,7 +51174,7 @@
         <v>54</v>
       </c>
       <c r="H143" s="5">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -51774,7 +51197,7 @@
         <v>58</v>
       </c>
       <c r="H144" s="5">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -51797,7 +51220,7 @@
         <v>3697</v>
       </c>
       <c r="H145" s="5">
-        <v>0.157638888888889</v>
+        <v>0.15763888888888899</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -51820,7 +51243,7 @@
         <v>3698</v>
       </c>
       <c r="H146" s="5">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -51843,7 +51266,7 @@
         <v>38</v>
       </c>
       <c r="H147" s="5">
-        <v>0.144444444444444</v>
+        <v>0.14444444444444399</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -51866,7 +51289,7 @@
         <v>40</v>
       </c>
       <c r="H148" s="5">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -51889,7 +51312,7 @@
         <v>44</v>
       </c>
       <c r="H149" s="5">
-        <v>0.130555555555556</v>
+        <v>0.13055555555555601</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -51912,7 +51335,7 @@
         <v>46</v>
       </c>
       <c r="H150" s="5">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -51935,7 +51358,7 @@
         <v>48</v>
       </c>
       <c r="H151" s="5">
-        <v>0.159027777777778</v>
+        <v>0.15902777777777799</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -51958,7 +51381,7 @@
         <v>50</v>
       </c>
       <c r="H152" s="5">
-        <v>0.168055555555556</v>
+        <v>0.16805555555555601</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -51981,7 +51404,7 @@
         <v>52</v>
       </c>
       <c r="H153" s="5">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -52090,7 +51513,7 @@
         <v>38</v>
       </c>
       <c r="H158" s="5">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -52159,7 +51582,7 @@
         <v>50</v>
       </c>
       <c r="H161" s="5">
-        <v>0.16875</v>
+        <v>0.16875000000000001</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -52182,7 +51605,7 @@
         <v>40</v>
       </c>
       <c r="H162" s="5">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -52251,7 +51674,7 @@
         <v>56</v>
       </c>
       <c r="H165" s="5">
-        <v>0.154861111111111</v>
+        <v>0.15486111111111101</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -52297,7 +51720,7 @@
         <v>48</v>
       </c>
       <c r="H167" s="5">
-        <v>0.159722222222222</v>
+        <v>0.15972222222222199</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -52343,7 +51766,7 @@
         <v>6</v>
       </c>
       <c r="H169" s="5">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -52389,10 +51812,10 @@
         <v>44</v>
       </c>
       <c r="H171" s="5">
-        <v>0.13125</v>
-      </c>
-    </row>
-    <row r="172" ht="15" customHeight="1" spans="1:8">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="15" customHeight="1">
       <c r="A172" t="s">
         <v>229</v>
       </c>
@@ -52412,7 +51835,7 @@
         <v>36</v>
       </c>
       <c r="H172" s="5">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -52475,7 +51898,7 @@
         <v>38</v>
       </c>
       <c r="H175" s="5">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -52544,7 +51967,7 @@
         <v>50</v>
       </c>
       <c r="H178" s="5">
-        <v>0.16875</v>
+        <v>0.16875000000000001</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -52567,7 +51990,7 @@
         <v>40</v>
       </c>
       <c r="H179" s="5">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -52636,7 +52059,7 @@
         <v>56</v>
       </c>
       <c r="H182" s="5">
-        <v>0.154861111111111</v>
+        <v>0.15486111111111101</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -52682,7 +52105,7 @@
         <v>48</v>
       </c>
       <c r="H184" s="5">
-        <v>0.159722222222222</v>
+        <v>0.15972222222222199</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -52728,7 +52151,7 @@
         <v>6</v>
       </c>
       <c r="H186" s="5">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -52774,10 +52197,10 @@
         <v>44</v>
       </c>
       <c r="H188" s="5">
-        <v>0.13125</v>
-      </c>
-    </row>
-    <row r="189" ht="15" customHeight="1" spans="1:8">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" ht="15" customHeight="1">
       <c r="A189" t="s">
         <v>229</v>
       </c>
@@ -52797,7 +52220,7 @@
         <v>36</v>
       </c>
       <c r="H189" s="5">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -52840,7 +52263,7 @@
         <v>38</v>
       </c>
       <c r="H191" s="5">
-        <v>0.145138888888889</v>
+        <v>0.14513888888888901</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -52909,7 +52332,7 @@
         <v>50</v>
       </c>
       <c r="H194" s="5">
-        <v>0.16875</v>
+        <v>0.16875000000000001</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -52932,7 +52355,7 @@
         <v>40</v>
       </c>
       <c r="H195" s="5">
-        <v>0.1625</v>
+        <v>0.16250000000000001</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -53001,7 +52424,7 @@
         <v>56</v>
       </c>
       <c r="H198" s="5">
-        <v>0.154861111111111</v>
+        <v>0.15486111111111101</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -53047,7 +52470,7 @@
         <v>48</v>
       </c>
       <c r="H200" s="5">
-        <v>0.159722222222222</v>
+        <v>0.15972222222222199</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -53093,7 +52516,7 @@
         <v>6</v>
       </c>
       <c r="H202" s="5">
-        <v>0.19375</v>
+        <v>0.19375000000000001</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -53139,10 +52562,10 @@
         <v>44</v>
       </c>
       <c r="H204" s="5">
-        <v>0.13125</v>
-      </c>
-    </row>
-    <row r="205" ht="15" customHeight="1" spans="1:8">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="15" customHeight="1">
       <c r="A205" t="s">
         <v>229</v>
       </c>
@@ -53162,26 +52585,25 @@
         <v>36</v>
       </c>
       <c r="H205" s="5">
-        <v>0.199305555555556</v>
+        <v>0.19930555555555601</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="33.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="24.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="10.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="25.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" customWidth="1"/>
+    <col min="5" max="5" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -53326,7 +52748,7 @@
         <v>3729</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" t="s">
         <v>3503</v>
       </c>
@@ -53837,14 +53259,13 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:Q152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
@@ -53867,7 +53288,7 @@
     <col min="17" max="17" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:17">
+    <row r="1" spans="1:17" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>3770</v>
       </c>
@@ -54693,7 +54114,7 @@
         <v>3913</v>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1" spans="1:17">
+    <row r="18" spans="1:17" ht="28" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>3914</v>
       </c>
@@ -55081,7 +54502,7 @@
         <v>3975</v>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1" spans="1:17">
+    <row r="26" spans="1:17" ht="28" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>3976</v>
       </c>
@@ -55128,7 +54549,7 @@
         <v>3953</v>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1" spans="1:17">
+    <row r="27" spans="1:17" ht="42" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>3985</v>
       </c>
@@ -55510,7 +54931,7 @@
         <v>4033</v>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1" spans="1:17">
+    <row r="35" spans="1:17" ht="28" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>4048</v>
       </c>
@@ -55804,7 +55225,7 @@
         <v>4072</v>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1" spans="1:17">
+    <row r="41" spans="1:17" ht="28" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>4096</v>
       </c>
@@ -56292,7 +55713,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="51" ht="28" customHeight="1" spans="1:17">
+    <row r="51" spans="1:17" ht="28" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>4171</v>
       </c>
@@ -56392,7 +55813,7 @@
         <v>4189</v>
       </c>
     </row>
-    <row r="53" ht="28" customHeight="1" spans="1:17">
+    <row r="53" spans="1:17" ht="28" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>4190</v>
       </c>
@@ -56589,7 +56010,7 @@
         <v>4220</v>
       </c>
     </row>
-    <row r="57" ht="84" customHeight="1" spans="1:17">
+    <row r="57" spans="1:17" ht="84" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>4221</v>
       </c>
@@ -56836,7 +56257,7 @@
         <v>4262</v>
       </c>
     </row>
-    <row r="62" ht="224" customHeight="1" spans="1:17">
+    <row r="62" spans="1:17" ht="224" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>4263</v>
       </c>
@@ -56883,7 +56304,7 @@
         <v>4271</v>
       </c>
     </row>
-    <row r="63" ht="28" customHeight="1" spans="1:17">
+    <row r="63" spans="1:17" ht="28" customHeight="1">
       <c r="A63" s="2" t="s">
         <v>4272</v>
       </c>
@@ -56923,7 +56344,6 @@
       <c r="N63" t="s">
         <v>4279</v>
       </c>
-      <c r="O63"/>
     </row>
     <row r="64" spans="1:17">
       <c r="A64" s="2" t="s">
@@ -56965,9 +56385,8 @@
       <c r="N64" t="s">
         <v>4285</v>
       </c>
-      <c r="O64"/>
-    </row>
-    <row r="65" ht="28" customHeight="1" spans="1:15">
+    </row>
+    <row r="65" spans="1:15" ht="28" customHeight="1">
       <c r="A65" s="2" t="s">
         <v>4286</v>
       </c>
@@ -57007,7 +56426,6 @@
       <c r="N65" t="s">
         <v>4292</v>
       </c>
-      <c r="O65"/>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="2" t="s">
@@ -57049,7 +56467,6 @@
       <c r="N66" t="s">
         <v>4299</v>
       </c>
-      <c r="O66"/>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="2" t="s">
@@ -57091,7 +56508,6 @@
       <c r="N67" t="s">
         <v>4306</v>
       </c>
-      <c r="O67"/>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="2" t="s">
@@ -57130,9 +56546,8 @@
       <c r="L68" s="2" t="s">
         <v>3787</v>
       </c>
-      <c r="O68"/>
-    </row>
-    <row r="69" ht="112" customHeight="1" spans="1:15">
+    </row>
+    <row r="69" spans="1:15" ht="112" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>4313</v>
       </c>
@@ -57172,7 +56587,6 @@
       <c r="N69" t="s">
         <v>4320</v>
       </c>
-      <c r="O69"/>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="2" t="s">
@@ -57214,7 +56628,6 @@
       <c r="N70" t="s">
         <v>4327</v>
       </c>
-      <c r="O70"/>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="2" t="s">
@@ -57256,7 +56669,6 @@
       <c r="N71" t="s">
         <v>4334</v>
       </c>
-      <c r="O71"/>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="2" t="s">
@@ -57298,7 +56710,6 @@
       <c r="N72" t="s">
         <v>4341</v>
       </c>
-      <c r="O72"/>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" s="2" t="s">
@@ -57642,7 +57053,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="82" ht="56" customHeight="1" spans="1:12">
+    <row r="82" spans="1:12" ht="56" customHeight="1">
       <c r="A82" s="2" t="s">
         <v>4395</v>
       </c>
@@ -57718,7 +57129,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="84" ht="28" customHeight="1" spans="1:12">
+    <row r="84" spans="1:12" ht="28" customHeight="1">
       <c r="A84" s="2" t="s">
         <v>4408</v>
       </c>
@@ -57756,7 +57167,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="85" ht="28" customHeight="1" spans="1:12">
+    <row r="85" spans="1:12" ht="28" customHeight="1">
       <c r="A85" s="2" t="s">
         <v>4414</v>
       </c>
@@ -58478,7 +57889,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="104" ht="28" customHeight="1" spans="1:12">
+    <row r="104" spans="1:12" ht="28" customHeight="1">
       <c r="A104" s="2" t="s">
         <v>4530</v>
       </c>
@@ -58972,7 +58383,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="117" ht="28" customHeight="1" spans="1:12">
+    <row r="117" spans="1:12" ht="28" customHeight="1">
       <c r="A117" s="2" t="s">
         <v>4609</v>
       </c>
@@ -59010,7 +58421,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="118" ht="28" customHeight="1" spans="1:12">
+    <row r="118" spans="1:12" ht="28" customHeight="1">
       <c r="A118" s="2" t="s">
         <v>4616</v>
       </c>
@@ -59352,7 +58763,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="127" ht="28" customHeight="1" spans="1:12">
+    <row r="127" spans="1:12" ht="28" customHeight="1">
       <c r="A127" s="2" t="s">
         <v>4671</v>
       </c>
@@ -59618,7 +59029,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="134" ht="168" customHeight="1" spans="1:12">
+    <row r="134" spans="1:12" ht="168" customHeight="1">
       <c r="A134" s="2" t="s">
         <v>4715</v>
       </c>
@@ -60278,29 +59689,27 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L152" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:L152" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I6" r:id="rId3" display="【奏李组】关于李子担心弄坏弄弄柔弱的身体的那些时候 邦TV#215 #203切片=&gt;https://www.bilibili.com/video/BV1uacQzjEFR|【奏李组】24年初的双月小故事：弄李还需要商量动作的清纯时候 邦TV#203切片=&gt;https://www.bilibili.com/video/BV1YgRbB6EvU|【奏李组】同队恋爱的危险分子潜伏期人物介绍by受害者 邦TV#203切片=&gt;https://www.bilibili.com/video/BV14H5q69E4H|【奏李组】已经在live上演杂技的爱吃醋的佐佐木李子 邦TV#203切片=&gt;https://www.bilibili.com/video/BV1aoLV6iEe2|【奏李组】后脑勺长着头发的福尔图娜（幸运女神） 邦TV#203切片=&gt;https://www.bilibili.com/video/BV18mLz6BECd"/>
+    <hyperlink ref="I6" r:id="rId1" display="【奏李组】关于李子担心弄坏弄弄柔弱的身体的那些时候 邦TV#215 #203切片=&gt;https://www.bilibili.com/video/BV1uacQzjEFR|【奏李组】24年初的双月小故事：弄李还需要商量动作的清纯时候 邦TV#203切片=&gt;https://www.bilibili.com/video/BV1YgRbB6EvU|【奏李组】同队恋爱的危险分子潜伏期人物介绍by受害者 邦TV#203切片=&gt;https://www.bilibili.com/video/BV14H5q69E4H|【奏李组】已经在live上演杂技的爱吃醋的佐佐木李子 邦TV#203切片=&gt;https://www.bilibili.com/video/BV1aoLV6iEe2|【奏李组】后脑勺长着头发的福尔图娜（幸运女神） 邦TV#203切片=&gt;https://www.bilibili.com/video/BV18mLz6BECd" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="65.1818181818182" customWidth="1"/>
+    <col min="3" max="3" width="65.1796875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -60374,7 +59783,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" ht="21" hidden="1" customHeight="1" spans="1:4">
+    <row r="6" spans="1:4" ht="21" hidden="1" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>105</v>
       </c>
@@ -60386,7 +59795,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" hidden="1" spans="1:4">
+    <row r="7" spans="1:4" hidden="1">
       <c r="A7" s="2" t="s">
         <v>105</v>
       </c>
@@ -60426,7 +59835,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:4">
+    <row r="10" spans="1:4" hidden="1">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -60760,30 +60169,29 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D33" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:D33" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="equal" val="similar"/>
-        <customFilter operator="equal" val="combine"/>
-      </customFilters>
+      <filters>
+        <filter val="similar"/>
+        <filter val="combine"/>
+      </filters>
     </filterColumn>
-    <extLst/>
   </autoFilter>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="117.181818181818" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="117.1796875" customWidth="1"/>
     <col min="3" max="3" width="9" style="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -61107,23 +60515,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.6363636363636" customWidth="1"/>
-    <col min="2" max="2" width="52.6363636363636" customWidth="1"/>
-    <col min="3" max="3" width="16.6363636363636" customWidth="1"/>
-    <col min="4" max="4" width="12.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" customWidth="1"/>
+    <col min="2" max="2" width="52.6328125" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61378,7 +60786,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" spans="1:4">
+    <row r="19" spans="1:4" ht="16.5" customHeight="1">
       <c r="A19" t="s">
         <v>219</v>
       </c>
@@ -61621,10 +61029,10 @@
         <v>219</v>
       </c>
       <c r="B36" t="s">
-        <v>244</v>
+        <v>3448</v>
       </c>
       <c r="C36" s="8">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
@@ -61635,7 +61043,7 @@
         <v>219</v>
       </c>
       <c r="B37" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C37" s="8">
         <v>46316</v>
@@ -61644,40 +61052,54 @@
         <v>243</v>
       </c>
     </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>219</v>
+      </c>
+      <c r="B38" t="s">
+        <v>245</v>
+      </c>
+      <c r="C38" s="8">
+        <v>46316</v>
+      </c>
+      <c r="D38" t="s">
+        <v>243</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A36 A37 A2:A35 A38:A1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"song,live,interview,discography"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D36 D37 D2:D35 D38:D998">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D999" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:P38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="29.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="57.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="11.3636363636364" customWidth="1"/>
+    <col min="1" max="2" width="29.7265625" customWidth="1"/>
+    <col min="3" max="3" width="57.90625" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
     <col min="5" max="5" width="20" style="13" customWidth="1"/>
-    <col min="6" max="6" width="23.2727272727273" customWidth="1"/>
-    <col min="7" max="7" width="9.27272727272727" customWidth="1"/>
-    <col min="8" max="8" width="25.1818181818182" customWidth="1"/>
-    <col min="9" max="9" width="38.3636363636364" customWidth="1"/>
-    <col min="10" max="10" width="35.1818181818182" customWidth="1"/>
-    <col min="11" max="11" width="55.6363636363636" customWidth="1"/>
-    <col min="12" max="12" width="51.3636363636364" customWidth="1"/>
-    <col min="13" max="14" width="50.6363636363636" customWidth="1"/>
-    <col min="15" max="15" width="51.3636363636364" customWidth="1"/>
-    <col min="16" max="16" width="21.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="23.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" customWidth="1"/>
+    <col min="8" max="8" width="25.1796875" customWidth="1"/>
+    <col min="9" max="9" width="38.36328125" customWidth="1"/>
+    <col min="10" max="10" width="35.1796875" customWidth="1"/>
+    <col min="11" max="11" width="55.6328125" customWidth="1"/>
+    <col min="12" max="12" width="51.36328125" customWidth="1"/>
+    <col min="13" max="14" width="50.6328125" customWidth="1"/>
+    <col min="15" max="15" width="51.36328125" customWidth="1"/>
+    <col min="16" max="16" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -61980,7 +61402,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:16">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -62030,7 +61452,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="8" ht="15.5" customHeight="1" spans="1:16">
+    <row r="8" spans="1:16" ht="15.5" customHeight="1">
       <c r="A8" s="43" t="s">
         <v>310</v>
       </c>
@@ -62124,7 +61546,7 @@
       </c>
       <c r="P9" s="43"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:16">
+    <row r="10" spans="1:16" ht="15" customHeight="1">
       <c r="A10" s="43" t="s">
         <v>18</v>
       </c>
@@ -62170,7 +61592,7 @@
       </c>
       <c r="P10" s="43"/>
     </row>
-    <row r="11" ht="14.5" customHeight="1" spans="1:16">
+    <row r="11" spans="1:16" ht="14.5" customHeight="1">
       <c r="A11" s="11" t="s">
         <v>20</v>
       </c>
@@ -62216,7 +61638,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="12" ht="14.5" customHeight="1" spans="1:16">
+    <row r="12" spans="1:16" ht="14.5" customHeight="1">
       <c r="A12" s="11" t="s">
         <v>22</v>
       </c>
@@ -62412,7 +61834,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="16" ht="14.5" customHeight="1" spans="1:16">
+    <row r="16" spans="1:16" ht="14.5" customHeight="1">
       <c r="A16" t="s">
         <v>361</v>
       </c>
@@ -62512,7 +61934,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:16">
+    <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" t="s">
         <v>377</v>
       </c>
@@ -62562,7 +61984,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:16">
+    <row r="19" spans="1:16" ht="15" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
@@ -62712,7 +62134,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="22" ht="14.5" customHeight="1" spans="1:16">
+    <row r="22" spans="1:16" ht="14.5" customHeight="1">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -62762,7 +62184,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="23" ht="14.5" customHeight="1" spans="1:16">
+    <row r="23" spans="1:16" ht="14.5" customHeight="1">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -62912,7 +62334,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:16">
+    <row r="26" spans="1:16" ht="14.5" customHeight="1">
       <c r="A26" t="s">
         <v>436</v>
       </c>
@@ -62962,7 +62384,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="27" s="43" customFormat="1" ht="15.5" customHeight="1" spans="1:16">
+    <row r="27" spans="1:16" s="43" customFormat="1" ht="15.5" customHeight="1">
       <c r="A27" t="s">
         <v>444</v>
       </c>
@@ -63012,7 +62434,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="28" s="43" customFormat="1" spans="1:16">
+    <row r="28" spans="1:16" s="43" customFormat="1">
       <c r="A28" s="55" t="s">
         <v>54</v>
       </c>
@@ -63062,7 +62484,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" s="43" customFormat="1" spans="1:16">
+    <row r="29" spans="1:16" s="43" customFormat="1">
       <c r="A29" t="s">
         <v>458</v>
       </c>
@@ -63112,7 +62534,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="30" s="11" customFormat="1" spans="1:16">
+    <row r="30" spans="1:16" s="11" customFormat="1">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -63162,7 +62584,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="31" s="11" customFormat="1" spans="1:16">
+    <row r="31" spans="1:16" s="11" customFormat="1">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -63212,7 +62634,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:16">
+    <row r="32" spans="1:16" ht="14.5" customHeight="1">
       <c r="A32" t="s">
         <v>482</v>
       </c>
@@ -63344,7 +62766,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="35" ht="98" customHeight="1" spans="1:16">
+    <row r="35" spans="1:16" ht="98" customHeight="1">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -63530,36 +62952,34 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P38" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:P38" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="L7" r:id="rId1" display="https://www.bilibili.com/video/BV1MP411h759"/>
-    <hyperlink ref="L13" r:id="rId2" display="https://www.bilibili.com/video/BV1Xg4y1k7GH"/>
-    <hyperlink ref="L14" r:id="rId3" display="https://www.bilibili.com/video/BV1Ai4y167MU"/>
-    <hyperlink ref="L18" r:id="rId4" display="https://www.bilibili.com/video/BV1Cz421e79N"/>
-    <hyperlink ref="L22" r:id="rId5" display="https://www.bilibili.com/video/BV1EvcdenE9h"/>
-    <hyperlink ref="L27" r:id="rId6" display="https://www.bilibili.com/video/BV1RtZmYGE3a"/>
-    <hyperlink ref="L32" r:id="rId7" display="https://www.bilibili.com/video/BV1X58m6AENA"/>
-    <hyperlink ref="L35" r:id="rId8" display="https://www.bilibili.com/video/BV1ZLeG6JEha"/>
+    <hyperlink ref="L7" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="L13" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="L14" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="L18" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="L22" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="L27" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="L32" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="L35" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:E200"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="32.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="67.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="27.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="13.5454545454545" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" customWidth="1"/>
+    <col min="3" max="3" width="67.54296875" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -63607,7 +63027,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="4" ht="14.5" customHeight="1" spans="1:5">
+    <row r="4" spans="1:5" ht="14.5" customHeight="1">
       <c r="A4" t="s">
         <v>368</v>
       </c>
@@ -63694,7 +63114,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" spans="1:5">
+    <row r="10" spans="1:5" ht="13.5" customHeight="1">
       <c r="A10" t="s">
         <v>274</v>
       </c>
@@ -63904,7 +63324,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:4">
+    <row r="25" spans="1:4" ht="18" customHeight="1">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -63918,7 +63338,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1" spans="1:4">
+    <row r="26" spans="1:4" ht="18" customHeight="1">
       <c r="A26" t="s">
         <v>341</v>
       </c>
@@ -64016,7 +63436,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:5">
+    <row r="33" spans="1:5" ht="14.5" customHeight="1">
       <c r="A33" t="s">
         <v>354</v>
       </c>
@@ -64033,7 +63453,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:5">
+    <row r="34" spans="1:5" ht="14.5" customHeight="1">
       <c r="A34" t="s">
         <v>361</v>
       </c>
@@ -64050,7 +63470,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="1:5">
+    <row r="35" spans="1:5" ht="14.5" customHeight="1">
       <c r="A35" t="s">
         <v>377</v>
       </c>
@@ -64067,7 +63487,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="36" ht="15.5" customHeight="1" spans="1:5">
+    <row r="36" spans="1:5" ht="15.5" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>36</v>
       </c>
@@ -64096,7 +63516,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="15">
       <c r="A38" s="4" t="s">
         <v>38</v>
       </c>
@@ -64108,7 +63528,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:5">
+    <row r="39" spans="1:5" ht="15" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>38</v>
       </c>
@@ -64125,7 +63545,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:5">
+    <row r="40" spans="1:5" ht="15" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>44</v>
       </c>
@@ -64138,7 +63558,7 @@
       </c>
       <c r="E40" s="8"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:5">
+    <row r="41" spans="1:5" ht="15" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>44</v>
       </c>
@@ -64155,7 +63575,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:5">
+    <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>46</v>
       </c>
@@ -64168,7 +63588,7 @@
       </c>
       <c r="E42" s="8"/>
     </row>
-    <row r="43" ht="14.5" customHeight="1" spans="1:5">
+    <row r="43" spans="1:5" ht="14.5" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>46</v>
       </c>
@@ -64185,7 +63605,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="44" ht="14.5" customHeight="1" spans="1:5">
+    <row r="44" spans="1:5" ht="14.5" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>427</v>
       </c>
@@ -64198,7 +63618,7 @@
       </c>
       <c r="E44" s="8"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:5">
+    <row r="45" spans="1:5" ht="15" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>427</v>
       </c>
@@ -64215,7 +63635,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:5">
+    <row r="46" spans="1:5" ht="15" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>436</v>
       </c>
@@ -64228,7 +63648,7 @@
       </c>
       <c r="E46" s="8"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:5">
+    <row r="47" spans="1:5" ht="15" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>436</v>
       </c>
@@ -64245,7 +63665,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:5">
+    <row r="48" spans="1:5" ht="15" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>444</v>
       </c>
@@ -64258,7 +63678,7 @@
       </c>
       <c r="E48" s="8"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:5">
+    <row r="49" spans="1:5" ht="15" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>444</v>
       </c>
@@ -64846,37 +64266,35 @@
       <c r="C200" s="42"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D62" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:D62" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C15" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="C17" r:id="rId2" display="https://www.animatetimes.com/news/details.php?id=1711341102&amp;p=2"/>
-    <hyperlink ref="C19" r:id="rId3" display="https://www.lisani.jp/0000271996/4/?show_more=1"/>
-    <hyperlink ref="C23" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="B26" r:id="rId4" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n&#10;佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n&#10;高尾：就像剑一样呢。 \n&#10;佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n&#10;高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n&#10;佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n&#10;——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n&#10;佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n&#10;——也是一首很容易入耳的歌呢。\n&#10;高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n&#10;佐佐木： 谢谢——！"/>
-    <hyperlink ref="C26" r:id="rId4" display="https://www.animatetimes.com/news/details.php?id=1711342991&amp;p=2"/>
-    <hyperlink ref="C28" r:id="rId5" display="https://www.lisani.jp/0000256138/?show_more=1"/>
-    <hyperlink ref="C29" r:id="rId6" display="https://www.animatetimes.com/news/details.php?id=1711342991"/>
-    <hyperlink ref="C32" r:id="rId7" display="https://natalie.mu/music/pp/avemujica01/page/2"/>
+    <hyperlink ref="C15" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="C17" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="C19" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="C23" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="B26" r:id="rId5" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n_x000a_佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n_x000a_高尾：就像剑一样呢。 \n_x000a_佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n_x000a_高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n_x000a_佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n_x000a_——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n_x000a_佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n_x000a_——也是一首很容易入耳的歌呢。\n_x000a_高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n_x000a_佐佐木： 谢谢——！" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
+    <hyperlink ref="C26" r:id="rId6" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
+    <hyperlink ref="C28" r:id="rId7" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
+    <hyperlink ref="C29" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
+    <hyperlink ref="C32" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F468"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="12.8181818181818" style="8" customWidth="1"/>
-    <col min="3" max="3" width="49.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="69.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="39.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="29.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" customWidth="1"/>
+    <col min="4" max="4" width="69.26953125" customWidth="1"/>
+    <col min="6" max="6" width="39.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -65144,7 +64562,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" ht="16" customHeight="1">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -65315,7 +64733,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" spans="1:6">
+    <row r="24" spans="1:6" ht="16" customHeight="1">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -65796,7 +65214,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="50" ht="13.5" customHeight="1" spans="1:6">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1">
       <c r="A50" t="s">
         <v>262</v>
       </c>
@@ -66730,7 +66148,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1" spans="1:6">
+    <row r="100" spans="1:6" ht="16" customHeight="1">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -66844,7 +66262,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1" spans="1:6">
+    <row r="106" spans="1:6" ht="16" customHeight="1">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -67052,7 +66470,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1" spans="1:6">
+    <row r="117" spans="1:6" ht="16" customHeight="1">
       <c r="A117" t="s">
         <v>10</v>
       </c>
@@ -67382,7 +66800,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1" spans="1:6">
+    <row r="135" spans="1:6" ht="16" customHeight="1">
       <c r="A135" t="s">
         <v>288</v>
       </c>
@@ -67590,7 +67008,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="146" ht="16" customHeight="1" spans="1:6">
+    <row r="146" spans="1:6" ht="16" customHeight="1">
       <c r="A146" t="s">
         <v>288</v>
       </c>
@@ -67755,7 +67173,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="155" ht="16" customHeight="1" spans="1:6">
+    <row r="155" spans="1:6" ht="16" customHeight="1">
       <c r="A155" t="s">
         <v>58</v>
       </c>
@@ -68045,7 +67463,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="171" ht="16" customHeight="1" spans="1:6">
+    <row r="171" spans="1:6" ht="16" customHeight="1">
       <c r="A171" t="s">
         <v>354</v>
       </c>
@@ -69973,7 +69391,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="274" ht="15" customHeight="1" spans="1:6">
+    <row r="274" spans="1:6" ht="15" customHeight="1">
       <c r="A274" s="4" t="s">
         <v>36</v>
       </c>
@@ -69993,7 +69411,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="275" ht="15" customHeight="1" spans="1:6">
+    <row r="275" spans="1:6" ht="15" customHeight="1">
       <c r="A275" s="4" t="s">
         <v>36</v>
       </c>
@@ -70013,7 +69431,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="276" ht="15" customHeight="1" spans="1:6">
+    <row r="276" spans="1:6" ht="15" customHeight="1">
       <c r="A276" s="4" t="s">
         <v>36</v>
       </c>
@@ -70033,7 +69451,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="277" ht="15" customHeight="1" spans="1:6">
+    <row r="277" spans="1:6" ht="15" customHeight="1">
       <c r="A277" s="4" t="s">
         <v>36</v>
       </c>
@@ -70053,7 +69471,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="278" ht="15" customHeight="1" spans="1:6">
+    <row r="278" spans="1:6" ht="15" customHeight="1">
       <c r="A278" s="4" t="s">
         <v>36</v>
       </c>
@@ -70073,7 +69491,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="279" ht="15" customHeight="1" spans="1:6">
+    <row r="279" spans="1:6" ht="15" customHeight="1">
       <c r="A279" s="4" t="s">
         <v>36</v>
       </c>
@@ -70093,7 +69511,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="280" ht="15" customHeight="1" spans="1:6">
+    <row r="280" spans="1:6" ht="15" customHeight="1">
       <c r="A280" s="4" t="s">
         <v>36</v>
       </c>
@@ -73413,7 +72831,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="458" ht="16" customHeight="1" spans="1:6">
+    <row r="458" spans="1:6" ht="16" customHeight="1">
       <c r="A458" t="s">
         <v>310</v>
       </c>
@@ -73628,259 +73046,258 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F468" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:F468" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.acfun.cn/v/ac47931167" tooltip="https://www.acfun.cn/v/ac47931167"/>
-    <hyperlink ref="F3" r:id="rId2" display="https://www.acfun.cn/v/ac47931167_2"/>
-    <hyperlink ref="F7" r:id="rId3" display="https://www.acfun.cn/v/ac47931167_3"/>
-    <hyperlink ref="F8" r:id="rId4" display="https://www.acfun.cn/v/ac47931167_4"/>
-    <hyperlink ref="F9" r:id="rId5" display="https://www.acfun.cn/v/ac47931167_5"/>
-    <hyperlink ref="F10" r:id="rId6" display="https://www.acfun.cn/v/ac47931167_6"/>
-    <hyperlink ref="F12" r:id="rId7" display="https://www.acfun.cn/v/ac47931167_7"/>
-    <hyperlink ref="F14" r:id="rId8" display="https://www.acfun.cn/v/ac47934758"/>
-    <hyperlink ref="F15" r:id="rId9" display="https://www.acfun.cn/v/ac47934758_2"/>
-    <hyperlink ref="F16" r:id="rId10" display="https://www.acfun.cn/v/ac47934758_3"/>
-    <hyperlink ref="F18" r:id="rId11" display="https://www.acfun.cn/v/ac47934758_4"/>
-    <hyperlink ref="F20" r:id="rId12" display="https://www.acfun.cn/v/ac47934758_5"/>
-    <hyperlink ref="F22" r:id="rId13" display="https://www.acfun.cn/v/ac47934758_6"/>
-    <hyperlink ref="F23" r:id="rId14" display="https://www.acfun.cn/v/ac47934758_7"/>
-    <hyperlink ref="F24" r:id="rId15" display="https://www.acfun.cn/v/ac47934758_8"/>
-    <hyperlink ref="F25" r:id="rId16" display="https://www.acfun.cn/v/ac47934758_9"/>
-    <hyperlink ref="F27" r:id="rId17" display="https://www.acfun.cn/v/ac47934758_10"/>
-    <hyperlink ref="F28" r:id="rId18" display="https://www.acfun.cn/v/ac47934815"/>
-    <hyperlink ref="F29" r:id="rId19" display="https://www.acfun.cn/v/ac47934815_2"/>
-    <hyperlink ref="F31" r:id="rId20" display="https://www.acfun.cn/v/ac47934815_3"/>
-    <hyperlink ref="F32" r:id="rId21" display="https://www.acfun.cn/v/ac47934815_4"/>
-    <hyperlink ref="F33" r:id="rId22" display="https://www.acfun.cn/v/ac47934815_5"/>
-    <hyperlink ref="F34" r:id="rId23" display="https://www.acfun.cn/v/ac47934815_6"/>
-    <hyperlink ref="F39" r:id="rId24" display="https://www.acfun.cn/v/ac47934815_7"/>
-    <hyperlink ref="F69" r:id="rId25" display="https://www.acfun.cn/v/ac47935101_2"/>
-    <hyperlink ref="F71" r:id="rId26" display="https://www.acfun.cn/v/ac47935101_3"/>
-    <hyperlink ref="F73" r:id="rId27" display="https://www.acfun.cn/v/ac47935101_4"/>
-    <hyperlink ref="F74" r:id="rId28" display="https://www.acfun.cn/v/ac47935101_5"/>
-    <hyperlink ref="F75" r:id="rId29" display="https://www.acfun.cn/v/ac47935101_6"/>
-    <hyperlink ref="F76" r:id="rId30" display="https://www.acfun.cn/v/ac47935101_7"/>
-    <hyperlink ref="F77" r:id="rId31" display="https://www.acfun.cn/v/ac47935101_8"/>
-    <hyperlink ref="F78" r:id="rId32" display="https://www.acfun.cn/v/ac47935101_9"/>
-    <hyperlink ref="F80" r:id="rId33" display="https://www.acfun.cn/v/ac47935101_10"/>
-    <hyperlink ref="F87" r:id="rId34" display="https://www.acfun.cn/v/ac48752881_2"/>
-    <hyperlink ref="F101" r:id="rId35" display="https://www.acfun.cn/v/ac47924476_8"/>
-    <hyperlink ref="F105" r:id="rId36" display="https://www.acfun.cn/v/ac47935303"/>
-    <hyperlink ref="F106" r:id="rId37" display="https://www.acfun.cn/v/ac47935303_2"/>
-    <hyperlink ref="F107" r:id="rId38" display="https://www.acfun.cn/v/ac47935303_3"/>
-    <hyperlink ref="F109" r:id="rId39" display="https://www.acfun.cn/v/ac47935303_4"/>
-    <hyperlink ref="F113" r:id="rId40" display="https://www.acfun.cn/v/ac47935303_5"/>
-    <hyperlink ref="F114" r:id="rId41" display="https://www.acfun.cn/v/ac47935303_6"/>
-    <hyperlink ref="F115" r:id="rId42" display="https://www.acfun.cn/v/ac47935303_7"/>
-    <hyperlink ref="F116" r:id="rId43" display="https://www.acfun.cn/v/ac47935303_8"/>
-    <hyperlink ref="F118" r:id="rId44" display="https://www.acfun.cn/v/ac47935303_9"/>
-    <hyperlink ref="F119" r:id="rId45" display="https://www.acfun.cn/v/ac47935303_10"/>
-    <hyperlink ref="F120" r:id="rId46" display="https://www.acfun.cn/v/ac48116488"/>
-    <hyperlink ref="F122" r:id="rId47" display="https://www.acfun.cn/v/ac48116488_2"/>
-    <hyperlink ref="F128" r:id="rId48" display="https://www.acfun.cn/v/ac48116488_3"/>
-    <hyperlink ref="F129" r:id="rId49" display="https://www.acfun.cn/v/ac48116488_4"/>
-    <hyperlink ref="F133" r:id="rId50" display="https://www.acfun.cn/v/ac48116488_5"/>
-    <hyperlink ref="F134" r:id="rId51" display="https://www.acfun.cn/v/ac47934950"/>
-    <hyperlink ref="F135" r:id="rId52" display="https://www.acfun.cn/v/ac47934950_2"/>
-    <hyperlink ref="F136" r:id="rId53" display="https://www.acfun.cn/v/ac47934950_3"/>
-    <hyperlink ref="F138" r:id="rId54" display="https://www.acfun.cn/v/ac47934950_4"/>
-    <hyperlink ref="F140" r:id="rId55" display="https://www.acfun.cn/v/ac47934950_5"/>
-    <hyperlink ref="F141" r:id="rId56" display="https://www.acfun.cn/v/ac47934950_6"/>
-    <hyperlink ref="F142" r:id="rId57" display="https://www.acfun.cn/v/ac47934950_7"/>
-    <hyperlink ref="F143" r:id="rId58" display="https://www.acfun.cn/v/ac47934950_8"/>
-    <hyperlink ref="F149" r:id="rId59" display="https://www.acfun.cn/v/ac47934950_9"/>
-    <hyperlink ref="F167" r:id="rId60" display="https://www.acfun.cn/v/ac48115972_7"/>
-    <hyperlink ref="F168" r:id="rId61" display="https://www.acfun.cn/v/ac47931569" tooltip="https://www.acfun.cn/v/ac47931569"/>
-    <hyperlink ref="F170" r:id="rId62" display="https://www.acfun.cn/v/ac47931569_2"/>
-    <hyperlink ref="F171" r:id="rId63" display="https://www.acfun.cn/v/ac47931569_3"/>
-    <hyperlink ref="F172" r:id="rId64" display="https://www.acfun.cn/v/ac47931569_4"/>
-    <hyperlink ref="F173" r:id="rId65" display="https://www.acfun.cn/v/ac47931569_5"/>
-    <hyperlink ref="F174" r:id="rId66" display="https://www.acfun.cn/v/ac47931569_6"/>
-    <hyperlink ref="F175" r:id="rId67" display="https://www.acfun.cn/v/ac47931569_7"/>
-    <hyperlink ref="F176" r:id="rId68" display="https://www.acfun.cn/v/ac47931569_8"/>
-    <hyperlink ref="F177" r:id="rId69" display="https://www.acfun.cn/v/ac47931569_9"/>
-    <hyperlink ref="F178" r:id="rId70" display="https://www.acfun.cn/v/ac47931569_10"/>
-    <hyperlink ref="F179" r:id="rId71" display="https://www.acfun.cn/v/ac47931603" tooltip="https://www.acfun.cn/v/ac47931603"/>
-    <hyperlink ref="F181" r:id="rId72" display="https://www.acfun.cn/v/ac47931603_2"/>
-    <hyperlink ref="F183" r:id="rId73" display="https://www.acfun.cn/v/ac47931603_3"/>
-    <hyperlink ref="F184" r:id="rId74" display="https://www.acfun.cn/v/ac47931603_4"/>
-    <hyperlink ref="F186" r:id="rId75" display="https://www.acfun.cn/v/ac47931603_5"/>
-    <hyperlink ref="F192" r:id="rId76" display="https://www.acfun.cn/v/ac47931603_6"/>
-    <hyperlink ref="F193" r:id="rId77" display="https://www.acfun.cn/v/ac47931603_7"/>
-    <hyperlink ref="F198" r:id="rId78" display="https://www.acfun.cn/v/ac47931603_8"/>
-    <hyperlink ref="F199" r:id="rId79" display="https://www.acfun.cn/v/ac47933063"/>
-    <hyperlink ref="F201" r:id="rId80" display="https://www.acfun.cn/v/ac47933063_2"/>
-    <hyperlink ref="F202" r:id="rId81" display="https://www.acfun.cn/v/ac47933063_3"/>
-    <hyperlink ref="F203" r:id="rId82" display="https://www.acfun.cn/v/ac47933063_4"/>
-    <hyperlink ref="F204" r:id="rId83" display="https://www.acfun.cn/v/ac47933063_5"/>
-    <hyperlink ref="F206" r:id="rId84" display="https://www.acfun.cn/v/ac47933063_6"/>
-    <hyperlink ref="F207" r:id="rId85" display="https://www.acfun.cn/v/ac47933063_7"/>
-    <hyperlink ref="F208" r:id="rId86" display="https://www.acfun.cn/v/ac47933063_8"/>
-    <hyperlink ref="F209" r:id="rId87" display="https://www.acfun.cn/v/ac47933063_9"/>
-    <hyperlink ref="F211" r:id="rId88" display="https://www.acfun.cn/v/ac47933063_10"/>
-    <hyperlink ref="F213" r:id="rId89" display="https://www.acfun.cn/v/ac48409409_1" tooltip="https://www.acfun.cn/v/ac48409409_1"/>
-    <hyperlink ref="F219" r:id="rId90" display="https://www.acfun.cn/v/ac48409409_2"/>
-    <hyperlink ref="F220" r:id="rId91" display="https://www.acfun.cn/v/ac48409409_3"/>
-    <hyperlink ref="F225" r:id="rId92" display="https://www.acfun.cn/v/ac48409409_4"/>
-    <hyperlink ref="F235" r:id="rId93" display="https://www.acfun.cn/v/ac47931075"/>
-    <hyperlink ref="F236" r:id="rId94" display="https://www.acfun.cn/v/ac47931075_2"/>
-    <hyperlink ref="F238" r:id="rId95" display="https://www.acfun.cn/v/ac47931075_3"/>
-    <hyperlink ref="F240" r:id="rId96" display="https://www.acfun.cn/v/ac47931075_4"/>
-    <hyperlink ref="F241" r:id="rId97" display="https://www.acfun.cn/v/ac47931075_5"/>
-    <hyperlink ref="F242" r:id="rId98" display="https://www.acfun.cn/v/ac47931075_6"/>
-    <hyperlink ref="F244" r:id="rId99" display="https://www.acfun.cn/v/ac47933675"/>
-    <hyperlink ref="F246" r:id="rId100" display="https://www.acfun.cn/v/ac47933675_2"/>
-    <hyperlink ref="F248" r:id="rId101" display="https://www.acfun.cn/v/ac47933675_3"/>
-    <hyperlink ref="F249" r:id="rId102" display="https://www.acfun.cn/v/ac47933675_4"/>
-    <hyperlink ref="F250" r:id="rId103" display="https://www.acfun.cn/v/ac47933675_5"/>
-    <hyperlink ref="F251" r:id="rId104" display="https://www.acfun.cn/v/ac47933675_6"/>
-    <hyperlink ref="F252" r:id="rId105" display="https://www.acfun.cn/v/ac47933675_7"/>
-    <hyperlink ref="F257" r:id="rId106" display="https://www.acfun.cn/v/ac47933675_8"/>
-    <hyperlink ref="F259" r:id="rId107" display="https://www.acfun.cn/v/ac47934854"/>
-    <hyperlink ref="F260" r:id="rId108" display="https://www.acfun.cn/v/ac47934854_2"/>
-    <hyperlink ref="F261" r:id="rId109" display="https://www.acfun.cn/v/ac47934854_3"/>
-    <hyperlink ref="F262" r:id="rId110" display="https://www.acfun.cn/v/ac47934854_4"/>
-    <hyperlink ref="F263" r:id="rId111" display="https://www.acfun.cn/v/ac47934854_5"/>
-    <hyperlink ref="F264" r:id="rId112" display="https://www.acfun.cn/v/ac47934854_6"/>
-    <hyperlink ref="F266" r:id="rId113" display="https://www.acfun.cn/v/ac47934854_7"/>
-    <hyperlink ref="F272" r:id="rId114" display="https://www.acfun.cn/v/ac47934854_8"/>
-    <hyperlink ref="F274" r:id="rId115" display="https://www.acfun.cn/v/ac47933636"/>
-    <hyperlink ref="F275" r:id="rId116" display="https://www.acfun.cn/v/ac47933636_2"/>
-    <hyperlink ref="F276" r:id="rId117" display="https://www.acfun.cn/v/ac47933636_3"/>
-    <hyperlink ref="F277" r:id="rId118" display="https://www.acfun.cn/v/ac47933636_4"/>
-    <hyperlink ref="F278" r:id="rId119" display="https://www.acfun.cn/v/ac47933636_5"/>
-    <hyperlink ref="F279" r:id="rId120" display="https://www.acfun.cn/v/ac47933636_6"/>
-    <hyperlink ref="F281" r:id="rId121" display="https://www.acfun.cn/v/ac47930865"/>
-    <hyperlink ref="F282" r:id="rId122" display="https://www.acfun.cn/v/ac47930865_2"/>
-    <hyperlink ref="F284" r:id="rId123" display="https://www.acfun.cn/v/ac47930865_3"/>
-    <hyperlink ref="F286" r:id="rId124" display="https://www.acfun.cn/v/ac47930865_4"/>
-    <hyperlink ref="F291" r:id="rId125" display="https://www.acfun.cn/v/ac47930865_5"/>
-    <hyperlink ref="F292" r:id="rId126" display="https://www.acfun.cn/v/ac47930865_6"/>
-    <hyperlink ref="F296" r:id="rId127" display="https://www.acfun.cn/v/ac47932379"/>
-    <hyperlink ref="F297" r:id="rId128" display="https://www.acfun.cn/v/ac47932379_2"/>
-    <hyperlink ref="F298" r:id="rId129" display="https://www.acfun.cn/v/ac47932379_3"/>
-    <hyperlink ref="F299" r:id="rId130" display="https://www.acfun.cn/v/ac47932379_4"/>
-    <hyperlink ref="F300" r:id="rId131" display="https://www.acfun.cn/v/ac47932379_5"/>
-    <hyperlink ref="F301" r:id="rId132" display="https://www.acfun.cn/v/ac47932379_6"/>
-    <hyperlink ref="F304" r:id="rId133" display="https://www.acfun.cn/v/ac47932379_7"/>
-    <hyperlink ref="F306" r:id="rId134" display="https://www.acfun.cn/v/ac47932379_8"/>
-    <hyperlink ref="F307" r:id="rId135" display="https://www.acfun.cn/v/ac47932379_9"/>
-    <hyperlink ref="F308" r:id="rId136" display="https://www.acfun.cn/v/ac47932379_10"/>
-    <hyperlink ref="F309" r:id="rId137" display="https://www.acfun.cn/v/ac48055738"/>
-    <hyperlink ref="F310" r:id="rId138" display="https://www.acfun.cn/v/ac48055738_2"/>
-    <hyperlink ref="F311" r:id="rId139" display="https://www.acfun.cn/v/ac48055738_3"/>
-    <hyperlink ref="F312" r:id="rId140" display="https://www.acfun.cn/v/ac48055738_4"/>
-    <hyperlink ref="F313" r:id="rId141" display="https://www.acfun.cn/v/ac48055738_5"/>
-    <hyperlink ref="F314" r:id="rId142" display="https://www.acfun.cn/v/ac48055738_6"/>
-    <hyperlink ref="F316" r:id="rId143" display="https://www.acfun.cn/v/ac48055738_7"/>
-    <hyperlink ref="F317" r:id="rId144" display="https://www.acfun.cn/v/ac48055738_8"/>
-    <hyperlink ref="F319" r:id="rId145" display="https://www.acfun.cn/v/ac48055738_9"/>
-    <hyperlink ref="F325" r:id="rId146" display="https://www.acfun.cn/v/ac48751334"/>
-    <hyperlink ref="F326" r:id="rId147" display="https://www.acfun.cn/v/ac48751334_2"/>
-    <hyperlink ref="F331" r:id="rId148" display="https://www.acfun.cn/v/ac48751334_3" tooltip="https://www.acfun.cn/v/ac48751334_3"/>
-    <hyperlink ref="F332" r:id="rId149" display="https://www.acfun.cn/v/ac47931260"/>
-    <hyperlink ref="F333" r:id="rId150" display="https://www.acfun.cn/v/ac47931260_2"/>
-    <hyperlink ref="F335" r:id="rId151" display="https://www.acfun.cn/v/ac47931260_3"/>
-    <hyperlink ref="F336" r:id="rId152" display="https://www.acfun.cn/v/ac47931260_4"/>
-    <hyperlink ref="F337" r:id="rId153" display="https://www.acfun.cn/v/ac47931260_5"/>
-    <hyperlink ref="F338" r:id="rId154" display="https://www.acfun.cn/v/ac47931260_6"/>
-    <hyperlink ref="F339" r:id="rId155" display="https://www.acfun.cn/v/ac47931260_7"/>
-    <hyperlink ref="F345" r:id="rId156" display="https://www.acfun.cn/v/ac47931260_8"/>
-    <hyperlink ref="F346" r:id="rId157" display="https://www.acfun.cn/v/ac47932208"/>
-    <hyperlink ref="F347" r:id="rId158" display="https://www.acfun.cn/v/ac47932208_2"/>
-    <hyperlink ref="F348" r:id="rId159" display="https://www.acfun.cn/v/ac47932208_3"/>
-    <hyperlink ref="F349" r:id="rId160" display="https://www.acfun.cn/v/ac47932208_4"/>
-    <hyperlink ref="F350" r:id="rId161" display="https://www.acfun.cn/v/ac47932208_5"/>
-    <hyperlink ref="F351" r:id="rId162" display="https://www.acfun.cn/v/ac47932208_6"/>
-    <hyperlink ref="F352" r:id="rId163" display="https://www.acfun.cn/v/ac47932208_7"/>
-    <hyperlink ref="F358" r:id="rId164" display="https://www.acfun.cn/v/ac47932208_8"/>
-    <hyperlink ref="F359" r:id="rId165" display="https://www.acfun.cn/v/ac47932208_9"/>
-    <hyperlink ref="F363" r:id="rId166" display="https://www.acfun.cn/v/ac47932208_10"/>
-    <hyperlink ref="F364" r:id="rId167" display="https://www.acfun.cn/v/ac47931830"/>
-    <hyperlink ref="F365" r:id="rId168" display="https://www.acfun.cn/v/ac47931830_2"/>
-    <hyperlink ref="F368" r:id="rId169" display="https://www.acfun.cn/v/ac47931830_3"/>
-    <hyperlink ref="F369" r:id="rId170" display="https://www.acfun.cn/v/ac47931830_4"/>
-    <hyperlink ref="F370" r:id="rId171" display="https://www.acfun.cn/v/ac47931830_5"/>
-    <hyperlink ref="F372" r:id="rId172" display="https://www.acfun.cn/v/ac47931830_6"/>
-    <hyperlink ref="F373" r:id="rId173" display="https://www.acfun.cn/v/ac47931830_7"/>
-    <hyperlink ref="F374" r:id="rId174" display="https://www.acfun.cn/v/ac47931830_8"/>
-    <hyperlink ref="F376" r:id="rId175" display="https://www.acfun.cn/v/ac47931830_9"/>
-    <hyperlink ref="F378" r:id="rId176" display="https://www.acfun.cn/v/ac47931830_10"/>
-    <hyperlink ref="F384" r:id="rId177" display="https://www.acfun.cn/v/ac48751840"/>
-    <hyperlink ref="F385" r:id="rId178" display="https://www.acfun.cn/v/ac48751840_2"/>
-    <hyperlink ref="F389" r:id="rId179" display="https://www.acfun.cn/v/ac48751840_3"/>
-    <hyperlink ref="F390" r:id="rId180" display="https://www.acfun.cn/v/ac47931318"/>
-    <hyperlink ref="F391" r:id="rId181" display="https://www.acfun.cn/v/ac47931318_2"/>
-    <hyperlink ref="F395" r:id="rId182" display="https://www.acfun.cn/v/ac47931318_3"/>
-    <hyperlink ref="F396" r:id="rId183" display="https://www.acfun.cn/v/ac47931318_4"/>
-    <hyperlink ref="F397" r:id="rId184" display="https://www.acfun.cn/v/ac47931318_5"/>
-    <hyperlink ref="F398" r:id="rId185" display="https://www.acfun.cn/v/ac47931318_6"/>
-    <hyperlink ref="F399" r:id="rId186" display="https://www.acfun.cn/v/ac47931318_7"/>
-    <hyperlink ref="F400" r:id="rId187" display="https://www.acfun.cn/v/ac47931318_8"/>
-    <hyperlink ref="F401" r:id="rId188" display="https://www.acfun.cn/v/ac47931318_9"/>
-    <hyperlink ref="F402" r:id="rId189" display="https://www.acfun.cn/v/ac47931318_10"/>
-    <hyperlink ref="F403" r:id="rId190" display="https://www.acfun.cn/v/ac48311717"/>
-    <hyperlink ref="F405" r:id="rId191" display="https://www.acfun.cn/v/ac48311717_2"/>
-    <hyperlink ref="F406" r:id="rId192" display="https://www.acfun.cn/v/ac48311717_3"/>
-    <hyperlink ref="F408" r:id="rId193" display="https://www.acfun.cn/v/ac48311717_4"/>
-    <hyperlink ref="F414" r:id="rId194" display="https://www.acfun.cn/v/ac48311717_5"/>
-    <hyperlink ref="F415" r:id="rId195" display="https://www.acfun.cn/v/ac48311717_6"/>
-    <hyperlink ref="F420" r:id="rId196" display="https://www.acfun.cn/v/ac48311717_7"/>
-    <hyperlink ref="F421" r:id="rId197" display="https://www.acfun.cn/v/ac47932123"/>
-    <hyperlink ref="F422" r:id="rId198" display="https://www.acfun.cn/v/ac47932123_2"/>
-    <hyperlink ref="F424" r:id="rId199" display="https://www.acfun.cn/v/ac47932123_3"/>
-    <hyperlink ref="F425" r:id="rId200" display="https://www.acfun.cn/v/ac47932123_4" tooltip="https://www.acfun.cn/v/ac47932123_4"/>
-    <hyperlink ref="F426" r:id="rId201" display="https://www.acfun.cn/v/ac47932123_5"/>
-    <hyperlink ref="F427" r:id="rId202" display="https://www.acfun.cn/v/ac47932123_6"/>
-    <hyperlink ref="F428" r:id="rId203" display="https://www.acfun.cn/v/ac47932123_7"/>
-    <hyperlink ref="F430" r:id="rId204" display="https://www.acfun.cn/v/ac47932123_8"/>
-    <hyperlink ref="F434" r:id="rId205" display="https://www.acfun.cn/v/ac47930836"/>
-    <hyperlink ref="F435" r:id="rId206" display="https://www.acfun.cn/v/ac47930836_2"/>
-    <hyperlink ref="F436" r:id="rId207" display="https://www.acfun.cn/v/ac47930836_3"/>
-    <hyperlink ref="F438" r:id="rId208" display="https://www.acfun.cn/v/ac47930836_4"/>
-    <hyperlink ref="F440" r:id="rId209" display="https://www.acfun.cn/v/ac47930836_5"/>
-    <hyperlink ref="F441" r:id="rId210" display="https://www.acfun.cn/v/ac47930836_6"/>
-    <hyperlink ref="F447" r:id="rId211" display="https://www.acfun.cn/v/ac47930836_7"/>
-    <hyperlink ref="F448" r:id="rId212" display="https://www.acfun.cn/v/ac47930836_8"/>
-    <hyperlink ref="F451" r:id="rId213" display="https://www.acfun.cn/v/ac47935835"/>
-    <hyperlink ref="F452" r:id="rId214" display="https://www.acfun.cn/v/ac47935862" tooltip="https://www.acfun.cn/v/ac47935862"/>
-    <hyperlink ref="F453" r:id="rId215" display="https://www.acfun.cn/v/ac47932937" tooltip="https://www.acfun.cn/v/ac47932937"/>
-    <hyperlink ref="F454" r:id="rId216" display="https://www.acfun.cn/v/ac47932937_2"/>
-    <hyperlink ref="F455" r:id="rId217" display="https://www.acfun.cn/v/ac47932937_3"/>
-    <hyperlink ref="F457" r:id="rId218" display="https://www.acfun.cn/v/ac47932937_4"/>
-    <hyperlink ref="F458" r:id="rId219" display="https://www.acfun.cn/v/ac47932937_5"/>
-    <hyperlink ref="F459" r:id="rId220" display="https://www.acfun.cn/v/ac47932763" tooltip="https://www.acfun.cn/v/ac47932763"/>
-    <hyperlink ref="F460" r:id="rId221" display="https://www.acfun.cn/v/ac47932763_2"/>
-    <hyperlink ref="F461" r:id="rId222" display="https://www.acfun.cn/v/ac47932763_3"/>
-    <hyperlink ref="F463" r:id="rId223" display="https://www.acfun.cn/v/ac47932763_4"/>
-    <hyperlink ref="F464" r:id="rId224" display="https://www.acfun.cn/v/ac47931710" tooltip="https://www.acfun.cn/v/ac47931710"/>
-    <hyperlink ref="F465" r:id="rId225" display="https://www.acfun.cn/v/ac47931710_2"/>
-    <hyperlink ref="F466" r:id="rId226" display="https://www.acfun.cn/v/ac47931710_3"/>
-    <hyperlink ref="F468" r:id="rId227" display="https://www.acfun.cn/v/ac47931710_4"/>
+    <hyperlink ref="F2" r:id="rId1" tooltip="https://www.acfun.cn/v/ac47931167" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
+    <hyperlink ref="F14" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
+    <hyperlink ref="F16" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
+    <hyperlink ref="F18" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
+    <hyperlink ref="F20" r:id="rId12" xr:uid="{00000000-0004-0000-0600-00000B000000}"/>
+    <hyperlink ref="F22" r:id="rId13" xr:uid="{00000000-0004-0000-0600-00000C000000}"/>
+    <hyperlink ref="F23" r:id="rId14" xr:uid="{00000000-0004-0000-0600-00000D000000}"/>
+    <hyperlink ref="F24" r:id="rId15" xr:uid="{00000000-0004-0000-0600-00000E000000}"/>
+    <hyperlink ref="F25" r:id="rId16" xr:uid="{00000000-0004-0000-0600-00000F000000}"/>
+    <hyperlink ref="F27" r:id="rId17" xr:uid="{00000000-0004-0000-0600-000010000000}"/>
+    <hyperlink ref="F28" r:id="rId18" xr:uid="{00000000-0004-0000-0600-000011000000}"/>
+    <hyperlink ref="F29" r:id="rId19" xr:uid="{00000000-0004-0000-0600-000012000000}"/>
+    <hyperlink ref="F31" r:id="rId20" xr:uid="{00000000-0004-0000-0600-000013000000}"/>
+    <hyperlink ref="F32" r:id="rId21" xr:uid="{00000000-0004-0000-0600-000014000000}"/>
+    <hyperlink ref="F33" r:id="rId22" xr:uid="{00000000-0004-0000-0600-000015000000}"/>
+    <hyperlink ref="F34" r:id="rId23" xr:uid="{00000000-0004-0000-0600-000016000000}"/>
+    <hyperlink ref="F39" r:id="rId24" xr:uid="{00000000-0004-0000-0600-000017000000}"/>
+    <hyperlink ref="F69" r:id="rId25" xr:uid="{00000000-0004-0000-0600-000018000000}"/>
+    <hyperlink ref="F71" r:id="rId26" xr:uid="{00000000-0004-0000-0600-000019000000}"/>
+    <hyperlink ref="F73" r:id="rId27" xr:uid="{00000000-0004-0000-0600-00001A000000}"/>
+    <hyperlink ref="F74" r:id="rId28" xr:uid="{00000000-0004-0000-0600-00001B000000}"/>
+    <hyperlink ref="F75" r:id="rId29" xr:uid="{00000000-0004-0000-0600-00001C000000}"/>
+    <hyperlink ref="F76" r:id="rId30" xr:uid="{00000000-0004-0000-0600-00001D000000}"/>
+    <hyperlink ref="F77" r:id="rId31" xr:uid="{00000000-0004-0000-0600-00001E000000}"/>
+    <hyperlink ref="F78" r:id="rId32" xr:uid="{00000000-0004-0000-0600-00001F000000}"/>
+    <hyperlink ref="F80" r:id="rId33" xr:uid="{00000000-0004-0000-0600-000020000000}"/>
+    <hyperlink ref="F87" r:id="rId34" xr:uid="{00000000-0004-0000-0600-000021000000}"/>
+    <hyperlink ref="F101" r:id="rId35" xr:uid="{00000000-0004-0000-0600-000022000000}"/>
+    <hyperlink ref="F105" r:id="rId36" xr:uid="{00000000-0004-0000-0600-000023000000}"/>
+    <hyperlink ref="F106" r:id="rId37" xr:uid="{00000000-0004-0000-0600-000024000000}"/>
+    <hyperlink ref="F107" r:id="rId38" xr:uid="{00000000-0004-0000-0600-000025000000}"/>
+    <hyperlink ref="F109" r:id="rId39" xr:uid="{00000000-0004-0000-0600-000026000000}"/>
+    <hyperlink ref="F113" r:id="rId40" xr:uid="{00000000-0004-0000-0600-000027000000}"/>
+    <hyperlink ref="F114" r:id="rId41" xr:uid="{00000000-0004-0000-0600-000028000000}"/>
+    <hyperlink ref="F115" r:id="rId42" xr:uid="{00000000-0004-0000-0600-000029000000}"/>
+    <hyperlink ref="F116" r:id="rId43" xr:uid="{00000000-0004-0000-0600-00002A000000}"/>
+    <hyperlink ref="F118" r:id="rId44" xr:uid="{00000000-0004-0000-0600-00002B000000}"/>
+    <hyperlink ref="F119" r:id="rId45" xr:uid="{00000000-0004-0000-0600-00002C000000}"/>
+    <hyperlink ref="F120" r:id="rId46" xr:uid="{00000000-0004-0000-0600-00002D000000}"/>
+    <hyperlink ref="F122" r:id="rId47" xr:uid="{00000000-0004-0000-0600-00002E000000}"/>
+    <hyperlink ref="F128" r:id="rId48" xr:uid="{00000000-0004-0000-0600-00002F000000}"/>
+    <hyperlink ref="F129" r:id="rId49" xr:uid="{00000000-0004-0000-0600-000030000000}"/>
+    <hyperlink ref="F133" r:id="rId50" xr:uid="{00000000-0004-0000-0600-000031000000}"/>
+    <hyperlink ref="F134" r:id="rId51" xr:uid="{00000000-0004-0000-0600-000032000000}"/>
+    <hyperlink ref="F135" r:id="rId52" xr:uid="{00000000-0004-0000-0600-000033000000}"/>
+    <hyperlink ref="F136" r:id="rId53" xr:uid="{00000000-0004-0000-0600-000034000000}"/>
+    <hyperlink ref="F138" r:id="rId54" xr:uid="{00000000-0004-0000-0600-000035000000}"/>
+    <hyperlink ref="F140" r:id="rId55" xr:uid="{00000000-0004-0000-0600-000036000000}"/>
+    <hyperlink ref="F141" r:id="rId56" xr:uid="{00000000-0004-0000-0600-000037000000}"/>
+    <hyperlink ref="F142" r:id="rId57" xr:uid="{00000000-0004-0000-0600-000038000000}"/>
+    <hyperlink ref="F143" r:id="rId58" xr:uid="{00000000-0004-0000-0600-000039000000}"/>
+    <hyperlink ref="F149" r:id="rId59" xr:uid="{00000000-0004-0000-0600-00003A000000}"/>
+    <hyperlink ref="F167" r:id="rId60" xr:uid="{00000000-0004-0000-0600-00003B000000}"/>
+    <hyperlink ref="F168" r:id="rId61" tooltip="https://www.acfun.cn/v/ac47931569" xr:uid="{00000000-0004-0000-0600-00003C000000}"/>
+    <hyperlink ref="F170" r:id="rId62" xr:uid="{00000000-0004-0000-0600-00003D000000}"/>
+    <hyperlink ref="F171" r:id="rId63" xr:uid="{00000000-0004-0000-0600-00003E000000}"/>
+    <hyperlink ref="F172" r:id="rId64" xr:uid="{00000000-0004-0000-0600-00003F000000}"/>
+    <hyperlink ref="F173" r:id="rId65" xr:uid="{00000000-0004-0000-0600-000040000000}"/>
+    <hyperlink ref="F174" r:id="rId66" xr:uid="{00000000-0004-0000-0600-000041000000}"/>
+    <hyperlink ref="F175" r:id="rId67" xr:uid="{00000000-0004-0000-0600-000042000000}"/>
+    <hyperlink ref="F176" r:id="rId68" xr:uid="{00000000-0004-0000-0600-000043000000}"/>
+    <hyperlink ref="F177" r:id="rId69" xr:uid="{00000000-0004-0000-0600-000044000000}"/>
+    <hyperlink ref="F178" r:id="rId70" xr:uid="{00000000-0004-0000-0600-000045000000}"/>
+    <hyperlink ref="F179" r:id="rId71" tooltip="https://www.acfun.cn/v/ac47931603" xr:uid="{00000000-0004-0000-0600-000046000000}"/>
+    <hyperlink ref="F181" r:id="rId72" xr:uid="{00000000-0004-0000-0600-000047000000}"/>
+    <hyperlink ref="F183" r:id="rId73" xr:uid="{00000000-0004-0000-0600-000048000000}"/>
+    <hyperlink ref="F184" r:id="rId74" xr:uid="{00000000-0004-0000-0600-000049000000}"/>
+    <hyperlink ref="F186" r:id="rId75" xr:uid="{00000000-0004-0000-0600-00004A000000}"/>
+    <hyperlink ref="F192" r:id="rId76" xr:uid="{00000000-0004-0000-0600-00004B000000}"/>
+    <hyperlink ref="F193" r:id="rId77" xr:uid="{00000000-0004-0000-0600-00004C000000}"/>
+    <hyperlink ref="F198" r:id="rId78" xr:uid="{00000000-0004-0000-0600-00004D000000}"/>
+    <hyperlink ref="F199" r:id="rId79" xr:uid="{00000000-0004-0000-0600-00004E000000}"/>
+    <hyperlink ref="F201" r:id="rId80" xr:uid="{00000000-0004-0000-0600-00004F000000}"/>
+    <hyperlink ref="F202" r:id="rId81" xr:uid="{00000000-0004-0000-0600-000050000000}"/>
+    <hyperlink ref="F203" r:id="rId82" xr:uid="{00000000-0004-0000-0600-000051000000}"/>
+    <hyperlink ref="F204" r:id="rId83" xr:uid="{00000000-0004-0000-0600-000052000000}"/>
+    <hyperlink ref="F206" r:id="rId84" xr:uid="{00000000-0004-0000-0600-000053000000}"/>
+    <hyperlink ref="F207" r:id="rId85" xr:uid="{00000000-0004-0000-0600-000054000000}"/>
+    <hyperlink ref="F208" r:id="rId86" xr:uid="{00000000-0004-0000-0600-000055000000}"/>
+    <hyperlink ref="F209" r:id="rId87" xr:uid="{00000000-0004-0000-0600-000056000000}"/>
+    <hyperlink ref="F211" r:id="rId88" xr:uid="{00000000-0004-0000-0600-000057000000}"/>
+    <hyperlink ref="F213" r:id="rId89" tooltip="https://www.acfun.cn/v/ac48409409_1" xr:uid="{00000000-0004-0000-0600-000058000000}"/>
+    <hyperlink ref="F219" r:id="rId90" xr:uid="{00000000-0004-0000-0600-000059000000}"/>
+    <hyperlink ref="F220" r:id="rId91" xr:uid="{00000000-0004-0000-0600-00005A000000}"/>
+    <hyperlink ref="F225" r:id="rId92" xr:uid="{00000000-0004-0000-0600-00005B000000}"/>
+    <hyperlink ref="F235" r:id="rId93" xr:uid="{00000000-0004-0000-0600-00005C000000}"/>
+    <hyperlink ref="F236" r:id="rId94" xr:uid="{00000000-0004-0000-0600-00005D000000}"/>
+    <hyperlink ref="F238" r:id="rId95" xr:uid="{00000000-0004-0000-0600-00005E000000}"/>
+    <hyperlink ref="F240" r:id="rId96" xr:uid="{00000000-0004-0000-0600-00005F000000}"/>
+    <hyperlink ref="F241" r:id="rId97" xr:uid="{00000000-0004-0000-0600-000060000000}"/>
+    <hyperlink ref="F242" r:id="rId98" xr:uid="{00000000-0004-0000-0600-000061000000}"/>
+    <hyperlink ref="F244" r:id="rId99" xr:uid="{00000000-0004-0000-0600-000062000000}"/>
+    <hyperlink ref="F246" r:id="rId100" xr:uid="{00000000-0004-0000-0600-000063000000}"/>
+    <hyperlink ref="F248" r:id="rId101" xr:uid="{00000000-0004-0000-0600-000064000000}"/>
+    <hyperlink ref="F249" r:id="rId102" xr:uid="{00000000-0004-0000-0600-000065000000}"/>
+    <hyperlink ref="F250" r:id="rId103" xr:uid="{00000000-0004-0000-0600-000066000000}"/>
+    <hyperlink ref="F251" r:id="rId104" xr:uid="{00000000-0004-0000-0600-000067000000}"/>
+    <hyperlink ref="F252" r:id="rId105" xr:uid="{00000000-0004-0000-0600-000068000000}"/>
+    <hyperlink ref="F257" r:id="rId106" xr:uid="{00000000-0004-0000-0600-000069000000}"/>
+    <hyperlink ref="F259" r:id="rId107" xr:uid="{00000000-0004-0000-0600-00006A000000}"/>
+    <hyperlink ref="F260" r:id="rId108" xr:uid="{00000000-0004-0000-0600-00006B000000}"/>
+    <hyperlink ref="F261" r:id="rId109" xr:uid="{00000000-0004-0000-0600-00006C000000}"/>
+    <hyperlink ref="F262" r:id="rId110" xr:uid="{00000000-0004-0000-0600-00006D000000}"/>
+    <hyperlink ref="F263" r:id="rId111" xr:uid="{00000000-0004-0000-0600-00006E000000}"/>
+    <hyperlink ref="F264" r:id="rId112" xr:uid="{00000000-0004-0000-0600-00006F000000}"/>
+    <hyperlink ref="F266" r:id="rId113" xr:uid="{00000000-0004-0000-0600-000070000000}"/>
+    <hyperlink ref="F272" r:id="rId114" xr:uid="{00000000-0004-0000-0600-000071000000}"/>
+    <hyperlink ref="F274" r:id="rId115" xr:uid="{00000000-0004-0000-0600-000072000000}"/>
+    <hyperlink ref="F275" r:id="rId116" xr:uid="{00000000-0004-0000-0600-000073000000}"/>
+    <hyperlink ref="F276" r:id="rId117" xr:uid="{00000000-0004-0000-0600-000074000000}"/>
+    <hyperlink ref="F277" r:id="rId118" xr:uid="{00000000-0004-0000-0600-000075000000}"/>
+    <hyperlink ref="F278" r:id="rId119" xr:uid="{00000000-0004-0000-0600-000076000000}"/>
+    <hyperlink ref="F279" r:id="rId120" xr:uid="{00000000-0004-0000-0600-000077000000}"/>
+    <hyperlink ref="F281" r:id="rId121" xr:uid="{00000000-0004-0000-0600-000078000000}"/>
+    <hyperlink ref="F282" r:id="rId122" xr:uid="{00000000-0004-0000-0600-000079000000}"/>
+    <hyperlink ref="F284" r:id="rId123" xr:uid="{00000000-0004-0000-0600-00007A000000}"/>
+    <hyperlink ref="F286" r:id="rId124" xr:uid="{00000000-0004-0000-0600-00007B000000}"/>
+    <hyperlink ref="F291" r:id="rId125" xr:uid="{00000000-0004-0000-0600-00007C000000}"/>
+    <hyperlink ref="F292" r:id="rId126" xr:uid="{00000000-0004-0000-0600-00007D000000}"/>
+    <hyperlink ref="F296" r:id="rId127" xr:uid="{00000000-0004-0000-0600-00007E000000}"/>
+    <hyperlink ref="F297" r:id="rId128" xr:uid="{00000000-0004-0000-0600-00007F000000}"/>
+    <hyperlink ref="F298" r:id="rId129" xr:uid="{00000000-0004-0000-0600-000080000000}"/>
+    <hyperlink ref="F299" r:id="rId130" xr:uid="{00000000-0004-0000-0600-000081000000}"/>
+    <hyperlink ref="F300" r:id="rId131" xr:uid="{00000000-0004-0000-0600-000082000000}"/>
+    <hyperlink ref="F301" r:id="rId132" xr:uid="{00000000-0004-0000-0600-000083000000}"/>
+    <hyperlink ref="F304" r:id="rId133" xr:uid="{00000000-0004-0000-0600-000084000000}"/>
+    <hyperlink ref="F306" r:id="rId134" xr:uid="{00000000-0004-0000-0600-000085000000}"/>
+    <hyperlink ref="F307" r:id="rId135" xr:uid="{00000000-0004-0000-0600-000086000000}"/>
+    <hyperlink ref="F308" r:id="rId136" xr:uid="{00000000-0004-0000-0600-000087000000}"/>
+    <hyperlink ref="F309" r:id="rId137" xr:uid="{00000000-0004-0000-0600-000088000000}"/>
+    <hyperlink ref="F310" r:id="rId138" xr:uid="{00000000-0004-0000-0600-000089000000}"/>
+    <hyperlink ref="F311" r:id="rId139" xr:uid="{00000000-0004-0000-0600-00008A000000}"/>
+    <hyperlink ref="F312" r:id="rId140" xr:uid="{00000000-0004-0000-0600-00008B000000}"/>
+    <hyperlink ref="F313" r:id="rId141" xr:uid="{00000000-0004-0000-0600-00008C000000}"/>
+    <hyperlink ref="F314" r:id="rId142" xr:uid="{00000000-0004-0000-0600-00008D000000}"/>
+    <hyperlink ref="F316" r:id="rId143" xr:uid="{00000000-0004-0000-0600-00008E000000}"/>
+    <hyperlink ref="F317" r:id="rId144" xr:uid="{00000000-0004-0000-0600-00008F000000}"/>
+    <hyperlink ref="F319" r:id="rId145" xr:uid="{00000000-0004-0000-0600-000090000000}"/>
+    <hyperlink ref="F325" r:id="rId146" xr:uid="{00000000-0004-0000-0600-000091000000}"/>
+    <hyperlink ref="F326" r:id="rId147" xr:uid="{00000000-0004-0000-0600-000092000000}"/>
+    <hyperlink ref="F331" r:id="rId148" tooltip="https://www.acfun.cn/v/ac48751334_3" xr:uid="{00000000-0004-0000-0600-000093000000}"/>
+    <hyperlink ref="F332" r:id="rId149" xr:uid="{00000000-0004-0000-0600-000094000000}"/>
+    <hyperlink ref="F333" r:id="rId150" xr:uid="{00000000-0004-0000-0600-000095000000}"/>
+    <hyperlink ref="F335" r:id="rId151" xr:uid="{00000000-0004-0000-0600-000096000000}"/>
+    <hyperlink ref="F336" r:id="rId152" xr:uid="{00000000-0004-0000-0600-000097000000}"/>
+    <hyperlink ref="F337" r:id="rId153" xr:uid="{00000000-0004-0000-0600-000098000000}"/>
+    <hyperlink ref="F338" r:id="rId154" xr:uid="{00000000-0004-0000-0600-000099000000}"/>
+    <hyperlink ref="F339" r:id="rId155" xr:uid="{00000000-0004-0000-0600-00009A000000}"/>
+    <hyperlink ref="F345" r:id="rId156" xr:uid="{00000000-0004-0000-0600-00009B000000}"/>
+    <hyperlink ref="F346" r:id="rId157" xr:uid="{00000000-0004-0000-0600-00009C000000}"/>
+    <hyperlink ref="F347" r:id="rId158" xr:uid="{00000000-0004-0000-0600-00009D000000}"/>
+    <hyperlink ref="F348" r:id="rId159" xr:uid="{00000000-0004-0000-0600-00009E000000}"/>
+    <hyperlink ref="F349" r:id="rId160" xr:uid="{00000000-0004-0000-0600-00009F000000}"/>
+    <hyperlink ref="F350" r:id="rId161" xr:uid="{00000000-0004-0000-0600-0000A0000000}"/>
+    <hyperlink ref="F351" r:id="rId162" xr:uid="{00000000-0004-0000-0600-0000A1000000}"/>
+    <hyperlink ref="F352" r:id="rId163" xr:uid="{00000000-0004-0000-0600-0000A2000000}"/>
+    <hyperlink ref="F358" r:id="rId164" xr:uid="{00000000-0004-0000-0600-0000A3000000}"/>
+    <hyperlink ref="F359" r:id="rId165" xr:uid="{00000000-0004-0000-0600-0000A4000000}"/>
+    <hyperlink ref="F363" r:id="rId166" xr:uid="{00000000-0004-0000-0600-0000A5000000}"/>
+    <hyperlink ref="F364" r:id="rId167" xr:uid="{00000000-0004-0000-0600-0000A6000000}"/>
+    <hyperlink ref="F365" r:id="rId168" xr:uid="{00000000-0004-0000-0600-0000A7000000}"/>
+    <hyperlink ref="F368" r:id="rId169" xr:uid="{00000000-0004-0000-0600-0000A8000000}"/>
+    <hyperlink ref="F369" r:id="rId170" xr:uid="{00000000-0004-0000-0600-0000A9000000}"/>
+    <hyperlink ref="F370" r:id="rId171" xr:uid="{00000000-0004-0000-0600-0000AA000000}"/>
+    <hyperlink ref="F372" r:id="rId172" xr:uid="{00000000-0004-0000-0600-0000AB000000}"/>
+    <hyperlink ref="F373" r:id="rId173" xr:uid="{00000000-0004-0000-0600-0000AC000000}"/>
+    <hyperlink ref="F374" r:id="rId174" xr:uid="{00000000-0004-0000-0600-0000AD000000}"/>
+    <hyperlink ref="F376" r:id="rId175" xr:uid="{00000000-0004-0000-0600-0000AE000000}"/>
+    <hyperlink ref="F378" r:id="rId176" xr:uid="{00000000-0004-0000-0600-0000AF000000}"/>
+    <hyperlink ref="F384" r:id="rId177" xr:uid="{00000000-0004-0000-0600-0000B0000000}"/>
+    <hyperlink ref="F385" r:id="rId178" xr:uid="{00000000-0004-0000-0600-0000B1000000}"/>
+    <hyperlink ref="F389" r:id="rId179" xr:uid="{00000000-0004-0000-0600-0000B2000000}"/>
+    <hyperlink ref="F390" r:id="rId180" xr:uid="{00000000-0004-0000-0600-0000B3000000}"/>
+    <hyperlink ref="F391" r:id="rId181" xr:uid="{00000000-0004-0000-0600-0000B4000000}"/>
+    <hyperlink ref="F395" r:id="rId182" xr:uid="{00000000-0004-0000-0600-0000B5000000}"/>
+    <hyperlink ref="F396" r:id="rId183" xr:uid="{00000000-0004-0000-0600-0000B6000000}"/>
+    <hyperlink ref="F397" r:id="rId184" xr:uid="{00000000-0004-0000-0600-0000B7000000}"/>
+    <hyperlink ref="F398" r:id="rId185" xr:uid="{00000000-0004-0000-0600-0000B8000000}"/>
+    <hyperlink ref="F399" r:id="rId186" xr:uid="{00000000-0004-0000-0600-0000B9000000}"/>
+    <hyperlink ref="F400" r:id="rId187" xr:uid="{00000000-0004-0000-0600-0000BA000000}"/>
+    <hyperlink ref="F401" r:id="rId188" xr:uid="{00000000-0004-0000-0600-0000BB000000}"/>
+    <hyperlink ref="F402" r:id="rId189" xr:uid="{00000000-0004-0000-0600-0000BC000000}"/>
+    <hyperlink ref="F403" r:id="rId190" xr:uid="{00000000-0004-0000-0600-0000BD000000}"/>
+    <hyperlink ref="F405" r:id="rId191" xr:uid="{00000000-0004-0000-0600-0000BE000000}"/>
+    <hyperlink ref="F406" r:id="rId192" xr:uid="{00000000-0004-0000-0600-0000BF000000}"/>
+    <hyperlink ref="F408" r:id="rId193" xr:uid="{00000000-0004-0000-0600-0000C0000000}"/>
+    <hyperlink ref="F414" r:id="rId194" xr:uid="{00000000-0004-0000-0600-0000C1000000}"/>
+    <hyperlink ref="F415" r:id="rId195" xr:uid="{00000000-0004-0000-0600-0000C2000000}"/>
+    <hyperlink ref="F420" r:id="rId196" xr:uid="{00000000-0004-0000-0600-0000C3000000}"/>
+    <hyperlink ref="F421" r:id="rId197" xr:uid="{00000000-0004-0000-0600-0000C4000000}"/>
+    <hyperlink ref="F422" r:id="rId198" xr:uid="{00000000-0004-0000-0600-0000C5000000}"/>
+    <hyperlink ref="F424" r:id="rId199" xr:uid="{00000000-0004-0000-0600-0000C6000000}"/>
+    <hyperlink ref="F425" r:id="rId200" tooltip="https://www.acfun.cn/v/ac47932123_4" xr:uid="{00000000-0004-0000-0600-0000C7000000}"/>
+    <hyperlink ref="F426" r:id="rId201" xr:uid="{00000000-0004-0000-0600-0000C8000000}"/>
+    <hyperlink ref="F427" r:id="rId202" xr:uid="{00000000-0004-0000-0600-0000C9000000}"/>
+    <hyperlink ref="F428" r:id="rId203" xr:uid="{00000000-0004-0000-0600-0000CA000000}"/>
+    <hyperlink ref="F430" r:id="rId204" xr:uid="{00000000-0004-0000-0600-0000CB000000}"/>
+    <hyperlink ref="F434" r:id="rId205" xr:uid="{00000000-0004-0000-0600-0000CC000000}"/>
+    <hyperlink ref="F435" r:id="rId206" xr:uid="{00000000-0004-0000-0600-0000CD000000}"/>
+    <hyperlink ref="F436" r:id="rId207" xr:uid="{00000000-0004-0000-0600-0000CE000000}"/>
+    <hyperlink ref="F438" r:id="rId208" xr:uid="{00000000-0004-0000-0600-0000CF000000}"/>
+    <hyperlink ref="F440" r:id="rId209" xr:uid="{00000000-0004-0000-0600-0000D0000000}"/>
+    <hyperlink ref="F441" r:id="rId210" xr:uid="{00000000-0004-0000-0600-0000D1000000}"/>
+    <hyperlink ref="F447" r:id="rId211" xr:uid="{00000000-0004-0000-0600-0000D2000000}"/>
+    <hyperlink ref="F448" r:id="rId212" xr:uid="{00000000-0004-0000-0600-0000D3000000}"/>
+    <hyperlink ref="F451" r:id="rId213" xr:uid="{00000000-0004-0000-0600-0000D4000000}"/>
+    <hyperlink ref="F452" r:id="rId214" tooltip="https://www.acfun.cn/v/ac47935862" xr:uid="{00000000-0004-0000-0600-0000D5000000}"/>
+    <hyperlink ref="F453" r:id="rId215" tooltip="https://www.acfun.cn/v/ac47932937" xr:uid="{00000000-0004-0000-0600-0000D6000000}"/>
+    <hyperlink ref="F454" r:id="rId216" xr:uid="{00000000-0004-0000-0600-0000D7000000}"/>
+    <hyperlink ref="F455" r:id="rId217" xr:uid="{00000000-0004-0000-0600-0000D8000000}"/>
+    <hyperlink ref="F457" r:id="rId218" xr:uid="{00000000-0004-0000-0600-0000D9000000}"/>
+    <hyperlink ref="F458" r:id="rId219" xr:uid="{00000000-0004-0000-0600-0000DA000000}"/>
+    <hyperlink ref="F459" r:id="rId220" tooltip="https://www.acfun.cn/v/ac47932763" xr:uid="{00000000-0004-0000-0600-0000DB000000}"/>
+    <hyperlink ref="F460" r:id="rId221" xr:uid="{00000000-0004-0000-0600-0000DC000000}"/>
+    <hyperlink ref="F461" r:id="rId222" xr:uid="{00000000-0004-0000-0600-0000DD000000}"/>
+    <hyperlink ref="F463" r:id="rId223" xr:uid="{00000000-0004-0000-0600-0000DE000000}"/>
+    <hyperlink ref="F464" r:id="rId224" tooltip="https://www.acfun.cn/v/ac47931710" xr:uid="{00000000-0004-0000-0600-0000DF000000}"/>
+    <hyperlink ref="F465" r:id="rId225" xr:uid="{00000000-0004-0000-0600-0000E0000000}"/>
+    <hyperlink ref="F466" r:id="rId226" xr:uid="{00000000-0004-0000-0600-0000E1000000}"/>
+    <hyperlink ref="F468" r:id="rId227" xr:uid="{00000000-0004-0000-0600-0000E2000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Sheet5" filterMode="1"/>
   <dimension ref="A1:I53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="52.4545454545455" style="6" customWidth="1"/>
+    <col min="1" max="1" width="52.453125" style="6" customWidth="1"/>
     <col min="2" max="2" width="20" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.4545454545455" style="6" customWidth="1"/>
-    <col min="4" max="4" width="30.8181818181818" style="6" customWidth="1"/>
-    <col min="5" max="5" width="28.6363636363636" style="6" customWidth="1"/>
-    <col min="6" max="6" width="48.0909090909091" style="6" customWidth="1"/>
-    <col min="7" max="7" width="13.5454545454545" style="6" customWidth="1"/>
+    <col min="3" max="3" width="38.453125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="28.6328125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="48.08984375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" style="6" customWidth="1"/>
     <col min="8" max="8" width="14" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.4545454545455" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="6" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="9" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -73912,7 +73329,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:9">
+    <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -73941,7 +73358,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="3" ht="16" hidden="1" customHeight="1" spans="1:9">
+    <row r="3" spans="1:9" ht="16" hidden="1" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -73970,7 +73387,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:9">
+    <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -73999,7 +73416,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:9">
+    <row r="5" spans="1:9" hidden="1">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -74022,7 +73439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:9">
+    <row r="6" spans="1:9" hidden="1">
       <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
@@ -74051,7 +73468,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="7" ht="16" hidden="1" customHeight="1" spans="1:9">
+    <row r="7" spans="1:9" ht="16" hidden="1" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
@@ -74077,7 +73494,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:9">
+    <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
@@ -74106,7 +73523,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:9">
+    <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -74129,7 +73546,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:9">
+    <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
@@ -74155,7 +73572,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:9">
+    <row r="11" spans="1:9" hidden="1">
       <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
@@ -74184,7 +73601,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:9">
+    <row r="12" spans="1:9" hidden="1">
       <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
@@ -74210,7 +73627,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:9">
+    <row r="13" spans="1:9" hidden="1">
       <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
@@ -74239,7 +73656,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:9">
+    <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="6" t="s">
         <v>27</v>
       </c>
@@ -75304,49 +74721,48 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H53" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:H53" xr:uid="{00000000-0009-0000-0000-000007000000}">
     <filterColumn colId="1">
       <filters>
+        <dateGroupItem year="2026" dateTimeGrouping="year"/>
         <dateGroupItem year="2025" dateTimeGrouping="year"/>
-        <dateGroupItem year="2026" dateTimeGrouping="year"/>
       </filters>
     </filterColumn>
-    <extLst/>
   </autoFilter>
+  <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.acfun.cn/v/ac48837138"/>
-    <hyperlink ref="F10" r:id="rId2" display="https://www.acfun.cn/v/ac48796276"/>
-    <hyperlink ref="F15" r:id="rId3" display="https://www.bilibili.com/video/BV1aAZYYAEEQ"/>
-    <hyperlink ref="F17" r:id="rId4" display="https://www.bilibili.com/video/BV1RV2eBeEAd"/>
-    <hyperlink ref="F19" r:id="rId5" display="https://www.bilibili.com/video/BV1pB3izpExm"/>
-    <hyperlink ref="F24" r:id="rId6" display="https://www.acfun.cn/v/ac48737511"/>
-    <hyperlink ref="F28" r:id="rId7" display="https://www.acfun.cn/v/ac48832641" tooltip="https://www.acfun.cn/v/ac48832641"/>
-    <hyperlink ref="F29" r:id="rId8" display="https://www.acfun.cn/v/ac48832628" tooltip="https://www.acfun.cn/v/ac48832628"/>
-    <hyperlink ref="F30" r:id="rId9" display="https://www.acfun.cn/v/ac48691288" tooltip="https://www.acfun.cn/v/ac48691288"/>
-    <hyperlink ref="F33" r:id="rId10" display="https://www.acfun.cn/v/ac48832656"/>
-    <hyperlink ref="F34" r:id="rId11" display="https://www.bilibili.com/video/BV1TFJW6FEeP"/>
-    <hyperlink ref="F36" r:id="rId12" display="https://www.bilibili.com/video/BV18RdHBnELz"/>
-    <hyperlink ref="F42" r:id="rId13" display="https://www.acfun.cn/v/ac48645465" tooltip="https://www.acfun.cn/v/ac48645465"/>
-    <hyperlink ref="F43" r:id="rId14" display="https://www.acfun.cn/v/ac48644820" tooltip="https://www.acfun.cn/v/ac48644820"/>
-    <hyperlink ref="F48" r:id="rId15" display="https://www.bilibili.com/video/BV17iYj6bE6G" tooltip="https://www.bilibili.com/video/BV17iYj6bE6G"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="F10" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
+    <hyperlink ref="F15" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
+    <hyperlink ref="F17" r:id="rId4" xr:uid="{00000000-0004-0000-0700-000003000000}"/>
+    <hyperlink ref="F19" r:id="rId5" xr:uid="{00000000-0004-0000-0700-000004000000}"/>
+    <hyperlink ref="F24" r:id="rId6" xr:uid="{00000000-0004-0000-0700-000005000000}"/>
+    <hyperlink ref="F28" r:id="rId7" tooltip="https://www.acfun.cn/v/ac48832641" xr:uid="{00000000-0004-0000-0700-000006000000}"/>
+    <hyperlink ref="F29" r:id="rId8" tooltip="https://www.acfun.cn/v/ac48832628" xr:uid="{00000000-0004-0000-0700-000007000000}"/>
+    <hyperlink ref="F30" r:id="rId9" tooltip="https://www.acfun.cn/v/ac48691288" xr:uid="{00000000-0004-0000-0700-000008000000}"/>
+    <hyperlink ref="F33" r:id="rId10" xr:uid="{00000000-0004-0000-0700-000009000000}"/>
+    <hyperlink ref="F34" r:id="rId11" xr:uid="{00000000-0004-0000-0700-00000A000000}"/>
+    <hyperlink ref="F36" r:id="rId12" xr:uid="{00000000-0004-0000-0700-00000B000000}"/>
+    <hyperlink ref="F42" r:id="rId13" tooltip="https://www.acfun.cn/v/ac48645465" xr:uid="{00000000-0004-0000-0700-00000C000000}"/>
+    <hyperlink ref="F43" r:id="rId14" tooltip="https://www.acfun.cn/v/ac48644820" xr:uid="{00000000-0004-0000-0700-00000D000000}"/>
+    <hyperlink ref="F48" r:id="rId15" tooltip="https://www.bilibili.com/video/BV17iYj6bE6G" xr:uid="{00000000-0004-0000-0700-00000E000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:G554"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="83.2727272727273" customWidth="1"/>
-    <col min="2" max="2" width="10.2727272727273" customWidth="1"/>
-    <col min="3" max="3" width="39.7272727272727" customWidth="1"/>
-    <col min="4" max="4" width="16.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="45.9090909090909" customWidth="1"/>
-    <col min="6" max="6" width="15.7272727272727" customWidth="1"/>
+    <col min="1" max="1" width="83.26953125" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
+    <col min="5" max="5" width="45.90625" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -75964,7 +75380,7 @@
       </c>
       <c r="G43" s="12"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:7">
+    <row r="44" spans="1:7" ht="15" customHeight="1">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -77224,7 +76640,7 @@
       </c>
       <c r="G136" s="12"/>
     </row>
-    <row r="137" ht="15" customHeight="1" spans="1:7">
+    <row r="137" spans="1:7" ht="15" customHeight="1">
       <c r="A137" s="6" t="s">
         <v>21</v>
       </c>
@@ -77527,7 +76943,7 @@
       </c>
       <c r="G159" s="12"/>
     </row>
-    <row r="160" ht="15" customHeight="1" spans="1:7">
+    <row r="160" spans="1:7" ht="15" customHeight="1">
       <c r="A160" s="6" t="s">
         <v>27</v>
       </c>
@@ -78368,7 +77784,7 @@
       </c>
       <c r="G222" s="12"/>
     </row>
-    <row r="223" ht="18" customHeight="1" spans="1:7">
+    <row r="223" spans="1:7" ht="18" customHeight="1">
       <c r="A223" t="s">
         <v>45</v>
       </c>
@@ -78440,7 +77856,7 @@
       </c>
       <c r="G226" s="12"/>
     </row>
-    <row r="227" ht="15" customHeight="1" spans="1:7">
+    <row r="227" spans="1:7" ht="15" customHeight="1">
       <c r="A227" t="s">
         <v>45</v>
       </c>
@@ -78677,7 +78093,7 @@
       </c>
       <c r="G242" s="12"/>
     </row>
-    <row r="243" ht="18" customHeight="1" spans="1:7">
+    <row r="243" spans="1:7" ht="18" customHeight="1">
       <c r="A243" t="s">
         <v>47</v>
       </c>
@@ -78749,7 +78165,7 @@
       </c>
       <c r="G246" s="12"/>
     </row>
-    <row r="247" ht="15" customHeight="1" spans="1:7">
+    <row r="247" spans="1:7" ht="15" customHeight="1">
       <c r="A247" t="s">
         <v>47</v>
       </c>
@@ -78986,7 +78402,7 @@
       </c>
       <c r="G262" s="12"/>
     </row>
-    <row r="263" ht="13.5" customHeight="1" spans="1:7">
+    <row r="263" spans="1:7" ht="13.5" customHeight="1">
       <c r="A263" t="s">
         <v>49</v>
       </c>
@@ -82801,15 +82217,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G554" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:G554" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G163" r:id="rId3" display="https://www.acfun.cn/v/ac47932379_3"/>
-    <hyperlink ref="G177" r:id="rId4" display="https://www.acfun.cn/v/ac47932379_4"/>
+    <hyperlink ref="G163" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="G177" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>